--- a/database/event/7365/event_7365_evp_summary.xlsx
+++ b/database/event/7365/event_7365_evp_summary.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,72 +418,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>evp_score</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>weighted_evp_score</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>z_score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>normalized_score</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Norm_Group_Score_Scaled</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Norm_Playoff_Score</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Norm_Group_Score</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Raw_Group_Score</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Raw_Playoff_Score</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>group_weighted_rounds_played</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>playoff_weighted_rounds_played</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>total_weighted_score</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>total_weighted_rounds_played</t>
         </is>
@@ -508,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.507300000000001</v>
+        <v>7.4863</v>
       </c>
       <c r="C2" t="n">
-        <v>2.977555</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>3.128388371351825</v>
+        <v>2.6029</v>
       </c>
       <c r="E2" t="n">
-        <v>122.8817</v>
+        <v>7.4863</v>
       </c>
       <c r="F2" t="n">
-        <v>37.45994275623698</v>
+        <v>4.1042</v>
       </c>
       <c r="G2" t="n">
-        <v>85.42175908730903</v>
+        <v>3.3822</v>
       </c>
       <c r="H2" t="n">
-        <v>39.42434587785664</v>
+        <v>4.1042</v>
       </c>
       <c r="I2" t="n">
-        <v>56.3543202338131</v>
+        <v>3.3266</v>
       </c>
       <c r="J2" t="n">
-        <v>85.42175908730903</v>
+        <v>3.3822</v>
       </c>
       <c r="K2" t="n">
         <v>119</v>
@@ -541,7 +529,7 @@
         <v>135</v>
       </c>
       <c r="M2" t="n">
-        <v>141.7761</v>
+        <v>6.7088</v>
       </c>
       <c r="N2" t="n">
         <v>254</v>
@@ -554,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.7847</v>
+        <v>6.2207</v>
       </c>
       <c r="C3" t="n">
-        <v>2.724645</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2.659922157276367</v>
+        <v>2.0917</v>
       </c>
       <c r="E3" t="n">
-        <v>102.4979</v>
+        <v>6.2207</v>
       </c>
       <c r="F3" t="n">
-        <v>-5.078906113357375</v>
+        <v>-0.2912</v>
       </c>
       <c r="G3" t="n">
-        <v>107.5768022908352</v>
+        <v>6.5119</v>
       </c>
       <c r="H3" t="n">
-        <v>-5.078906113357375</v>
+        <v>-0.2912</v>
       </c>
       <c r="I3" t="n">
-        <v>-4.941638380563933</v>
+        <v>-0.2912</v>
       </c>
       <c r="J3" t="n">
-        <v>107.5768022908352</v>
+        <v>6.767</v>
       </c>
       <c r="K3" t="n">
         <v>81</v>
@@ -587,7 +575,7 @@
         <v>155</v>
       </c>
       <c r="M3" t="n">
-        <v>102.6352</v>
+        <v>6.4758</v>
       </c>
       <c r="N3" t="n">
         <v>236</v>
@@ -600,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.131</v>
+        <v>5.42</v>
       </c>
       <c r="C4" t="n">
-        <v>2.14585</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1.778306093438095</v>
+        <v>1.7682</v>
       </c>
       <c r="E4" t="n">
-        <v>64.13720000000001</v>
+        <v>5.42</v>
       </c>
       <c r="F4" t="n">
-        <v>34.39858537627838</v>
+        <v>3.9833</v>
       </c>
       <c r="G4" t="n">
-        <v>29.7386137489491</v>
+        <v>1.4367</v>
       </c>
       <c r="H4" t="n">
-        <v>35.24329787234346</v>
+        <v>3.9833</v>
       </c>
       <c r="I4" t="n">
-        <v>29.63400421698549</v>
+        <v>3.2286</v>
       </c>
       <c r="J4" t="n">
-        <v>29.7386137489491</v>
+        <v>1.4367</v>
       </c>
       <c r="K4" t="n">
         <v>70</v>
@@ -633,7 +621,7 @@
         <v>59</v>
       </c>
       <c r="M4" t="n">
-        <v>59.3726</v>
+        <v>4.6653</v>
       </c>
       <c r="N4" t="n">
         <v>129</v>
@@ -646,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.3074</v>
+        <v>4.0318</v>
       </c>
       <c r="C5" t="n">
-        <v>1.85759</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1.421919912169246</v>
+        <v>1.2074</v>
       </c>
       <c r="E5" t="n">
-        <v>48.6302</v>
+        <v>4.0318</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.244003950277598</v>
+        <v>0.0857</v>
       </c>
       <c r="G5" t="n">
-        <v>49.87420077141522</v>
+        <v>3.9461</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.244003950277598</v>
+        <v>0.0857</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.090838298741918</v>
+        <v>0.0857</v>
       </c>
       <c r="J5" t="n">
-        <v>49.87420077141522</v>
+        <v>3.9461</v>
       </c>
       <c r="K5" t="n">
         <v>73</v>
@@ -679,7 +667,7 @@
         <v>136</v>
       </c>
       <c r="M5" t="n">
-        <v>48.7834</v>
+        <v>4.0318</v>
       </c>
       <c r="N5" t="n">
         <v>209</v>
@@ -688,369 +676,369 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.7651</v>
+        <v>3.9896</v>
       </c>
       <c r="C6" t="n">
-        <v>1.667785</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1.212617679980751</v>
+        <v>1.1903</v>
       </c>
       <c r="E6" t="n">
-        <v>39.5231</v>
+        <v>3.9896</v>
       </c>
       <c r="F6" t="n">
-        <v>22.62817952292655</v>
+        <v>4.253</v>
       </c>
       <c r="G6" t="n">
-        <v>16.89490156986664</v>
+        <v>-0.2634</v>
       </c>
       <c r="H6" t="n">
-        <v>22.62817952292655</v>
+        <v>4.5504</v>
       </c>
       <c r="I6" t="n">
-        <v>24.73470674578158</v>
+        <v>3.6882</v>
       </c>
       <c r="J6" t="n">
-        <v>16.89490156986664</v>
+        <v>-0.2634</v>
       </c>
       <c r="K6" t="n">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="L6" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="M6" t="n">
-        <v>41.6296</v>
+        <v>3.4248</v>
       </c>
       <c r="N6" t="n">
-        <v>152</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.7265</v>
+        <v>3.783</v>
       </c>
       <c r="C7" t="n">
-        <v>1.654275</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1.198445557261767</v>
+        <v>1.1069</v>
       </c>
       <c r="E7" t="n">
-        <v>38.9064</v>
+        <v>3.783</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.469550539385194</v>
+        <v>1.1717</v>
       </c>
       <c r="G7" t="n">
-        <v>43.37597713992317</v>
+        <v>2.6113</v>
       </c>
       <c r="H7" t="n">
-        <v>-4.469550539385194</v>
+        <v>1.1717</v>
       </c>
       <c r="I7" t="n">
-        <v>-6.388907077319377</v>
+        <v>1.1717</v>
       </c>
       <c r="J7" t="n">
-        <v>43.37597713992317</v>
+        <v>2.6113</v>
       </c>
       <c r="K7" t="n">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="L7" t="n">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="M7" t="n">
-        <v>36.9871</v>
+        <v>3.783</v>
       </c>
       <c r="N7" t="n">
-        <v>254</v>
+        <v>236</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.4169</v>
+        <v>3.313</v>
       </c>
       <c r="C8" t="n">
-        <v>1.195915</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7673476195835334</v>
+        <v>0.917</v>
       </c>
       <c r="E8" t="n">
-        <v>20.1486</v>
+        <v>3.313</v>
       </c>
       <c r="F8" t="n">
-        <v>37.56993049800549</v>
+        <v>2.0974</v>
       </c>
       <c r="G8" t="n">
-        <v>-17.42134879780535</v>
+        <v>1.2156</v>
       </c>
       <c r="H8" t="n">
-        <v>39.58345932984064</v>
+        <v>2.0974</v>
       </c>
       <c r="I8" t="n">
-        <v>33.28338922629244</v>
+        <v>2.0974</v>
       </c>
       <c r="J8" t="n">
-        <v>-17.42134879780535</v>
+        <v>1.2156</v>
       </c>
       <c r="K8" t="n">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="L8" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M8" t="n">
-        <v>15.862</v>
+        <v>3.313</v>
       </c>
       <c r="N8" t="n">
-        <v>129</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.376</v>
+        <v>3.0065</v>
       </c>
       <c r="C9" t="n">
-        <v>1.1816</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7553540294258646</v>
+        <v>0.7932</v>
       </c>
       <c r="E9" t="n">
-        <v>19.6267</v>
+        <v>3.0065</v>
       </c>
       <c r="F9" t="n">
-        <v>30.27997528316063</v>
+        <v>2.9232</v>
       </c>
       <c r="G9" t="n">
-        <v>-10.65325621396127</v>
+        <v>0.0833</v>
       </c>
       <c r="H9" t="n">
-        <v>30.30916649088289</v>
+        <v>2.9232</v>
       </c>
       <c r="I9" t="n">
-        <v>33.1307405485927</v>
+        <v>2.3693</v>
       </c>
       <c r="J9" t="n">
-        <v>-10.65325621396127</v>
+        <v>0.0833</v>
       </c>
       <c r="K9" t="n">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="L9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="M9" t="n">
-        <v>22.4775</v>
+        <v>2.4526</v>
       </c>
       <c r="N9" t="n">
-        <v>152</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.2226</v>
+        <v>2.6334</v>
       </c>
       <c r="C10" t="n">
-        <v>1.12791</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.711045912119576</v>
+        <v>0.6425</v>
       </c>
       <c r="E10" t="n">
-        <v>17.6988</v>
+        <v>2.6334</v>
       </c>
       <c r="F10" t="n">
-        <v>26.12863090859804</v>
+        <v>0.3714</v>
       </c>
       <c r="G10" t="n">
-        <v>-8.429837537056912</v>
+        <v>2.262</v>
       </c>
       <c r="H10" t="n">
-        <v>26.12863090859804</v>
+        <v>0.3714</v>
       </c>
       <c r="I10" t="n">
-        <v>21.97001998320556</v>
+        <v>0.3714</v>
       </c>
       <c r="J10" t="n">
-        <v>-8.429837537056912</v>
+        <v>2.262</v>
       </c>
       <c r="K10" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="L10" t="n">
-        <v>59</v>
+        <v>155</v>
       </c>
       <c r="M10" t="n">
-        <v>13.5402</v>
+        <v>2.6334</v>
       </c>
       <c r="N10" t="n">
-        <v>129</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>Maden</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.069</v>
+        <v>2.124</v>
       </c>
       <c r="C11" t="n">
-        <v>1.07415</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6677847484776576</v>
+        <v>0.4367</v>
       </c>
       <c r="E11" t="n">
-        <v>15.8164</v>
+        <v>2.124</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.470606265618449</v>
+        <v>1.0962</v>
       </c>
       <c r="G11" t="n">
-        <v>21.2870287722613</v>
+        <v>1.0278</v>
       </c>
       <c r="H11" t="n">
-        <v>-5.470606265618449</v>
+        <v>1.0962</v>
       </c>
       <c r="I11" t="n">
-        <v>-7.819845592896041</v>
+        <v>1.0962</v>
       </c>
       <c r="J11" t="n">
-        <v>21.2870287722613</v>
+        <v>1.0278</v>
       </c>
       <c r="K11" t="n">
-        <v>119</v>
+        <v>73</v>
       </c>
       <c r="L11" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M11" t="n">
-        <v>13.4672</v>
+        <v>2.124</v>
       </c>
       <c r="N11" t="n">
-        <v>254</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>b0RUP</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.1278</v>
+        <v>1.7368</v>
       </c>
       <c r="C12" t="n">
-        <v>0.74473</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4256630389296084</v>
+        <v>0.2803</v>
       </c>
       <c r="E12" t="n">
-        <v>5.2813</v>
+        <v>1.7368</v>
       </c>
       <c r="F12" t="n">
-        <v>1.407789071445656</v>
+        <v>-0.5996</v>
       </c>
       <c r="G12" t="n">
-        <v>3.873483350353122</v>
+        <v>2.3364</v>
       </c>
       <c r="H12" t="n">
-        <v>1.407789071445656</v>
+        <v>-0.5996</v>
       </c>
       <c r="I12" t="n">
-        <v>1.183726546560912</v>
+        <v>-0.486</v>
       </c>
       <c r="J12" t="n">
-        <v>3.873483350353122</v>
+        <v>2.3364</v>
       </c>
       <c r="K12" t="n">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="L12" t="n">
-        <v>59</v>
+        <v>135</v>
       </c>
       <c r="M12" t="n">
-        <v>5.0572</v>
+        <v>1.8504</v>
       </c>
       <c r="N12" t="n">
-        <v>129</v>
+        <v>254</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>maxster</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.0165</v>
+        <v>1.235</v>
       </c>
       <c r="C13" t="n">
-        <v>0.705775</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3994594911787352</v>
+        <v>0.0776</v>
       </c>
       <c r="E13" t="n">
-        <v>4.1411</v>
+        <v>1.235</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.12037030505262</v>
+        <v>1.5467</v>
       </c>
       <c r="G13" t="n">
-        <v>11.26147934032102</v>
+        <v>-0.3117</v>
       </c>
       <c r="H13" t="n">
-        <v>-7.12037030505262</v>
+        <v>1.5467</v>
       </c>
       <c r="I13" t="n">
-        <v>-6.243688075301397</v>
+        <v>1.5467</v>
       </c>
       <c r="J13" t="n">
-        <v>11.26147934032102</v>
+        <v>-0.3117</v>
       </c>
       <c r="K13" t="n">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="L13" t="n">
-        <v>136</v>
+        <v>61</v>
       </c>
       <c r="M13" t="n">
-        <v>5.0178</v>
+        <v>1.235</v>
       </c>
       <c r="N13" t="n">
-        <v>209</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14">
@@ -1060,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.7571</v>
+        <v>1.0767</v>
       </c>
       <c r="C14" t="n">
-        <v>0.614985</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3402322733748229</v>
+        <v>0.0136</v>
       </c>
       <c r="E14" t="n">
-        <v>1.564</v>
+        <v>1.0767</v>
       </c>
       <c r="F14" t="n">
-        <v>4.901204364349461</v>
+        <v>1.0985</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.337177862641063</v>
+        <v>-0.0218</v>
       </c>
       <c r="H14" t="n">
-        <v>4.901204364349461</v>
+        <v>1.0985</v>
       </c>
       <c r="I14" t="n">
-        <v>4.1211327988524</v>
+        <v>0.8904</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.337177862641063</v>
+        <v>-0.0218</v>
       </c>
       <c r="K14" t="n">
         <v>70</v>
@@ -1093,7 +1081,7 @@
         <v>59</v>
       </c>
       <c r="M14" t="n">
-        <v>0.784</v>
+        <v>0.8685999999999999</v>
       </c>
       <c r="N14" t="n">
         <v>129</v>
@@ -1102,81 +1090,81 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>JamYoung</t>
+          <t>headtr1ck</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.4305</v>
+        <v>0.9917</v>
       </c>
       <c r="C15" t="n">
-        <v>0.500675</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2692383498877844</v>
+        <v>-0.0207</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.525</v>
+        <v>0.9917</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.525046512206776</v>
+        <v>1.8274</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0.8357</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.525046512206776</v>
+        <v>1.8274</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.667017809138938</v>
+        <v>1.8274</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-0.8357</v>
       </c>
       <c r="K15" t="n">
         <v>91</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.667</v>
+        <v>0.9916999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>91</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.0196</v>
+        <v>0.7060999999999999</v>
       </c>
       <c r="C16" t="n">
-        <v>0.35686</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1852166279465244</v>
+        <v>-0.1361</v>
       </c>
       <c r="E16" t="n">
-        <v>-5.181</v>
+        <v>0.7060999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>-6.333104179958197</v>
+        <v>0.5647</v>
       </c>
       <c r="G16" t="n">
-        <v>1.152121763901601</v>
+        <v>0.1414</v>
       </c>
       <c r="H16" t="n">
-        <v>-6.333104179958197</v>
+        <v>0.5647</v>
       </c>
       <c r="I16" t="n">
-        <v>-9.05272549447478</v>
+        <v>0.4577</v>
       </c>
       <c r="J16" t="n">
-        <v>1.152121763901601</v>
+        <v>0.1414</v>
       </c>
       <c r="K16" t="n">
         <v>119</v>
@@ -1185,7 +1173,7 @@
         <v>135</v>
       </c>
       <c r="M16" t="n">
-        <v>-7.9006</v>
+        <v>0.5991</v>
       </c>
       <c r="N16" t="n">
         <v>254</v>
@@ -1194,216 +1182,216 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Moseyuh</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.0066</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="C17" t="n">
-        <v>0.35231</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1826547102533249</v>
+        <v>-0.1565</v>
       </c>
       <c r="E17" t="n">
-        <v>-5.2925</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>-5.292456052407733</v>
+        <v>0.7948</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0.1391</v>
       </c>
       <c r="H17" t="n">
-        <v>-5.292456052407733</v>
+        <v>0.7948</v>
       </c>
       <c r="I17" t="n">
-        <v>-5.78514715638563</v>
+        <v>0.7948</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0.1391</v>
       </c>
       <c r="K17" t="n">
         <v>91</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="M17" t="n">
-        <v>-5.7851</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>91</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5528</v>
+        <v>0.5888</v>
       </c>
       <c r="C18" t="n">
-        <v>0.19348</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.09650476383295435</v>
+        <v>-0.1835</v>
       </c>
       <c r="E18" t="n">
-        <v>-9.041</v>
+        <v>0.5888</v>
       </c>
       <c r="F18" t="n">
-        <v>-9.040994822574334</v>
+        <v>-0.5429</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1.1317</v>
       </c>
       <c r="H18" t="n">
-        <v>-9.040994822574334</v>
+        <v>-0.5429</v>
       </c>
       <c r="I18" t="n">
-        <v>-9.882648995246418</v>
+        <v>-0.44</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1.1317</v>
       </c>
       <c r="K18" t="n">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="M18" t="n">
-        <v>-9.8826</v>
+        <v>0.6917</v>
       </c>
       <c r="N18" t="n">
-        <v>91</v>
+        <v>254</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Maden</t>
+          <t>ChildKing</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.4885</v>
+        <v>0.5131</v>
       </c>
       <c r="C19" t="n">
-        <v>0.170975</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0848273289808885</v>
+        <v>-0.2141</v>
       </c>
       <c r="E19" t="n">
-        <v>-9.549099999999999</v>
+        <v>0.5131</v>
       </c>
       <c r="F19" t="n">
-        <v>5.418522639706152</v>
+        <v>0.5131</v>
       </c>
       <c r="G19" t="n">
-        <v>-14.96762360857419</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>5.418522639706152</v>
+        <v>0.5131</v>
       </c>
       <c r="I19" t="n">
-        <v>4.751377209592182</v>
+        <v>0.5131</v>
       </c>
       <c r="J19" t="n">
-        <v>-14.96762360857419</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="L19" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-10.2162</v>
+        <v>0.5131</v>
       </c>
       <c r="N19" t="n">
-        <v>209</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ChildKing</t>
+          <t>JamYoung</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.3544</v>
+        <v>0.4703</v>
       </c>
       <c r="C20" t="n">
-        <v>0.12404</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0.06084825564193994</v>
+        <v>-0.2314</v>
       </c>
       <c r="E20" t="n">
-        <v>-10.5925</v>
+        <v>0.4703</v>
       </c>
       <c r="F20" t="n">
-        <v>-10.59247348177842</v>
+        <v>0.4703</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>-10.59247348177842</v>
+        <v>0.4703</v>
       </c>
       <c r="I20" t="n">
-        <v>-6.743556691102178</v>
+        <v>0.4703</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-6.7436</v>
+        <v>0.4703</v>
       </c>
       <c r="N20" t="n">
-        <v>53</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>kaze</t>
+          <t>Moseyuh</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.3492</v>
+        <v>0.3931</v>
       </c>
       <c r="C21" t="n">
-        <v>0.12222</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0.05992865849720823</v>
+        <v>-0.2626</v>
       </c>
       <c r="E21" t="n">
-        <v>-10.6325</v>
+        <v>0.3931</v>
       </c>
       <c r="F21" t="n">
-        <v>-10.63248680381975</v>
+        <v>0.3931</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>-10.63248680381975</v>
+        <v>0.3931</v>
       </c>
       <c r="I21" t="n">
-        <v>-11.62229788765882</v>
+        <v>0.3931</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1415,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-11.6223</v>
+        <v>0.3931</v>
       </c>
       <c r="N21" t="n">
         <v>91</v>
@@ -1424,219 +1412,219 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>headtr1ck</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2502</v>
+        <v>0.3612</v>
       </c>
       <c r="C22" t="n">
-        <v>0.08756999999999998</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0.04258568125489767</v>
+        <v>-0.2754</v>
       </c>
       <c r="E22" t="n">
-        <v>-11.3871</v>
+        <v>0.3612</v>
       </c>
       <c r="F22" t="n">
-        <v>9.125035179957491</v>
+        <v>0.7421</v>
       </c>
       <c r="G22" t="n">
-        <v>-20.51214604663732</v>
+        <v>-0.3809</v>
       </c>
       <c r="H22" t="n">
-        <v>9.125035179957491</v>
+        <v>0.7421</v>
       </c>
       <c r="I22" t="n">
-        <v>9.974512929443023</v>
+        <v>0.7421</v>
       </c>
       <c r="J22" t="n">
-        <v>-20.51214604663732</v>
+        <v>-0.3809</v>
       </c>
       <c r="K22" t="n">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="L22" t="n">
-        <v>61</v>
+        <v>155</v>
       </c>
       <c r="M22" t="n">
-        <v>-10.5376</v>
+        <v>0.3612</v>
       </c>
       <c r="N22" t="n">
-        <v>152</v>
+        <v>236</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.1365</v>
+        <v>0.2352</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.047775</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.02300914773767156</v>
+        <v>-0.3263</v>
       </c>
       <c r="E23" t="n">
-        <v>-14.2413</v>
+        <v>0.2352</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9361059862862903</v>
+        <v>0.0071</v>
       </c>
       <c r="G23" t="n">
-        <v>-15.17736557641737</v>
+        <v>0.2281</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9361059862862903</v>
+        <v>0.0071</v>
       </c>
       <c r="I23" t="n">
-        <v>0.910805824494769</v>
+        <v>0.0071</v>
       </c>
       <c r="J23" t="n">
-        <v>-15.17736557641737</v>
+        <v>0.2281</v>
       </c>
       <c r="K23" t="n">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="L23" t="n">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="M23" t="n">
-        <v>-14.2666</v>
+        <v>0.2352</v>
       </c>
       <c r="N23" t="n">
-        <v>236</v>
+        <v>209</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>maxster</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.2004</v>
+        <v>0.2162</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.07013999999999999</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.03397043053357198</v>
+        <v>-0.334</v>
       </c>
       <c r="E24" t="n">
-        <v>-14.7182</v>
+        <v>0.2162</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.949782784950587</v>
+        <v>0.2162</v>
       </c>
       <c r="G24" t="n">
-        <v>-11.7684218903312</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.949782784950587</v>
+        <v>0.2162</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.224387188354395</v>
+        <v>0.2162</v>
       </c>
       <c r="J24" t="n">
-        <v>-11.7684218903312</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>91</v>
       </c>
       <c r="L24" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-14.9928</v>
+        <v>0.2162</v>
       </c>
       <c r="N24" t="n">
-        <v>152</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Starry</t>
+          <t>VLDN</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.6651</v>
+        <v>0.1324</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.232785</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1172264180190845</v>
+        <v>-0.3679</v>
       </c>
       <c r="E25" t="n">
-        <v>-18.3408</v>
+        <v>0.1324</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.718424163575325</v>
+        <v>-1.7822</v>
       </c>
       <c r="G25" t="n">
-        <v>-12.62239793522879</v>
+        <v>1.9146</v>
       </c>
       <c r="H25" t="n">
-        <v>-5.718424163575325</v>
+        <v>-1.7822</v>
       </c>
       <c r="I25" t="n">
-        <v>-6.044700617352896</v>
+        <v>-1.7822</v>
       </c>
       <c r="J25" t="n">
-        <v>-12.62239793522879</v>
+        <v>1.9146</v>
       </c>
       <c r="K25" t="n">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="L25" t="n">
-        <v>36</v>
+        <v>136</v>
       </c>
       <c r="M25" t="n">
-        <v>-18.6671</v>
+        <v>0.1324000000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>124</v>
+        <v>209</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Westmelon</t>
+          <t>Starry</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.7267</v>
+        <v>0.1114</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.254345</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.1287528600147721</v>
+        <v>-0.3764</v>
       </c>
       <c r="E26" t="n">
-        <v>-18.8424</v>
+        <v>0.1114</v>
       </c>
       <c r="F26" t="n">
-        <v>-5.629913810267784</v>
+        <v>0.3816</v>
       </c>
       <c r="G26" t="n">
-        <v>-13.21244446468298</v>
+        <v>-0.2702</v>
       </c>
       <c r="H26" t="n">
-        <v>-5.629913810267784</v>
+        <v>0.3816</v>
       </c>
       <c r="I26" t="n">
-        <v>-5.951140123766546</v>
+        <v>0.3816</v>
       </c>
       <c r="J26" t="n">
-        <v>-13.21244446468298</v>
+        <v>-0.2702</v>
       </c>
       <c r="K26" t="n">
         <v>88</v>
@@ -1645,7 +1633,7 @@
         <v>36</v>
       </c>
       <c r="M26" t="n">
-        <v>-19.1636</v>
+        <v>0.1114</v>
       </c>
       <c r="N26" t="n">
         <v>124</v>
@@ -1654,47 +1642,47 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>Jee</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.8635</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.302225</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.154784877757054</v>
+        <v>-0.3841</v>
       </c>
       <c r="E27" t="n">
-        <v>-19.9751</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>1.441672037780759</v>
+        <v>1.0923</v>
       </c>
       <c r="G27" t="n">
-        <v>-21.41673012076686</v>
+        <v>-1</v>
       </c>
       <c r="H27" t="n">
-        <v>1.441672037780759</v>
+        <v>1.0923</v>
       </c>
       <c r="I27" t="n">
-        <v>1.40270792865155</v>
+        <v>1.0923</v>
       </c>
       <c r="J27" t="n">
-        <v>-21.41673012076686</v>
+        <v>-1</v>
       </c>
       <c r="K27" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="L27" t="n">
-        <v>155</v>
+        <v>36</v>
       </c>
       <c r="M27" t="n">
-        <v>-20.014</v>
+        <v>0.09230000000000005</v>
       </c>
       <c r="N27" t="n">
-        <v>236</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28">
@@ -1704,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.9592000000000001</v>
+        <v>0.0629</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.33572</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.1733481070844158</v>
+        <v>-0.396</v>
       </c>
       <c r="E28" t="n">
-        <v>-20.7828</v>
+        <v>0.0629</v>
       </c>
       <c r="F28" t="n">
-        <v>-9.681268243534641</v>
+        <v>-0.07190000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>-11.10150926035009</v>
+        <v>0.1348</v>
       </c>
       <c r="H28" t="n">
-        <v>-9.681268243534641</v>
+        <v>-0.07190000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>-10.23365291809067</v>
+        <v>-0.07190000000000001</v>
       </c>
       <c r="J28" t="n">
-        <v>-11.10150926035009</v>
+        <v>0.1348</v>
       </c>
       <c r="K28" t="n">
         <v>88</v>
@@ -1737,7 +1725,7 @@
         <v>36</v>
       </c>
       <c r="M28" t="n">
-        <v>-21.3352</v>
+        <v>0.0629</v>
       </c>
       <c r="N28" t="n">
         <v>124</v>
@@ -1746,262 +1734,262 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>VLDN</t>
+          <t>Westmelon</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.6231</v>
+        <v>-0.0456</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.568085</v>
+        <v>-0</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.3106395736997974</v>
+        <v>-0.4398</v>
       </c>
       <c r="E29" t="n">
-        <v>-26.7566</v>
+        <v>-0.0456</v>
       </c>
       <c r="F29" t="n">
-        <v>-32.17885160111634</v>
+        <v>0.2578</v>
       </c>
       <c r="G29" t="n">
-        <v>5.422276006753608</v>
+        <v>-0.3034</v>
       </c>
       <c r="H29" t="n">
-        <v>-32.17885160111634</v>
+        <v>0.2578</v>
       </c>
       <c r="I29" t="n">
-        <v>-28.21689089347138</v>
+        <v>0.2578</v>
       </c>
       <c r="J29" t="n">
-        <v>5.422276006753608</v>
+        <v>-0.3034</v>
       </c>
       <c r="K29" t="n">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="L29" t="n">
-        <v>136</v>
+        <v>36</v>
       </c>
       <c r="M29" t="n">
-        <v>-22.7946</v>
+        <v>-0.04560000000000003</v>
       </c>
       <c r="N29" t="n">
-        <v>209</v>
+        <v>124</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>kaze</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.9125</v>
+        <v>-0.092</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.6693749999999999</v>
+        <v>-0</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.3754070557331306</v>
+        <v>-0.4585</v>
       </c>
       <c r="E30" t="n">
-        <v>-29.5747</v>
+        <v>-0.092</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.005854606782805818</v>
+        <v>-0.092</v>
       </c>
       <c r="G30" t="n">
-        <v>-29.56887036010944</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.005854606782805818</v>
+        <v>-0.092</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.008368747233079787</v>
+        <v>-0.092</v>
       </c>
       <c r="J30" t="n">
-        <v>-29.56887036010944</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="L30" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-29.5772</v>
+        <v>-0.092</v>
       </c>
       <c r="N30" t="n">
-        <v>254</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Jee</t>
+          <t>b0RUP</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-2.0679</v>
+        <v>-0.3675</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.7237649999999999</v>
+        <v>-0</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.4114988348322179</v>
+        <v>-0.5698</v>
       </c>
       <c r="E31" t="n">
-        <v>-31.1451</v>
+        <v>-0.3675</v>
       </c>
       <c r="F31" t="n">
-        <v>-5.000447066662128</v>
+        <v>-0.8894</v>
       </c>
       <c r="G31" t="n">
-        <v>-26.14469597776507</v>
+        <v>0.5219</v>
       </c>
       <c r="H31" t="n">
-        <v>-5.000447066662128</v>
+        <v>-0.8894</v>
       </c>
       <c r="I31" t="n">
-        <v>-5.285757860255462</v>
+        <v>-0.7209</v>
       </c>
       <c r="J31" t="n">
-        <v>-26.14469597776507</v>
+        <v>0.5219</v>
       </c>
       <c r="K31" t="n">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="L31" t="n">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M31" t="n">
-        <v>-31.4305</v>
+        <v>-0.199</v>
       </c>
       <c r="N31" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-2.712</v>
+        <v>-0.4248</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.9492</v>
+        <v>-0</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.5714572716657186</v>
+        <v>-0.593</v>
       </c>
       <c r="E32" t="n">
-        <v>-38.1052</v>
+        <v>-0.4248</v>
       </c>
       <c r="F32" t="n">
-        <v>-38.10522168637794</v>
+        <v>0.0062</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-0.431</v>
       </c>
       <c r="H32" t="n">
-        <v>-38.10522168637794</v>
+        <v>0.0062</v>
       </c>
       <c r="I32" t="n">
-        <v>-24.25918017270908</v>
+        <v>0.005</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-0.431</v>
       </c>
       <c r="K32" t="n">
-        <v>53</v>
+        <v>119</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="M32" t="n">
-        <v>-24.2592</v>
+        <v>-0.426</v>
       </c>
       <c r="N32" t="n">
-        <v>53</v>
+        <v>254</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>advent</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-2.9048</v>
+        <v>-0.648</v>
       </c>
       <c r="C33" t="n">
-        <v>-1.01668</v>
+        <v>-0</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6227555936502239</v>
+        <v>-0.6831</v>
       </c>
       <c r="E33" t="n">
-        <v>-40.3373</v>
+        <v>-0.648</v>
       </c>
       <c r="F33" t="n">
-        <v>-40.33730373394076</v>
+        <v>0.9855</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-1.6335</v>
       </c>
       <c r="H33" t="n">
-        <v>-40.33730373394076</v>
+        <v>0.9855</v>
       </c>
       <c r="I33" t="n">
-        <v>-44.09242810556889</v>
+        <v>0.9855</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>-1.6335</v>
       </c>
       <c r="K33" t="n">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="M33" t="n">
-        <v>-44.0924</v>
+        <v>-0.6479999999999999</v>
       </c>
       <c r="N33" t="n">
-        <v>91</v>
+        <v>236</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>flying</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-3.8797</v>
+        <v>-0.6528</v>
       </c>
       <c r="C34" t="n">
-        <v>-1.357895</v>
+        <v>-0</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9090609909578742</v>
+        <v>-0.6851</v>
       </c>
       <c r="E34" t="n">
-        <v>-52.795</v>
+        <v>-0.6528</v>
       </c>
       <c r="F34" t="n">
-        <v>-52.79496536357017</v>
+        <v>-0.6528</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-52.79496536357017</v>
+        <v>-0.6528</v>
       </c>
       <c r="I34" t="n">
-        <v>-33.61120918041104</v>
+        <v>-0.6528</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2013,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-33.6112</v>
+        <v>-0.6528</v>
       </c>
       <c r="N34" t="n">
         <v>53</v>
@@ -2022,47 +2010,47 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>es3tag</t>
+          <t>Snappi</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-4.1392</v>
+        <v>-1.1475</v>
       </c>
       <c r="C35" t="n">
-        <v>-1.44872</v>
+        <v>-0</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9934369522887478</v>
+        <v>-0.8849</v>
       </c>
       <c r="E35" t="n">
-        <v>-56.4663</v>
+        <v>-1.1475</v>
       </c>
       <c r="F35" t="n">
-        <v>-27.90625207467417</v>
+        <v>-1.4478</v>
       </c>
       <c r="G35" t="n">
-        <v>-28.56006278429244</v>
+        <v>0.3003</v>
       </c>
       <c r="H35" t="n">
-        <v>-27.90625207467417</v>
+        <v>-1.4478</v>
       </c>
       <c r="I35" t="n">
-        <v>-30.50413139694114</v>
+        <v>-1.4478</v>
       </c>
       <c r="J35" t="n">
-        <v>-28.56006278429244</v>
+        <v>0.3003</v>
       </c>
       <c r="K35" t="n">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="L35" t="n">
-        <v>61</v>
+        <v>136</v>
       </c>
       <c r="M35" t="n">
-        <v>-59.0642</v>
+        <v>-1.1475</v>
       </c>
       <c r="N35" t="n">
-        <v>152</v>
+        <v>209</v>
       </c>
     </row>
     <row r="36">
@@ -2072,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-4.1567</v>
+        <v>-1.3945</v>
       </c>
       <c r="C36" t="n">
-        <v>-1.454845</v>
+        <v>-0</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9992564585307322</v>
+        <v>-0.9847</v>
       </c>
       <c r="E36" t="n">
-        <v>-56.7195</v>
+        <v>-1.3945</v>
       </c>
       <c r="F36" t="n">
-        <v>-56.71953201901985</v>
+        <v>-1.3945</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-56.71953201901985</v>
+        <v>-1.3945</v>
       </c>
       <c r="I36" t="n">
-        <v>-36.10973209619281</v>
+        <v>-1.3945</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2105,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-36.1097</v>
+        <v>-1.3945</v>
       </c>
       <c r="N36" t="n">
         <v>53</v>
@@ -2114,231 +2102,231 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Snappi</t>
+          <t>flying</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-4.3222</v>
+        <v>-1.4679</v>
       </c>
       <c r="C37" t="n">
-        <v>-1.51277</v>
+        <v>-0</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.055177655554465</v>
+        <v>-1.0144</v>
       </c>
       <c r="E37" t="n">
-        <v>-59.1528</v>
+        <v>-1.4679</v>
       </c>
       <c r="F37" t="n">
-        <v>-45.00005877392505</v>
+        <v>-1.4679</v>
       </c>
       <c r="G37" t="n">
-        <v>-14.15270488165008</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-45.00005877392505</v>
+        <v>-1.4679</v>
       </c>
       <c r="I37" t="n">
-        <v>-39.4595109969553</v>
+        <v>-1.4679</v>
       </c>
       <c r="J37" t="n">
-        <v>-14.15270488165008</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="L37" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-53.6122</v>
+        <v>-1.4679</v>
       </c>
       <c r="N37" t="n">
-        <v>209</v>
+        <v>53</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>EmiliaQAQ</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-4.9172</v>
+        <v>-1.7105</v>
       </c>
       <c r="C38" t="n">
-        <v>-1.72102</v>
+        <v>-0</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.269427655478996</v>
+        <v>-1.1124</v>
       </c>
       <c r="E38" t="n">
-        <v>-68.4752</v>
+        <v>-1.7105</v>
       </c>
       <c r="F38" t="n">
-        <v>-38.08480966204124</v>
+        <v>-1.7105</v>
       </c>
       <c r="G38" t="n">
-        <v>-30.39035597514896</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-38.08480966204124</v>
+        <v>-1.7105</v>
       </c>
       <c r="I38" t="n">
-        <v>-40.25781681993548</v>
+        <v>-1.7105</v>
       </c>
       <c r="J38" t="n">
-        <v>-30.39035597514896</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>88</v>
+        <v>53</v>
       </c>
       <c r="L38" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-70.6482</v>
+        <v>-1.7105</v>
       </c>
       <c r="N38" t="n">
-        <v>124</v>
+        <v>53</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>advent</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-4.984</v>
+        <v>-1.7347</v>
       </c>
       <c r="C39" t="n">
-        <v>-1.7444</v>
+        <v>-0</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.294866899380211</v>
+        <v>-1.1221</v>
       </c>
       <c r="E39" t="n">
-        <v>-69.5821</v>
+        <v>-1.7347</v>
       </c>
       <c r="F39" t="n">
-        <v>-69.58207279163135</v>
+        <v>-1.7347</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-69.58207279163135</v>
+        <v>-1.7347</v>
       </c>
       <c r="I39" t="n">
-        <v>-44.29849679226981</v>
+        <v>-1.7347</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-44.2985</v>
+        <v>-1.7347</v>
       </c>
       <c r="N39" t="n">
-        <v>53</v>
+        <v>91</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>es3tag</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-5.7928</v>
+        <v>-1.9454</v>
       </c>
       <c r="C40" t="n">
-        <v>-2.02748</v>
+        <v>-0</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.625995867548803</v>
+        <v>-1.2073</v>
       </c>
       <c r="E40" t="n">
-        <v>-83.9901</v>
+        <v>-1.9454</v>
       </c>
       <c r="F40" t="n">
-        <v>3.626316769151297</v>
+        <v>-0.9454</v>
       </c>
       <c r="G40" t="n">
-        <v>-87.61640519724659</v>
+        <v>-1</v>
       </c>
       <c r="H40" t="n">
-        <v>3.626316769151297</v>
+        <v>-0.9454</v>
       </c>
       <c r="I40" t="n">
-        <v>3.528308207822884</v>
+        <v>-0.9454</v>
       </c>
       <c r="J40" t="n">
-        <v>-87.61640519724659</v>
+        <v>-1</v>
       </c>
       <c r="K40" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="L40" t="n">
-        <v>155</v>
+        <v>61</v>
       </c>
       <c r="M40" t="n">
-        <v>-84.0881</v>
+        <v>-1.9454</v>
       </c>
       <c r="N40" t="n">
-        <v>236</v>
+        <v>152</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>EmiliaQAQ</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-6.6658</v>
+        <v>-3.2274</v>
       </c>
       <c r="C41" t="n">
-        <v>-2.33303</v>
+        <v>-0</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.037282074964435</v>
+        <v>-1.7252</v>
       </c>
       <c r="E41" t="n">
-        <v>-101.8859</v>
+        <v>-3.2274</v>
       </c>
       <c r="F41" t="n">
-        <v>2.954597874435231</v>
+        <v>-2.2274</v>
       </c>
       <c r="G41" t="n">
-        <v>-104.8404872657651</v>
+        <v>-1</v>
       </c>
       <c r="H41" t="n">
-        <v>2.954597874435231</v>
+        <v>-2.2274</v>
       </c>
       <c r="I41" t="n">
-        <v>2.874743877828873</v>
+        <v>-2.2274</v>
       </c>
       <c r="J41" t="n">
-        <v>-104.8404872657651</v>
+        <v>-1</v>
       </c>
       <c r="K41" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="L41" t="n">
-        <v>155</v>
+        <v>36</v>
       </c>
       <c r="M41" t="n">
-        <v>-101.9657</v>
+        <v>-3.2274</v>
       </c>
       <c r="N41" t="n">
-        <v>236</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -2356,52 +2344,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>opponent</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>opponent_rank</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>match_stage</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>round_differential</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>total_rounds</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>rating</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>perf_score_raw</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>perf_score_weighted</t>
         </is>
@@ -2441,10 +2429,10 @@
         <v>1.5</v>
       </c>
       <c r="I2" t="n">
-        <v>1.06343162894536</v>
+        <v>0.784</v>
       </c>
       <c r="J2" t="n">
-        <v>21.26863257890719</v>
+        <v>15.68</v>
       </c>
     </row>
     <row r="3">
@@ -2481,10 +2469,10 @@
         <v>1.05</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2604033495705693</v>
+        <v>0.1597</v>
       </c>
       <c r="J3" t="n">
-        <v>-5.208066991411386</v>
+        <v>3.194</v>
       </c>
     </row>
     <row r="4">
@@ -2521,10 +2509,10 @@
         <v>1.03</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3193178785232338</v>
+        <v>0.1183</v>
       </c>
       <c r="J4" t="n">
-        <v>-6.386357570464676</v>
+        <v>2.366</v>
       </c>
     </row>
     <row r="5">
@@ -2561,10 +2549,10 @@
         <v>0.66</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.366963578731176</v>
+        <v>-0.5612</v>
       </c>
       <c r="J5" t="n">
-        <v>-27.33927157462351</v>
+        <v>-11.224</v>
       </c>
     </row>
     <row r="6">
@@ -2601,10 +2589,10 @@
         <v>0.47</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.680672954881014</v>
+        <v>-0.7915</v>
       </c>
       <c r="J6" t="n">
-        <v>-33.61345909762028</v>
+        <v>-15.83</v>
       </c>
     </row>
     <row r="7">
@@ -2641,10 +2629,10 @@
         <v>1.44</v>
       </c>
       <c r="I7" t="n">
-        <v>1.441584317214277</v>
+        <v>1.108</v>
       </c>
       <c r="J7" t="n">
-        <v>28.83168634428554</v>
+        <v>22.16</v>
       </c>
     </row>
     <row r="8">
@@ -2681,10 +2669,10 @@
         <v>1.25</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9635604045295414</v>
+        <v>0.6803</v>
       </c>
       <c r="J8" t="n">
-        <v>19.27120809059083</v>
+        <v>13.606</v>
       </c>
     </row>
     <row r="9">
@@ -2721,10 +2709,10 @@
         <v>1.16</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5754116568361775</v>
+        <v>0.4176</v>
       </c>
       <c r="J9" t="n">
-        <v>11.50823313672355</v>
+        <v>8.352</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2749,10 @@
         <v>1.08</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2976292341017017</v>
+        <v>0.1848</v>
       </c>
       <c r="J10" t="n">
-        <v>5.952584682034034</v>
+        <v>3.696</v>
       </c>
     </row>
     <row r="11">
@@ -2801,10 +2789,10 @@
         <v>0.99</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01055010972120544</v>
+        <v>-0.1759</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2110021944241088</v>
+        <v>-3.518</v>
       </c>
     </row>
     <row r="12">
@@ -2841,10 +2829,10 @@
         <v>1.35</v>
       </c>
       <c r="I12" t="n">
-        <v>0.887179721508037</v>
+        <v>0.5869</v>
       </c>
       <c r="J12" t="n">
-        <v>35.48718886032148</v>
+        <v>23.476</v>
       </c>
     </row>
     <row r="13">
@@ -2881,10 +2869,10 @@
         <v>1.06</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1013220725791462</v>
+        <v>0.1587</v>
       </c>
       <c r="J13" t="n">
-        <v>-4.052882903165848</v>
+        <v>6.348</v>
       </c>
     </row>
     <row r="14">
@@ -2921,10 +2909,10 @@
         <v>0.98</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4575490920134981</v>
+        <v>-0.0634</v>
       </c>
       <c r="J14" t="n">
-        <v>-18.30196368053992</v>
+        <v>-2.536</v>
       </c>
     </row>
     <row r="15">
@@ -2961,10 +2949,10 @@
         <v>0.83</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.9119832393863742</v>
+        <v>-0.3375</v>
       </c>
       <c r="J15" t="n">
-        <v>-36.47932957545497</v>
+        <v>-13.5</v>
       </c>
     </row>
     <row r="16">
@@ -3001,10 +2989,10 @@
         <v>0.74</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.111506601666245</v>
+        <v>-0.4656</v>
       </c>
       <c r="J16" t="n">
-        <v>-44.4602640666498</v>
+        <v>-18.624</v>
       </c>
     </row>
     <row r="17">
@@ -3041,10 +3029,10 @@
         <v>1.28</v>
       </c>
       <c r="I17" t="n">
-        <v>1.049199147456606</v>
+        <v>0.8032</v>
       </c>
       <c r="J17" t="n">
-        <v>41.96796589826424</v>
+        <v>32.128</v>
       </c>
     </row>
     <row r="18">
@@ -3081,10 +3069,10 @@
         <v>1.27</v>
       </c>
       <c r="I18" t="n">
-        <v>1.023645662190869</v>
+        <v>0.7798</v>
       </c>
       <c r="J18" t="n">
-        <v>40.94582648763478</v>
+        <v>31.192</v>
       </c>
     </row>
     <row r="19">
@@ -3121,10 +3109,10 @@
         <v>1.12</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5465144784546592</v>
+        <v>0.3842</v>
       </c>
       <c r="J19" t="n">
-        <v>21.86057913818637</v>
+        <v>15.368</v>
       </c>
     </row>
     <row r="20">
@@ -3161,10 +3149,10 @@
         <v>0.97</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1568242827263651</v>
+        <v>-0.22</v>
       </c>
       <c r="J20" t="n">
-        <v>-6.272971309054603</v>
+        <v>-8.800000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -3201,10 +3189,10 @@
         <v>0.85</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5019946663367664</v>
+        <v>-0.5768</v>
       </c>
       <c r="J21" t="n">
-        <v>-20.07978665347066</v>
+        <v>-23.072</v>
       </c>
     </row>
     <row r="22">
@@ -3241,10 +3229,10 @@
         <v>1.66</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8355175686453921</v>
+        <v>0.953</v>
       </c>
       <c r="J22" t="n">
-        <v>17.54586894155323</v>
+        <v>20.013</v>
       </c>
     </row>
     <row r="23">
@@ -3281,10 +3269,10 @@
         <v>1.15</v>
       </c>
       <c r="I23" t="n">
-        <v>0.02842698339885877</v>
+        <v>0.3214</v>
       </c>
       <c r="J23" t="n">
-        <v>0.5969666513760341</v>
+        <v>6.7494</v>
       </c>
     </row>
     <row r="24">
@@ -3321,10 +3309,10 @@
         <v>0.78</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.7586722353200621</v>
+        <v>-0.4042</v>
       </c>
       <c r="J24" t="n">
-        <v>-15.9321169417213</v>
+        <v>-8.488200000000001</v>
       </c>
     </row>
     <row r="25">
@@ -3361,10 +3349,10 @@
         <v>0.75</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.8019076601370285</v>
+        <v>-0.4463</v>
       </c>
       <c r="J25" t="n">
-        <v>-16.8400608628776</v>
+        <v>-9.372299999999999</v>
       </c>
     </row>
     <row r="26">
@@ -3401,10 +3389,10 @@
         <v>0.49</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.109432470326958</v>
+        <v>-0.7713</v>
       </c>
       <c r="J26" t="n">
-        <v>-23.29808187686611</v>
+        <v>-16.1973</v>
       </c>
     </row>
     <row r="27">
@@ -3441,10 +3429,10 @@
         <v>1.63</v>
       </c>
       <c r="I27" t="n">
-        <v>1.407023951400646</v>
+        <v>0.8499</v>
       </c>
       <c r="J27" t="n">
-        <v>29.54750297941358</v>
+        <v>17.8479</v>
       </c>
     </row>
     <row r="28">
@@ -3481,10 +3469,10 @@
         <v>1.29</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8132422142169951</v>
+        <v>0.4449</v>
       </c>
       <c r="J28" t="n">
-        <v>17.0780864985569</v>
+        <v>9.3429</v>
       </c>
     </row>
     <row r="29">
@@ -3521,10 +3509,10 @@
         <v>1.17</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4233815892807145</v>
+        <v>0.254</v>
       </c>
       <c r="J29" t="n">
-        <v>8.891013374895003</v>
+        <v>5.334</v>
       </c>
     </row>
     <row r="30">
@@ -3561,10 +3549,10 @@
         <v>1.04</v>
       </c>
       <c r="I30" t="n">
-        <v>0.05721553789142537</v>
+        <v>0.0311</v>
       </c>
       <c r="J30" t="n">
-        <v>1.201526295719933</v>
+        <v>0.6531</v>
       </c>
     </row>
     <row r="31">
@@ -3601,10 +3589,10 @@
         <v>0.82</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4080512891349991</v>
+        <v>-0.3905</v>
       </c>
       <c r="J31" t="n">
-        <v>-8.569077071834981</v>
+        <v>-8.2005</v>
       </c>
     </row>
     <row r="32">
@@ -3641,10 +3629,10 @@
         <v>1.75</v>
       </c>
       <c r="I32" t="n">
-        <v>1.153894158926241</v>
+        <v>1.7361</v>
       </c>
       <c r="J32" t="n">
-        <v>34.61682476778723</v>
+        <v>52.083</v>
       </c>
     </row>
     <row r="33">
@@ -3681,10 +3669,10 @@
         <v>1.02</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.1564875516707398</v>
+        <v>0.0356</v>
       </c>
       <c r="J33" t="n">
-        <v>-4.694626550122194</v>
+        <v>1.068</v>
       </c>
     </row>
     <row r="34">
@@ -3721,10 +3709,10 @@
         <v>0.91</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3748638046644671</v>
+        <v>-0.4055</v>
       </c>
       <c r="J34" t="n">
-        <v>-11.24591413993401</v>
+        <v>-12.165</v>
       </c>
     </row>
     <row r="35">
@@ -3761,10 +3749,10 @@
         <v>0.87</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4406564353081844</v>
+        <v>-0.5175</v>
       </c>
       <c r="J35" t="n">
-        <v>-13.21969305924553</v>
+        <v>-15.525</v>
       </c>
     </row>
     <row r="36">
@@ -3801,10 +3789,10 @@
         <v>0.85</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4717206813688135</v>
+        <v>-0.5705</v>
       </c>
       <c r="J36" t="n">
-        <v>-14.1516204410644</v>
+        <v>-17.115</v>
       </c>
     </row>
     <row r="37">
@@ -3841,10 +3829,10 @@
         <v>1.44</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8174926830802995</v>
+        <v>0.6612</v>
       </c>
       <c r="J37" t="n">
-        <v>24.52478049240899</v>
+        <v>19.836</v>
       </c>
     </row>
     <row r="38">
@@ -3881,10 +3869,10 @@
         <v>1.3</v>
       </c>
       <c r="I38" t="n">
-        <v>0.553016200362062</v>
+        <v>0.4869</v>
       </c>
       <c r="J38" t="n">
-        <v>16.59048601086186</v>
+        <v>14.607</v>
       </c>
     </row>
     <row r="39">
@@ -3921,10 +3909,10 @@
         <v>1.01</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.3248376599996882</v>
+        <v>-0.012</v>
       </c>
       <c r="J39" t="n">
-        <v>-9.745129799990645</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="40">
@@ -3961,10 +3949,10 @@
         <v>0.99</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3681102708080616</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="J40" t="n">
-        <v>-11.04330812424185</v>
+        <v>-2.421</v>
       </c>
     </row>
     <row r="41">
@@ -4001,10 +3989,10 @@
         <v>0.77</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.7280219543235499</v>
+        <v>-0.4452</v>
       </c>
       <c r="J41" t="n">
-        <v>-21.8406586297065</v>
+        <v>-13.356</v>
       </c>
     </row>
     <row r="42">
@@ -4041,10 +4029,10 @@
         <v>1.58</v>
       </c>
       <c r="I42" t="n">
-        <v>0.9411434924427052</v>
+        <v>1.3968</v>
       </c>
       <c r="J42" t="n">
-        <v>22.58744381862493</v>
+        <v>33.5232</v>
       </c>
     </row>
     <row r="43">
@@ -4081,10 +4069,10 @@
         <v>1.39</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6871285925993553</v>
+        <v>1.0129</v>
       </c>
       <c r="J43" t="n">
-        <v>16.49108622238453</v>
+        <v>24.3096</v>
       </c>
     </row>
     <row r="44">
@@ -4121,10 +4109,10 @@
         <v>1.33</v>
       </c>
       <c r="I44" t="n">
-        <v>0.5903665061421504</v>
+        <v>0.8811</v>
       </c>
       <c r="J44" t="n">
-        <v>14.16879614741161</v>
+        <v>21.1464</v>
       </c>
     </row>
     <row r="45">
@@ -4161,10 +4149,10 @@
         <v>0.93</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.3842021842183171</v>
+        <v>-0.3784</v>
       </c>
       <c r="J45" t="n">
-        <v>-9.220852421239609</v>
+        <v>-9.0816</v>
       </c>
     </row>
     <row r="46">
@@ -4201,10 +4189,10 @@
         <v>0.59</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.8305138275999715</v>
+        <v>-1.1782</v>
       </c>
       <c r="J46" t="n">
-        <v>-19.93233186239932</v>
+        <v>-28.2768</v>
       </c>
     </row>
     <row r="47">
@@ -4241,10 +4229,10 @@
         <v>1.49</v>
       </c>
       <c r="I47" t="n">
-        <v>0.884716739752946</v>
+        <v>0.7346</v>
       </c>
       <c r="J47" t="n">
-        <v>21.2332017540707</v>
+        <v>17.6304</v>
       </c>
     </row>
     <row r="48">
@@ -4281,10 +4269,10 @@
         <v>1.35</v>
       </c>
       <c r="I48" t="n">
-        <v>0.6350130909842386</v>
+        <v>0.5665</v>
       </c>
       <c r="J48" t="n">
-        <v>15.24031418362173</v>
+        <v>13.596</v>
       </c>
     </row>
     <row r="49">
@@ -4321,10 +4309,10 @@
         <v>1.1</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.0609838709346076</v>
+        <v>0.2058</v>
       </c>
       <c r="J49" t="n">
-        <v>-1.463612902430582</v>
+        <v>4.9392</v>
       </c>
     </row>
     <row r="50">
@@ -4361,10 +4349,10 @@
         <v>0.92</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.5086436942581212</v>
+        <v>-0.2092</v>
       </c>
       <c r="J50" t="n">
-        <v>-12.20744866219491</v>
+        <v>-5.0208</v>
       </c>
     </row>
     <row r="51">
@@ -4401,10 +4389,10 @@
         <v>0.41</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.124817188099608</v>
+        <v>-0.8694</v>
       </c>
       <c r="J51" t="n">
-        <v>-26.9956125143906</v>
+        <v>-20.8656</v>
       </c>
     </row>
     <row r="52">
@@ -4441,10 +4429,10 @@
         <v>1.26</v>
       </c>
       <c r="I52" t="n">
-        <v>0.568358609798719</v>
+        <v>0.496</v>
       </c>
       <c r="J52" t="n">
-        <v>13.07224802537054</v>
+        <v>11.408</v>
       </c>
     </row>
     <row r="53">
@@ -4481,10 +4469,10 @@
         <v>1.16</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3687469640702465</v>
+        <v>0.3541</v>
       </c>
       <c r="J53" t="n">
-        <v>8.48118017361567</v>
+        <v>8.144299999999999</v>
       </c>
     </row>
     <row r="54">
@@ -4521,10 +4509,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.5365463538658648</v>
+        <v>-0.3464</v>
       </c>
       <c r="J54" t="n">
-        <v>-12.34056613891489</v>
+        <v>-7.9672</v>
       </c>
     </row>
     <row r="55">
@@ -4561,10 +4549,10 @@
         <v>0.72</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.6822097646751382</v>
+        <v>-0.4764</v>
       </c>
       <c r="J55" t="n">
-        <v>-15.69082458752818</v>
+        <v>-10.9572</v>
       </c>
     </row>
     <row r="56">
@@ -4601,10 +4589,10 @@
         <v>0.64</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.7932419181227137</v>
+        <v>-0.5822000000000001</v>
       </c>
       <c r="J56" t="n">
-        <v>-18.24456411682242</v>
+        <v>-13.3906</v>
       </c>
     </row>
     <row r="57">
@@ -4641,10 +4629,10 @@
         <v>2.04</v>
       </c>
       <c r="I57" t="n">
-        <v>1.103027284291023</v>
+        <v>2.0116</v>
       </c>
       <c r="J57" t="n">
-        <v>25.36962753869353</v>
+        <v>46.2668</v>
       </c>
     </row>
     <row r="58">
@@ -4681,10 +4669,10 @@
         <v>1.19</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4031242333125567</v>
+        <v>0.5857</v>
       </c>
       <c r="J58" t="n">
-        <v>9.271857366188804</v>
+        <v>13.4711</v>
       </c>
     </row>
     <row r="59">
@@ -4721,10 +4709,10 @@
         <v>0.82</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.4056031025673601</v>
+        <v>-0.651</v>
       </c>
       <c r="J59" t="n">
-        <v>-9.328871359049282</v>
+        <v>-14.973</v>
       </c>
     </row>
     <row r="60">
@@ -4761,10 +4749,10 @@
         <v>0.76</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.5146645872055101</v>
+        <v>-0.7952</v>
       </c>
       <c r="J60" t="n">
-        <v>-11.83728550572673</v>
+        <v>-18.2896</v>
       </c>
     </row>
     <row r="61">
@@ -4801,10 +4789,10 @@
         <v>0.65</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.6863748471387724</v>
+        <v>-1.0396</v>
       </c>
       <c r="J61" t="n">
-        <v>-15.78662148419176</v>
+        <v>-23.9108</v>
       </c>
     </row>
     <row r="62">
@@ -4841,10 +4829,10 @@
         <v>2.28</v>
       </c>
       <c r="I62" t="n">
-        <v>2.035457062150308</v>
+        <v>1.3983</v>
       </c>
       <c r="J62" t="n">
-        <v>32.56731299440492</v>
+        <v>22.3728</v>
       </c>
     </row>
     <row r="63">
@@ -4881,10 +4869,10 @@
         <v>1.76</v>
       </c>
       <c r="I63" t="n">
-        <v>1.485079337191925</v>
+        <v>0.9043</v>
       </c>
       <c r="J63" t="n">
-        <v>23.7612693950708</v>
+        <v>14.4688</v>
       </c>
     </row>
     <row r="64">
@@ -4921,10 +4909,10 @@
         <v>1.37</v>
       </c>
       <c r="I64" t="n">
-        <v>0.6845382350438615</v>
+        <v>0.4355</v>
       </c>
       <c r="J64" t="n">
-        <v>10.95261176070178</v>
+        <v>6.968</v>
       </c>
     </row>
     <row r="65">
@@ -4961,10 +4949,10 @@
         <v>1.16</v>
       </c>
       <c r="I65" t="n">
-        <v>0.3589861115970682</v>
+        <v>0.1649</v>
       </c>
       <c r="J65" t="n">
-        <v>5.743777785553092</v>
+        <v>2.6384</v>
       </c>
     </row>
     <row r="66">
@@ -5001,10 +4989,10 @@
         <v>1.01</v>
       </c>
       <c r="I66" t="n">
-        <v>0.1474979425243782</v>
+        <v>-0.0857</v>
       </c>
       <c r="J66" t="n">
-        <v>2.359967080390052</v>
+        <v>-1.3712</v>
       </c>
     </row>
     <row r="67">
@@ -5041,10 +5029,10 @@
         <v>1.06</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.2850569082342867</v>
+        <v>0.2976</v>
       </c>
       <c r="J67" t="n">
-        <v>-4.560910531748587</v>
+        <v>4.7616</v>
       </c>
     </row>
     <row r="68">
@@ -5081,10 +5069,10 @@
         <v>0.76</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.7288447052296779</v>
+        <v>-0.2849</v>
       </c>
       <c r="J68" t="n">
-        <v>-11.66151528367485</v>
+        <v>-4.5584</v>
       </c>
     </row>
     <row r="69">
@@ -5121,10 +5109,10 @@
         <v>0.72</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.8052951466596352</v>
+        <v>-0.3488</v>
       </c>
       <c r="J69" t="n">
-        <v>-12.88472234655416</v>
+        <v>-5.5808</v>
       </c>
     </row>
     <row r="70">
@@ -5161,10 +5149,10 @@
         <v>0.5</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.281102879274333</v>
+        <v>-0.7022</v>
       </c>
       <c r="J70" t="n">
-        <v>-20.49764606838933</v>
+        <v>-11.2352</v>
       </c>
     </row>
     <row r="71">
@@ -5201,10 +5189,10 @@
         <v>0.29</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.546441462839897</v>
+        <v>-0.9636</v>
       </c>
       <c r="J71" t="n">
-        <v>-24.74306340543836</v>
+        <v>-15.4176</v>
       </c>
     </row>
     <row r="72">
@@ -5241,10 +5229,10 @@
         <v>1.43</v>
       </c>
       <c r="I72" t="n">
-        <v>0.5235135851857461</v>
+        <v>0.7034</v>
       </c>
       <c r="J72" t="n">
-        <v>10.47027170371492</v>
+        <v>14.068</v>
       </c>
     </row>
     <row r="73">
@@ -5281,10 +5269,10 @@
         <v>1</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.3547451835746122</v>
+        <v>0.0364</v>
       </c>
       <c r="J73" t="n">
-        <v>-7.094903671492244</v>
+        <v>0.728</v>
       </c>
     </row>
     <row r="74">
@@ -5321,10 +5309,10 @@
         <v>0.89</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.6341567985489479</v>
+        <v>-0.2225</v>
       </c>
       <c r="J74" t="n">
-        <v>-12.68313597097896</v>
+        <v>-4.45</v>
       </c>
     </row>
     <row r="75">
@@ -5361,10 +5349,10 @@
         <v>0.85</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.7089162558323392</v>
+        <v>-0.2902</v>
       </c>
       <c r="J75" t="n">
-        <v>-14.17832511664678</v>
+        <v>-5.804</v>
       </c>
     </row>
     <row r="76">
@@ -5401,10 +5389,10 @@
         <v>0.52</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.137629320731971</v>
+        <v>-0.7328</v>
       </c>
       <c r="J76" t="n">
-        <v>-22.75258641463942</v>
+        <v>-14.656</v>
       </c>
     </row>
     <row r="77">
@@ -5441,10 +5429,10 @@
         <v>2.1</v>
       </c>
       <c r="I77" t="n">
-        <v>1.136221182390586</v>
+        <v>2.0045</v>
       </c>
       <c r="J77" t="n">
-        <v>22.72442364781172</v>
+        <v>40.09</v>
       </c>
     </row>
     <row r="78">
@@ -5481,10 +5469,10 @@
         <v>1.78</v>
       </c>
       <c r="I78" t="n">
-        <v>0.9251042607753468</v>
+        <v>1.6904</v>
       </c>
       <c r="J78" t="n">
-        <v>18.50208521550694</v>
+        <v>33.808</v>
       </c>
     </row>
     <row r="79">
@@ -5521,10 +5509,10 @@
         <v>1.11</v>
       </c>
       <c r="I79" t="n">
-        <v>0.08504155848920604</v>
+        <v>0.2187</v>
       </c>
       <c r="J79" t="n">
-        <v>1.700831169784121</v>
+        <v>4.374</v>
       </c>
     </row>
     <row r="80">
@@ -5561,10 +5549,10 @@
         <v>1</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.08921484543331466</v>
+        <v>-0.1587</v>
       </c>
       <c r="J80" t="n">
-        <v>-1.784296908666293</v>
+        <v>-3.174</v>
       </c>
     </row>
     <row r="81">
@@ -5601,10 +5589,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.8376738857809295</v>
+        <v>-1.2589</v>
       </c>
       <c r="J81" t="n">
-        <v>-16.75347771561859</v>
+        <v>-25.178</v>
       </c>
     </row>
     <row r="82">
@@ -5641,10 +5629,10 @@
         <v>1.67</v>
       </c>
       <c r="I82" t="n">
-        <v>0.5622780327455847</v>
+        <v>1.5108</v>
       </c>
       <c r="J82" t="n">
-        <v>11.80783868765728</v>
+        <v>31.7268</v>
       </c>
     </row>
     <row r="83">
@@ -5681,10 +5669,10 @@
         <v>1.39</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3756448160967031</v>
+        <v>0.9518</v>
       </c>
       <c r="J83" t="n">
-        <v>7.888541138030766</v>
+        <v>19.9878</v>
       </c>
     </row>
     <row r="84">
@@ -5721,10 +5709,10 @@
         <v>1.25</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2087897798531625</v>
+        <v>0.5942</v>
       </c>
       <c r="J84" t="n">
-        <v>4.384585376916412</v>
+        <v>12.4782</v>
       </c>
     </row>
     <row r="85">
@@ -5761,10 +5749,10 @@
         <v>1.16</v>
       </c>
       <c r="I85" t="n">
-        <v>0.1184830466318091</v>
+        <v>0.3632</v>
       </c>
       <c r="J85" t="n">
-        <v>2.48814397926799</v>
+        <v>7.6272</v>
       </c>
     </row>
     <row r="86">
@@ -5801,10 +5789,10 @@
         <v>0.93</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.1754420631017947</v>
+        <v>-0.4133</v>
       </c>
       <c r="J86" t="n">
-        <v>-3.684283325137689</v>
+        <v>-8.6793</v>
       </c>
     </row>
     <row r="87">
@@ -5841,10 +5829,10 @@
         <v>1.02</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.1546725290812397</v>
+        <v>0.1203</v>
       </c>
       <c r="J87" t="n">
-        <v>-3.248123110706033</v>
+        <v>2.5263</v>
       </c>
     </row>
     <row r="88">
@@ -5881,10 +5869,10 @@
         <v>0.99</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.1956979616780326</v>
+        <v>0.0257</v>
       </c>
       <c r="J88" t="n">
-        <v>-4.109657195238685</v>
+        <v>0.5397</v>
       </c>
     </row>
     <row r="89">
@@ -5921,10 +5909,10 @@
         <v>0.91</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.3191929218381668</v>
+        <v>-0.1435</v>
       </c>
       <c r="J89" t="n">
-        <v>-6.703051358601503</v>
+        <v>-3.0135</v>
       </c>
     </row>
     <row r="90">
@@ -5961,10 +5949,10 @@
         <v>0.82</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.5020109582583075</v>
+        <v>-0.3176</v>
       </c>
       <c r="J90" t="n">
-        <v>-10.54223012342446</v>
+        <v>-6.6696</v>
       </c>
     </row>
     <row r="91">
@@ -6001,10 +5989,10 @@
         <v>0.67</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.6851197435985641</v>
+        <v>-0.5353</v>
       </c>
       <c r="J91" t="n">
-        <v>-14.38751461556985</v>
+        <v>-11.2413</v>
       </c>
     </row>
     <row r="92">
@@ -6041,10 +6029,10 @@
         <v>1.2</v>
       </c>
       <c r="I92" t="n">
-        <v>0.06603631446529255</v>
+        <v>0.434</v>
       </c>
       <c r="J92" t="n">
-        <v>1.386762603771144</v>
+        <v>9.114000000000001</v>
       </c>
     </row>
     <row r="93">
@@ -6081,10 +6069,10 @@
         <v>0.89</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.4539905776318477</v>
+        <v>-0.1704</v>
       </c>
       <c r="J93" t="n">
-        <v>-9.533802130268803</v>
+        <v>-3.5784</v>
       </c>
     </row>
     <row r="94">
@@ -6121,10 +6109,10 @@
         <v>0.86</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.555437824046397</v>
+        <v>-0.2342</v>
       </c>
       <c r="J94" t="n">
-        <v>-11.66419430497434</v>
+        <v>-4.9182</v>
       </c>
     </row>
     <row r="95">
@@ -6161,10 +6149,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.9059015998829106</v>
+        <v>-0.5032</v>
       </c>
       <c r="J95" t="n">
-        <v>-19.02393359754112</v>
+        <v>-10.5672</v>
       </c>
     </row>
     <row r="96">
@@ -6201,10 +6189,10 @@
         <v>0.67</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.9367269216168709</v>
+        <v>-0.5304</v>
       </c>
       <c r="J96" t="n">
-        <v>-19.67126535395429</v>
+        <v>-11.1384</v>
       </c>
     </row>
     <row r="97">
@@ -6241,10 +6229,10 @@
         <v>2.18</v>
       </c>
       <c r="I97" t="n">
-        <v>1.330820959872116</v>
+        <v>1.3691</v>
       </c>
       <c r="J97" t="n">
-        <v>27.94724015731444</v>
+        <v>28.7511</v>
       </c>
     </row>
     <row r="98">
@@ -6281,10 +6269,10 @@
         <v>1.24</v>
       </c>
       <c r="I98" t="n">
-        <v>0.356419415541335</v>
+        <v>0.3304</v>
       </c>
       <c r="J98" t="n">
-        <v>7.484807726368035</v>
+        <v>6.9384</v>
       </c>
     </row>
     <row r="99">
@@ -6321,10 +6309,10 @@
         <v>1.04</v>
       </c>
       <c r="I99" t="n">
-        <v>0.04521786871268491</v>
+        <v>0.0139</v>
       </c>
       <c r="J99" t="n">
-        <v>0.9495752429663832</v>
+        <v>0.2919</v>
       </c>
     </row>
     <row r="100">
@@ -6361,10 +6349,10 @@
         <v>0.95</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.07548714696717872</v>
+        <v>-0.201</v>
       </c>
       <c r="J100" t="n">
-        <v>-1.585230086310753</v>
+        <v>-4.221</v>
       </c>
     </row>
     <row r="101">
@@ -6401,10 +6389,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.08891860362204249</v>
+        <v>-0.2188</v>
       </c>
       <c r="J101" t="n">
-        <v>-1.867290676062892</v>
+        <v>-4.5948</v>
       </c>
     </row>
     <row r="102">
@@ -6441,10 +6429,10 @@
         <v>1.81</v>
       </c>
       <c r="I102" t="n">
-        <v>0.6664059471926588</v>
+        <v>1.7159</v>
       </c>
       <c r="J102" t="n">
-        <v>12.66171299666052</v>
+        <v>32.6021</v>
       </c>
     </row>
     <row r="103">
@@ -6481,10 +6469,10 @@
         <v>1.51</v>
       </c>
       <c r="I103" t="n">
-        <v>0.4903966346443525</v>
+        <v>1.1658</v>
       </c>
       <c r="J103" t="n">
-        <v>9.317536058242696</v>
+        <v>22.1502</v>
       </c>
     </row>
     <row r="104">
@@ -6521,10 +6509,10 @@
         <v>1.21</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1919820093162293</v>
+        <v>0.4559</v>
       </c>
       <c r="J104" t="n">
-        <v>3.647658177008357</v>
+        <v>8.662100000000001</v>
       </c>
     </row>
     <row r="105">
@@ -6561,10 +6549,10 @@
         <v>1.15</v>
       </c>
       <c r="I105" t="n">
-        <v>0.145983087305479</v>
+        <v>0.3074</v>
       </c>
       <c r="J105" t="n">
-        <v>2.7736786588041</v>
+        <v>5.8406</v>
       </c>
     </row>
     <row r="106">
@@ -6601,10 +6589,10 @@
         <v>1.11</v>
       </c>
       <c r="I106" t="n">
-        <v>0.1166623567907334</v>
+        <v>0.2028</v>
       </c>
       <c r="J106" t="n">
-        <v>2.216584779023934</v>
+        <v>3.8532</v>
       </c>
     </row>
     <row r="107">
@@ -6641,10 +6629,10 @@
         <v>1.03</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.1244723562657374</v>
+        <v>0.2054</v>
       </c>
       <c r="J107" t="n">
-        <v>-2.36497476904901</v>
+        <v>3.9026</v>
       </c>
     </row>
     <row r="108">
@@ -6681,10 +6669,10 @@
         <v>0.79</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.410748182986409</v>
+        <v>-0.2738</v>
       </c>
       <c r="J108" t="n">
-        <v>-7.804215476741772</v>
+        <v>-5.2022</v>
       </c>
     </row>
     <row r="109">
@@ -6721,10 +6709,10 @@
         <v>0.76</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.4584736575407777</v>
+        <v>-0.3245</v>
       </c>
       <c r="J109" t="n">
-        <v>-8.710999493274777</v>
+        <v>-6.1655</v>
       </c>
     </row>
     <row r="110">
@@ -6761,10 +6749,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.7650104302808285</v>
+        <v>-0.6425999999999999</v>
       </c>
       <c r="J110" t="n">
-        <v>-14.53519817533574</v>
+        <v>-12.2094</v>
       </c>
     </row>
     <row r="111">
@@ -6801,10 +6789,10 @@
         <v>0.53</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.7959012321941569</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="J111" t="n">
-        <v>-15.12212341168898</v>
+        <v>-12.958</v>
       </c>
     </row>
     <row r="112">
@@ -6841,10 +6829,10 @@
         <v>1.1</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.1284675331344536</v>
+        <v>0.386</v>
       </c>
       <c r="J112" t="n">
-        <v>-2.055480530151258</v>
+        <v>6.176</v>
       </c>
     </row>
     <row r="113">
@@ -6881,10 +6869,10 @@
         <v>0.58</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.7567237668324408</v>
+        <v>-0.5748</v>
       </c>
       <c r="J113" t="n">
-        <v>-12.10758026931905</v>
+        <v>-9.1968</v>
       </c>
     </row>
     <row r="114">
@@ -6921,10 +6909,10 @@
         <v>0.57</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.7706311213786103</v>
+        <v>-0.5901999999999999</v>
       </c>
       <c r="J114" t="n">
-        <v>-12.33009794205777</v>
+        <v>-9.443199999999999</v>
       </c>
     </row>
     <row r="115">
@@ -6961,10 +6949,10 @@
         <v>0.57</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.7706311213786103</v>
+        <v>-0.5901999999999999</v>
       </c>
       <c r="J115" t="n">
-        <v>-12.33009794205777</v>
+        <v>-9.443199999999999</v>
       </c>
     </row>
     <row r="116">
@@ -7001,10 +6989,10 @@
         <v>0.34</v>
       </c>
       <c r="I116" t="n">
-        <v>-1.009634939287771</v>
+        <v>-0.8979</v>
       </c>
       <c r="J116" t="n">
-        <v>-16.15415902860434</v>
+        <v>-14.3664</v>
       </c>
     </row>
     <row r="117">
@@ -7041,10 +7029,10 @@
         <v>1.77</v>
       </c>
       <c r="I117" t="n">
-        <v>0.6576748639433194</v>
+        <v>1.6079</v>
       </c>
       <c r="J117" t="n">
-        <v>10.52279782309311</v>
+        <v>25.7264</v>
       </c>
     </row>
     <row r="118">
@@ -7081,10 +7069,10 @@
         <v>1.58</v>
       </c>
       <c r="I118" t="n">
-        <v>0.5357079382504356</v>
+        <v>1.2497</v>
       </c>
       <c r="J118" t="n">
-        <v>8.57132701200697</v>
+        <v>19.9952</v>
       </c>
     </row>
     <row r="119">
@@ -7121,10 +7109,10 @@
         <v>1.45</v>
       </c>
       <c r="I119" t="n">
-        <v>0.3922828856028821</v>
+        <v>0.9513</v>
       </c>
       <c r="J119" t="n">
-        <v>6.276526169646114</v>
+        <v>15.2208</v>
       </c>
     </row>
     <row r="120">
@@ -7161,10 +7149,10 @@
         <v>1.38</v>
       </c>
       <c r="I120" t="n">
-        <v>0.3278685558157247</v>
+        <v>0.7954</v>
       </c>
       <c r="J120" t="n">
-        <v>5.245896893051595</v>
+        <v>12.7264</v>
       </c>
     </row>
     <row r="121">
@@ -7201,10 +7189,10 @@
         <v>1.2</v>
       </c>
       <c r="I121" t="n">
-        <v>0.2008044338114899</v>
+        <v>0.3929</v>
       </c>
       <c r="J121" t="n">
-        <v>3.212870940983838</v>
+        <v>6.2864</v>
       </c>
     </row>
     <row r="122">
@@ -7241,10 +7229,10 @@
         <v>1.13</v>
       </c>
       <c r="I122" t="n">
-        <v>-0.01461499965855112</v>
+        <v>0.32</v>
       </c>
       <c r="J122" t="n">
-        <v>-0.2922999931710224</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="123">
@@ -7281,10 +7269,10 @@
         <v>1.1</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.05524320976819631</v>
+        <v>0.2714</v>
       </c>
       <c r="J123" t="n">
-        <v>-1.104864195363926</v>
+        <v>5.428</v>
       </c>
     </row>
     <row r="124">
@@ -7321,10 +7309,10 @@
         <v>0.86</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.4523014365099414</v>
+        <v>-0.2512</v>
       </c>
       <c r="J124" t="n">
-        <v>-9.046028730198829</v>
+        <v>-5.024</v>
       </c>
     </row>
     <row r="125">
@@ -7361,10 +7349,10 @@
         <v>0.68</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.6907299017853652</v>
+        <v>-0.5229</v>
       </c>
       <c r="J125" t="n">
-        <v>-13.8145980357073</v>
+        <v>-10.458</v>
       </c>
     </row>
     <row r="126">
@@ -7401,10 +7389,10 @@
         <v>0.66</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.7118098473272307</v>
+        <v>-0.5495</v>
       </c>
       <c r="J126" t="n">
-        <v>-14.23619694654461</v>
+        <v>-10.99</v>
       </c>
     </row>
     <row r="127">
@@ -7441,10 +7429,10 @@
         <v>1.79</v>
       </c>
       <c r="I127" t="n">
-        <v>0.6431406273130746</v>
+        <v>1.7297</v>
       </c>
       <c r="J127" t="n">
-        <v>12.86281254626149</v>
+        <v>34.594</v>
       </c>
     </row>
     <row r="128">
@@ -7481,10 +7469,10 @@
         <v>1.43</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4393193080410294</v>
+        <v>1.0597</v>
       </c>
       <c r="J128" t="n">
-        <v>8.786386160820587</v>
+        <v>21.194</v>
       </c>
     </row>
     <row r="129">
@@ -7521,10 +7509,10 @@
         <v>1.26</v>
       </c>
       <c r="I129" t="n">
-        <v>0.289278172435241</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="J129" t="n">
-        <v>5.785563448704819</v>
+        <v>13.356</v>
       </c>
     </row>
     <row r="130">
@@ -7561,10 +7549,10 @@
         <v>1.04</v>
       </c>
       <c r="I130" t="n">
-        <v>0.04993655753097242</v>
+        <v>0.0353</v>
       </c>
       <c r="J130" t="n">
-        <v>0.9987311506194484</v>
+        <v>0.706</v>
       </c>
     </row>
     <row r="131">
@@ -7601,10 +7589,10 @@
         <v>0.67</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.6190869161387087</v>
+        <v>-1.0264</v>
       </c>
       <c r="J131" t="n">
-        <v>-12.38173832277417</v>
+        <v>-20.528</v>
       </c>
     </row>
     <row r="132">
@@ -7641,10 +7629,10 @@
         <v>1.58</v>
       </c>
       <c r="I132" t="n">
-        <v>0.2560533515587223</v>
+        <v>0.9192</v>
       </c>
       <c r="J132" t="n">
-        <v>4.865013679615724</v>
+        <v>17.4648</v>
       </c>
     </row>
     <row r="133">
@@ -7681,10 +7669,10 @@
         <v>0.79</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.5936891571225189</v>
+        <v>-0.3433</v>
       </c>
       <c r="J133" t="n">
-        <v>-11.28009398532786</v>
+        <v>-6.5227</v>
       </c>
     </row>
     <row r="134">
@@ -7721,10 +7709,10 @@
         <v>0.66</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.7670309400674348</v>
+        <v>-0.5354</v>
       </c>
       <c r="J134" t="n">
-        <v>-14.57358786128126</v>
+        <v>-10.1726</v>
       </c>
     </row>
     <row r="135">
@@ -7761,10 +7749,10 @@
         <v>0.6</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.8316514054327171</v>
+        <v>-0.615</v>
       </c>
       <c r="J135" t="n">
-        <v>-15.80137670322162</v>
+        <v>-11.685</v>
       </c>
     </row>
     <row r="136">
@@ -7801,10 +7789,10 @@
         <v>0.52</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.9092054144976917</v>
+        <v>-0.7156</v>
       </c>
       <c r="J136" t="n">
-        <v>-17.27490287545614</v>
+        <v>-13.5964</v>
       </c>
     </row>
     <row r="137">
@@ -7841,10 +7829,10 @@
         <v>2.09</v>
       </c>
       <c r="I137" t="n">
-        <v>0.4837081548694343</v>
+        <v>2.0593</v>
       </c>
       <c r="J137" t="n">
-        <v>9.190454942519251</v>
+        <v>39.1267</v>
       </c>
     </row>
     <row r="138">
@@ -7881,10 +7869,10 @@
         <v>1.7</v>
       </c>
       <c r="I138" t="n">
-        <v>0.3702988460228676</v>
+        <v>1.5294</v>
       </c>
       <c r="J138" t="n">
-        <v>7.035678074434483</v>
+        <v>29.0586</v>
       </c>
     </row>
     <row r="139">
@@ -7921,10 +7909,10 @@
         <v>1.3</v>
       </c>
       <c r="I139" t="n">
-        <v>0.152987962669208</v>
+        <v>0.6685</v>
       </c>
       <c r="J139" t="n">
-        <v>2.906771290714952</v>
+        <v>12.7015</v>
       </c>
     </row>
     <row r="140">
@@ -7961,10 +7949,10 @@
         <v>0.99</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.007506501031444588</v>
+        <v>-0.23</v>
       </c>
       <c r="J140" t="n">
-        <v>-0.1426235195974472</v>
+        <v>-4.37</v>
       </c>
     </row>
     <row r="141">
@@ -8001,10 +7989,10 @@
         <v>0.73</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4881434662554781</v>
+        <v>-0.9194</v>
       </c>
       <c r="J141" t="n">
-        <v>-9.274725858854083</v>
+        <v>-17.4686</v>
       </c>
     </row>
     <row r="142">
@@ -8041,10 +8029,10 @@
         <v>1.09</v>
       </c>
       <c r="I142" t="n">
-        <v>-0.07988306718094171</v>
+        <v>0.3044</v>
       </c>
       <c r="J142" t="n">
-        <v>-1.517778276437892</v>
+        <v>5.7836</v>
       </c>
     </row>
     <row r="143">
@@ -8081,10 +8069,10 @@
         <v>0.96</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.2305361616433685</v>
+        <v>0.0075</v>
       </c>
       <c r="J143" t="n">
-        <v>-4.380187071224002</v>
+        <v>0.1425</v>
       </c>
     </row>
     <row r="144">
@@ -8121,10 +8109,10 @@
         <v>0.68</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.6785299194925732</v>
+        <v>-0.4853</v>
       </c>
       <c r="J144" t="n">
-        <v>-12.89206847035889</v>
+        <v>-9.220700000000001</v>
       </c>
     </row>
     <row r="145">
@@ -8161,10 +8149,10 @@
         <v>0.6</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.7775019306421401</v>
+        <v>-0.5978</v>
       </c>
       <c r="J145" t="n">
-        <v>-14.77253668220066</v>
+        <v>-11.3582</v>
       </c>
     </row>
     <row r="146">
@@ -8201,10 +8189,10 @@
         <v>0.49</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.8912000959228241</v>
+        <v>-0.7398</v>
       </c>
       <c r="J146" t="n">
-        <v>-16.93280182253366</v>
+        <v>-14.0562</v>
       </c>
     </row>
     <row r="147">
@@ -8241,10 +8229,10 @@
         <v>1.96</v>
       </c>
       <c r="I147" t="n">
-        <v>0.4574113655182726</v>
+        <v>1.9574</v>
       </c>
       <c r="J147" t="n">
-        <v>8.690815944847179</v>
+        <v>37.1906</v>
       </c>
     </row>
     <row r="148">
@@ -8281,10 +8269,10 @@
         <v>1.57</v>
       </c>
       <c r="I148" t="n">
-        <v>0.3303707919234117</v>
+        <v>1.2873</v>
       </c>
       <c r="J148" t="n">
-        <v>6.277045046544822</v>
+        <v>24.4587</v>
       </c>
     </row>
     <row r="149">
@@ -8321,10 +8309,10 @@
         <v>1.21</v>
       </c>
       <c r="I149" t="n">
-        <v>0.1168150341190374</v>
+        <v>0.4575</v>
       </c>
       <c r="J149" t="n">
-        <v>2.219485648261711</v>
+        <v>8.692500000000001</v>
       </c>
     </row>
     <row r="150">
@@ -8361,10 +8349,10 @@
         <v>1.15</v>
       </c>
       <c r="I150" t="n">
-        <v>0.08755114286229546</v>
+        <v>0.3087</v>
       </c>
       <c r="J150" t="n">
-        <v>1.663471714383614</v>
+        <v>5.8653</v>
       </c>
     </row>
     <row r="151">
@@ -8401,10 +8389,10 @@
         <v>0.88</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.1168815700338922</v>
+        <v>-0.5677</v>
       </c>
       <c r="J151" t="n">
-        <v>-2.220749830643952</v>
+        <v>-10.7863</v>
       </c>
     </row>
     <row r="152">
@@ -8441,10 +8429,10 @@
         <v>1.33</v>
       </c>
       <c r="I152" t="n">
-        <v>0.5337465928943478</v>
+        <v>0.5039</v>
       </c>
       <c r="J152" t="n">
-        <v>12.80991822946435</v>
+        <v>12.0936</v>
       </c>
     </row>
     <row r="153">
@@ -8481,10 +8469,10 @@
         <v>1.31</v>
       </c>
       <c r="I153" t="n">
-        <v>0.5058329443448216</v>
+        <v>0.4777</v>
       </c>
       <c r="J153" t="n">
-        <v>12.13999066427572</v>
+        <v>11.4648</v>
       </c>
     </row>
     <row r="154">
@@ -8521,10 +8509,10 @@
         <v>1.18</v>
       </c>
       <c r="I154" t="n">
-        <v>0.274264845953573</v>
+        <v>0.2866</v>
       </c>
       <c r="J154" t="n">
-        <v>6.582356302885753</v>
+        <v>6.8784</v>
       </c>
     </row>
     <row r="155">
@@ -8561,10 +8549,10 @@
         <v>1.07</v>
       </c>
       <c r="I155" t="n">
-        <v>0.02876439347250656</v>
+        <v>0.0919</v>
       </c>
       <c r="J155" t="n">
-        <v>0.6903454433401576</v>
+        <v>2.2056</v>
       </c>
     </row>
     <row r="156">
@@ -8601,10 +8589,10 @@
         <v>0.97</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.1041539935617627</v>
+        <v>-0.1442</v>
       </c>
       <c r="J156" t="n">
-        <v>-2.499695845482305</v>
+        <v>-3.4608</v>
       </c>
     </row>
     <row r="157">
@@ -8641,10 +8629,10 @@
         <v>1.28</v>
       </c>
       <c r="I157" t="n">
-        <v>0.3584108596337373</v>
+        <v>0.5098</v>
       </c>
       <c r="J157" t="n">
-        <v>8.601860631209695</v>
+        <v>12.2352</v>
       </c>
     </row>
     <row r="158">
@@ -8681,10 +8669,10 @@
         <v>0.97</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.1320508333754212</v>
+        <v>-0.058</v>
       </c>
       <c r="J158" t="n">
-        <v>-3.169220001010108</v>
+        <v>-1.392</v>
       </c>
     </row>
     <row r="159">
@@ -8721,10 +8709,10 @@
         <v>0.9</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.2479778828689526</v>
+        <v>-0.2114</v>
       </c>
       <c r="J159" t="n">
-        <v>-5.951469188854862</v>
+        <v>-5.0736</v>
       </c>
     </row>
     <row r="160">
@@ -8761,10 +8749,10 @@
         <v>0.85</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.3036147187371336</v>
+        <v>-0.2956</v>
       </c>
       <c r="J160" t="n">
-        <v>-7.286753249691206</v>
+        <v>-7.0944</v>
       </c>
     </row>
     <row r="161">
@@ -8801,10 +8789,10 @@
         <v>0.77</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3789486865542543</v>
+        <v>-0.4155</v>
       </c>
       <c r="J161" t="n">
-        <v>-9.094768477302104</v>
+        <v>-9.972</v>
       </c>
     </row>
     <row r="162">
@@ -8841,10 +8829,10 @@
         <v>1.32</v>
       </c>
       <c r="I162" t="n">
-        <v>0.3134279585986848</v>
+        <v>0.5577</v>
       </c>
       <c r="J162" t="n">
-        <v>6.58198713057238</v>
+        <v>11.7117</v>
       </c>
     </row>
     <row r="163">
@@ -8881,10 +8869,10 @@
         <v>1.14</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.01435327745445115</v>
+        <v>0.3059</v>
       </c>
       <c r="J163" t="n">
-        <v>-0.3014188265434742</v>
+        <v>6.4239</v>
       </c>
     </row>
     <row r="164">
@@ -8921,10 +8909,10 @@
         <v>0.95</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.2695099078879224</v>
+        <v>-0.119</v>
       </c>
       <c r="J164" t="n">
-        <v>-5.65970806564637</v>
+        <v>-2.499</v>
       </c>
     </row>
     <row r="165">
@@ -8961,10 +8949,10 @@
         <v>0.76</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.4677868307380431</v>
+        <v>-0.4324</v>
       </c>
       <c r="J165" t="n">
-        <v>-9.823523445498903</v>
+        <v>-9.080399999999999</v>
       </c>
     </row>
     <row r="166">
@@ -9001,10 +8989,10 @@
         <v>0.66</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.5441260253332625</v>
+        <v>-0.5657</v>
       </c>
       <c r="J166" t="n">
-        <v>-11.42664653199851</v>
+        <v>-11.8797</v>
       </c>
     </row>
     <row r="167">
@@ -9041,10 +9029,10 @@
         <v>1.65</v>
       </c>
       <c r="I167" t="n">
-        <v>0.8605792739975857</v>
+        <v>1.5017</v>
       </c>
       <c r="J167" t="n">
-        <v>18.0721647539493</v>
+        <v>31.5357</v>
       </c>
     </row>
     <row r="168">
@@ -9081,10 +9069,10 @@
         <v>1.18</v>
       </c>
       <c r="I168" t="n">
-        <v>0.2359744744287412</v>
+        <v>0.448</v>
       </c>
       <c r="J168" t="n">
-        <v>4.955463963003566</v>
+        <v>9.407999999999999</v>
       </c>
     </row>
     <row r="169">
@@ -9121,10 +9109,10 @@
         <v>1.15</v>
       </c>
       <c r="I169" t="n">
-        <v>0.1838528481647361</v>
+        <v>0.3661</v>
       </c>
       <c r="J169" t="n">
-        <v>3.860909811459459</v>
+        <v>7.6881</v>
       </c>
     </row>
     <row r="170">
@@ -9161,10 +9149,10 @@
         <v>1.07</v>
       </c>
       <c r="I170" t="n">
-        <v>0.05708407334353003</v>
+        <v>0.1382</v>
       </c>
       <c r="J170" t="n">
-        <v>1.198765540214131</v>
+        <v>2.9022</v>
       </c>
     </row>
     <row r="171">
@@ -9201,10 +9189,10 @@
         <v>1.05</v>
       </c>
       <c r="I171" t="n">
-        <v>0.02599216368089379</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="J171" t="n">
-        <v>0.5458354372987696</v>
+        <v>1.5813</v>
       </c>
     </row>
     <row r="172">
@@ -9241,10 +9229,10 @@
         <v>1.17</v>
       </c>
       <c r="I172" t="n">
-        <v>0.05406363062350757</v>
+        <v>0.364</v>
       </c>
       <c r="J172" t="n">
-        <v>1.135336243093659</v>
+        <v>7.644</v>
       </c>
     </row>
     <row r="173">
@@ -9281,10 +9269,10 @@
         <v>1.01</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.139521869530904</v>
+        <v>0.0743</v>
       </c>
       <c r="J173" t="n">
-        <v>-2.929959260148983</v>
+        <v>1.5603</v>
       </c>
     </row>
     <row r="174">
@@ -9321,10 +9309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.2330151514162197</v>
+        <v>-0.1129</v>
       </c>
       <c r="J174" t="n">
-        <v>-4.893318179740613</v>
+        <v>-2.3709</v>
       </c>
     </row>
     <row r="175">
@@ -9361,10 +9349,10 @@
         <v>0.86</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3531985043771553</v>
+        <v>-0.2717</v>
       </c>
       <c r="J175" t="n">
-        <v>-7.417168591920261</v>
+        <v>-5.7057</v>
       </c>
     </row>
     <row r="176">
@@ -9401,10 +9389,10 @@
         <v>0.68</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5140416139993671</v>
+        <v>-0.5332</v>
       </c>
       <c r="J176" t="n">
-        <v>-10.79487389398671</v>
+        <v>-11.1972</v>
       </c>
     </row>
     <row r="177">
@@ -9441,10 +9429,10 @@
         <v>2.02</v>
       </c>
       <c r="I177" t="n">
-        <v>1.130327544868109</v>
+        <v>2.0478</v>
       </c>
       <c r="J177" t="n">
-        <v>23.73687844223029</v>
+        <v>43.0038</v>
       </c>
     </row>
     <row r="178">
@@ -9481,10 +9469,10 @@
         <v>1.52</v>
       </c>
       <c r="I178" t="n">
-        <v>0.7511431681691522</v>
+        <v>1.2503</v>
       </c>
       <c r="J178" t="n">
-        <v>15.7740065315522</v>
+        <v>26.2563</v>
       </c>
     </row>
     <row r="179">
@@ -9521,10 +9509,10 @@
         <v>0.93</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1137723267235032</v>
+        <v>-0.3976</v>
       </c>
       <c r="J179" t="n">
-        <v>-2.389218861193566</v>
+        <v>-8.349600000000001</v>
       </c>
     </row>
     <row r="180">
@@ -9561,10 +9549,10 @@
         <v>0.86</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1980750678505148</v>
+        <v>-0.5888</v>
       </c>
       <c r="J180" t="n">
-        <v>-4.159576424860812</v>
+        <v>-12.3648</v>
       </c>
     </row>
     <row r="181">
@@ -9601,10 +9589,10 @@
         <v>0.79</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2622072850587236</v>
+        <v>-0.759</v>
       </c>
       <c r="J181" t="n">
-        <v>-5.506352986233195</v>
+        <v>-15.939</v>
       </c>
     </row>
     <row r="182">
@@ -9641,10 +9629,10 @@
         <v>1.1</v>
       </c>
       <c r="I182" t="n">
-        <v>0.1121399321966757</v>
+        <v>0.3842</v>
       </c>
       <c r="J182" t="n">
-        <v>5.943416406423812</v>
+        <v>20.3626</v>
       </c>
     </row>
     <row r="183">
@@ -9681,10 +9669,10 @@
         <v>1.08</v>
       </c>
       <c r="I183" t="n">
-        <v>0.0821000863161597</v>
+        <v>0.3224</v>
       </c>
       <c r="J183" t="n">
-        <v>4.351304574756464</v>
+        <v>17.0872</v>
       </c>
     </row>
     <row r="184">
@@ -9721,10 +9709,10 @@
         <v>1.08</v>
       </c>
       <c r="I184" t="n">
-        <v>0.0821000863161597</v>
+        <v>0.3224</v>
       </c>
       <c r="J184" t="n">
-        <v>4.351304574756464</v>
+        <v>17.0872</v>
       </c>
     </row>
     <row r="185">
@@ -9761,10 +9749,10 @@
         <v>0.99</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.07353101592005042</v>
+        <v>-0.0878</v>
       </c>
       <c r="J185" t="n">
-        <v>-3.897143843762672</v>
+        <v>-4.6534</v>
       </c>
     </row>
     <row r="186">
@@ -9801,10 +9789,10 @@
         <v>0.84</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.3179798926802981</v>
+        <v>-0.5723</v>
       </c>
       <c r="J186" t="n">
-        <v>-16.8529343120558</v>
+        <v>-30.3319</v>
       </c>
     </row>
     <row r="187">
@@ -9841,10 +9829,10 @@
         <v>1.5</v>
       </c>
       <c r="I187" t="n">
-        <v>0.6121645111041832</v>
+        <v>0.7342</v>
       </c>
       <c r="J187" t="n">
-        <v>32.44471908852171</v>
+        <v>38.9126</v>
       </c>
     </row>
     <row r="188">
@@ -9881,10 +9869,10 @@
         <v>1.19</v>
       </c>
       <c r="I188" t="n">
-        <v>0.2155091249962693</v>
+        <v>0.3366</v>
       </c>
       <c r="J188" t="n">
-        <v>11.42198362480227</v>
+        <v>17.8398</v>
       </c>
     </row>
     <row r="189">
@@ -9921,10 +9909,10 @@
         <v>1.1</v>
       </c>
       <c r="I189" t="n">
-        <v>0.02691170762628851</v>
+        <v>0.1863</v>
       </c>
       <c r="J189" t="n">
-        <v>1.426320504193291</v>
+        <v>9.873900000000001</v>
       </c>
     </row>
     <row r="190">
@@ -9961,10 +9949,10 @@
         <v>0.93</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2656285631180615</v>
+        <v>-0.2015</v>
       </c>
       <c r="J190" t="n">
-        <v>-14.07831384525726</v>
+        <v>-10.6795</v>
       </c>
     </row>
     <row r="191">
@@ -10001,10 +9989,10 @@
         <v>0.74</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4424319091763919</v>
+        <v>-0.4835</v>
       </c>
       <c r="J191" t="n">
-        <v>-23.44889118634877</v>
+        <v>-25.6255</v>
       </c>
     </row>
     <row r="192">
@@ -10041,10 +10029,10 @@
         <v>2.69</v>
       </c>
       <c r="I192" t="n">
-        <v>0.6391550991150338</v>
+        <v>2.0593</v>
       </c>
       <c r="J192" t="n">
-        <v>9.587326486725507</v>
+        <v>30.8895</v>
       </c>
     </row>
     <row r="193">
@@ -10081,10 +10069,10 @@
         <v>1.64</v>
       </c>
       <c r="I193" t="n">
-        <v>0.3491156205242736</v>
+        <v>1.3271</v>
       </c>
       <c r="J193" t="n">
-        <v>5.236734307864104</v>
+        <v>19.9065</v>
       </c>
     </row>
     <row r="194">
@@ -10121,10 +10109,10 @@
         <v>1.26</v>
       </c>
       <c r="I194" t="n">
-        <v>0.1427125940814146</v>
+        <v>0.5059</v>
       </c>
       <c r="J194" t="n">
-        <v>2.140688911221219</v>
+        <v>7.5885</v>
       </c>
     </row>
     <row r="195">
@@ -10161,10 +10149,10 @@
         <v>1.15</v>
       </c>
       <c r="I195" t="n">
-        <v>0.1016198577244625</v>
+        <v>0.2518</v>
       </c>
       <c r="J195" t="n">
-        <v>1.524297865866938</v>
+        <v>3.777</v>
       </c>
     </row>
     <row r="196">
@@ -10201,10 +10189,10 @@
         <v>1.07</v>
       </c>
       <c r="I196" t="n">
-        <v>0.07281723425936622</v>
+        <v>0.0423</v>
       </c>
       <c r="J196" t="n">
-        <v>1.092258513890493</v>
+        <v>0.6345</v>
       </c>
     </row>
     <row r="197">
@@ -10241,10 +10229,10 @@
         <v>0.89</v>
       </c>
       <c r="I197" t="n">
-        <v>-0.2718410932175637</v>
+        <v>-0.0453</v>
       </c>
       <c r="J197" t="n">
-        <v>-4.077616398263455</v>
+        <v>-0.6795</v>
       </c>
     </row>
     <row r="198">
@@ -10281,10 +10269,10 @@
         <v>0.67</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.4509071701807258</v>
+        <v>-0.3945</v>
       </c>
       <c r="J198" t="n">
-        <v>-6.763607552710888</v>
+        <v>-5.9175</v>
       </c>
     </row>
     <row r="199">
@@ -10321,10 +10309,10 @@
         <v>0.53</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.6292697816482861</v>
+        <v>-0.6393</v>
       </c>
       <c r="J199" t="n">
-        <v>-9.439046724724291</v>
+        <v>-9.589499999999999</v>
       </c>
     </row>
     <row r="200">
@@ -10361,10 +10349,10 @@
         <v>0.48</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.6727194729520006</v>
+        <v>-0.7105</v>
       </c>
       <c r="J200" t="n">
-        <v>-10.09079209428001</v>
+        <v>-10.6575</v>
       </c>
     </row>
     <row r="201">
@@ -10401,10 +10389,10 @@
         <v>0.48</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.6727194729520006</v>
+        <v>-0.7105</v>
       </c>
       <c r="J201" t="n">
-        <v>-10.09079209428001</v>
+        <v>-10.6575</v>
       </c>
     </row>
     <row r="202">
@@ -10441,10 +10429,10 @@
         <v>1.47</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3551534929710601</v>
+        <v>0.6833</v>
       </c>
       <c r="J202" t="n">
-        <v>8.168530338334383</v>
+        <v>15.7159</v>
       </c>
     </row>
     <row r="203">
@@ -10481,10 +10469,10 @@
         <v>1.34</v>
       </c>
       <c r="I203" t="n">
-        <v>0.2848767106528749</v>
+        <v>0.5249</v>
       </c>
       <c r="J203" t="n">
-        <v>6.552164345016123</v>
+        <v>12.0727</v>
       </c>
     </row>
     <row r="204">
@@ -10521,10 +10509,10 @@
         <v>1.09</v>
       </c>
       <c r="I204" t="n">
-        <v>0.06651371735691541</v>
+        <v>0.1357</v>
       </c>
       <c r="J204" t="n">
-        <v>1.529815499209054</v>
+        <v>3.1211</v>
       </c>
     </row>
     <row r="205">
@@ -10561,10 +10549,10 @@
         <v>0.92</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.1844722279197799</v>
+        <v>-0.2309</v>
       </c>
       <c r="J205" t="n">
-        <v>-4.242861242154938</v>
+        <v>-5.3107</v>
       </c>
     </row>
     <row r="206">
@@ -10601,10 +10589,10 @@
         <v>0.91</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.2047195159012219</v>
+        <v>-0.2476</v>
       </c>
       <c r="J206" t="n">
-        <v>-4.708548865728104</v>
+        <v>-5.6948</v>
       </c>
     </row>
     <row r="207">
@@ -10641,10 +10629,10 @@
         <v>1.1</v>
       </c>
       <c r="I207" t="n">
-        <v>0.03273512281626955</v>
+        <v>0.2545</v>
       </c>
       <c r="J207" t="n">
-        <v>0.7529078247741997</v>
+        <v>5.8535</v>
       </c>
     </row>
     <row r="208">
@@ -10681,10 +10669,10 @@
         <v>1.1</v>
       </c>
       <c r="I208" t="n">
-        <v>0.03273512281626955</v>
+        <v>0.2545</v>
       </c>
       <c r="J208" t="n">
-        <v>0.7529078247741997</v>
+        <v>5.8535</v>
       </c>
     </row>
     <row r="209">
@@ -10721,10 +10709,10 @@
         <v>1.07</v>
       </c>
       <c r="I209" t="n">
-        <v>0.005383029825116851</v>
+        <v>0.2022</v>
       </c>
       <c r="J209" t="n">
-        <v>0.1238096859776876</v>
+        <v>4.6506</v>
       </c>
     </row>
     <row r="210">
@@ -10761,10 +10749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.452169784438301</v>
+        <v>-0.3502</v>
       </c>
       <c r="J210" t="n">
-        <v>-10.39990504208092</v>
+        <v>-8.054600000000001</v>
       </c>
     </row>
     <row r="211">
@@ -10801,10 +10789,10 @@
         <v>0.57</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.7095089326009156</v>
+        <v>-0.6717</v>
       </c>
       <c r="J211" t="n">
-        <v>-16.31870544982106</v>
+        <v>-15.4491</v>
       </c>
     </row>
     <row r="212">
@@ -10841,10 +10829,10 @@
         <v>1.33</v>
       </c>
       <c r="I212" t="n">
-        <v>0.2219231908715659</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="J212" t="n">
-        <v>5.326156580917581</v>
+        <v>13.56</v>
       </c>
     </row>
     <row r="213">
@@ -10881,10 +10869,10 @@
         <v>1.09</v>
       </c>
       <c r="I213" t="n">
-        <v>0.02672479040526768</v>
+        <v>0.2176</v>
       </c>
       <c r="J213" t="n">
-        <v>0.6413949697264242</v>
+        <v>5.2224</v>
       </c>
     </row>
     <row r="214">
@@ -10921,10 +10909,10 @@
         <v>1.03</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.06602301522660434</v>
+        <v>0.1009</v>
       </c>
       <c r="J214" t="n">
-        <v>-1.584552365438504</v>
+        <v>2.4216</v>
       </c>
     </row>
     <row r="215">
@@ -10961,10 +10949,10 @@
         <v>0.78</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.5268228345595395</v>
+        <v>-0.408</v>
       </c>
       <c r="J215" t="n">
-        <v>-12.64374802942895</v>
+        <v>-9.792</v>
       </c>
     </row>
     <row r="216">
@@ -11001,10 +10989,10 @@
         <v>0.68</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.6421567362885966</v>
+        <v>-0.5429</v>
       </c>
       <c r="J216" t="n">
-        <v>-15.41176167092632</v>
+        <v>-13.0296</v>
       </c>
     </row>
     <row r="217">
@@ -11041,10 +11029,10 @@
         <v>1.7</v>
       </c>
       <c r="I217" t="n">
-        <v>0.4717034476365942</v>
+        <v>1.646</v>
       </c>
       <c r="J217" t="n">
-        <v>11.32088274327826</v>
+        <v>39.504</v>
       </c>
     </row>
     <row r="218">
@@ -11081,10 +11069,10 @@
         <v>1.36</v>
       </c>
       <c r="I218" t="n">
-        <v>0.3031598940675897</v>
+        <v>0.9735</v>
       </c>
       <c r="J218" t="n">
-        <v>7.275837457622153</v>
+        <v>23.364</v>
       </c>
     </row>
     <row r="219">
@@ -11121,10 +11109,10 @@
         <v>0.89</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.2716858548201994</v>
+        <v>-0.4764</v>
       </c>
       <c r="J219" t="n">
-        <v>-6.520460515684785</v>
+        <v>-11.4336</v>
       </c>
     </row>
     <row r="220">
@@ -11161,10 +11149,10 @@
         <v>0.87</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.2991829117033228</v>
+        <v>-0.5306</v>
       </c>
       <c r="J220" t="n">
-        <v>-7.180389880879748</v>
+        <v>-12.7344</v>
       </c>
     </row>
     <row r="221">
@@ -11201,10 +11189,10 @@
         <v>0.76</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.431481758668272</v>
+        <v>-0.8018999999999999</v>
       </c>
       <c r="J221" t="n">
-        <v>-10.35556220803853</v>
+        <v>-19.2456</v>
       </c>
     </row>
     <row r="222">
@@ -11241,10 +11229,10 @@
         <v>1.42</v>
       </c>
       <c r="I222" t="n">
-        <v>0.2871557497666339</v>
+        <v>0.6808999999999999</v>
       </c>
       <c r="J222" t="n">
-        <v>6.891737994399213</v>
+        <v>16.3416</v>
       </c>
     </row>
     <row r="223">
@@ -11281,10 +11269,10 @@
         <v>1.1</v>
       </c>
       <c r="I223" t="n">
-        <v>0.08274215836274011</v>
+        <v>0.2402</v>
       </c>
       <c r="J223" t="n">
-        <v>1.985811800705763</v>
+        <v>5.7648</v>
       </c>
     </row>
     <row r="224">
@@ -11321,10 +11309,10 @@
         <v>0.86</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.3747116642076828</v>
+        <v>-0.284</v>
       </c>
       <c r="J224" t="n">
-        <v>-8.993079940984387</v>
+        <v>-6.816</v>
       </c>
     </row>
     <row r="225">
@@ -11361,10 +11349,10 @@
         <v>0.8</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.4621087750926265</v>
+        <v>-0.3758</v>
       </c>
       <c r="J225" t="n">
-        <v>-11.09061060222304</v>
+        <v>-9.0192</v>
       </c>
     </row>
     <row r="226">
@@ -11401,10 +11389,10 @@
         <v>0.66</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.6312705040504849</v>
+        <v>-0.5661</v>
       </c>
       <c r="J226" t="n">
-        <v>-15.15049209721164</v>
+        <v>-13.5864</v>
       </c>
     </row>
     <row r="227">
@@ -11441,10 +11429,10 @@
         <v>1.22</v>
       </c>
       <c r="I227" t="n">
-        <v>0.2368372000199748</v>
+        <v>0.6813</v>
       </c>
       <c r="J227" t="n">
-        <v>5.684092800479394</v>
+        <v>16.3512</v>
       </c>
     </row>
     <row r="228">
@@ -11481,10 +11469,10 @@
         <v>1.21</v>
       </c>
       <c r="I228" t="n">
-        <v>0.2294882057399524</v>
+        <v>0.6564</v>
       </c>
       <c r="J228" t="n">
-        <v>5.507716937758858</v>
+        <v>15.7536</v>
       </c>
     </row>
     <row r="229">
@@ -11521,10 +11509,10 @@
         <v>1.15</v>
       </c>
       <c r="I229" t="n">
-        <v>0.1815557272836457</v>
+        <v>0.4993</v>
       </c>
       <c r="J229" t="n">
-        <v>4.357337454807498</v>
+        <v>11.9832</v>
       </c>
     </row>
     <row r="230">
@@ -11561,10 +11549,10 @@
         <v>0.87</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2496486709626923</v>
+        <v>-0.5097</v>
       </c>
       <c r="J230" t="n">
-        <v>-5.991568103104615</v>
+        <v>-12.2328</v>
       </c>
     </row>
     <row r="231">
@@ -11601,10 +11589,10 @@
         <v>0.85</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.2778485469099811</v>
+        <v>-0.5629999999999999</v>
       </c>
       <c r="J231" t="n">
-        <v>-6.668365125839546</v>
+        <v>-13.512</v>
       </c>
     </row>
     <row r="232">
@@ -11641,10 +11629,10 @@
         <v>0.89</v>
       </c>
       <c r="I232" t="n">
-        <v>-0.3209110371488505</v>
+        <v>-0.053</v>
       </c>
       <c r="J232" t="n">
-        <v>-4.813665557232757</v>
+        <v>-0.795</v>
       </c>
     </row>
     <row r="233">
@@ -11681,10 +11669,10 @@
         <v>0.67</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.527152424253897</v>
+        <v>-0.4036</v>
       </c>
       <c r="J233" t="n">
-        <v>-7.907286363808455</v>
+        <v>-6.054</v>
       </c>
     </row>
     <row r="234">
@@ -11721,10 +11709,10 @@
         <v>0.61</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.6293408088645541</v>
+        <v>-0.5198</v>
       </c>
       <c r="J234" t="n">
-        <v>-9.440112132968311</v>
+        <v>-7.797</v>
       </c>
     </row>
     <row r="235">
@@ -11761,10 +11749,10 @@
         <v>0.55</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.704598230940198</v>
+        <v>-0.6163</v>
       </c>
       <c r="J235" t="n">
-        <v>-10.56897346410297</v>
+        <v>-9.2445</v>
       </c>
     </row>
     <row r="236">
@@ -11801,10 +11789,10 @@
         <v>0.4</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.8381779923461349</v>
+        <v>-0.8209</v>
       </c>
       <c r="J236" t="n">
-        <v>-12.57266988519202</v>
+        <v>-12.3135</v>
       </c>
     </row>
     <row r="237">
@@ -11841,10 +11829,10 @@
         <v>2.31</v>
       </c>
       <c r="I237" t="n">
-        <v>1.202618308412042</v>
+        <v>2.0593</v>
       </c>
       <c r="J237" t="n">
-        <v>18.03927462618063</v>
+        <v>30.8895</v>
       </c>
     </row>
     <row r="238">
@@ -11881,10 +11869,10 @@
         <v>1.99</v>
       </c>
       <c r="I238" t="n">
-        <v>1.021069141505158</v>
+        <v>1.9263</v>
       </c>
       <c r="J238" t="n">
-        <v>15.31603712257737</v>
+        <v>28.8945</v>
       </c>
     </row>
     <row r="239">
@@ -11921,10 +11909,10 @@
         <v>1.74</v>
       </c>
       <c r="I239" t="n">
-        <v>0.8276000761221701</v>
+        <v>1.5051</v>
       </c>
       <c r="J239" t="n">
-        <v>12.41400114183255</v>
+        <v>22.5765</v>
       </c>
     </row>
     <row r="240">
@@ -11961,10 +11949,10 @@
         <v>1.01</v>
       </c>
       <c r="I240" t="n">
-        <v>0.0937274300917408</v>
+        <v>-0.1629</v>
       </c>
       <c r="J240" t="n">
-        <v>1.405911451376112</v>
+        <v>-2.4435</v>
       </c>
     </row>
     <row r="241">
@@ -12001,10 +11989,10 @@
         <v>0.91</v>
       </c>
       <c r="I241" t="n">
-        <v>0.01682348889465922</v>
+        <v>-0.5304</v>
       </c>
       <c r="J241" t="n">
-        <v>0.2523523334198883</v>
+        <v>-7.956</v>
       </c>
     </row>
     <row r="242">
@@ -12041,10 +12029,10 @@
         <v>1.96</v>
       </c>
       <c r="I242" t="n">
-        <v>0.6938158527625207</v>
+        <v>1.1943</v>
       </c>
       <c r="J242" t="n">
-        <v>15.95776461353798</v>
+        <v>27.4689</v>
       </c>
     </row>
     <row r="243">
@@ -12081,10 +12069,10 @@
         <v>1.32</v>
       </c>
       <c r="I243" t="n">
-        <v>0.349788069823267</v>
+        <v>0.4947</v>
       </c>
       <c r="J243" t="n">
-        <v>8.045125605935141</v>
+        <v>11.3781</v>
       </c>
     </row>
     <row r="244">
@@ -12121,10 +12109,10 @@
         <v>1.15</v>
       </c>
       <c r="I244" t="n">
-        <v>0.1621716851144827</v>
+        <v>0.2349</v>
       </c>
       <c r="J244" t="n">
-        <v>3.729948757633101</v>
+        <v>5.4027</v>
       </c>
     </row>
     <row r="245">
@@ -12161,10 +12149,10 @@
         <v>0.75</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.3271930777293515</v>
+        <v>-0.4805</v>
       </c>
       <c r="J245" t="n">
-        <v>-7.525440787775084</v>
+        <v>-11.0515</v>
       </c>
     </row>
     <row r="246">
@@ -12201,10 +12189,10 @@
         <v>0.62</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.4407789893425058</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="J246" t="n">
-        <v>-10.13791675487763</v>
+        <v>-14.7568</v>
       </c>
     </row>
     <row r="247">
@@ -12241,10 +12229,10 @@
         <v>1.15</v>
       </c>
       <c r="I247" t="n">
-        <v>0.1453080255744262</v>
+        <v>0.3502</v>
       </c>
       <c r="J247" t="n">
-        <v>3.342084588211801</v>
+        <v>8.054600000000001</v>
       </c>
     </row>
     <row r="248">
@@ -12281,10 +12269,10 @@
         <v>0.98</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.07526781461363932</v>
+        <v>-0.0023</v>
       </c>
       <c r="J248" t="n">
-        <v>-1.731159736113704</v>
+        <v>-0.0529</v>
       </c>
     </row>
     <row r="249">
@@ -12321,10 +12309,10 @@
         <v>0.97</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.08685716172646427</v>
+        <v>-0.0253</v>
       </c>
       <c r="J249" t="n">
-        <v>-1.997714719708678</v>
+        <v>-0.5819</v>
       </c>
     </row>
     <row r="250">
@@ -12361,10 +12349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.3135085768932286</v>
+        <v>-0.3359</v>
       </c>
       <c r="J250" t="n">
-        <v>-7.210697268544258</v>
+        <v>-7.7257</v>
       </c>
     </row>
     <row r="251">
@@ -12401,10 +12389,10 @@
         <v>0.53</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.5440775694453238</v>
+        <v>-0.7134</v>
       </c>
       <c r="J251" t="n">
-        <v>-12.51378409724245</v>
+        <v>-16.4082</v>
       </c>
     </row>
     <row r="252">
@@ -12441,10 +12429,10 @@
         <v>0.93</v>
       </c>
       <c r="I252" t="n">
-        <v>-0.2478273252884466</v>
+        <v>0.0545</v>
       </c>
       <c r="J252" t="n">
-        <v>-3.717409879326699</v>
+        <v>0.8175</v>
       </c>
     </row>
     <row r="253">
@@ -12481,10 +12469,10 @@
         <v>0.59</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.5528460502622693</v>
+        <v>-0.4912</v>
       </c>
       <c r="J253" t="n">
-        <v>-8.292690753934039</v>
+        <v>-7.368</v>
       </c>
     </row>
     <row r="254">
@@ -12521,10 +12509,10 @@
         <v>0.5</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.6941227182034834</v>
+        <v>-0.6591</v>
       </c>
       <c r="J254" t="n">
-        <v>-10.41184077305225</v>
+        <v>-9.8865</v>
       </c>
     </row>
     <row r="255">
@@ -12561,10 +12549,10 @@
         <v>0.43</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.7644319237430942</v>
+        <v>-0.7611</v>
       </c>
       <c r="J255" t="n">
-        <v>-11.46647885614641</v>
+        <v>-11.4165</v>
       </c>
     </row>
     <row r="256">
@@ -12601,10 +12589,10 @@
         <v>0.35</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.8317744179613378</v>
+        <v>-0.8686</v>
       </c>
       <c r="J256" t="n">
-        <v>-12.47661626942007</v>
+        <v>-13.029</v>
       </c>
     </row>
     <row r="257">
@@ -12641,10 +12629,10 @@
         <v>1.96</v>
       </c>
       <c r="I257" t="n">
-        <v>1.030562992892322</v>
+        <v>1.8983</v>
       </c>
       <c r="J257" t="n">
-        <v>15.45844489338483</v>
+        <v>28.4745</v>
       </c>
     </row>
     <row r="258">
@@ -12681,10 +12669,10 @@
         <v>1.65</v>
       </c>
       <c r="I258" t="n">
-        <v>0.780912116555711</v>
+        <v>1.3508</v>
       </c>
       <c r="J258" t="n">
-        <v>11.71368174833566</v>
+        <v>20.262</v>
       </c>
     </row>
     <row r="259">
@@ -12721,10 +12709,10 @@
         <v>1.53</v>
       </c>
       <c r="I259" t="n">
-        <v>0.598527379662381</v>
+        <v>1.0827</v>
       </c>
       <c r="J259" t="n">
-        <v>8.977910694935716</v>
+        <v>16.2405</v>
       </c>
     </row>
     <row r="260">
@@ -12761,10 +12749,10 @@
         <v>1.39</v>
       </c>
       <c r="I260" t="n">
-        <v>0.440129201217883</v>
+        <v>0.7865</v>
       </c>
       <c r="J260" t="n">
-        <v>6.601938018268244</v>
+        <v>11.7975</v>
       </c>
     </row>
     <row r="261">
@@ -12801,10 +12789,10 @@
         <v>1.24</v>
       </c>
       <c r="I261" t="n">
-        <v>0.3091704076323776</v>
+        <v>0.4635</v>
       </c>
       <c r="J261" t="n">
-        <v>4.637556114485664</v>
+        <v>6.9525</v>
       </c>
     </row>
     <row r="262">
@@ -12841,10 +12829,10 @@
         <v>2.72</v>
       </c>
       <c r="I262" t="n">
-        <v>0.792758892571785</v>
+        <v>2.0593</v>
       </c>
       <c r="J262" t="n">
-        <v>13.47690117372034</v>
+        <v>35.0081</v>
       </c>
     </row>
     <row r="263">
@@ -12881,10 +12869,10 @@
         <v>1.43</v>
       </c>
       <c r="I263" t="n">
-        <v>0.3240201291342343</v>
+        <v>0.9651</v>
       </c>
       <c r="J263" t="n">
-        <v>5.508342195281983</v>
+        <v>16.4067</v>
       </c>
     </row>
     <row r="264">
@@ -12921,10 +12909,10 @@
         <v>1.3</v>
       </c>
       <c r="I264" t="n">
-        <v>0.2054539951695184</v>
+        <v>0.6464</v>
       </c>
       <c r="J264" t="n">
-        <v>3.492717917881813</v>
+        <v>10.9888</v>
       </c>
     </row>
     <row r="265">
@@ -12961,10 +12949,10 @@
         <v>0.86</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.1004980695079978</v>
+        <v>-0.6287</v>
       </c>
       <c r="J265" t="n">
-        <v>-1.708467181635962</v>
+        <v>-10.6879</v>
       </c>
     </row>
     <row r="266">
@@ -13001,10 +12989,10 @@
         <v>0.73</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.3107681320441628</v>
+        <v>-0.9264</v>
       </c>
       <c r="J266" t="n">
-        <v>-5.283058244750767</v>
+        <v>-15.7488</v>
       </c>
     </row>
     <row r="267">
@@ -13041,10 +13029,10 @@
         <v>0.95</v>
       </c>
       <c r="I267" t="n">
-        <v>-0.2671132286860858</v>
+        <v>-0.0196</v>
       </c>
       <c r="J267" t="n">
-        <v>-4.540924887663458</v>
+        <v>-0.3332</v>
       </c>
     </row>
     <row r="268">
@@ -13081,10 +13069,10 @@
         <v>0.86</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.3611009101520706</v>
+        <v>-0.1809</v>
       </c>
       <c r="J268" t="n">
-        <v>-6.138715472585201</v>
+        <v>-3.0753</v>
       </c>
     </row>
     <row r="269">
@@ -13121,10 +13109,10 @@
         <v>0.8</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.4383988034028307</v>
+        <v>-0.2844</v>
       </c>
       <c r="J269" t="n">
-        <v>-7.452779657848121</v>
+        <v>-4.8348</v>
       </c>
     </row>
     <row r="270">
@@ -13161,10 +13149,10 @@
         <v>0.7</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.5935503743173602</v>
+        <v>-0.4621</v>
       </c>
       <c r="J270" t="n">
-        <v>-10.09035636339512</v>
+        <v>-7.8557</v>
       </c>
     </row>
     <row r="271">
@@ -13201,10 +13189,10 @@
         <v>0.59</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.6994604918783643</v>
+        <v>-0.6156</v>
       </c>
       <c r="J271" t="n">
-        <v>-11.89082836193219</v>
+        <v>-10.4652</v>
       </c>
     </row>
     <row r="272">
@@ -13241,10 +13229,10 @@
         <v>2.12</v>
       </c>
       <c r="I272" t="n">
-        <v>0.6456007915263665</v>
+        <v>2.0593</v>
       </c>
       <c r="J272" t="n">
-        <v>12.91201583052733</v>
+        <v>41.186</v>
       </c>
     </row>
     <row r="273">
@@ -13281,10 +13269,10 @@
         <v>1.43</v>
       </c>
       <c r="I273" t="n">
-        <v>0.3346000277959342</v>
+        <v>1.027</v>
       </c>
       <c r="J273" t="n">
-        <v>6.692000555918685</v>
+        <v>20.54</v>
       </c>
     </row>
     <row r="274">
@@ -13321,10 +13309,10 @@
         <v>1.33</v>
       </c>
       <c r="I274" t="n">
-        <v>0.2536878504716688</v>
+        <v>0.7991</v>
       </c>
       <c r="J274" t="n">
-        <v>5.073757009433375</v>
+        <v>15.982</v>
       </c>
     </row>
     <row r="275">
@@ -13361,10 +13349,10 @@
         <v>0.92</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.213615404373279</v>
+        <v>-0.4478</v>
       </c>
       <c r="J275" t="n">
-        <v>-4.272308087465579</v>
+        <v>-8.956</v>
       </c>
     </row>
     <row r="276">
@@ -13401,10 +13389,10 @@
         <v>0.71</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.4533376931280571</v>
+        <v>-0.9526</v>
       </c>
       <c r="J276" t="n">
-        <v>-9.066753862561141</v>
+        <v>-19.052</v>
       </c>
     </row>
     <row r="277">
@@ -13441,10 +13429,10 @@
         <v>2.12</v>
       </c>
       <c r="I277" t="n">
-        <v>0.7728464312619416</v>
+        <v>1.4194</v>
       </c>
       <c r="J277" t="n">
-        <v>15.45692862523883</v>
+        <v>28.388</v>
       </c>
     </row>
     <row r="278">
@@ -13481,10 +13469,10 @@
         <v>0.78</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.4849747181161419</v>
+        <v>-0.4007</v>
       </c>
       <c r="J278" t="n">
-        <v>-9.699494362322838</v>
+        <v>-8.013999999999999</v>
       </c>
     </row>
     <row r="279">
@@ -13521,10 +13509,10 @@
         <v>0.73</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.5254400844985668</v>
+        <v>-0.4706</v>
       </c>
       <c r="J279" t="n">
-        <v>-10.50880168997134</v>
+        <v>-9.412000000000001</v>
       </c>
     </row>
     <row r="280">
@@ -13561,10 +13549,10 @@
         <v>0.61</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.6110467325445714</v>
+        <v>-0.6262</v>
       </c>
       <c r="J280" t="n">
-        <v>-12.22093465089143</v>
+        <v>-12.524</v>
       </c>
     </row>
     <row r="281">
@@ -13601,10 +13589,10 @@
         <v>0.52</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.6673597295132295</v>
+        <v>-0.7347</v>
       </c>
       <c r="J281" t="n">
-        <v>-13.34719459026459</v>
+        <v>-14.694</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7365/event_7365_evp_summary.xlsx
+++ b/database/event/7365/event_7365_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>7.4863</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>2.1488</v>
       </c>
       <c r="D2" t="n">
         <v>2.6029</v>
@@ -545,7 +545,7 @@
         <v>6.2207</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1.7855</v>
       </c>
       <c r="D3" t="n">
         <v>2.0917</v>
@@ -591,7 +591,7 @@
         <v>5.42</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1.5557</v>
       </c>
       <c r="D4" t="n">
         <v>1.7682</v>
@@ -637,7 +637,7 @@
         <v>4.0318</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1.1573</v>
       </c>
       <c r="D5" t="n">
         <v>1.2074</v>
@@ -683,7 +683,7 @@
         <v>3.9896</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1.1451</v>
       </c>
       <c r="D6" t="n">
         <v>1.1903</v>
@@ -729,7 +729,7 @@
         <v>3.783</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1.0858</v>
       </c>
       <c r="D7" t="n">
         <v>1.1069</v>
@@ -775,7 +775,7 @@
         <v>3.313</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>0.9509</v>
       </c>
       <c r="D8" t="n">
         <v>0.917</v>
@@ -821,7 +821,7 @@
         <v>3.0065</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>0.863</v>
       </c>
       <c r="D9" t="n">
         <v>0.7932</v>
@@ -867,7 +867,7 @@
         <v>2.6334</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>0.7559</v>
       </c>
       <c r="D10" t="n">
         <v>0.6425</v>
@@ -913,7 +913,7 @@
         <v>2.124</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>0.6097</v>
       </c>
       <c r="D11" t="n">
         <v>0.4367</v>
@@ -959,7 +959,7 @@
         <v>1.7368</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.4985</v>
       </c>
       <c r="D12" t="n">
         <v>0.2803</v>
@@ -1005,7 +1005,7 @@
         <v>1.235</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>0.3545</v>
       </c>
       <c r="D13" t="n">
         <v>0.0776</v>
@@ -1051,7 +1051,7 @@
         <v>1.0767</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.309</v>
       </c>
       <c r="D14" t="n">
         <v>0.0136</v>
@@ -1097,7 +1097,7 @@
         <v>0.9917</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.2847</v>
       </c>
       <c r="D15" t="n">
         <v>-0.0207</v>
@@ -1143,7 +1143,7 @@
         <v>0.7060999999999999</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>0.2027</v>
       </c>
       <c r="D16" t="n">
         <v>-0.1361</v>
@@ -1189,7 +1189,7 @@
         <v>0.6556999999999999</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.1882</v>
       </c>
       <c r="D17" t="n">
         <v>-0.1565</v>
@@ -1235,7 +1235,7 @@
         <v>0.5888</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.169</v>
       </c>
       <c r="D18" t="n">
         <v>-0.1835</v>
@@ -1281,7 +1281,7 @@
         <v>0.5131</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.1473</v>
       </c>
       <c r="D19" t="n">
         <v>-0.2141</v>
@@ -1327,7 +1327,7 @@
         <v>0.4703</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.135</v>
       </c>
       <c r="D20" t="n">
         <v>-0.2314</v>
@@ -1373,7 +1373,7 @@
         <v>0.3931</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>0.1128</v>
       </c>
       <c r="D21" t="n">
         <v>-0.2626</v>
@@ -1419,7 +1419,7 @@
         <v>0.3612</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>0.1037</v>
       </c>
       <c r="D22" t="n">
         <v>-0.2754</v>
@@ -1465,7 +1465,7 @@
         <v>0.2352</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.0675</v>
       </c>
       <c r="D23" t="n">
         <v>-0.3263</v>
@@ -1511,7 +1511,7 @@
         <v>0.2162</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>0.0621</v>
       </c>
       <c r="D24" t="n">
         <v>-0.334</v>
@@ -1557,7 +1557,7 @@
         <v>0.1324</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.038</v>
       </c>
       <c r="D25" t="n">
         <v>-0.3679</v>
@@ -1603,7 +1603,7 @@
         <v>0.1114</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="D26" t="n">
         <v>-0.3764</v>
@@ -1649,7 +1649,7 @@
         <v>0.09229999999999999</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>0.0265</v>
       </c>
       <c r="D27" t="n">
         <v>-0.3841</v>
@@ -1695,7 +1695,7 @@
         <v>0.0629</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.0181</v>
       </c>
       <c r="D28" t="n">
         <v>-0.396</v>
@@ -1741,7 +1741,7 @@
         <v>-0.0456</v>
       </c>
       <c r="C29" t="n">
-        <v>-0</v>
+        <v>-0.0131</v>
       </c>
       <c r="D29" t="n">
         <v>-0.4398</v>
@@ -1787,7 +1787,7 @@
         <v>-0.092</v>
       </c>
       <c r="C30" t="n">
-        <v>-0</v>
+        <v>-0.0264</v>
       </c>
       <c r="D30" t="n">
         <v>-0.4585</v>
@@ -1833,7 +1833,7 @@
         <v>-0.3675</v>
       </c>
       <c r="C31" t="n">
-        <v>-0</v>
+        <v>-0.1055</v>
       </c>
       <c r="D31" t="n">
         <v>-0.5698</v>
@@ -1879,7 +1879,7 @@
         <v>-0.4248</v>
       </c>
       <c r="C32" t="n">
-        <v>-0</v>
+        <v>-0.1219</v>
       </c>
       <c r="D32" t="n">
         <v>-0.593</v>
@@ -1925,7 +1925,7 @@
         <v>-0.648</v>
       </c>
       <c r="C33" t="n">
-        <v>-0</v>
+        <v>-0.186</v>
       </c>
       <c r="D33" t="n">
         <v>-0.6831</v>
@@ -1971,7 +1971,7 @@
         <v>-0.6528</v>
       </c>
       <c r="C34" t="n">
-        <v>-0</v>
+        <v>-0.1874</v>
       </c>
       <c r="D34" t="n">
         <v>-0.6851</v>
@@ -2017,7 +2017,7 @@
         <v>-1.1475</v>
       </c>
       <c r="C35" t="n">
-        <v>-0</v>
+        <v>-0.3294</v>
       </c>
       <c r="D35" t="n">
         <v>-0.8849</v>
@@ -2063,7 +2063,7 @@
         <v>-1.3945</v>
       </c>
       <c r="C36" t="n">
-        <v>-0</v>
+        <v>-0.4003</v>
       </c>
       <c r="D36" t="n">
         <v>-0.9847</v>
@@ -2109,7 +2109,7 @@
         <v>-1.4679</v>
       </c>
       <c r="C37" t="n">
-        <v>-0</v>
+        <v>-0.4213</v>
       </c>
       <c r="D37" t="n">
         <v>-1.0144</v>
@@ -2155,7 +2155,7 @@
         <v>-1.7105</v>
       </c>
       <c r="C38" t="n">
-        <v>-0</v>
+        <v>-0.491</v>
       </c>
       <c r="D38" t="n">
         <v>-1.1124</v>
@@ -2201,7 +2201,7 @@
         <v>-1.7347</v>
       </c>
       <c r="C39" t="n">
-        <v>-0</v>
+        <v>-0.4979</v>
       </c>
       <c r="D39" t="n">
         <v>-1.1221</v>
@@ -2247,7 +2247,7 @@
         <v>-1.9454</v>
       </c>
       <c r="C40" t="n">
-        <v>-0</v>
+        <v>-0.5584</v>
       </c>
       <c r="D40" t="n">
         <v>-1.2073</v>
@@ -2293,7 +2293,7 @@
         <v>-3.2274</v>
       </c>
       <c r="C41" t="n">
-        <v>-0</v>
+        <v>-0.9264</v>
       </c>
       <c r="D41" t="n">
         <v>-1.7252</v>

--- a/database/event/7365/event_7365_evp_summary.xlsx
+++ b/database/event/7365/event_7365_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>2.1488</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6029</v>
+        <v>2.5386</v>
       </c>
       <c r="E2" t="n">
         <v>7.4863</v>
@@ -548,7 +548,7 @@
         <v>1.7855</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0917</v>
+        <v>2.0344</v>
       </c>
       <c r="E3" t="n">
         <v>6.2207</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.42</v>
+        <v>5.4206</v>
       </c>
       <c r="C4" t="n">
-        <v>1.5557</v>
+        <v>1.5559</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7682</v>
+        <v>1.7157</v>
       </c>
       <c r="E4" t="n">
-        <v>5.42</v>
+        <v>5.4206</v>
       </c>
       <c r="F4" t="n">
-        <v>3.9833</v>
+        <v>3.9839</v>
       </c>
       <c r="G4" t="n">
         <v>1.4367</v>
       </c>
       <c r="H4" t="n">
-        <v>3.9833</v>
+        <v>3.9839</v>
       </c>
       <c r="I4" t="n">
-        <v>3.2286</v>
+        <v>3.2291</v>
       </c>
       <c r="J4" t="n">
         <v>1.4367</v>
@@ -621,7 +621,7 @@
         <v>59</v>
       </c>
       <c r="M4" t="n">
-        <v>4.6653</v>
+        <v>4.6658</v>
       </c>
       <c r="N4" t="n">
         <v>129</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.0318</v>
+        <v>4.9625</v>
       </c>
       <c r="C5" t="n">
-        <v>1.1573</v>
+        <v>1.4244</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2074</v>
+        <v>1.5332</v>
       </c>
       <c r="E5" t="n">
-        <v>4.0318</v>
+        <v>4.9625</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0857</v>
+        <v>1.0164</v>
       </c>
       <c r="G5" t="n">
         <v>3.9461</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0857</v>
+        <v>1.0164</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0857</v>
+        <v>1.0164</v>
       </c>
       <c r="J5" t="n">
         <v>3.9461</v>
@@ -667,7 +667,7 @@
         <v>136</v>
       </c>
       <c r="M5" t="n">
-        <v>4.0318</v>
+        <v>4.9625</v>
       </c>
       <c r="N5" t="n">
         <v>209</v>
@@ -676,93 +676,93 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.9896</v>
+        <v>4.2753</v>
       </c>
       <c r="C6" t="n">
-        <v>1.1451</v>
+        <v>1.2272</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1903</v>
+        <v>1.2594</v>
       </c>
       <c r="E6" t="n">
-        <v>3.9896</v>
+        <v>4.2753</v>
       </c>
       <c r="F6" t="n">
-        <v>4.253</v>
+        <v>1.664</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2634</v>
+        <v>2.6113</v>
       </c>
       <c r="H6" t="n">
-        <v>4.5504</v>
+        <v>1.664</v>
       </c>
       <c r="I6" t="n">
-        <v>3.6882</v>
+        <v>1.664</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2634</v>
+        <v>2.6113</v>
       </c>
       <c r="K6" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="L6" t="n">
-        <v>59</v>
+        <v>155</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4248</v>
+        <v>4.2753</v>
       </c>
       <c r="N6" t="n">
-        <v>129</v>
+        <v>236</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.783</v>
+        <v>4.1301</v>
       </c>
       <c r="C7" t="n">
-        <v>1.0858</v>
+        <v>1.1855</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1069</v>
+        <v>1.2015</v>
       </c>
       <c r="E7" t="n">
-        <v>3.783</v>
+        <v>4.1301</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1717</v>
+        <v>4.3935</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6113</v>
+        <v>-0.2634</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1717</v>
+        <v>5.1155</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1717</v>
+        <v>4.1463</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6113</v>
+        <v>-0.2634</v>
       </c>
       <c r="K7" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="L7" t="n">
-        <v>155</v>
+        <v>59</v>
       </c>
       <c r="M7" t="n">
-        <v>3.783</v>
+        <v>3.8829</v>
       </c>
       <c r="N7" t="n">
-        <v>236</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8">
@@ -778,7 +778,7 @@
         <v>0.9509</v>
       </c>
       <c r="D8" t="n">
-        <v>0.917</v>
+        <v>0.876</v>
       </c>
       <c r="E8" t="n">
         <v>3.313</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.0065</v>
+        <v>3.1698</v>
       </c>
       <c r="C9" t="n">
-        <v>0.863</v>
+        <v>0.9098000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7932</v>
+        <v>0.8189</v>
       </c>
       <c r="E9" t="n">
-        <v>3.0065</v>
+        <v>3.1698</v>
       </c>
       <c r="F9" t="n">
-        <v>2.9232</v>
+        <v>3.0865</v>
       </c>
       <c r="G9" t="n">
         <v>0.0833</v>
       </c>
       <c r="H9" t="n">
-        <v>2.9232</v>
+        <v>3.0865</v>
       </c>
       <c r="I9" t="n">
-        <v>2.3693</v>
+        <v>2.5017</v>
       </c>
       <c r="J9" t="n">
         <v>0.0833</v>
@@ -851,7 +851,7 @@
         <v>59</v>
       </c>
       <c r="M9" t="n">
-        <v>2.4526</v>
+        <v>2.585</v>
       </c>
       <c r="N9" t="n">
         <v>129</v>
@@ -870,7 +870,7 @@
         <v>0.7559</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6425</v>
+        <v>0.6052</v>
       </c>
       <c r="E10" t="n">
         <v>2.6334</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.124</v>
+        <v>2.2071</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6097</v>
+        <v>0.6335</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4367</v>
+        <v>0.4354</v>
       </c>
       <c r="E11" t="n">
-        <v>2.124</v>
+        <v>2.2071</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0962</v>
+        <v>1.1793</v>
       </c>
       <c r="G11" t="n">
         <v>1.0278</v>
       </c>
       <c r="H11" t="n">
-        <v>1.0962</v>
+        <v>1.1793</v>
       </c>
       <c r="I11" t="n">
-        <v>1.0962</v>
+        <v>1.1793</v>
       </c>
       <c r="J11" t="n">
         <v>1.0278</v>
@@ -943,7 +943,7 @@
         <v>136</v>
       </c>
       <c r="M11" t="n">
-        <v>2.124</v>
+        <v>2.2071</v>
       </c>
       <c r="N11" t="n">
         <v>209</v>
@@ -962,7 +962,7 @@
         <v>0.4985</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2803</v>
+        <v>0.248</v>
       </c>
       <c r="E12" t="n">
         <v>1.7368</v>
@@ -998,265 +998,265 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>maxster</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.235</v>
+        <v>1.2919</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3545</v>
+        <v>0.3708</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0776</v>
+        <v>0.0708</v>
       </c>
       <c r="E13" t="n">
-        <v>1.235</v>
+        <v>1.2919</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5467</v>
+        <v>1.6728</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.3117</v>
+        <v>-0.3809</v>
       </c>
       <c r="H13" t="n">
-        <v>1.5467</v>
+        <v>1.6728</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5467</v>
+        <v>1.6728</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.3117</v>
+        <v>-0.3809</v>
       </c>
       <c r="K13" t="n">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="L13" t="n">
-        <v>61</v>
+        <v>155</v>
       </c>
       <c r="M13" t="n">
-        <v>1.235</v>
+        <v>1.2919</v>
       </c>
       <c r="N13" t="n">
-        <v>152</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Buzz</t>
+          <t>maxster</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.0767</v>
+        <v>1.235</v>
       </c>
       <c r="C14" t="n">
-        <v>0.309</v>
+        <v>0.3545</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0136</v>
+        <v>0.0481</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0767</v>
+        <v>1.235</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0985</v>
+        <v>1.5467</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0218</v>
+        <v>-0.3117</v>
       </c>
       <c r="H14" t="n">
-        <v>1.0985</v>
+        <v>1.5467</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8904</v>
+        <v>1.5467</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.0218</v>
+        <v>-0.3117</v>
       </c>
       <c r="K14" t="n">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="L14" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8685999999999999</v>
+        <v>1.235</v>
       </c>
       <c r="N14" t="n">
-        <v>129</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>headtr1ck</t>
+          <t>Buzz</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9917</v>
+        <v>1.0767</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2847</v>
+        <v>0.309</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0207</v>
+        <v>-0.015</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9917</v>
+        <v>1.0767</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8274</v>
+        <v>1.0985</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.8357</v>
+        <v>-0.0218</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8274</v>
+        <v>1.0985</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8274</v>
+        <v>0.8904</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.8357</v>
+        <v>-0.0218</v>
       </c>
       <c r="K15" t="n">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="L15" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9916999999999999</v>
+        <v>0.8685999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>152</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>headtr1ck</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7060999999999999</v>
+        <v>0.9917</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2027</v>
+        <v>0.2847</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1361</v>
+        <v>-0.0488</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7060999999999999</v>
+        <v>0.9917</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5647</v>
+        <v>1.8274</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1414</v>
+        <v>-0.8357</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5647</v>
+        <v>1.8274</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4577</v>
+        <v>1.8274</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1414</v>
+        <v>-0.8357</v>
       </c>
       <c r="K16" t="n">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="L16" t="n">
-        <v>135</v>
+        <v>61</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5991</v>
+        <v>0.9916999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>254</v>
+        <v>152</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>Moseyuh</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6556999999999999</v>
+        <v>0.9702</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1882</v>
+        <v>0.2785</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1565</v>
+        <v>-0.0574</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6556999999999999</v>
+        <v>0.9702</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7948</v>
+        <v>0.9702</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1391</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7948</v>
+        <v>0.9702</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7948</v>
+        <v>0.9702</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1391</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>91</v>
       </c>
       <c r="L17" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6556999999999999</v>
+        <v>0.9702</v>
       </c>
       <c r="N17" t="n">
-        <v>152</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5888</v>
+        <v>0.7060999999999999</v>
       </c>
       <c r="C18" t="n">
-        <v>0.169</v>
+        <v>0.2027</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1835</v>
+        <v>-0.1626</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5888</v>
+        <v>0.7060999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5429</v>
+        <v>0.5647</v>
       </c>
       <c r="G18" t="n">
-        <v>1.1317</v>
+        <v>0.1414</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5429</v>
+        <v>0.5647</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.44</v>
+        <v>0.4577</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1317</v>
+        <v>0.1414</v>
       </c>
       <c r="K18" t="n">
         <v>119</v>
@@ -1265,7 +1265,7 @@
         <v>135</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6917</v>
+        <v>0.5991</v>
       </c>
       <c r="N18" t="n">
         <v>254</v>
@@ -1274,231 +1274,231 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ChildKing</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5131</v>
+        <v>0.6959</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1473</v>
+        <v>0.1997</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2141</v>
+        <v>-0.1667</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5131</v>
+        <v>0.6959</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5131</v>
+        <v>0.835</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0.1391</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5131</v>
+        <v>0.835</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5131</v>
+        <v>0.835</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.1391</v>
       </c>
       <c r="K19" t="n">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5131</v>
+        <v>0.6959</v>
       </c>
       <c r="N19" t="n">
-        <v>53</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>JamYoung</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.4703</v>
+        <v>0.5888</v>
       </c>
       <c r="C20" t="n">
-        <v>0.135</v>
+        <v>0.169</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2314</v>
+        <v>-0.2093</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4703</v>
+        <v>0.5888</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4703</v>
+        <v>-0.5429</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1.1317</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4703</v>
+        <v>-0.5429</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4703</v>
+        <v>-0.44</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1.1317</v>
       </c>
       <c r="K20" t="n">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4703</v>
+        <v>0.6917</v>
       </c>
       <c r="N20" t="n">
-        <v>91</v>
+        <v>254</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Moseyuh</t>
+          <t>ChildKing</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.3931</v>
+        <v>0.5131</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1128</v>
+        <v>0.1473</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2626</v>
+        <v>-0.2395</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3931</v>
+        <v>0.5131</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3931</v>
+        <v>0.5131</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3931</v>
+        <v>0.5131</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3931</v>
+        <v>0.5131</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>91</v>
+        <v>53</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3931</v>
+        <v>0.5131</v>
       </c>
       <c r="N21" t="n">
-        <v>91</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.3612</v>
+        <v>0.4744</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1037</v>
+        <v>0.1362</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2754</v>
+        <v>-0.2549</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3612</v>
+        <v>0.4744</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7421</v>
+        <v>0.2463</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3809</v>
+        <v>0.2281</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7421</v>
+        <v>0.2463</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7421</v>
+        <v>0.2463</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3809</v>
+        <v>0.2281</v>
       </c>
       <c r="K22" t="n">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="L22" t="n">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3612</v>
+        <v>0.4744</v>
       </c>
       <c r="N22" t="n">
-        <v>236</v>
+        <v>209</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>JamYoung</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2352</v>
+        <v>0.4703</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0675</v>
+        <v>0.135</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3263</v>
+        <v>-0.2565</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2352</v>
+        <v>0.4703</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0071</v>
+        <v>0.4703</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2281</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0071</v>
+        <v>0.4703</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0071</v>
+        <v>0.4703</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2281</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="L23" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2352</v>
+        <v>0.4703</v>
       </c>
       <c r="N23" t="n">
-        <v>209</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24">
@@ -1514,7 +1514,7 @@
         <v>0.0621</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.334</v>
+        <v>-0.3578</v>
       </c>
       <c r="E24" t="n">
         <v>0.2162</v>
@@ -1560,7 +1560,7 @@
         <v>0.038</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3679</v>
+        <v>-0.3912</v>
       </c>
       <c r="E25" t="n">
         <v>0.1324</v>
@@ -1606,7 +1606,7 @@
         <v>0.032</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3764</v>
+        <v>-0.3995</v>
       </c>
       <c r="E26" t="n">
         <v>0.1114</v>
@@ -1652,7 +1652,7 @@
         <v>0.0265</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3841</v>
+        <v>-0.4071</v>
       </c>
       <c r="E27" t="n">
         <v>0.09229999999999999</v>
@@ -1698,7 +1698,7 @@
         <v>0.0181</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.396</v>
+        <v>-0.4189</v>
       </c>
       <c r="E28" t="n">
         <v>0.0629</v>
@@ -1744,7 +1744,7 @@
         <v>-0.0131</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4398</v>
+        <v>-0.4621</v>
       </c>
       <c r="E29" t="n">
         <v>-0.0456</v>
@@ -1790,7 +1790,7 @@
         <v>-0.0264</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.4585</v>
+        <v>-0.4806</v>
       </c>
       <c r="E30" t="n">
         <v>-0.092</v>
@@ -1836,7 +1836,7 @@
         <v>-0.1055</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5698</v>
+        <v>-0.5903</v>
       </c>
       <c r="E31" t="n">
         <v>-0.3675</v>
@@ -1882,7 +1882,7 @@
         <v>-0.1219</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.593</v>
+        <v>-0.6132</v>
       </c>
       <c r="E32" t="n">
         <v>-0.4248</v>
@@ -1928,7 +1928,7 @@
         <v>-0.186</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6831</v>
+        <v>-0.7020999999999999</v>
       </c>
       <c r="E33" t="n">
         <v>-0.648</v>
@@ -1974,7 +1974,7 @@
         <v>-0.1874</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.6851</v>
+        <v>-0.704</v>
       </c>
       <c r="E34" t="n">
         <v>-0.6528</v>
@@ -2020,7 +2020,7 @@
         <v>-0.3294</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8849</v>
+        <v>-0.9011</v>
       </c>
       <c r="E35" t="n">
         <v>-1.1475</v>
@@ -2066,7 +2066,7 @@
         <v>-0.4003</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9847</v>
+        <v>-0.9995000000000001</v>
       </c>
       <c r="E36" t="n">
         <v>-1.3945</v>
@@ -2112,7 +2112,7 @@
         <v>-0.4213</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0144</v>
+        <v>-1.0287</v>
       </c>
       <c r="E37" t="n">
         <v>-1.4679</v>
@@ -2158,7 +2158,7 @@
         <v>-0.491</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1124</v>
+        <v>-1.1254</v>
       </c>
       <c r="E38" t="n">
         <v>-1.7105</v>
@@ -2204,7 +2204,7 @@
         <v>-0.4979</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1221</v>
+        <v>-1.135</v>
       </c>
       <c r="E39" t="n">
         <v>-1.7347</v>
@@ -2250,7 +2250,7 @@
         <v>-0.5584</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2073</v>
+        <v>-1.219</v>
       </c>
       <c r="E40" t="n">
         <v>-1.9454</v>
@@ -2296,7 +2296,7 @@
         <v>-0.9264</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.7252</v>
+        <v>-1.7297</v>
       </c>
       <c r="E41" t="n">
         <v>-3.2274</v>

--- a/database/event/7365/event_7365_evp_summary.xlsx
+++ b/database/event/7365/event_7365_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.4863</v>
+        <v>6.4967</v>
       </c>
       <c r="C2" t="n">
-        <v>2.1488</v>
+        <v>1.8648</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5386</v>
+        <v>2.2949</v>
       </c>
       <c r="E2" t="n">
-        <v>7.4863</v>
+        <v>6.4967</v>
       </c>
       <c r="F2" t="n">
-        <v>4.1042</v>
+        <v>3.6572</v>
       </c>
       <c r="G2" t="n">
-        <v>3.3822</v>
+        <v>2.8395</v>
       </c>
       <c r="H2" t="n">
-        <v>4.1042</v>
+        <v>7.3992</v>
       </c>
       <c r="I2" t="n">
-        <v>3.3266</v>
+        <v>3.8472</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3822</v>
+        <v>2.8395</v>
       </c>
       <c r="K2" t="n">
         <v>119</v>
@@ -529,7 +529,7 @@
         <v>135</v>
       </c>
       <c r="M2" t="n">
-        <v>6.7088</v>
+        <v>6.6867</v>
       </c>
       <c r="N2" t="n">
         <v>254</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.2207</v>
+        <v>6.1608</v>
       </c>
       <c r="C3" t="n">
-        <v>1.7855</v>
+        <v>1.7684</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0344</v>
+        <v>2.1433</v>
       </c>
       <c r="E3" t="n">
-        <v>6.2207</v>
+        <v>6.1608</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2912</v>
+        <v>0.0348</v>
       </c>
       <c r="G3" t="n">
-        <v>6.5119</v>
+        <v>6.126</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2912</v>
+        <v>0.0348</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2912</v>
+        <v>0.0348</v>
       </c>
       <c r="J3" t="n">
-        <v>6.767</v>
+        <v>6.126</v>
       </c>
       <c r="K3" t="n">
         <v>81</v>
@@ -575,7 +575,7 @@
         <v>155</v>
       </c>
       <c r="M3" t="n">
-        <v>6.4758</v>
+        <v>6.1608</v>
       </c>
       <c r="N3" t="n">
         <v>236</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.4206</v>
+        <v>4.6943</v>
       </c>
       <c r="C4" t="n">
-        <v>1.5559</v>
+        <v>1.3474</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7157</v>
+        <v>1.4812</v>
       </c>
       <c r="E4" t="n">
-        <v>5.4206</v>
+        <v>4.6943</v>
       </c>
       <c r="F4" t="n">
-        <v>3.9839</v>
+        <v>3.5741</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4367</v>
+        <v>1.1202</v>
       </c>
       <c r="H4" t="n">
-        <v>3.9839</v>
+        <v>7.1066</v>
       </c>
       <c r="I4" t="n">
-        <v>3.2291</v>
+        <v>3.6951</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4367</v>
+        <v>1.1202</v>
       </c>
       <c r="K4" t="n">
         <v>70</v>
@@ -621,7 +621,7 @@
         <v>59</v>
       </c>
       <c r="M4" t="n">
-        <v>4.6658</v>
+        <v>4.815300000000001</v>
       </c>
       <c r="N4" t="n">
         <v>129</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.9625</v>
+        <v>4.5626</v>
       </c>
       <c r="C5" t="n">
-        <v>1.4244</v>
+        <v>1.3096</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5332</v>
+        <v>1.4218</v>
       </c>
       <c r="E5" t="n">
-        <v>4.9625</v>
+        <v>4.5626</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0164</v>
+        <v>1.1918</v>
       </c>
       <c r="G5" t="n">
-        <v>3.9461</v>
+        <v>3.3708</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0164</v>
+        <v>1.1918</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0164</v>
+        <v>1.1918</v>
       </c>
       <c r="J5" t="n">
-        <v>3.9461</v>
+        <v>3.3708</v>
       </c>
       <c r="K5" t="n">
         <v>73</v>
@@ -667,7 +667,7 @@
         <v>136</v>
       </c>
       <c r="M5" t="n">
-        <v>4.9625</v>
+        <v>4.5626</v>
       </c>
       <c r="N5" t="n">
         <v>209</v>
@@ -676,93 +676,93 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.2753</v>
+        <v>3.9376</v>
       </c>
       <c r="C6" t="n">
-        <v>1.2272</v>
+        <v>1.1302</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2594</v>
+        <v>1.1396</v>
       </c>
       <c r="E6" t="n">
-        <v>4.2753</v>
+        <v>3.9376</v>
       </c>
       <c r="F6" t="n">
-        <v>1.664</v>
+        <v>3.9828</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6113</v>
+        <v>-0.0452</v>
       </c>
       <c r="H6" t="n">
-        <v>1.664</v>
+        <v>8.5466</v>
       </c>
       <c r="I6" t="n">
-        <v>1.664</v>
+        <v>4.4438</v>
       </c>
       <c r="J6" t="n">
-        <v>2.6113</v>
+        <v>-0.0452</v>
       </c>
       <c r="K6" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="L6" t="n">
-        <v>155</v>
+        <v>59</v>
       </c>
       <c r="M6" t="n">
-        <v>4.2753</v>
+        <v>4.3986</v>
       </c>
       <c r="N6" t="n">
-        <v>236</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.1301</v>
+        <v>3.8964</v>
       </c>
       <c r="C7" t="n">
-        <v>1.1855</v>
+        <v>1.1184</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2015</v>
+        <v>1.121</v>
       </c>
       <c r="E7" t="n">
-        <v>4.1301</v>
+        <v>3.8964</v>
       </c>
       <c r="F7" t="n">
-        <v>4.3935</v>
+        <v>1.6932</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2634</v>
+        <v>2.2032</v>
       </c>
       <c r="H7" t="n">
-        <v>5.1155</v>
+        <v>1.6932</v>
       </c>
       <c r="I7" t="n">
-        <v>4.1463</v>
+        <v>1.6932</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2634</v>
+        <v>2.2032</v>
       </c>
       <c r="K7" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="L7" t="n">
-        <v>59</v>
+        <v>155</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8829</v>
+        <v>3.8964</v>
       </c>
       <c r="N7" t="n">
-        <v>129</v>
+        <v>236</v>
       </c>
     </row>
     <row r="8">
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.313</v>
+        <v>3.6528</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9509</v>
+        <v>1.0485</v>
       </c>
       <c r="D8" t="n">
-        <v>0.876</v>
+        <v>1.011</v>
       </c>
       <c r="E8" t="n">
-        <v>3.313</v>
+        <v>3.6528</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0974</v>
+        <v>2.8699</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2156</v>
+        <v>0.7829</v>
       </c>
       <c r="H8" t="n">
-        <v>2.0974</v>
+        <v>2.9421</v>
       </c>
       <c r="I8" t="n">
-        <v>2.0974</v>
+        <v>2.9421</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2156</v>
+        <v>0.7829</v>
       </c>
       <c r="K8" t="n">
         <v>91</v>
@@ -805,7 +805,7 @@
         <v>61</v>
       </c>
       <c r="M8" t="n">
-        <v>3.313</v>
+        <v>3.725</v>
       </c>
       <c r="N8" t="n">
         <v>152</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.1698</v>
+        <v>2.9575</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9098000000000001</v>
+        <v>0.8489</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8189</v>
+        <v>0.6971000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1698</v>
+        <v>2.9575</v>
       </c>
       <c r="F9" t="n">
-        <v>3.0865</v>
+        <v>2.9171</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0833</v>
+        <v>0.0404</v>
       </c>
       <c r="H9" t="n">
-        <v>3.0865</v>
+        <v>4.7918</v>
       </c>
       <c r="I9" t="n">
-        <v>2.5017</v>
+        <v>2.4915</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0833</v>
+        <v>0.0404</v>
       </c>
       <c r="K9" t="n">
         <v>70</v>
@@ -851,7 +851,7 @@
         <v>59</v>
       </c>
       <c r="M9" t="n">
-        <v>2.585</v>
+        <v>2.5319</v>
       </c>
       <c r="N9" t="n">
         <v>129</v>
@@ -860,47 +860,47 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>Buzz</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.6334</v>
+        <v>2.3665</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7559</v>
+        <v>0.6793</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6052</v>
+        <v>0.4303</v>
       </c>
       <c r="E10" t="n">
-        <v>2.6334</v>
+        <v>2.3665</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3714</v>
+        <v>2.2032</v>
       </c>
       <c r="G10" t="n">
-        <v>2.262</v>
+        <v>0.1633</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3714</v>
+        <v>2.2765</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3714</v>
+        <v>1.1837</v>
       </c>
       <c r="J10" t="n">
-        <v>2.262</v>
+        <v>0.1633</v>
       </c>
       <c r="K10" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="L10" t="n">
-        <v>155</v>
+        <v>59</v>
       </c>
       <c r="M10" t="n">
-        <v>2.6334</v>
+        <v>1.347</v>
       </c>
       <c r="N10" t="n">
-        <v>236</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11">
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.2071</v>
+        <v>2.3231</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6335</v>
+        <v>0.6667999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4354</v>
+        <v>0.4107</v>
       </c>
       <c r="E11" t="n">
-        <v>2.2071</v>
+        <v>2.3231</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1793</v>
+        <v>1.3117</v>
       </c>
       <c r="G11" t="n">
-        <v>1.0278</v>
+        <v>1.0114</v>
       </c>
       <c r="H11" t="n">
-        <v>1.1793</v>
+        <v>1.3117</v>
       </c>
       <c r="I11" t="n">
-        <v>1.1793</v>
+        <v>1.3117</v>
       </c>
       <c r="J11" t="n">
-        <v>1.0278</v>
+        <v>1.0114</v>
       </c>
       <c r="K11" t="n">
         <v>73</v>
@@ -943,7 +943,7 @@
         <v>136</v>
       </c>
       <c r="M11" t="n">
-        <v>2.2071</v>
+        <v>2.3231</v>
       </c>
       <c r="N11" t="n">
         <v>209</v>
@@ -952,231 +952,231 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.7368</v>
+        <v>2.1787</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4985</v>
+        <v>0.6254</v>
       </c>
       <c r="D12" t="n">
-        <v>0.248</v>
+        <v>0.3456</v>
       </c>
       <c r="E12" t="n">
-        <v>1.7368</v>
+        <v>2.1787</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5996</v>
+        <v>0.5515</v>
       </c>
       <c r="G12" t="n">
-        <v>2.3364</v>
+        <v>1.6272</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5996</v>
+        <v>0.5515</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.486</v>
+        <v>0.5515</v>
       </c>
       <c r="J12" t="n">
-        <v>2.3364</v>
+        <v>1.6272</v>
       </c>
       <c r="K12" t="n">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="L12" t="n">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="M12" t="n">
-        <v>1.8504</v>
+        <v>2.1787</v>
       </c>
       <c r="N12" t="n">
-        <v>254</v>
+        <v>236</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>maxster</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.2919</v>
+        <v>1.9647</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3708</v>
+        <v>0.5639</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0708</v>
+        <v>0.2489</v>
       </c>
       <c r="E13" t="n">
-        <v>1.2919</v>
+        <v>1.9647</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6728</v>
+        <v>2.094</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.3809</v>
+        <v>-0.1293</v>
       </c>
       <c r="H13" t="n">
-        <v>1.6728</v>
+        <v>2.094</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6728</v>
+        <v>2.094</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.3809</v>
+        <v>-0.1293</v>
       </c>
       <c r="K13" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="L13" t="n">
-        <v>155</v>
+        <v>61</v>
       </c>
       <c r="M13" t="n">
-        <v>1.2919</v>
+        <v>1.9647</v>
       </c>
       <c r="N13" t="n">
-        <v>236</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>maxster</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.235</v>
+        <v>1.4451</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3545</v>
+        <v>0.4148</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0481</v>
+        <v>0.0144</v>
       </c>
       <c r="E14" t="n">
-        <v>1.235</v>
+        <v>1.4451</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5467</v>
+        <v>1.1639</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.3117</v>
+        <v>0.2812</v>
       </c>
       <c r="H14" t="n">
-        <v>1.5467</v>
+        <v>1.1639</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5467</v>
+        <v>0.6052</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.3117</v>
+        <v>0.2812</v>
       </c>
       <c r="K14" t="n">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="L14" t="n">
-        <v>61</v>
+        <v>135</v>
       </c>
       <c r="M14" t="n">
-        <v>1.235</v>
+        <v>0.8864</v>
       </c>
       <c r="N14" t="n">
-        <v>152</v>
+        <v>254</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Buzz</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.0767</v>
+        <v>1.4356</v>
       </c>
       <c r="C15" t="n">
-        <v>0.309</v>
+        <v>0.4121</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.015</v>
+        <v>0.0101</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0767</v>
+        <v>1.4356</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0985</v>
+        <v>1.9641</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0218</v>
+        <v>-0.5285</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0985</v>
+        <v>1.9641</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8904</v>
+        <v>1.9641</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.0218</v>
+        <v>-0.5285</v>
       </c>
       <c r="K15" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="L15" t="n">
-        <v>59</v>
+        <v>155</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8685999999999999</v>
+        <v>1.4356</v>
       </c>
       <c r="N15" t="n">
-        <v>129</v>
+        <v>236</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>headtr1ck</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9917</v>
+        <v>1.3951</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2847</v>
+        <v>0.4004</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0488</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9917</v>
+        <v>1.3951</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8274</v>
+        <v>-0.4854</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.8357</v>
+        <v>1.8805</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8274</v>
+        <v>-0.4854</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8274</v>
+        <v>-0.2524</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.8357</v>
+        <v>1.8805</v>
       </c>
       <c r="K16" t="n">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="L16" t="n">
-        <v>61</v>
+        <v>135</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9916999999999999</v>
+        <v>1.6281</v>
       </c>
       <c r="N16" t="n">
-        <v>152</v>
+        <v>254</v>
       </c>
     </row>
     <row r="17">
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9702</v>
+        <v>1.3758</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2785</v>
+        <v>0.3949</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0574</v>
+        <v>-0.0169</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9702</v>
+        <v>1.3758</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9702</v>
+        <v>1.3758</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9702</v>
+        <v>1.3758</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9702</v>
+        <v>1.3758</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9702</v>
+        <v>1.3758</v>
       </c>
       <c r="N17" t="n">
         <v>91</v>
@@ -1228,81 +1228,81 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7060999999999999</v>
+        <v>1.2073</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2027</v>
+        <v>0.3465</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1626</v>
+        <v>-0.093</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7060999999999999</v>
+        <v>1.2073</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5647</v>
+        <v>0.5783</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1414</v>
+        <v>0.629</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5647</v>
+        <v>0.5783</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4577</v>
+        <v>0.5783</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1414</v>
+        <v>0.629</v>
       </c>
       <c r="K18" t="n">
-        <v>119</v>
+        <v>73</v>
       </c>
       <c r="L18" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5991</v>
+        <v>1.2073</v>
       </c>
       <c r="N18" t="n">
-        <v>254</v>
+        <v>209</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>headtr1ck</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6959</v>
+        <v>1.1878</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1997</v>
+        <v>0.3409</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1667</v>
+        <v>-0.1018</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6959</v>
+        <v>1.1878</v>
       </c>
       <c r="F19" t="n">
-        <v>0.835</v>
+        <v>1.7424</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1391</v>
+        <v>-0.5546</v>
       </c>
       <c r="H19" t="n">
-        <v>0.835</v>
+        <v>1.7424</v>
       </c>
       <c r="I19" t="n">
-        <v>0.835</v>
+        <v>1.7424</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1391</v>
+        <v>-0.5546</v>
       </c>
       <c r="K19" t="n">
         <v>91</v>
@@ -1311,7 +1311,7 @@
         <v>61</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6959</v>
+        <v>1.1878</v>
       </c>
       <c r="N19" t="n">
         <v>152</v>
@@ -1320,47 +1320,47 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5888</v>
+        <v>1.1554</v>
       </c>
       <c r="C20" t="n">
-        <v>0.169</v>
+        <v>0.3316</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2093</v>
+        <v>-0.1164</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5888</v>
+        <v>1.1554</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5429</v>
+        <v>1.1798</v>
       </c>
       <c r="G20" t="n">
-        <v>1.1317</v>
+        <v>-0.0244</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5429</v>
+        <v>1.1798</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.44</v>
+        <v>1.1798</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1317</v>
+        <v>-0.0244</v>
       </c>
       <c r="K20" t="n">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="L20" t="n">
-        <v>135</v>
+        <v>61</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6917</v>
+        <v>1.1554</v>
       </c>
       <c r="N20" t="n">
-        <v>254</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5131</v>
+        <v>0.9532</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1473</v>
+        <v>0.2736</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2395</v>
+        <v>-0.2077</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5131</v>
+        <v>0.9532</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5131</v>
+        <v>0.9532</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5131</v>
+        <v>0.9532</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5131</v>
+        <v>0.9532</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5131</v>
+        <v>0.9532</v>
       </c>
       <c r="N21" t="n">
         <v>53</v>
@@ -1412,185 +1412,185 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>JamYoung</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.4744</v>
+        <v>0.7734</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1362</v>
+        <v>0.222</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2549</v>
+        <v>-0.2889</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4744</v>
+        <v>0.7734</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2463</v>
+        <v>0.7734</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2281</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2463</v>
+        <v>0.7734</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2463</v>
+        <v>0.7734</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2281</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="L22" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4744</v>
+        <v>0.7734</v>
       </c>
       <c r="N22" t="n">
-        <v>209</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>JamYoung</t>
+          <t>Jee</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.4703</v>
+        <v>0.6903</v>
       </c>
       <c r="C23" t="n">
-        <v>0.135</v>
+        <v>0.1981</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2565</v>
+        <v>-0.3264</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4703</v>
+        <v>0.6903</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4703</v>
+        <v>1.4373</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-0.747</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4703</v>
+        <v>1.4373</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4703</v>
+        <v>1.4373</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-0.747</v>
       </c>
       <c r="K23" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4703</v>
+        <v>0.6903</v>
       </c>
       <c r="N23" t="n">
-        <v>91</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2162</v>
+        <v>0.5836</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0621</v>
+        <v>0.1675</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3578</v>
+        <v>-0.3745</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2162</v>
+        <v>0.5836</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2162</v>
+        <v>-0.3833</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.9669</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2162</v>
+        <v>-0.3833</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2162</v>
+        <v>-0.1993</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.9669</v>
       </c>
       <c r="K24" t="n">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2162</v>
+        <v>0.7675999999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>91</v>
+        <v>254</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>VLDN</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1324</v>
+        <v>0.4057</v>
       </c>
       <c r="C25" t="n">
-        <v>0.038</v>
+        <v>0.1164</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3912</v>
+        <v>-0.4549</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1324</v>
+        <v>0.4057</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.7822</v>
+        <v>0.4057</v>
       </c>
       <c r="G25" t="n">
-        <v>1.9146</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.7822</v>
+        <v>0.4057</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.7822</v>
+        <v>0.4057</v>
       </c>
       <c r="J25" t="n">
-        <v>1.9146</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="L25" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1324000000000001</v>
+        <v>0.4057</v>
       </c>
       <c r="N25" t="n">
-        <v>209</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26">
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1114</v>
+        <v>0.3808</v>
       </c>
       <c r="C26" t="n">
-        <v>0.032</v>
+        <v>0.1093</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3995</v>
+        <v>-0.4661</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1114</v>
+        <v>0.3808</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3816</v>
+        <v>0.4474</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.2702</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3816</v>
+        <v>0.4474</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3816</v>
+        <v>0.4474</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.2702</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="K26" t="n">
         <v>88</v>
@@ -1633,7 +1633,7 @@
         <v>36</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1114</v>
+        <v>0.3808</v>
       </c>
       <c r="N26" t="n">
         <v>124</v>
@@ -1642,127 +1642,127 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Jee</t>
+          <t>kaze</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.3781</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0265</v>
+        <v>0.1085</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4071</v>
+        <v>-0.4673</v>
       </c>
       <c r="E27" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.3781</v>
       </c>
       <c r="F27" t="n">
-        <v>1.0923</v>
+        <v>0.3781</v>
       </c>
       <c r="G27" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.0923</v>
+        <v>0.3781</v>
       </c>
       <c r="I27" t="n">
-        <v>1.0923</v>
+        <v>0.3781</v>
       </c>
       <c r="J27" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="L27" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.09230000000000005</v>
+        <v>0.3781</v>
       </c>
       <c r="N27" t="n">
-        <v>124</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>VLDN</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0629</v>
+        <v>0.213</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0181</v>
+        <v>0.0611</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4189</v>
+        <v>-0.5419</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0629</v>
+        <v>0.213</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.07190000000000001</v>
+        <v>-1.5224</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1348</v>
+        <v>1.7354</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.07190000000000001</v>
+        <v>-1.5224</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.07190000000000001</v>
+        <v>-1.5224</v>
       </c>
       <c r="J28" t="n">
-        <v>0.1348</v>
+        <v>1.7354</v>
       </c>
       <c r="K28" t="n">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="L28" t="n">
-        <v>36</v>
+        <v>136</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0629</v>
+        <v>0.2130000000000001</v>
       </c>
       <c r="N28" t="n">
-        <v>124</v>
+        <v>209</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Westmelon</t>
+          <t>z4kr</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.0456</v>
+        <v>0.1535</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0131</v>
+        <v>0.0441</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4621</v>
+        <v>-0.5687</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.0456</v>
+        <v>0.1535</v>
       </c>
       <c r="F29" t="n">
-        <v>0.2578</v>
+        <v>-0.0824</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.3034</v>
+        <v>0.2359</v>
       </c>
       <c r="H29" t="n">
-        <v>0.2578</v>
+        <v>-0.0824</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2578</v>
+        <v>-0.0824</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.3034</v>
+        <v>0.2359</v>
       </c>
       <c r="K29" t="n">
         <v>88</v>
@@ -1771,7 +1771,7 @@
         <v>36</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.04560000000000003</v>
+        <v>0.1535</v>
       </c>
       <c r="N29" t="n">
         <v>124</v>
@@ -1780,139 +1780,139 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>kaze</t>
+          <t>Westmelon</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.092</v>
+        <v>0.1012</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0264</v>
+        <v>0.029</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.4806</v>
+        <v>-0.5923</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.092</v>
+        <v>0.1012</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.092</v>
+        <v>0.2149</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>-0.1137</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.092</v>
+        <v>0.2149</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.092</v>
+        <v>0.2149</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>-0.1137</v>
       </c>
       <c r="K30" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.092</v>
+        <v>0.1012</v>
       </c>
       <c r="N30" t="n">
-        <v>91</v>
+        <v>124</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>b0RUP</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3675</v>
+        <v>-0.1282</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1055</v>
+        <v>-0.0368</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5903</v>
+        <v>-0.6959</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.3675</v>
+        <v>-0.1282</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.8894</v>
+        <v>0.2462</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5219</v>
+        <v>-0.3744</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.8894</v>
+        <v>0.2462</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7209</v>
+        <v>0.128</v>
       </c>
       <c r="J31" t="n">
-        <v>0.5219</v>
+        <v>-0.3744</v>
       </c>
       <c r="K31" t="n">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="L31" t="n">
-        <v>59</v>
+        <v>135</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.199</v>
+        <v>-0.2464</v>
       </c>
       <c r="N31" t="n">
-        <v>129</v>
+        <v>254</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>b0RUP</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.4248</v>
+        <v>-0.2723</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1219</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6132</v>
+        <v>-0.7609</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.4248</v>
+        <v>-0.2723</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0062</v>
+        <v>-0.901</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.431</v>
+        <v>0.6287</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0062</v>
+        <v>-0.901</v>
       </c>
       <c r="I32" t="n">
-        <v>0.005</v>
+        <v>-0.4685</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.431</v>
+        <v>0.6287</v>
       </c>
       <c r="K32" t="n">
-        <v>119</v>
+        <v>70</v>
       </c>
       <c r="L32" t="n">
-        <v>135</v>
+        <v>59</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.426</v>
+        <v>0.1602</v>
       </c>
       <c r="N32" t="n">
-        <v>254</v>
+        <v>129</v>
       </c>
     </row>
     <row r="33">
@@ -1922,31 +1922,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.648</v>
+        <v>-0.386</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.186</v>
+        <v>-0.1108</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7020999999999999</v>
+        <v>-0.8123</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.648</v>
+        <v>-0.386</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9855</v>
+        <v>1.1446</v>
       </c>
       <c r="G33" t="n">
-        <v>-1.6335</v>
+        <v>-1.5306</v>
       </c>
       <c r="H33" t="n">
-        <v>0.9855</v>
+        <v>1.1446</v>
       </c>
       <c r="I33" t="n">
-        <v>0.9855</v>
+        <v>1.1446</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.6335</v>
+        <v>-1.5306</v>
       </c>
       <c r="K33" t="n">
         <v>81</v>
@@ -1955,7 +1955,7 @@
         <v>155</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.6479999999999999</v>
+        <v>-0.3859999999999999</v>
       </c>
       <c r="N33" t="n">
         <v>236</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6528</v>
+        <v>-0.5053</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1874</v>
+        <v>-0.145</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.704</v>
+        <v>-0.8661</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6528</v>
+        <v>-0.5053</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.6528</v>
+        <v>-0.5053</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.6528</v>
+        <v>-0.5053</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6528</v>
+        <v>-0.5053</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.6528</v>
+        <v>-0.5053</v>
       </c>
       <c r="N34" t="n">
         <v>53</v>
@@ -2014,31 +2014,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.1475</v>
+        <v>-0.8294</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3294</v>
+        <v>-0.2381</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9011</v>
+        <v>-1.0124</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.1475</v>
+        <v>-0.8294</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.4478</v>
+        <v>-1.3687</v>
       </c>
       <c r="G35" t="n">
-        <v>0.3003</v>
+        <v>0.5393</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.4478</v>
+        <v>-1.3687</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.4478</v>
+        <v>-1.3687</v>
       </c>
       <c r="J35" t="n">
-        <v>0.3003</v>
+        <v>0.5393</v>
       </c>
       <c r="K35" t="n">
         <v>73</v>
@@ -2047,7 +2047,7 @@
         <v>136</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.1475</v>
+        <v>-0.8294</v>
       </c>
       <c r="N35" t="n">
         <v>209</v>
@@ -2056,32 +2056,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>flying</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.3945</v>
+        <v>-0.991</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.4003</v>
+        <v>-0.2845</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9995000000000001</v>
+        <v>-1.0854</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.3945</v>
+        <v>-0.991</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.3945</v>
+        <v>-0.991</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.3945</v>
+        <v>-0.991</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.3945</v>
+        <v>-0.991</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.3945</v>
+        <v>-0.991</v>
       </c>
       <c r="N36" t="n">
         <v>53</v>
@@ -2102,32 +2102,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>flying</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.4679</v>
+        <v>-1.0632</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.4213</v>
+        <v>-0.3052</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0287</v>
+        <v>-1.118</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.4679</v>
+        <v>-1.0632</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.4679</v>
+        <v>-1.0632</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.4679</v>
+        <v>-1.0632</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.4679</v>
+        <v>-1.0632</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.4679</v>
+        <v>-1.0632</v>
       </c>
       <c r="N37" t="n">
         <v>53</v>
@@ -2148,139 +2148,139 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>advent</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.7105</v>
+        <v>-1.2124</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.491</v>
+        <v>-0.348</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1254</v>
+        <v>-1.1854</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.7105</v>
+        <v>-1.2124</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.7105</v>
+        <v>-1.2124</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.7105</v>
+        <v>-1.2124</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.7105</v>
+        <v>-1.2124</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.7105</v>
+        <v>-1.2124</v>
       </c>
       <c r="N38" t="n">
-        <v>53</v>
+        <v>91</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>advent</t>
+          <t>es3tag</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.7347</v>
+        <v>-1.3966</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.4979</v>
+        <v>-0.4009</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.135</v>
+        <v>-1.2685</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.7347</v>
+        <v>-1.3966</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.7347</v>
+        <v>-0.6375999999999999</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>-0.759</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.7347</v>
+        <v>-0.6375999999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.7347</v>
+        <v>-0.6375999999999999</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>-0.759</v>
       </c>
       <c r="K39" t="n">
         <v>91</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.7347</v>
+        <v>-1.3966</v>
       </c>
       <c r="N39" t="n">
-        <v>91</v>
+        <v>152</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>es3tag</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.9454</v>
+        <v>-1.4703</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5584</v>
+        <v>-0.422</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.219</v>
+        <v>-1.3018</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.9454</v>
+        <v>-1.4703</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.9454</v>
+        <v>-1.4703</v>
       </c>
       <c r="G40" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.9454</v>
+        <v>-1.4703</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.9454</v>
+        <v>-1.4703</v>
       </c>
       <c r="J40" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>91</v>
+        <v>53</v>
       </c>
       <c r="L40" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.9454</v>
+        <v>-1.4703</v>
       </c>
       <c r="N40" t="n">
-        <v>152</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41">
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.2274</v>
+        <v>-2.7123</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.9264</v>
+        <v>-0.7785</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.7297</v>
+        <v>-1.8625</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.2274</v>
+        <v>-2.7123</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.2274</v>
+        <v>-1.7295</v>
       </c>
       <c r="G41" t="n">
-        <v>-1</v>
+        <v>-0.9828</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.2274</v>
+        <v>-1.7295</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.2274</v>
+        <v>-1.7295</v>
       </c>
       <c r="J41" t="n">
-        <v>-1</v>
+        <v>-0.9828</v>
       </c>
       <c r="K41" t="n">
         <v>88</v>
@@ -2323,7 +2323,7 @@
         <v>36</v>
       </c>
       <c r="M41" t="n">
-        <v>-3.2274</v>
+        <v>-2.7123</v>
       </c>
       <c r="N41" t="n">
         <v>124</v>
@@ -2429,10 +2429,10 @@
         <v>1.5</v>
       </c>
       <c r="I2" t="n">
-        <v>0.784</v>
+        <v>0.9774</v>
       </c>
       <c r="J2" t="n">
-        <v>15.68</v>
+        <v>19.548</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1597</v>
+        <v>0.1532</v>
       </c>
       <c r="J3" t="n">
-        <v>3.194</v>
+        <v>3.064</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.03</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1183</v>
+        <v>0.1045</v>
       </c>
       <c r="J4" t="n">
-        <v>2.366</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.66</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5612</v>
+        <v>-0.3672</v>
       </c>
       <c r="J5" t="n">
-        <v>-11.224</v>
+        <v>-7.344</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.47</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7915</v>
+        <v>-0.5407</v>
       </c>
       <c r="J6" t="n">
-        <v>-15.83</v>
+        <v>-10.814</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.44</v>
       </c>
       <c r="I7" t="n">
-        <v>1.108</v>
+        <v>1.0676</v>
       </c>
       <c r="J7" t="n">
-        <v>22.16</v>
+        <v>21.352</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.25</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6803</v>
+        <v>0.6813</v>
       </c>
       <c r="J8" t="n">
-        <v>13.606</v>
+        <v>13.626</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.16</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4176</v>
+        <v>0.4657</v>
       </c>
       <c r="J9" t="n">
-        <v>8.352</v>
+        <v>9.314</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.08</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1848</v>
+        <v>0.2487</v>
       </c>
       <c r="J10" t="n">
-        <v>3.696</v>
+        <v>4.974</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.99</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1759</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.518</v>
+        <v>-1.99</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.35</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5869</v>
+        <v>0.7066</v>
       </c>
       <c r="J12" t="n">
-        <v>23.476</v>
+        <v>28.264</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.06</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1587</v>
+        <v>0.1635</v>
       </c>
       <c r="J13" t="n">
-        <v>6.348</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.98</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0634</v>
+        <v>-0.0354</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.536</v>
+        <v>-1.416</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.83</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3375</v>
+        <v>-0.2077</v>
       </c>
       <c r="J15" t="n">
-        <v>-13.5</v>
+        <v>-8.308</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.74</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4656</v>
+        <v>-0.2971</v>
       </c>
       <c r="J16" t="n">
-        <v>-18.624</v>
+        <v>-11.884</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.28</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8032</v>
+        <v>0.78</v>
       </c>
       <c r="J17" t="n">
-        <v>32.128</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.27</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7798</v>
+        <v>0.7559</v>
       </c>
       <c r="J18" t="n">
-        <v>31.192</v>
+        <v>30.236</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.12</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3842</v>
+        <v>0.3769</v>
       </c>
       <c r="J19" t="n">
-        <v>15.368</v>
+        <v>15.076</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.97</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.22</v>
+        <v>-0.1554</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.800000000000001</v>
+        <v>-6.216</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.85</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5768</v>
+        <v>-0.5167</v>
       </c>
       <c r="J21" t="n">
-        <v>-23.072</v>
+        <v>-20.668</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.66</v>
       </c>
       <c r="I22" t="n">
-        <v>0.953</v>
+        <v>0.6924</v>
       </c>
       <c r="J22" t="n">
-        <v>20.013</v>
+        <v>14.5404</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.15</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3214</v>
+        <v>0.2719</v>
       </c>
       <c r="J23" t="n">
-        <v>6.7494</v>
+        <v>5.7099</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.78</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4042</v>
+        <v>-0.2549</v>
       </c>
       <c r="J24" t="n">
-        <v>-8.488200000000001</v>
+        <v>-5.3529</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.75</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4463</v>
+        <v>-0.2843</v>
       </c>
       <c r="J25" t="n">
-        <v>-9.372299999999999</v>
+        <v>-5.9703</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.49</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.7713</v>
+        <v>-0.5251</v>
       </c>
       <c r="J26" t="n">
-        <v>-16.1973</v>
+        <v>-11.0271</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.63</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8499</v>
+        <v>0.5887</v>
       </c>
       <c r="J27" t="n">
-        <v>17.8479</v>
+        <v>12.3627</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.29</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4449</v>
+        <v>0.3664</v>
       </c>
       <c r="J28" t="n">
-        <v>9.3429</v>
+        <v>7.6944</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.17</v>
       </c>
       <c r="I29" t="n">
-        <v>0.254</v>
+        <v>0.2462</v>
       </c>
       <c r="J29" t="n">
-        <v>5.334</v>
+        <v>5.1702</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.04</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0311</v>
+        <v>0.0612</v>
       </c>
       <c r="J30" t="n">
-        <v>0.6531</v>
+        <v>1.2852</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.82</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3905</v>
+        <v>-0.2388</v>
       </c>
       <c r="J31" t="n">
-        <v>-8.2005</v>
+        <v>-5.0148</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.75</v>
       </c>
       <c r="I32" t="n">
-        <v>1.7361</v>
+        <v>1.2261</v>
       </c>
       <c r="J32" t="n">
-        <v>52.083</v>
+        <v>36.783</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.02</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0356</v>
+        <v>0.0776</v>
       </c>
       <c r="J33" t="n">
-        <v>1.068</v>
+        <v>2.328</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.91</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.4055</v>
+        <v>-0.3424</v>
       </c>
       <c r="J34" t="n">
-        <v>-12.165</v>
+        <v>-10.272</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.87</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.5175</v>
+        <v>-0.4568</v>
       </c>
       <c r="J35" t="n">
-        <v>-15.525</v>
+        <v>-13.704</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.85</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5705</v>
+        <v>-0.5117</v>
       </c>
       <c r="J36" t="n">
-        <v>-17.115</v>
+        <v>-15.351</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.44</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6612</v>
+        <v>0.6163</v>
       </c>
       <c r="J37" t="n">
-        <v>19.836</v>
+        <v>18.489</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.3</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4869</v>
+        <v>0.4811</v>
       </c>
       <c r="J38" t="n">
-        <v>14.607</v>
+        <v>14.433</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.01</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.012</v>
+        <v>0.0221</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.36</v>
+        <v>0.663</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.99</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.08069999999999999</v>
+        <v>-0.0301</v>
       </c>
       <c r="J40" t="n">
-        <v>-2.421</v>
+        <v>-0.903</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.77</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4452</v>
+        <v>-0.2799</v>
       </c>
       <c r="J41" t="n">
-        <v>-13.356</v>
+        <v>-8.397</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.58</v>
       </c>
       <c r="I42" t="n">
-        <v>1.3968</v>
+        <v>0.9796</v>
       </c>
       <c r="J42" t="n">
-        <v>33.5232</v>
+        <v>23.5104</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.39</v>
       </c>
       <c r="I43" t="n">
-        <v>1.0129</v>
+        <v>0.7327</v>
       </c>
       <c r="J43" t="n">
-        <v>24.3096</v>
+        <v>17.5848</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.33</v>
       </c>
       <c r="I44" t="n">
-        <v>0.8811</v>
+        <v>0.652</v>
       </c>
       <c r="J44" t="n">
-        <v>21.1464</v>
+        <v>15.648</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.93</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.3784</v>
+        <v>-0.3047</v>
       </c>
       <c r="J45" t="n">
-        <v>-9.0816</v>
+        <v>-7.3128</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.59</v>
       </c>
       <c r="I46" t="n">
-        <v>-1.1782</v>
+        <v>-1.1774</v>
       </c>
       <c r="J46" t="n">
-        <v>-28.2768</v>
+        <v>-28.2576</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.49</v>
       </c>
       <c r="I47" t="n">
-        <v>0.7346</v>
+        <v>0.6746</v>
       </c>
       <c r="J47" t="n">
-        <v>17.6304</v>
+        <v>16.1904</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.35</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5665</v>
+        <v>0.5394</v>
       </c>
       <c r="J48" t="n">
-        <v>13.596</v>
+        <v>12.9456</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.1</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2058</v>
+        <v>0.2347</v>
       </c>
       <c r="J49" t="n">
-        <v>4.9392</v>
+        <v>5.6328</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.92</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2092</v>
+        <v>-0.1175</v>
       </c>
       <c r="J50" t="n">
-        <v>-5.0208</v>
+        <v>-2.82</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.41</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.8694</v>
+        <v>-0.6027</v>
       </c>
       <c r="J51" t="n">
-        <v>-20.8656</v>
+        <v>-14.4648</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.26</v>
       </c>
       <c r="I52" t="n">
-        <v>0.496</v>
+        <v>0.4792</v>
       </c>
       <c r="J52" t="n">
-        <v>11.408</v>
+        <v>11.0216</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.16</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3541</v>
+        <v>0.3683</v>
       </c>
       <c r="J53" t="n">
-        <v>8.144299999999999</v>
+        <v>8.4709</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.3464</v>
+        <v>-0.2191</v>
       </c>
       <c r="J54" t="n">
-        <v>-7.9672</v>
+        <v>-5.0393</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.72</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.4764</v>
+        <v>-0.3073</v>
       </c>
       <c r="J55" t="n">
-        <v>-10.9572</v>
+        <v>-7.0679</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.64</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.5822000000000001</v>
+        <v>-0.383</v>
       </c>
       <c r="J56" t="n">
-        <v>-13.3906</v>
+        <v>-8.808999999999999</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>2.04</v>
       </c>
       <c r="I57" t="n">
-        <v>2.0116</v>
+        <v>1.5812</v>
       </c>
       <c r="J57" t="n">
-        <v>46.2668</v>
+        <v>36.3676</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.19</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5857</v>
+        <v>0.4674</v>
       </c>
       <c r="J58" t="n">
-        <v>13.4711</v>
+        <v>10.7502</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.82</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.651</v>
+        <v>-0.5953000000000001</v>
       </c>
       <c r="J59" t="n">
-        <v>-14.973</v>
+        <v>-13.6919</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.76</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.7952</v>
+        <v>-0.75</v>
       </c>
       <c r="J60" t="n">
-        <v>-18.2896</v>
+        <v>-17.25</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.65</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.0396</v>
+        <v>-1.0198</v>
       </c>
       <c r="J61" t="n">
-        <v>-23.9108</v>
+        <v>-23.4554</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>2.28</v>
       </c>
       <c r="I62" t="n">
-        <v>1.3983</v>
+        <v>0.9188</v>
       </c>
       <c r="J62" t="n">
-        <v>22.3728</v>
+        <v>14.7008</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.76</v>
       </c>
       <c r="I63" t="n">
-        <v>0.9043</v>
+        <v>0.6301</v>
       </c>
       <c r="J63" t="n">
-        <v>14.4688</v>
+        <v>10.0816</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.37</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4355</v>
+        <v>0.4005</v>
       </c>
       <c r="J64" t="n">
-        <v>6.968</v>
+        <v>6.408</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.16</v>
       </c>
       <c r="I65" t="n">
-        <v>0.1649</v>
+        <v>0.1986</v>
       </c>
       <c r="J65" t="n">
-        <v>2.6384</v>
+        <v>3.1776</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1.01</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.0857</v>
+        <v>-0.0243</v>
       </c>
       <c r="J66" t="n">
-        <v>-1.3712</v>
+        <v>-0.3888</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.06</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2976</v>
+        <v>0.243</v>
       </c>
       <c r="J67" t="n">
-        <v>4.7616</v>
+        <v>3.888</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.76</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.2849</v>
+        <v>-0.2339</v>
       </c>
       <c r="J68" t="n">
-        <v>-4.5584</v>
+        <v>-3.7424</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.72</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.3488</v>
+        <v>-0.2739</v>
       </c>
       <c r="J69" t="n">
-        <v>-5.5808</v>
+        <v>-4.3824</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.5</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.7022</v>
+        <v>-0.4771</v>
       </c>
       <c r="J70" t="n">
-        <v>-11.2352</v>
+        <v>-7.6336</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.29</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.9636</v>
+        <v>-0.6746</v>
       </c>
       <c r="J71" t="n">
-        <v>-15.4176</v>
+        <v>-10.7936</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.43</v>
       </c>
       <c r="I72" t="n">
-        <v>0.7034</v>
+        <v>0.6492</v>
       </c>
       <c r="J72" t="n">
-        <v>14.068</v>
+        <v>12.984</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1</v>
       </c>
       <c r="I73" t="n">
-        <v>0.0364</v>
+        <v>0.0109</v>
       </c>
       <c r="J73" t="n">
-        <v>0.728</v>
+        <v>0.218</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.89</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.2225</v>
+        <v>-0.1384</v>
       </c>
       <c r="J74" t="n">
-        <v>-4.45</v>
+        <v>-2.768</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.85</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2902</v>
+        <v>-0.1807</v>
       </c>
       <c r="J75" t="n">
-        <v>-5.804</v>
+        <v>-3.614</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.52</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.7328</v>
+        <v>-0.4954</v>
       </c>
       <c r="J76" t="n">
-        <v>-14.656</v>
+        <v>-9.907999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>2.1</v>
       </c>
       <c r="I77" t="n">
-        <v>2.0045</v>
+        <v>1.556</v>
       </c>
       <c r="J77" t="n">
-        <v>40.09</v>
+        <v>31.12</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.78</v>
       </c>
       <c r="I78" t="n">
-        <v>1.6904</v>
+        <v>1.1837</v>
       </c>
       <c r="J78" t="n">
-        <v>33.808</v>
+        <v>23.674</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.11</v>
       </c>
       <c r="I79" t="n">
-        <v>0.2187</v>
+        <v>0.3047</v>
       </c>
       <c r="J79" t="n">
-        <v>4.374</v>
+        <v>6.094</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1587</v>
+        <v>-0.0751</v>
       </c>
       <c r="J80" t="n">
-        <v>-3.174</v>
+        <v>-1.502</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.2589</v>
+        <v>-1.2726</v>
       </c>
       <c r="J81" t="n">
-        <v>-25.178</v>
+        <v>-25.452</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.67</v>
       </c>
       <c r="I82" t="n">
-        <v>1.5108</v>
+        <v>1.0596</v>
       </c>
       <c r="J82" t="n">
-        <v>31.7268</v>
+        <v>22.2516</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.39</v>
       </c>
       <c r="I83" t="n">
-        <v>0.9518</v>
+        <v>0.7106</v>
       </c>
       <c r="J83" t="n">
-        <v>19.9878</v>
+        <v>14.9226</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.25</v>
       </c>
       <c r="I84" t="n">
-        <v>0.5942</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="J84" t="n">
-        <v>12.4782</v>
+        <v>11.1027</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.16</v>
       </c>
       <c r="I85" t="n">
-        <v>0.3632</v>
+        <v>0.3997</v>
       </c>
       <c r="J85" t="n">
-        <v>7.6272</v>
+        <v>8.393700000000001</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.93</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4133</v>
+        <v>-0.3333</v>
       </c>
       <c r="J86" t="n">
-        <v>-8.6793</v>
+        <v>-6.9993</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.02</v>
       </c>
       <c r="I87" t="n">
-        <v>0.1203</v>
+        <v>0.0953</v>
       </c>
       <c r="J87" t="n">
-        <v>2.5263</v>
+        <v>2.0013</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.99</v>
       </c>
       <c r="I88" t="n">
-        <v>0.0257</v>
+        <v>-0.0072</v>
       </c>
       <c r="J88" t="n">
-        <v>0.5397</v>
+        <v>-0.1512</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.91</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1435</v>
+        <v>-0.112</v>
       </c>
       <c r="J89" t="n">
-        <v>-3.0135</v>
+        <v>-2.352</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.82</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3176</v>
+        <v>-0.2047</v>
       </c>
       <c r="J90" t="n">
-        <v>-6.6696</v>
+        <v>-4.2987</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.67</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5353</v>
+        <v>-0.3503</v>
       </c>
       <c r="J91" t="n">
-        <v>-11.2413</v>
+        <v>-7.3563</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.2</v>
       </c>
       <c r="I92" t="n">
-        <v>0.434</v>
+        <v>0.3604</v>
       </c>
       <c r="J92" t="n">
-        <v>9.114000000000001</v>
+        <v>7.5684</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.89</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.1704</v>
+        <v>-0.1316</v>
       </c>
       <c r="J93" t="n">
-        <v>-3.5784</v>
+        <v>-2.7636</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.86</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2342</v>
+        <v>-0.1625</v>
       </c>
       <c r="J94" t="n">
-        <v>-4.9182</v>
+        <v>-3.4125</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.5032</v>
+        <v>-0.3287</v>
       </c>
       <c r="J95" t="n">
-        <v>-10.5672</v>
+        <v>-6.9027</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.67</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5304</v>
+        <v>-0.3476</v>
       </c>
       <c r="J96" t="n">
-        <v>-11.1384</v>
+        <v>-7.2996</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>2.18</v>
       </c>
       <c r="I97" t="n">
-        <v>1.3691</v>
+        <v>0.9046</v>
       </c>
       <c r="J97" t="n">
-        <v>28.7511</v>
+        <v>18.9966</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.24</v>
       </c>
       <c r="I98" t="n">
-        <v>0.3304</v>
+        <v>0.3218</v>
       </c>
       <c r="J98" t="n">
-        <v>6.9384</v>
+        <v>6.7578</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.04</v>
       </c>
       <c r="I99" t="n">
-        <v>0.0139</v>
+        <v>0.0514</v>
       </c>
       <c r="J99" t="n">
-        <v>0.2919</v>
+        <v>1.0794</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.95</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.201</v>
+        <v>-0.1029</v>
       </c>
       <c r="J100" t="n">
-        <v>-4.221</v>
+        <v>-2.1609</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.2188</v>
+        <v>-0.1153</v>
       </c>
       <c r="J101" t="n">
-        <v>-4.5948</v>
+        <v>-2.4213</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.81</v>
       </c>
       <c r="I102" t="n">
-        <v>1.7159</v>
+        <v>1.2067</v>
       </c>
       <c r="J102" t="n">
-        <v>32.6021</v>
+        <v>22.9273</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.51</v>
       </c>
       <c r="I103" t="n">
-        <v>1.1658</v>
+        <v>0.8486</v>
       </c>
       <c r="J103" t="n">
-        <v>22.1502</v>
+        <v>16.1234</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.21</v>
       </c>
       <c r="I104" t="n">
-        <v>0.4559</v>
+        <v>0.4634</v>
       </c>
       <c r="J104" t="n">
-        <v>8.662100000000001</v>
+        <v>8.804600000000001</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.15</v>
       </c>
       <c r="I105" t="n">
-        <v>0.3074</v>
+        <v>0.3741</v>
       </c>
       <c r="J105" t="n">
-        <v>5.8406</v>
+        <v>7.1079</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>1.11</v>
       </c>
       <c r="I106" t="n">
-        <v>0.2028</v>
+        <v>0.294</v>
       </c>
       <c r="J106" t="n">
-        <v>3.8532</v>
+        <v>5.586</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.03</v>
       </c>
       <c r="I107" t="n">
-        <v>0.2054</v>
+        <v>0.1905</v>
       </c>
       <c r="J107" t="n">
-        <v>3.9026</v>
+        <v>3.6195</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.79</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.2738</v>
+        <v>-0.217</v>
       </c>
       <c r="J108" t="n">
-        <v>-5.2022</v>
+        <v>-4.123</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.76</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.3245</v>
+        <v>-0.2464</v>
       </c>
       <c r="J109" t="n">
-        <v>-6.1655</v>
+        <v>-4.6816</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.6425999999999999</v>
+        <v>-0.4321</v>
       </c>
       <c r="J110" t="n">
-        <v>-12.2094</v>
+        <v>-8.209899999999999</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.53</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.4601</v>
       </c>
       <c r="J111" t="n">
-        <v>-12.958</v>
+        <v>-8.741899999999999</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.1</v>
       </c>
       <c r="I112" t="n">
-        <v>0.386</v>
+        <v>0.4005</v>
       </c>
       <c r="J112" t="n">
-        <v>6.176</v>
+        <v>6.408</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.58</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.5748</v>
+        <v>-0.3963</v>
       </c>
       <c r="J113" t="n">
-        <v>-9.1968</v>
+        <v>-6.3408</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.57</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.5901999999999999</v>
+        <v>-0.4056</v>
       </c>
       <c r="J114" t="n">
-        <v>-9.443199999999999</v>
+        <v>-6.4896</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.57</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.5901999999999999</v>
+        <v>-0.4056</v>
       </c>
       <c r="J115" t="n">
-        <v>-9.443199999999999</v>
+        <v>-6.4896</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.34</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.8979</v>
+        <v>-0.6226</v>
       </c>
       <c r="J116" t="n">
-        <v>-14.3664</v>
+        <v>-9.961600000000001</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.77</v>
       </c>
       <c r="I117" t="n">
-        <v>1.6079</v>
+        <v>1.1354</v>
       </c>
       <c r="J117" t="n">
-        <v>25.7264</v>
+        <v>18.1664</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.58</v>
       </c>
       <c r="I118" t="n">
-        <v>1.2497</v>
+        <v>0.9156</v>
       </c>
       <c r="J118" t="n">
-        <v>19.9952</v>
+        <v>14.6496</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.45</v>
       </c>
       <c r="I119" t="n">
-        <v>0.9513</v>
+        <v>0.7638</v>
       </c>
       <c r="J119" t="n">
-        <v>15.2208</v>
+        <v>12.2208</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.38</v>
       </c>
       <c r="I120" t="n">
-        <v>0.7954</v>
+        <v>0.6777</v>
       </c>
       <c r="J120" t="n">
-        <v>12.7264</v>
+        <v>10.8432</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1.2</v>
       </c>
       <c r="I121" t="n">
-        <v>0.3929</v>
+        <v>0.4342</v>
       </c>
       <c r="J121" t="n">
-        <v>6.2864</v>
+        <v>6.9472</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.13</v>
       </c>
       <c r="I122" t="n">
-        <v>0.32</v>
+        <v>0.339</v>
       </c>
       <c r="J122" t="n">
-        <v>6.4</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.1</v>
       </c>
       <c r="I123" t="n">
-        <v>0.2714</v>
+        <v>0.2826</v>
       </c>
       <c r="J123" t="n">
-        <v>5.428</v>
+        <v>5.652</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.86</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.2512</v>
+        <v>-0.1646</v>
       </c>
       <c r="J124" t="n">
-        <v>-5.024</v>
+        <v>-3.292</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.68</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.5229</v>
+        <v>-0.3414</v>
       </c>
       <c r="J125" t="n">
-        <v>-10.458</v>
+        <v>-6.828</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.66</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5495</v>
+        <v>-0.3602</v>
       </c>
       <c r="J126" t="n">
-        <v>-10.99</v>
+        <v>-7.204</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.79</v>
       </c>
       <c r="I127" t="n">
-        <v>1.7297</v>
+        <v>1.2166</v>
       </c>
       <c r="J127" t="n">
-        <v>34.594</v>
+        <v>24.332</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.43</v>
       </c>
       <c r="I128" t="n">
-        <v>1.0597</v>
+        <v>0.7694</v>
       </c>
       <c r="J128" t="n">
-        <v>21.194</v>
+        <v>15.388</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.26</v>
       </c>
       <c r="I129" t="n">
-        <v>0.6677999999999999</v>
+        <v>0.5455</v>
       </c>
       <c r="J129" t="n">
-        <v>13.356</v>
+        <v>10.91</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.04</v>
       </c>
       <c r="I130" t="n">
-        <v>0.0353</v>
+        <v>0.1099</v>
       </c>
       <c r="J130" t="n">
-        <v>0.706</v>
+        <v>2.198</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.67</v>
       </c>
       <c r="I131" t="n">
-        <v>-1.0264</v>
+        <v>-1.0046</v>
       </c>
       <c r="J131" t="n">
-        <v>-20.528</v>
+        <v>-20.092</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.58</v>
       </c>
       <c r="I132" t="n">
-        <v>0.9192</v>
+        <v>1.1187</v>
       </c>
       <c r="J132" t="n">
-        <v>17.4648</v>
+        <v>21.2553</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.79</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.3433</v>
+        <v>-0.2281</v>
       </c>
       <c r="J133" t="n">
-        <v>-6.5227</v>
+        <v>-4.3339</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.66</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.5354</v>
+        <v>-0.3527</v>
       </c>
       <c r="J134" t="n">
-        <v>-10.1726</v>
+        <v>-6.7013</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.6</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.615</v>
+        <v>-0.4089</v>
       </c>
       <c r="J135" t="n">
-        <v>-11.685</v>
+        <v>-7.7691</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.52</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.7156</v>
+        <v>-0.4829</v>
       </c>
       <c r="J136" t="n">
-        <v>-13.5964</v>
+        <v>-9.1751</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>2.09</v>
       </c>
       <c r="I137" t="n">
-        <v>2.0593</v>
+        <v>1.8009</v>
       </c>
       <c r="J137" t="n">
-        <v>39.1267</v>
+        <v>34.2171</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.7</v>
       </c>
       <c r="I138" t="n">
-        <v>1.5294</v>
+        <v>1.3502</v>
       </c>
       <c r="J138" t="n">
-        <v>29.0586</v>
+        <v>25.6538</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.3</v>
       </c>
       <c r="I139" t="n">
-        <v>0.6685</v>
+        <v>0.7632</v>
       </c>
       <c r="J139" t="n">
-        <v>12.7015</v>
+        <v>14.5008</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.99</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.23</v>
+        <v>-0.1417</v>
       </c>
       <c r="J140" t="n">
-        <v>-4.37</v>
+        <v>-2.6923</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.73</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.9194</v>
+        <v>-0.8842</v>
       </c>
       <c r="J141" t="n">
-        <v>-17.4686</v>
+        <v>-16.7998</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.09</v>
       </c>
       <c r="I142" t="n">
-        <v>0.3044</v>
+        <v>0.3202</v>
       </c>
       <c r="J142" t="n">
-        <v>5.7836</v>
+        <v>6.0838</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.96</v>
       </c>
       <c r="I143" t="n">
-        <v>0.0075</v>
+        <v>-0.0281</v>
       </c>
       <c r="J143" t="n">
-        <v>0.1425</v>
+        <v>-0.5339</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.68</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.4853</v>
+        <v>-0.3242</v>
       </c>
       <c r="J144" t="n">
-        <v>-9.220700000000001</v>
+        <v>-6.1598</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.6</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.5978</v>
+        <v>-0.3994</v>
       </c>
       <c r="J145" t="n">
-        <v>-11.3582</v>
+        <v>-7.5886</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.49</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.7398</v>
+        <v>-0.5017</v>
       </c>
       <c r="J146" t="n">
-        <v>-14.0562</v>
+        <v>-9.532299999999999</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.96</v>
       </c>
       <c r="I147" t="n">
-        <v>1.9574</v>
+        <v>1.6552</v>
       </c>
       <c r="J147" t="n">
-        <v>37.1906</v>
+        <v>31.4488</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.57</v>
       </c>
       <c r="I148" t="n">
-        <v>1.2873</v>
+        <v>1.1961</v>
       </c>
       <c r="J148" t="n">
-        <v>24.4587</v>
+        <v>22.7259</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.21</v>
       </c>
       <c r="I149" t="n">
-        <v>0.4575</v>
+        <v>0.5545</v>
       </c>
       <c r="J149" t="n">
-        <v>8.692500000000001</v>
+        <v>10.5355</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.15</v>
       </c>
       <c r="I150" t="n">
-        <v>0.3087</v>
+        <v>0.4029</v>
       </c>
       <c r="J150" t="n">
-        <v>5.8653</v>
+        <v>7.6551</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.88</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5677</v>
+        <v>-0.4955</v>
       </c>
       <c r="J151" t="n">
-        <v>-10.7863</v>
+        <v>-9.4145</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.33</v>
       </c>
       <c r="I152" t="n">
-        <v>0.5039</v>
+        <v>0.4381</v>
       </c>
       <c r="J152" t="n">
-        <v>12.0936</v>
+        <v>10.5144</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.31</v>
       </c>
       <c r="I153" t="n">
-        <v>0.4777</v>
+        <v>0.4149</v>
       </c>
       <c r="J153" t="n">
-        <v>11.4648</v>
+        <v>9.957599999999999</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.18</v>
       </c>
       <c r="I154" t="n">
-        <v>0.2866</v>
+        <v>0.2596</v>
       </c>
       <c r="J154" t="n">
-        <v>6.8784</v>
+        <v>6.2304</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.07</v>
       </c>
       <c r="I155" t="n">
-        <v>0.0919</v>
+        <v>0.1115</v>
       </c>
       <c r="J155" t="n">
-        <v>2.2056</v>
+        <v>2.676</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.97</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.1442</v>
+        <v>-0.0673</v>
       </c>
       <c r="J156" t="n">
-        <v>-3.4608</v>
+        <v>-1.6152</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.28</v>
       </c>
       <c r="I157" t="n">
-        <v>0.5098</v>
+        <v>0.4595</v>
       </c>
       <c r="J157" t="n">
-        <v>12.2352</v>
+        <v>11.028</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.97</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.058</v>
+        <v>-0.0467</v>
       </c>
       <c r="J158" t="n">
-        <v>-1.392</v>
+        <v>-1.1208</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.9</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.2114</v>
+        <v>-0.1292</v>
       </c>
       <c r="J159" t="n">
-        <v>-5.0736</v>
+        <v>-3.1008</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.85</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2956</v>
+        <v>-0.1826</v>
       </c>
       <c r="J160" t="n">
-        <v>-7.0944</v>
+        <v>-4.3824</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.77</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4155</v>
+        <v>-0.2633</v>
       </c>
       <c r="J161" t="n">
-        <v>-9.972</v>
+        <v>-6.3192</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.32</v>
       </c>
       <c r="I162" t="n">
-        <v>0.5577</v>
+        <v>0.6659</v>
       </c>
       <c r="J162" t="n">
-        <v>11.7117</v>
+        <v>13.9839</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.14</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3059</v>
+        <v>0.3359</v>
       </c>
       <c r="J163" t="n">
-        <v>6.4239</v>
+        <v>7.0539</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.95</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.119</v>
+        <v>-0.0728</v>
       </c>
       <c r="J164" t="n">
-        <v>-2.499</v>
+        <v>-1.5288</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.76</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.4324</v>
+        <v>-0.2745</v>
       </c>
       <c r="J165" t="n">
-        <v>-9.080399999999999</v>
+        <v>-5.7645</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.66</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.5657</v>
+        <v>-0.37</v>
       </c>
       <c r="J166" t="n">
-        <v>-11.8797</v>
+        <v>-7.77</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.65</v>
       </c>
       <c r="I167" t="n">
-        <v>1.5017</v>
+        <v>1.3248</v>
       </c>
       <c r="J167" t="n">
-        <v>31.5357</v>
+        <v>27.8208</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.18</v>
       </c>
       <c r="I168" t="n">
-        <v>0.448</v>
+        <v>0.5088</v>
       </c>
       <c r="J168" t="n">
-        <v>9.407999999999999</v>
+        <v>10.6848</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.15</v>
       </c>
       <c r="I169" t="n">
-        <v>0.3661</v>
+        <v>0.4328</v>
       </c>
       <c r="J169" t="n">
-        <v>7.6881</v>
+        <v>9.088800000000001</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.07</v>
       </c>
       <c r="I170" t="n">
-        <v>0.1382</v>
+        <v>0.2101</v>
       </c>
       <c r="J170" t="n">
-        <v>2.9022</v>
+        <v>4.4121</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1.05</v>
       </c>
       <c r="I171" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.1474</v>
       </c>
       <c r="J171" t="n">
-        <v>1.5813</v>
+        <v>3.0954</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.17</v>
       </c>
       <c r="I172" t="n">
-        <v>0.364</v>
+        <v>0.4061</v>
       </c>
       <c r="J172" t="n">
-        <v>7.644</v>
+        <v>8.5281</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.01</v>
       </c>
       <c r="I173" t="n">
-        <v>0.0743</v>
+        <v>0.0513</v>
       </c>
       <c r="J173" t="n">
-        <v>1.5603</v>
+        <v>1.0773</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.1129</v>
+        <v>-0.0824</v>
       </c>
       <c r="J174" t="n">
-        <v>-2.3709</v>
+        <v>-1.7304</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.86</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2717</v>
+        <v>-0.1696</v>
       </c>
       <c r="J175" t="n">
-        <v>-5.7057</v>
+        <v>-3.5616</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.68</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5332</v>
+        <v>-0.3472</v>
       </c>
       <c r="J176" t="n">
-        <v>-11.1972</v>
+        <v>-7.2912</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>2.02</v>
       </c>
       <c r="I177" t="n">
-        <v>2.0478</v>
+        <v>1.7693</v>
       </c>
       <c r="J177" t="n">
-        <v>43.0038</v>
+        <v>37.1553</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.52</v>
       </c>
       <c r="I178" t="n">
-        <v>1.2503</v>
+        <v>1.1612</v>
       </c>
       <c r="J178" t="n">
-        <v>26.2563</v>
+        <v>24.3852</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.93</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.3976</v>
+        <v>-0.3199</v>
       </c>
       <c r="J179" t="n">
-        <v>-8.349600000000001</v>
+        <v>-6.7179</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.86</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.5888</v>
+        <v>-0.5218</v>
       </c>
       <c r="J180" t="n">
-        <v>-12.3648</v>
+        <v>-10.9578</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.79</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.759</v>
+        <v>-0.7064</v>
       </c>
       <c r="J181" t="n">
-        <v>-15.939</v>
+        <v>-14.8344</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.1</v>
       </c>
       <c r="I182" t="n">
-        <v>0.3842</v>
+        <v>0.3428</v>
       </c>
       <c r="J182" t="n">
-        <v>20.3626</v>
+        <v>18.1684</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.08</v>
       </c>
       <c r="I183" t="n">
-        <v>0.3224</v>
+        <v>0.2845</v>
       </c>
       <c r="J183" t="n">
-        <v>17.0872</v>
+        <v>15.0785</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.08</v>
       </c>
       <c r="I184" t="n">
-        <v>0.3224</v>
+        <v>0.2845</v>
       </c>
       <c r="J184" t="n">
-        <v>17.0872</v>
+        <v>15.0785</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.99</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.0878</v>
+        <v>-0.0571</v>
       </c>
       <c r="J185" t="n">
-        <v>-4.6534</v>
+        <v>-3.0263</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.84</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.5723</v>
+        <v>-0.5208</v>
       </c>
       <c r="J186" t="n">
-        <v>-30.3319</v>
+        <v>-27.6024</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.5</v>
       </c>
       <c r="I187" t="n">
-        <v>0.7342</v>
+        <v>0.9121</v>
       </c>
       <c r="J187" t="n">
-        <v>38.9126</v>
+        <v>48.3413</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.19</v>
       </c>
       <c r="I188" t="n">
-        <v>0.3366</v>
+        <v>0.3958</v>
       </c>
       <c r="J188" t="n">
-        <v>17.8398</v>
+        <v>20.9774</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.1</v>
       </c>
       <c r="I189" t="n">
-        <v>0.1863</v>
+        <v>0.2289</v>
       </c>
       <c r="J189" t="n">
-        <v>9.873900000000001</v>
+        <v>12.1317</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.93</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2015</v>
+        <v>-0.1098</v>
       </c>
       <c r="J190" t="n">
-        <v>-10.6795</v>
+        <v>-5.8194</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.74</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4835</v>
+        <v>-0.3079</v>
       </c>
       <c r="J191" t="n">
-        <v>-25.6255</v>
+        <v>-16.3187</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>2.69</v>
       </c>
       <c r="I192" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J192" t="n">
-        <v>30.8895</v>
+        <v>27.507</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.64</v>
       </c>
       <c r="I193" t="n">
-        <v>1.3271</v>
+        <v>1.2484</v>
       </c>
       <c r="J193" t="n">
-        <v>19.9065</v>
+        <v>18.726</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.26</v>
       </c>
       <c r="I194" t="n">
-        <v>0.5059</v>
+        <v>0.6315</v>
       </c>
       <c r="J194" t="n">
-        <v>7.5885</v>
+        <v>9.4725</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.15</v>
       </c>
       <c r="I195" t="n">
-        <v>0.2518</v>
+        <v>0.3598</v>
       </c>
       <c r="J195" t="n">
-        <v>3.777</v>
+        <v>5.397</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1.07</v>
       </c>
       <c r="I196" t="n">
-        <v>0.0423</v>
+        <v>0.1363</v>
       </c>
       <c r="J196" t="n">
-        <v>0.6345</v>
+        <v>2.0445</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>0.89</v>
       </c>
       <c r="I197" t="n">
-        <v>-0.0453</v>
+        <v>-0.0683</v>
       </c>
       <c r="J197" t="n">
-        <v>-0.6795</v>
+        <v>-1.0245</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.67</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.3945</v>
+        <v>-0.3111</v>
       </c>
       <c r="J198" t="n">
-        <v>-5.9175</v>
+        <v>-4.6665</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.53</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.6393</v>
+        <v>-0.4387</v>
       </c>
       <c r="J199" t="n">
-        <v>-9.589499999999999</v>
+        <v>-6.5805</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.48</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.7105</v>
+        <v>-0.4857</v>
       </c>
       <c r="J200" t="n">
-        <v>-10.6575</v>
+        <v>-7.2855</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.48</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.7105</v>
+        <v>-0.4857</v>
       </c>
       <c r="J201" t="n">
-        <v>-10.6575</v>
+        <v>-7.2855</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.47</v>
       </c>
       <c r="I202" t="n">
-        <v>0.6833</v>
+        <v>0.6022999999999999</v>
       </c>
       <c r="J202" t="n">
-        <v>15.7159</v>
+        <v>13.8529</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.34</v>
       </c>
       <c r="I203" t="n">
-        <v>0.5249</v>
+        <v>0.4543</v>
       </c>
       <c r="J203" t="n">
-        <v>12.0727</v>
+        <v>10.4489</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.09</v>
       </c>
       <c r="I204" t="n">
-        <v>0.1357</v>
+        <v>0.1441</v>
       </c>
       <c r="J204" t="n">
-        <v>3.1211</v>
+        <v>3.3143</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.92</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2309</v>
+        <v>-0.1272</v>
       </c>
       <c r="J205" t="n">
-        <v>-5.3107</v>
+        <v>-2.9256</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.91</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.2476</v>
+        <v>-0.1387</v>
       </c>
       <c r="J206" t="n">
-        <v>-5.6948</v>
+        <v>-3.1901</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.1</v>
       </c>
       <c r="I207" t="n">
-        <v>0.2545</v>
+        <v>0.2041</v>
       </c>
       <c r="J207" t="n">
-        <v>5.8535</v>
+        <v>4.6943</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.1</v>
       </c>
       <c r="I208" t="n">
-        <v>0.2545</v>
+        <v>0.2041</v>
       </c>
       <c r="J208" t="n">
-        <v>5.8535</v>
+        <v>4.6943</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.07</v>
       </c>
       <c r="I209" t="n">
-        <v>0.2022</v>
+        <v>0.1547</v>
       </c>
       <c r="J209" t="n">
-        <v>4.6506</v>
+        <v>3.5581</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.3502</v>
+        <v>-0.2206</v>
       </c>
       <c r="J210" t="n">
-        <v>-8.054600000000001</v>
+        <v>-5.0738</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.57</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.6717</v>
+        <v>-0.4491</v>
       </c>
       <c r="J211" t="n">
-        <v>-15.4491</v>
+        <v>-10.3293</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.33</v>
       </c>
       <c r="I212" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.6764</v>
       </c>
       <c r="J212" t="n">
-        <v>13.56</v>
+        <v>16.2336</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.09</v>
       </c>
       <c r="I213" t="n">
-        <v>0.2176</v>
+        <v>0.2304</v>
       </c>
       <c r="J213" t="n">
-        <v>5.2224</v>
+        <v>5.5296</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.03</v>
       </c>
       <c r="I214" t="n">
-        <v>0.1009</v>
+        <v>0.09520000000000001</v>
       </c>
       <c r="J214" t="n">
-        <v>2.4216</v>
+        <v>2.2848</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.78</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.408</v>
+        <v>-0.2568</v>
       </c>
       <c r="J215" t="n">
-        <v>-9.792</v>
+        <v>-6.1632</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.68</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.5429</v>
+        <v>-0.3531</v>
       </c>
       <c r="J216" t="n">
-        <v>-13.0296</v>
+        <v>-8.474399999999999</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.7</v>
       </c>
       <c r="I217" t="n">
-        <v>1.646</v>
+        <v>1.4218</v>
       </c>
       <c r="J217" t="n">
-        <v>39.504</v>
+        <v>34.1232</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.36</v>
       </c>
       <c r="I218" t="n">
-        <v>0.9735</v>
+        <v>0.9575</v>
       </c>
       <c r="J218" t="n">
-        <v>23.364</v>
+        <v>22.98</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.89</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.4764</v>
+        <v>-0.4104</v>
       </c>
       <c r="J219" t="n">
-        <v>-11.4336</v>
+        <v>-9.849600000000001</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.87</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.5306</v>
+        <v>-0.4667</v>
       </c>
       <c r="J220" t="n">
-        <v>-12.7344</v>
+        <v>-11.2008</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.76</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.8018999999999999</v>
+        <v>-0.7563</v>
       </c>
       <c r="J221" t="n">
-        <v>-19.2456</v>
+        <v>-18.1512</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.42</v>
       </c>
       <c r="I222" t="n">
-        <v>0.6808999999999999</v>
+        <v>0.8365</v>
       </c>
       <c r="J222" t="n">
-        <v>16.3416</v>
+        <v>20.076</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.1</v>
       </c>
       <c r="I223" t="n">
-        <v>0.2402</v>
+        <v>0.2549</v>
       </c>
       <c r="J223" t="n">
-        <v>5.7648</v>
+        <v>6.1176</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.86</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.284</v>
+        <v>-0.1738</v>
       </c>
       <c r="J224" t="n">
-        <v>-6.816</v>
+        <v>-4.1712</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.8</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.3758</v>
+        <v>-0.2352</v>
       </c>
       <c r="J225" t="n">
-        <v>-9.0192</v>
+        <v>-5.6448</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.66</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.5661</v>
+        <v>-0.3703</v>
       </c>
       <c r="J226" t="n">
-        <v>-13.5864</v>
+        <v>-8.8872</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.22</v>
       </c>
       <c r="I227" t="n">
-        <v>0.6813</v>
+        <v>0.6472</v>
       </c>
       <c r="J227" t="n">
-        <v>16.3512</v>
+        <v>15.5328</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.21</v>
       </c>
       <c r="I228" t="n">
-        <v>0.6564</v>
+        <v>0.622</v>
       </c>
       <c r="J228" t="n">
-        <v>15.7536</v>
+        <v>14.928</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.15</v>
       </c>
       <c r="I229" t="n">
-        <v>0.4993</v>
+        <v>0.4668</v>
       </c>
       <c r="J229" t="n">
-        <v>11.9832</v>
+        <v>11.2032</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.87</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.5097</v>
+        <v>-0.4511</v>
       </c>
       <c r="J230" t="n">
-        <v>-12.2328</v>
+        <v>-10.8264</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.85</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.5629999999999999</v>
+        <v>-0.506</v>
       </c>
       <c r="J231" t="n">
-        <v>-13.512</v>
+        <v>-12.144</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>0.89</v>
       </c>
       <c r="I232" t="n">
-        <v>-0.053</v>
+        <v>-0.0741</v>
       </c>
       <c r="J232" t="n">
-        <v>-0.795</v>
+        <v>-1.1115</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>0.67</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.4036</v>
+        <v>-0.314</v>
       </c>
       <c r="J233" t="n">
-        <v>-6.054</v>
+        <v>-4.71</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.61</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.5198</v>
+        <v>-0.3679</v>
       </c>
       <c r="J234" t="n">
-        <v>-7.797</v>
+        <v>-5.5185</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.55</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.6163</v>
+        <v>-0.4227</v>
       </c>
       <c r="J235" t="n">
-        <v>-9.2445</v>
+        <v>-6.3405</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.4</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.8209</v>
+        <v>-0.5642</v>
       </c>
       <c r="J236" t="n">
-        <v>-12.3135</v>
+        <v>-8.462999999999999</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>2.31</v>
       </c>
       <c r="I237" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J237" t="n">
-        <v>30.8895</v>
+        <v>27.507</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.99</v>
       </c>
       <c r="I238" t="n">
-        <v>1.9263</v>
+        <v>1.6333</v>
       </c>
       <c r="J238" t="n">
-        <v>28.8945</v>
+        <v>24.4995</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.74</v>
       </c>
       <c r="I239" t="n">
-        <v>1.5051</v>
+        <v>1.3574</v>
       </c>
       <c r="J239" t="n">
-        <v>22.5765</v>
+        <v>20.361</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>1.01</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.1629</v>
+        <v>-0.077</v>
       </c>
       <c r="J240" t="n">
-        <v>-2.4435</v>
+        <v>-1.155</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.91</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.5304</v>
+        <v>-0.4541</v>
       </c>
       <c r="J241" t="n">
-        <v>-7.956</v>
+        <v>-6.8115</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.96</v>
       </c>
       <c r="I242" t="n">
-        <v>1.1943</v>
+        <v>1.0716</v>
       </c>
       <c r="J242" t="n">
-        <v>27.4689</v>
+        <v>24.6468</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.32</v>
       </c>
       <c r="I243" t="n">
-        <v>0.4947</v>
+        <v>0.4285</v>
       </c>
       <c r="J243" t="n">
-        <v>11.3781</v>
+        <v>9.855499999999999</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.15</v>
       </c>
       <c r="I244" t="n">
-        <v>0.2349</v>
+        <v>0.2236</v>
       </c>
       <c r="J244" t="n">
-        <v>5.4027</v>
+        <v>5.1428</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.75</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.4805</v>
+        <v>-0.3049</v>
       </c>
       <c r="J245" t="n">
-        <v>-11.0515</v>
+        <v>-7.0127</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.62</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.6415999999999999</v>
+        <v>-0.4258</v>
       </c>
       <c r="J246" t="n">
-        <v>-14.7568</v>
+        <v>-9.7934</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.15</v>
       </c>
       <c r="I247" t="n">
-        <v>0.3502</v>
+        <v>0.2943</v>
       </c>
       <c r="J247" t="n">
-        <v>8.054600000000001</v>
+        <v>6.7689</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.98</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.0023</v>
+        <v>-0.0243</v>
       </c>
       <c r="J248" t="n">
-        <v>-0.0529</v>
+        <v>-0.5589</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.97</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.0253</v>
+        <v>-0.0388</v>
       </c>
       <c r="J249" t="n">
-        <v>-0.5819</v>
+        <v>-0.8924</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.3359</v>
+        <v>-0.2154</v>
       </c>
       <c r="J250" t="n">
-        <v>-7.7257</v>
+        <v>-4.9542</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.53</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.7134</v>
+        <v>-0.4808</v>
       </c>
       <c r="J251" t="n">
-        <v>-16.4082</v>
+        <v>-11.0584</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>0.93</v>
       </c>
       <c r="I252" t="n">
-        <v>0.0545</v>
+        <v>0.0179</v>
       </c>
       <c r="J252" t="n">
-        <v>0.8175</v>
+        <v>0.2685</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>0.59</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.4912</v>
+        <v>-0.3766</v>
       </c>
       <c r="J253" t="n">
-        <v>-7.368</v>
+        <v>-5.649</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.5</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.6591</v>
+        <v>-0.457</v>
       </c>
       <c r="J254" t="n">
-        <v>-9.8865</v>
+        <v>-6.855</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.43</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.7611</v>
+        <v>-0.5234</v>
       </c>
       <c r="J255" t="n">
-        <v>-11.4165</v>
+        <v>-7.851</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.35</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.8686</v>
+        <v>-0.6008</v>
       </c>
       <c r="J256" t="n">
-        <v>-13.029</v>
+        <v>-9.012</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.96</v>
       </c>
       <c r="I257" t="n">
-        <v>1.8983</v>
+        <v>1.6076</v>
       </c>
       <c r="J257" t="n">
-        <v>28.4745</v>
+        <v>24.114</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.65</v>
       </c>
       <c r="I258" t="n">
-        <v>1.3508</v>
+        <v>1.2606</v>
       </c>
       <c r="J258" t="n">
-        <v>20.262</v>
+        <v>18.909</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.53</v>
       </c>
       <c r="I259" t="n">
-        <v>1.0827</v>
+        <v>1.1249</v>
       </c>
       <c r="J259" t="n">
-        <v>16.2405</v>
+        <v>16.8735</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>1.39</v>
       </c>
       <c r="I260" t="n">
-        <v>0.7865</v>
+        <v>0.9235</v>
       </c>
       <c r="J260" t="n">
-        <v>11.7975</v>
+        <v>13.8525</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>1.24</v>
       </c>
       <c r="I261" t="n">
-        <v>0.4635</v>
+        <v>0.5857</v>
       </c>
       <c r="J261" t="n">
-        <v>6.9525</v>
+        <v>8.785500000000001</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>2.72</v>
       </c>
       <c r="I262" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J262" t="n">
-        <v>35.0081</v>
+        <v>31.1746</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.43</v>
       </c>
       <c r="I263" t="n">
-        <v>0.9651</v>
+        <v>1.0136</v>
       </c>
       <c r="J263" t="n">
-        <v>16.4067</v>
+        <v>17.2312</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.3</v>
       </c>
       <c r="I264" t="n">
-        <v>0.6464</v>
+        <v>0.7544</v>
       </c>
       <c r="J264" t="n">
-        <v>10.9888</v>
+        <v>12.8248</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.86</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.6287</v>
+        <v>-0.5613</v>
       </c>
       <c r="J265" t="n">
-        <v>-10.6879</v>
+        <v>-9.5421</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.73</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.9264</v>
+        <v>-0.8923</v>
       </c>
       <c r="J266" t="n">
-        <v>-15.7488</v>
+        <v>-15.1691</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>0.95</v>
       </c>
       <c r="I267" t="n">
-        <v>-0.0196</v>
+        <v>-0.0456</v>
       </c>
       <c r="J267" t="n">
-        <v>-0.3332</v>
+        <v>-0.7752</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.86</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.1809</v>
+        <v>-0.1522</v>
       </c>
       <c r="J268" t="n">
-        <v>-3.0753</v>
+        <v>-2.5874</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.8</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.2844</v>
+        <v>-0.2137</v>
       </c>
       <c r="J269" t="n">
-        <v>-4.8348</v>
+        <v>-3.6329</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.7</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.4621</v>
+        <v>-0.3077</v>
       </c>
       <c r="J270" t="n">
-        <v>-7.8557</v>
+        <v>-5.2309</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.59</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.6156</v>
+        <v>-0.4111</v>
       </c>
       <c r="J271" t="n">
-        <v>-10.4652</v>
+        <v>-6.9887</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>2.12</v>
       </c>
       <c r="I272" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J272" t="n">
-        <v>41.186</v>
+        <v>36.676</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.43</v>
       </c>
       <c r="I273" t="n">
-        <v>1.027</v>
+        <v>1.0295</v>
       </c>
       <c r="J273" t="n">
-        <v>20.54</v>
+        <v>20.59</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.33</v>
       </c>
       <c r="I274" t="n">
-        <v>0.7991</v>
+        <v>0.8376</v>
       </c>
       <c r="J274" t="n">
-        <v>15.982</v>
+        <v>16.752</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.92</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.4478</v>
+        <v>-0.3687</v>
       </c>
       <c r="J275" t="n">
-        <v>-8.956</v>
+        <v>-7.374</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.71</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.9526</v>
+        <v>-0.9214</v>
       </c>
       <c r="J276" t="n">
-        <v>-19.052</v>
+        <v>-18.428</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>2.12</v>
       </c>
       <c r="I277" t="n">
-        <v>1.4194</v>
+        <v>1.5673</v>
       </c>
       <c r="J277" t="n">
-        <v>28.388</v>
+        <v>31.346</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>0.78</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.4007</v>
+        <v>-0.2532</v>
       </c>
       <c r="J278" t="n">
-        <v>-8.013999999999999</v>
+        <v>-5.064</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.73</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.4706</v>
+        <v>-0.302</v>
       </c>
       <c r="J279" t="n">
-        <v>-9.412000000000001</v>
+        <v>-6.04</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.61</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.6262</v>
+        <v>-0.4149</v>
       </c>
       <c r="J280" t="n">
-        <v>-12.524</v>
+        <v>-8.298</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.52</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.7347</v>
+        <v>-0.4969</v>
       </c>
       <c r="J281" t="n">
-        <v>-14.694</v>
+        <v>-9.938000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7365/event_7365_evp_summary.xlsx
+++ b/database/event/7365/event_7365_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.4967</v>
+        <v>6.5962</v>
       </c>
       <c r="C2" t="n">
-        <v>1.8648</v>
+        <v>1.8933</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2949</v>
+        <v>2.3785</v>
       </c>
       <c r="E2" t="n">
-        <v>6.4967</v>
+        <v>6.5962</v>
       </c>
       <c r="F2" t="n">
-        <v>3.6572</v>
+        <v>3.649</v>
       </c>
       <c r="G2" t="n">
-        <v>2.8395</v>
+        <v>2.9472</v>
       </c>
       <c r="H2" t="n">
-        <v>7.3992</v>
+        <v>7.1453</v>
       </c>
       <c r="I2" t="n">
-        <v>3.8472</v>
+        <v>3.8584</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8395</v>
+        <v>2.9472</v>
       </c>
       <c r="K2" t="n">
         <v>119</v>
@@ -529,7 +529,7 @@
         <v>135</v>
       </c>
       <c r="M2" t="n">
-        <v>6.6867</v>
+        <v>6.8056</v>
       </c>
       <c r="N2" t="n">
         <v>254</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.1608</v>
+        <v>6.2481</v>
       </c>
       <c r="C3" t="n">
-        <v>1.7684</v>
+        <v>1.7934</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1433</v>
+        <v>2.2201</v>
       </c>
       <c r="E3" t="n">
-        <v>6.1608</v>
+        <v>6.2481</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0348</v>
+        <v>0.0573</v>
       </c>
       <c r="G3" t="n">
-        <v>6.126</v>
+        <v>6.1908</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0348</v>
+        <v>0.0573</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0348</v>
+        <v>0.0573</v>
       </c>
       <c r="J3" t="n">
-        <v>6.126</v>
+        <v>6.4484</v>
       </c>
       <c r="K3" t="n">
         <v>81</v>
@@ -575,7 +575,7 @@
         <v>155</v>
       </c>
       <c r="M3" t="n">
-        <v>6.1608</v>
+        <v>6.5057</v>
       </c>
       <c r="N3" t="n">
         <v>236</v>
@@ -584,93 +584,93 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.6943</v>
+        <v>5.0505</v>
       </c>
       <c r="C4" t="n">
-        <v>1.3474</v>
+        <v>1.4497</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4812</v>
+        <v>1.6749</v>
       </c>
       <c r="E4" t="n">
-        <v>4.6943</v>
+        <v>5.0505</v>
       </c>
       <c r="F4" t="n">
-        <v>3.5741</v>
+        <v>1.315</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1202</v>
+        <v>3.7355</v>
       </c>
       <c r="H4" t="n">
-        <v>7.1066</v>
+        <v>1.315</v>
       </c>
       <c r="I4" t="n">
-        <v>3.6951</v>
+        <v>1.315</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1202</v>
+        <v>3.7355</v>
       </c>
       <c r="K4" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L4" t="n">
-        <v>59</v>
+        <v>136</v>
       </c>
       <c r="M4" t="n">
-        <v>4.815300000000001</v>
+        <v>5.0505</v>
       </c>
       <c r="N4" t="n">
-        <v>129</v>
+        <v>209</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.5626</v>
+        <v>4.7975</v>
       </c>
       <c r="C5" t="n">
-        <v>1.3096</v>
+        <v>1.377</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4218</v>
+        <v>1.5597</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5626</v>
+        <v>4.7975</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1918</v>
+        <v>3.5338</v>
       </c>
       <c r="G5" t="n">
-        <v>3.3708</v>
+        <v>1.2637</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1918</v>
+        <v>6.7651</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1918</v>
+        <v>3.6531</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3708</v>
+        <v>1.2637</v>
       </c>
       <c r="K5" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="L5" t="n">
-        <v>136</v>
+        <v>59</v>
       </c>
       <c r="M5" t="n">
-        <v>4.5626</v>
+        <v>4.9168</v>
       </c>
       <c r="N5" t="n">
-        <v>209</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6">
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.9376</v>
+        <v>4.1271</v>
       </c>
       <c r="C6" t="n">
-        <v>1.1302</v>
+        <v>1.1846</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1396</v>
+        <v>1.2545</v>
       </c>
       <c r="E6" t="n">
-        <v>3.9376</v>
+        <v>4.1271</v>
       </c>
       <c r="F6" t="n">
-        <v>3.9828</v>
+        <v>4.1437</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0452</v>
+        <v>-0.0166</v>
       </c>
       <c r="H6" t="n">
-        <v>8.5466</v>
+        <v>8.7776</v>
       </c>
       <c r="I6" t="n">
-        <v>4.4438</v>
+        <v>4.7398</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0452</v>
+        <v>-0.0166</v>
       </c>
       <c r="K6" t="n">
         <v>70</v>
@@ -713,7 +713,7 @@
         <v>59</v>
       </c>
       <c r="M6" t="n">
-        <v>4.3986</v>
+        <v>4.723199999999999</v>
       </c>
       <c r="N6" t="n">
         <v>129</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.8964</v>
+        <v>4.1116</v>
       </c>
       <c r="C7" t="n">
-        <v>1.1184</v>
+        <v>1.1802</v>
       </c>
       <c r="D7" t="n">
-        <v>1.121</v>
+        <v>1.2475</v>
       </c>
       <c r="E7" t="n">
-        <v>3.8964</v>
+        <v>4.1116</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6932</v>
+        <v>1.6743</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2032</v>
+        <v>2.4373</v>
       </c>
       <c r="H7" t="n">
-        <v>1.6932</v>
+        <v>1.6743</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6932</v>
+        <v>1.6743</v>
       </c>
       <c r="J7" t="n">
-        <v>2.2032</v>
+        <v>2.4373</v>
       </c>
       <c r="K7" t="n">
         <v>81</v>
@@ -759,7 +759,7 @@
         <v>155</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8964</v>
+        <v>4.1116</v>
       </c>
       <c r="N7" t="n">
         <v>236</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.6528</v>
+        <v>3.4638</v>
       </c>
       <c r="C8" t="n">
-        <v>1.0485</v>
+        <v>0.9942</v>
       </c>
       <c r="D8" t="n">
-        <v>1.011</v>
+        <v>0.9526</v>
       </c>
       <c r="E8" t="n">
-        <v>3.6528</v>
+        <v>3.4638</v>
       </c>
       <c r="F8" t="n">
-        <v>2.8699</v>
+        <v>2.5708</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7829</v>
+        <v>0.893</v>
       </c>
       <c r="H8" t="n">
-        <v>2.9421</v>
+        <v>2.9017</v>
       </c>
       <c r="I8" t="n">
-        <v>2.9421</v>
+        <v>2.9017</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7829</v>
+        <v>0.893</v>
       </c>
       <c r="K8" t="n">
         <v>91</v>
@@ -805,7 +805,7 @@
         <v>61</v>
       </c>
       <c r="M8" t="n">
-        <v>3.725</v>
+        <v>3.7947</v>
       </c>
       <c r="N8" t="n">
         <v>152</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.9575</v>
+        <v>3.034</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8489</v>
+        <v>0.8709</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6971000000000001</v>
+        <v>0.7569</v>
       </c>
       <c r="E9" t="n">
-        <v>2.9575</v>
+        <v>3.034</v>
       </c>
       <c r="F9" t="n">
-        <v>2.9171</v>
+        <v>2.8713</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0404</v>
+        <v>0.1627</v>
       </c>
       <c r="H9" t="n">
-        <v>4.7918</v>
+        <v>4.5791</v>
       </c>
       <c r="I9" t="n">
-        <v>2.4915</v>
+        <v>2.4727</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0404</v>
+        <v>0.1627</v>
       </c>
       <c r="K9" t="n">
         <v>70</v>
@@ -851,7 +851,7 @@
         <v>59</v>
       </c>
       <c r="M9" t="n">
-        <v>2.5319</v>
+        <v>2.6354</v>
       </c>
       <c r="N9" t="n">
         <v>129</v>
@@ -860,47 +860,47 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Buzz</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.3665</v>
+        <v>2.4615</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6793</v>
+        <v>0.7065</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4303</v>
+        <v>0.4963</v>
       </c>
       <c r="E10" t="n">
-        <v>2.3665</v>
+        <v>2.4615</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2032</v>
+        <v>0.5719</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1633</v>
+        <v>1.8896</v>
       </c>
       <c r="H10" t="n">
-        <v>2.2765</v>
+        <v>0.5719</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1837</v>
+        <v>0.5719</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1633</v>
+        <v>1.8896</v>
       </c>
       <c r="K10" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="L10" t="n">
-        <v>59</v>
+        <v>155</v>
       </c>
       <c r="M10" t="n">
-        <v>1.347</v>
+        <v>2.4615</v>
       </c>
       <c r="N10" t="n">
-        <v>129</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.3231</v>
+        <v>2.3612</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6667999999999999</v>
+        <v>0.6777</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4107</v>
+        <v>0.4507</v>
       </c>
       <c r="E11" t="n">
-        <v>2.3231</v>
+        <v>2.3612</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3117</v>
+        <v>1.2167</v>
       </c>
       <c r="G11" t="n">
-        <v>1.0114</v>
+        <v>1.1445</v>
       </c>
       <c r="H11" t="n">
-        <v>1.3117</v>
+        <v>1.2167</v>
       </c>
       <c r="I11" t="n">
-        <v>1.3117</v>
+        <v>1.2167</v>
       </c>
       <c r="J11" t="n">
-        <v>1.0114</v>
+        <v>1.1445</v>
       </c>
       <c r="K11" t="n">
         <v>73</v>
@@ -943,7 +943,7 @@
         <v>136</v>
       </c>
       <c r="M11" t="n">
-        <v>2.3231</v>
+        <v>2.3612</v>
       </c>
       <c r="N11" t="n">
         <v>209</v>
@@ -952,47 +952,47 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>Buzz</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.1787</v>
+        <v>2.3486</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6254</v>
+        <v>0.6741</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3456</v>
+        <v>0.4449</v>
       </c>
       <c r="E12" t="n">
-        <v>2.1787</v>
+        <v>2.3486</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5515</v>
+        <v>2.1696</v>
       </c>
       <c r="G12" t="n">
-        <v>1.6272</v>
+        <v>0.179</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5515</v>
+        <v>2.2641</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5515</v>
+        <v>1.2226</v>
       </c>
       <c r="J12" t="n">
-        <v>1.6272</v>
+        <v>0.179</v>
       </c>
       <c r="K12" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="L12" t="n">
-        <v>155</v>
+        <v>59</v>
       </c>
       <c r="M12" t="n">
-        <v>2.1787</v>
+        <v>1.4016</v>
       </c>
       <c r="N12" t="n">
-        <v>236</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.9647</v>
+        <v>1.9503</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5639</v>
+        <v>0.5598</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2489</v>
+        <v>0.2636</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9647</v>
+        <v>1.9503</v>
       </c>
       <c r="F13" t="n">
-        <v>2.094</v>
+        <v>2.0969</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1293</v>
+        <v>-0.1466</v>
       </c>
       <c r="H13" t="n">
-        <v>2.094</v>
+        <v>2.0969</v>
       </c>
       <c r="I13" t="n">
-        <v>2.094</v>
+        <v>2.0969</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.1293</v>
+        <v>-0.1466</v>
       </c>
       <c r="K13" t="n">
         <v>91</v>
@@ -1035,7 +1035,7 @@
         <v>61</v>
       </c>
       <c r="M13" t="n">
-        <v>1.9647</v>
+        <v>1.9503</v>
       </c>
       <c r="N13" t="n">
         <v>152</v>
@@ -1044,127 +1044,127 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.4451</v>
+        <v>1.751</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4148</v>
+        <v>0.5026</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0144</v>
+        <v>0.1729</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4451</v>
+        <v>1.751</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1639</v>
+        <v>2.1447</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2812</v>
+        <v>-0.3937</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1639</v>
+        <v>2.1447</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6052</v>
+        <v>2.1447</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2812</v>
+        <v>-0.3937</v>
       </c>
       <c r="K14" t="n">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="L14" t="n">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8864</v>
+        <v>1.751</v>
       </c>
       <c r="N14" t="n">
-        <v>254</v>
+        <v>236</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.4356</v>
+        <v>1.6288</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4121</v>
+        <v>0.4675</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0101</v>
+        <v>0.1173</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4356</v>
+        <v>1.6288</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9641</v>
+        <v>-0.3983</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.5285</v>
+        <v>2.0271</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9641</v>
+        <v>-0.3983</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9641</v>
+        <v>-0.2151</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5285</v>
+        <v>2.0271</v>
       </c>
       <c r="K15" t="n">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="L15" t="n">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="M15" t="n">
-        <v>1.4356</v>
+        <v>1.812</v>
       </c>
       <c r="N15" t="n">
-        <v>236</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.3951</v>
+        <v>1.3869</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4004</v>
+        <v>0.3981</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.0071</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3951</v>
+        <v>1.3869</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4854</v>
+        <v>1.1082</v>
       </c>
       <c r="G16" t="n">
-        <v>1.8805</v>
+        <v>0.2787</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4854</v>
+        <v>1.1082</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2524</v>
+        <v>0.5984</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8805</v>
+        <v>0.2787</v>
       </c>
       <c r="K16" t="n">
         <v>119</v>
@@ -1173,7 +1173,7 @@
         <v>135</v>
       </c>
       <c r="M16" t="n">
-        <v>1.6281</v>
+        <v>0.8771</v>
       </c>
       <c r="N16" t="n">
         <v>254</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.3758</v>
+        <v>1.3817</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3949</v>
+        <v>0.3966</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0169</v>
+        <v>0.0048</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3758</v>
+        <v>1.3817</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3758</v>
+        <v>1.3817</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3758</v>
+        <v>1.3817</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3758</v>
+        <v>1.3817</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.3758</v>
+        <v>1.3817</v>
       </c>
       <c r="N17" t="n">
         <v>91</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.2073</v>
+        <v>1.3078</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3465</v>
+        <v>0.3754</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.093</v>
+        <v>-0.0289</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2073</v>
+        <v>1.3078</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5783</v>
+        <v>0.5074</v>
       </c>
       <c r="G18" t="n">
-        <v>0.629</v>
+        <v>0.8004</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5783</v>
+        <v>0.5074</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5783</v>
+        <v>0.5074</v>
       </c>
       <c r="J18" t="n">
-        <v>0.629</v>
+        <v>0.8004</v>
       </c>
       <c r="K18" t="n">
         <v>73</v>
@@ -1265,7 +1265,7 @@
         <v>136</v>
       </c>
       <c r="M18" t="n">
-        <v>1.2073</v>
+        <v>1.3078</v>
       </c>
       <c r="N18" t="n">
         <v>209</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.1878</v>
+        <v>1.1933</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3409</v>
+        <v>0.3425</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1018</v>
+        <v>-0.081</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1878</v>
+        <v>1.1933</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7424</v>
+        <v>1.774</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5546</v>
+        <v>-0.5807</v>
       </c>
       <c r="H19" t="n">
-        <v>1.7424</v>
+        <v>1.774</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7424</v>
+        <v>1.774</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5546</v>
+        <v>-0.5807</v>
       </c>
       <c r="K19" t="n">
         <v>91</v>
@@ -1311,7 +1311,7 @@
         <v>61</v>
       </c>
       <c r="M19" t="n">
-        <v>1.1878</v>
+        <v>1.1933</v>
       </c>
       <c r="N19" t="n">
         <v>152</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.1554</v>
+        <v>1.0818</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3316</v>
+        <v>0.3105</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1164</v>
+        <v>-0.1317</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1554</v>
+        <v>1.0818</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1798</v>
+        <v>1.1437</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0244</v>
+        <v>-0.0619</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1798</v>
+        <v>1.1437</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1798</v>
+        <v>1.1437</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0244</v>
+        <v>-0.0619</v>
       </c>
       <c r="K20" t="n">
         <v>91</v>
@@ -1357,7 +1357,7 @@
         <v>61</v>
       </c>
       <c r="M20" t="n">
-        <v>1.1554</v>
+        <v>1.0818</v>
       </c>
       <c r="N20" t="n">
         <v>152</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9532</v>
+        <v>0.8784999999999999</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2736</v>
+        <v>0.2522</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2077</v>
+        <v>-0.2243</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9532</v>
+        <v>0.8784999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9532</v>
+        <v>0.8784999999999999</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9532</v>
+        <v>0.8784999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9532</v>
+        <v>0.8784999999999999</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.9532</v>
+        <v>0.8784999999999999</v>
       </c>
       <c r="N21" t="n">
         <v>53</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7734</v>
+        <v>0.7537</v>
       </c>
       <c r="C22" t="n">
-        <v>0.222</v>
+        <v>0.2163</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2889</v>
+        <v>-0.2811</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7734</v>
+        <v>0.7537</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7734</v>
+        <v>0.7537</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7734</v>
+        <v>0.7537</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7734</v>
+        <v>0.7537</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7734</v>
+        <v>0.7537</v>
       </c>
       <c r="N22" t="n">
         <v>91</v>
@@ -1458,185 +1458,185 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Jee</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6903</v>
+        <v>0.7039</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1981</v>
+        <v>0.202</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3264</v>
+        <v>-0.3038</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6903</v>
+        <v>0.7039</v>
       </c>
       <c r="F23" t="n">
-        <v>1.4373</v>
+        <v>-0.3548</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.747</v>
+        <v>1.0587</v>
       </c>
       <c r="H23" t="n">
-        <v>1.4373</v>
+        <v>-0.3548</v>
       </c>
       <c r="I23" t="n">
-        <v>1.4373</v>
+        <v>-0.1916</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.747</v>
+        <v>1.0587</v>
       </c>
       <c r="K23" t="n">
-        <v>88</v>
+        <v>119</v>
       </c>
       <c r="L23" t="n">
-        <v>36</v>
+        <v>135</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6903</v>
+        <v>0.8671</v>
       </c>
       <c r="N23" t="n">
-        <v>124</v>
+        <v>254</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>Jee</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5836</v>
+        <v>0.5737</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1675</v>
+        <v>0.1647</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3745</v>
+        <v>-0.363</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5836</v>
+        <v>0.5737</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3833</v>
+        <v>1.3522</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9669</v>
+        <v>-0.7785</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.3833</v>
+        <v>1.3522</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1993</v>
+        <v>1.3522</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9669</v>
+        <v>-0.7785</v>
       </c>
       <c r="K24" t="n">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="L24" t="n">
-        <v>135</v>
+        <v>36</v>
       </c>
       <c r="M24" t="n">
-        <v>0.7675999999999999</v>
+        <v>0.5737000000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>254</v>
+        <v>124</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>VLDN</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.4057</v>
+        <v>0.454</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1164</v>
+        <v>0.1303</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4549</v>
+        <v>-0.4175</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4057</v>
+        <v>0.454</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4057</v>
+        <v>-1.5139</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1.9679</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4057</v>
+        <v>-1.5139</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4057</v>
+        <v>-1.5139</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1.9679</v>
       </c>
       <c r="K25" t="n">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4057</v>
+        <v>0.454</v>
       </c>
       <c r="N25" t="n">
-        <v>91</v>
+        <v>209</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Starry</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.3808</v>
+        <v>0.3837</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1093</v>
+        <v>0.1101</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4661</v>
+        <v>-0.4495</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3808</v>
+        <v>0.3837</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4474</v>
+        <v>0.3837</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.06660000000000001</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4474</v>
+        <v>0.3837</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4474</v>
+        <v>0.3837</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.06660000000000001</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="L26" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3808</v>
+        <v>0.3837</v>
       </c>
       <c r="N26" t="n">
-        <v>124</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27">
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.3781</v>
+        <v>0.3229</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1085</v>
+        <v>0.0927</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4673</v>
+        <v>-0.4772</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3781</v>
+        <v>0.3229</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3781</v>
+        <v>0.3229</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3781</v>
+        <v>0.3229</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3781</v>
+        <v>0.3229</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.3781</v>
+        <v>0.3229</v>
       </c>
       <c r="N27" t="n">
         <v>91</v>
@@ -1688,47 +1688,47 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>VLDN</t>
+          <t>Starry</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.213</v>
+        <v>0.3052</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0611</v>
+        <v>0.0876</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5419</v>
+        <v>-0.4853</v>
       </c>
       <c r="E28" t="n">
-        <v>0.213</v>
+        <v>0.3052</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.5224</v>
+        <v>0.3905</v>
       </c>
       <c r="G28" t="n">
-        <v>1.7354</v>
+        <v>-0.0853</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.5224</v>
+        <v>0.3905</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.5224</v>
+        <v>0.3905</v>
       </c>
       <c r="J28" t="n">
-        <v>1.7354</v>
+        <v>-0.0853</v>
       </c>
       <c r="K28" t="n">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="L28" t="n">
-        <v>136</v>
+        <v>36</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2130000000000001</v>
+        <v>0.3052</v>
       </c>
       <c r="N28" t="n">
-        <v>209</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29">
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1535</v>
+        <v>0.1493</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0441</v>
+        <v>0.0429</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5687</v>
+        <v>-0.5562</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1535</v>
+        <v>0.1493</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.0824</v>
+        <v>-0.0702</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2359</v>
+        <v>0.2195</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.0824</v>
+        <v>-0.0702</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0824</v>
+        <v>-0.0702</v>
       </c>
       <c r="J29" t="n">
-        <v>0.2359</v>
+        <v>0.2195</v>
       </c>
       <c r="K29" t="n">
         <v>88</v>
@@ -1771,7 +1771,7 @@
         <v>36</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1535</v>
+        <v>0.1493</v>
       </c>
       <c r="N29" t="n">
         <v>124</v>
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.1012</v>
+        <v>0.0737</v>
       </c>
       <c r="C30" t="n">
-        <v>0.029</v>
+        <v>0.0212</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5923</v>
+        <v>-0.5907</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1012</v>
+        <v>0.0737</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2149</v>
+        <v>0.2093</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.1137</v>
+        <v>-0.1356</v>
       </c>
       <c r="H30" t="n">
-        <v>0.2149</v>
+        <v>0.2093</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2149</v>
+        <v>0.2093</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.1137</v>
+        <v>-0.1356</v>
       </c>
       <c r="K30" t="n">
         <v>88</v>
@@ -1817,7 +1817,7 @@
         <v>36</v>
       </c>
       <c r="M30" t="n">
-        <v>0.1012</v>
+        <v>0.07370000000000002</v>
       </c>
       <c r="N30" t="n">
         <v>124</v>
@@ -1826,93 +1826,93 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>b0RUP</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.1282</v>
+        <v>-0.0151</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0368</v>
+        <v>-0.0043</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6959</v>
+        <v>-0.6311</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.1282</v>
+        <v>-0.0151</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2462</v>
+        <v>-0.725</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.3744</v>
+        <v>0.7099</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2462</v>
+        <v>-0.725</v>
       </c>
       <c r="I31" t="n">
-        <v>0.128</v>
+        <v>-0.3915</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.3744</v>
+        <v>0.7099</v>
       </c>
       <c r="K31" t="n">
-        <v>119</v>
+        <v>70</v>
       </c>
       <c r="L31" t="n">
-        <v>135</v>
+        <v>59</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.2464</v>
+        <v>0.3184</v>
       </c>
       <c r="N31" t="n">
-        <v>254</v>
+        <v>129</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>b0RUP</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.2723</v>
+        <v>-0.0849</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.07820000000000001</v>
+        <v>-0.0244</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7609</v>
+        <v>-0.6629</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.2723</v>
+        <v>-0.0849</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.901</v>
+        <v>0.2817</v>
       </c>
       <c r="G32" t="n">
-        <v>0.6287</v>
+        <v>-0.3666</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.901</v>
+        <v>0.2817</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.4685</v>
+        <v>0.1521</v>
       </c>
       <c r="J32" t="n">
-        <v>0.6287</v>
+        <v>-0.3666</v>
       </c>
       <c r="K32" t="n">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="L32" t="n">
-        <v>59</v>
+        <v>135</v>
       </c>
       <c r="M32" t="n">
-        <v>0.1602</v>
+        <v>-0.2145</v>
       </c>
       <c r="N32" t="n">
-        <v>129</v>
+        <v>254</v>
       </c>
     </row>
     <row r="33">
@@ -1922,31 +1922,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.386</v>
+        <v>-0.221</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1108</v>
+        <v>-0.0634</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8123</v>
+        <v>-0.7248</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.386</v>
+        <v>-0.221</v>
       </c>
       <c r="F33" t="n">
-        <v>1.1446</v>
+        <v>1.1407</v>
       </c>
       <c r="G33" t="n">
-        <v>-1.5306</v>
+        <v>-1.3617</v>
       </c>
       <c r="H33" t="n">
-        <v>1.1446</v>
+        <v>1.1407</v>
       </c>
       <c r="I33" t="n">
-        <v>1.1446</v>
+        <v>1.1407</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.5306</v>
+        <v>-1.3617</v>
       </c>
       <c r="K33" t="n">
         <v>81</v>
@@ -1955,7 +1955,7 @@
         <v>155</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.3859999999999999</v>
+        <v>-0.2209999999999999</v>
       </c>
       <c r="N33" t="n">
         <v>236</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.5053</v>
+        <v>-0.5647</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.145</v>
+        <v>-0.1621</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8661</v>
+        <v>-0.8813</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.5053</v>
+        <v>-0.5647</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.5053</v>
+        <v>-0.5647</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.5053</v>
+        <v>-0.5647</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.5053</v>
+        <v>-0.5647</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.5053</v>
+        <v>-0.5647</v>
       </c>
       <c r="N34" t="n">
         <v>53</v>
@@ -2014,31 +2014,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.8294</v>
+        <v>-0.6645</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2381</v>
+        <v>-0.1907</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.0124</v>
+        <v>-0.9267</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.8294</v>
+        <v>-0.6645</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.3687</v>
+        <v>-1.3426</v>
       </c>
       <c r="G35" t="n">
-        <v>0.5393</v>
+        <v>0.6781</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.3687</v>
+        <v>-1.3426</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.3687</v>
+        <v>-1.3426</v>
       </c>
       <c r="J35" t="n">
-        <v>0.5393</v>
+        <v>0.6781</v>
       </c>
       <c r="K35" t="n">
         <v>73</v>
@@ -2047,7 +2047,7 @@
         <v>136</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.8294</v>
+        <v>-0.6645</v>
       </c>
       <c r="N35" t="n">
         <v>209</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.991</v>
+        <v>-1.0431</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2845</v>
+        <v>-0.2994</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0854</v>
+        <v>-1.099</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.991</v>
+        <v>-1.0431</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.991</v>
+        <v>-1.0431</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.991</v>
+        <v>-1.0431</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.991</v>
+        <v>-1.0431</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.991</v>
+        <v>-1.0431</v>
       </c>
       <c r="N36" t="n">
         <v>53</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.0632</v>
+        <v>-1.1147</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3052</v>
+        <v>-0.32</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.118</v>
+        <v>-1.1316</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.0632</v>
+        <v>-1.1147</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.0632</v>
+        <v>-1.1147</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.0632</v>
+        <v>-1.1147</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.0632</v>
+        <v>-1.1147</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.0632</v>
+        <v>-1.1147</v>
       </c>
       <c r="N37" t="n">
         <v>53</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.2124</v>
+        <v>-1.2519</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.348</v>
+        <v>-0.3593</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1854</v>
+        <v>-1.1941</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.2124</v>
+        <v>-1.2519</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.2124</v>
+        <v>-1.2519</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.2124</v>
+        <v>-1.2519</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.2124</v>
+        <v>-1.2519</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.2124</v>
+        <v>-1.2519</v>
       </c>
       <c r="N38" t="n">
         <v>91</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.3966</v>
+        <v>-1.3427</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.4009</v>
+        <v>-0.3854</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2685</v>
+        <v>-1.2354</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.3966</v>
+        <v>-1.3427</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.6375999999999999</v>
+        <v>-0.5759</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.759</v>
+        <v>-0.7668</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.6375999999999999</v>
+        <v>-0.5759</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.6375999999999999</v>
+        <v>-0.5759</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.759</v>
+        <v>-0.7668</v>
       </c>
       <c r="K39" t="n">
         <v>91</v>
@@ -2231,7 +2231,7 @@
         <v>61</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.3966</v>
+        <v>-1.3427</v>
       </c>
       <c r="N39" t="n">
         <v>152</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.4703</v>
+        <v>-1.4992</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.422</v>
+        <v>-0.4303</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3018</v>
+        <v>-1.3067</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.4703</v>
+        <v>-1.4992</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.4703</v>
+        <v>-1.4992</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.4703</v>
+        <v>-1.4992</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.4703</v>
+        <v>-1.4992</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.4703</v>
+        <v>-1.4992</v>
       </c>
       <c r="N40" t="n">
         <v>53</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.7123</v>
+        <v>-2.7051</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.7785</v>
+        <v>-0.7765</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.8625</v>
+        <v>-1.8556</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.7123</v>
+        <v>-2.7051</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.7295</v>
+        <v>-1.7064</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.9828</v>
+        <v>-0.9987</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.7295</v>
+        <v>-1.7064</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.7295</v>
+        <v>-1.7064</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.9828</v>
+        <v>-0.9987</v>
       </c>
       <c r="K41" t="n">
         <v>88</v>
@@ -2323,7 +2323,7 @@
         <v>36</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.7123</v>
+        <v>-2.7051</v>
       </c>
       <c r="N41" t="n">
         <v>124</v>
@@ -2429,10 +2429,10 @@
         <v>1.5</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9774</v>
+        <v>0.9219000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>19.548</v>
+        <v>18.438</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1532</v>
+        <v>0.1579</v>
       </c>
       <c r="J3" t="n">
-        <v>3.064</v>
+        <v>3.158</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.03</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1045</v>
+        <v>0.1091</v>
       </c>
       <c r="J4" t="n">
-        <v>2.09</v>
+        <v>2.182</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.66</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3672</v>
+        <v>-0.3788</v>
       </c>
       <c r="J5" t="n">
-        <v>-7.344</v>
+        <v>-7.576</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.47</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5407</v>
+        <v>-0.5439000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>-10.814</v>
+        <v>-10.878</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.44</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0676</v>
+        <v>1.0312</v>
       </c>
       <c r="J7" t="n">
-        <v>21.352</v>
+        <v>20.624</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.25</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6813</v>
+        <v>0.653</v>
       </c>
       <c r="J8" t="n">
-        <v>13.626</v>
+        <v>13.06</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.16</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4657</v>
+        <v>0.4589</v>
       </c>
       <c r="J9" t="n">
-        <v>9.314</v>
+        <v>9.178000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.08</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2487</v>
+        <v>0.2593</v>
       </c>
       <c r="J10" t="n">
-        <v>4.974</v>
+        <v>5.186</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.99</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.09950000000000001</v>
+        <v>-0.0906</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.99</v>
+        <v>-1.812</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.35</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7066</v>
+        <v>0.6778</v>
       </c>
       <c r="J12" t="n">
-        <v>28.264</v>
+        <v>27.112</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.06</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1635</v>
+        <v>0.1714</v>
       </c>
       <c r="J13" t="n">
-        <v>6.54</v>
+        <v>6.856</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.98</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0354</v>
+        <v>-0.0422</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.416</v>
+        <v>-1.688</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.83</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2077</v>
+        <v>-0.2215</v>
       </c>
       <c r="J15" t="n">
-        <v>-8.308</v>
+        <v>-8.859999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.74</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2971</v>
+        <v>-0.3097</v>
       </c>
       <c r="J16" t="n">
-        <v>-11.884</v>
+        <v>-12.388</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.28</v>
       </c>
       <c r="I17" t="n">
-        <v>0.78</v>
+        <v>0.735</v>
       </c>
       <c r="J17" t="n">
-        <v>31.2</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.27</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7559</v>
+        <v>0.7138</v>
       </c>
       <c r="J18" t="n">
-        <v>30.236</v>
+        <v>28.552</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.12</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3769</v>
+        <v>0.3741</v>
       </c>
       <c r="J19" t="n">
-        <v>15.076</v>
+        <v>14.964</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.97</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1554</v>
+        <v>-0.1529</v>
       </c>
       <c r="J20" t="n">
-        <v>-6.216</v>
+        <v>-6.116</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.85</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5167</v>
+        <v>-0.4886</v>
       </c>
       <c r="J21" t="n">
-        <v>-20.668</v>
+        <v>-19.544</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.66</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6924</v>
+        <v>0.7748</v>
       </c>
       <c r="J22" t="n">
-        <v>14.5404</v>
+        <v>16.2708</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.15</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2719</v>
+        <v>0.2771</v>
       </c>
       <c r="J23" t="n">
-        <v>5.7099</v>
+        <v>5.8191</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.78</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2549</v>
+        <v>-0.2689</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.3529</v>
+        <v>-5.6469</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.75</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2843</v>
+        <v>-0.2978</v>
       </c>
       <c r="J25" t="n">
-        <v>-5.9703</v>
+        <v>-6.2538</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.49</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5251</v>
+        <v>-0.5289</v>
       </c>
       <c r="J26" t="n">
-        <v>-11.0271</v>
+        <v>-11.1069</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.63</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5887</v>
+        <v>0.6741</v>
       </c>
       <c r="J27" t="n">
-        <v>12.3627</v>
+        <v>14.1561</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.29</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3664</v>
+        <v>0.4028</v>
       </c>
       <c r="J28" t="n">
-        <v>7.6944</v>
+        <v>8.4588</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.17</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2462</v>
+        <v>0.2638</v>
       </c>
       <c r="J29" t="n">
-        <v>5.1702</v>
+        <v>5.5398</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.04</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0612</v>
+        <v>0.0765</v>
       </c>
       <c r="J30" t="n">
-        <v>1.2852</v>
+        <v>1.6065</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.82</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2388</v>
+        <v>-0.248</v>
       </c>
       <c r="J31" t="n">
-        <v>-5.0148</v>
+        <v>-5.208</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.75</v>
       </c>
       <c r="I32" t="n">
-        <v>1.2261</v>
+        <v>1.3296</v>
       </c>
       <c r="J32" t="n">
-        <v>36.783</v>
+        <v>39.888</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.02</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0776</v>
+        <v>0.0886</v>
       </c>
       <c r="J33" t="n">
-        <v>2.328</v>
+        <v>2.658</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.91</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3424</v>
+        <v>-0.3309</v>
       </c>
       <c r="J34" t="n">
-        <v>-10.272</v>
+        <v>-9.927</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.87</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4568</v>
+        <v>-0.4355</v>
       </c>
       <c r="J35" t="n">
-        <v>-13.704</v>
+        <v>-13.065</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.85</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5117</v>
+        <v>-0.4851</v>
       </c>
       <c r="J36" t="n">
-        <v>-15.351</v>
+        <v>-14.553</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.44</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6163</v>
+        <v>0.6913</v>
       </c>
       <c r="J37" t="n">
-        <v>18.489</v>
+        <v>20.739</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.3</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4811</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="J38" t="n">
-        <v>14.433</v>
+        <v>16.134</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.01</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0221</v>
+        <v>0.0322</v>
       </c>
       <c r="J39" t="n">
-        <v>0.663</v>
+        <v>0.966</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.99</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.0301</v>
+        <v>-0.0326</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.903</v>
+        <v>-0.978</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.77</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2799</v>
+        <v>-0.2905</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.397</v>
+        <v>-8.715</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.58</v>
       </c>
       <c r="I42" t="n">
-        <v>0.9796</v>
+        <v>1.0746</v>
       </c>
       <c r="J42" t="n">
-        <v>23.5104</v>
+        <v>25.7904</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.39</v>
       </c>
       <c r="I43" t="n">
-        <v>0.7327</v>
+        <v>0.8095</v>
       </c>
       <c r="J43" t="n">
-        <v>17.5848</v>
+        <v>19.428</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.33</v>
       </c>
       <c r="I44" t="n">
-        <v>0.652</v>
+        <v>0.7215</v>
       </c>
       <c r="J44" t="n">
-        <v>15.648</v>
+        <v>17.316</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.93</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.3047</v>
+        <v>-0.2907</v>
       </c>
       <c r="J45" t="n">
-        <v>-7.3128</v>
+        <v>-6.9768</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.59</v>
       </c>
       <c r="I46" t="n">
-        <v>-1.1774</v>
+        <v>-1.0649</v>
       </c>
       <c r="J46" t="n">
-        <v>-28.2576</v>
+        <v>-25.5576</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.49</v>
       </c>
       <c r="I47" t="n">
-        <v>0.6746</v>
+        <v>0.7544</v>
       </c>
       <c r="J47" t="n">
-        <v>16.1904</v>
+        <v>18.1056</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.35</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5394</v>
+        <v>0.6024</v>
       </c>
       <c r="J48" t="n">
-        <v>12.9456</v>
+        <v>14.4576</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.1</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2347</v>
+        <v>0.244</v>
       </c>
       <c r="J49" t="n">
-        <v>5.6328</v>
+        <v>5.856</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.92</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1175</v>
+        <v>-0.1281</v>
       </c>
       <c r="J50" t="n">
-        <v>-2.82</v>
+        <v>-3.0744</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.41</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6027</v>
+        <v>-0.6008</v>
       </c>
       <c r="J51" t="n">
-        <v>-14.4648</v>
+        <v>-14.4192</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.26</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4792</v>
+        <v>0.5269</v>
       </c>
       <c r="J52" t="n">
-        <v>11.0216</v>
+        <v>12.1187</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.16</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3683</v>
+        <v>0.3846</v>
       </c>
       <c r="J53" t="n">
-        <v>8.4709</v>
+        <v>8.845800000000001</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2191</v>
+        <v>-0.2348</v>
       </c>
       <c r="J54" t="n">
-        <v>-5.0393</v>
+        <v>-5.4004</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.72</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3073</v>
+        <v>-0.3214</v>
       </c>
       <c r="J55" t="n">
-        <v>-7.0679</v>
+        <v>-7.3922</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.64</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.383</v>
+        <v>-0.3945</v>
       </c>
       <c r="J56" t="n">
-        <v>-8.808999999999999</v>
+        <v>-9.073499999999999</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>2.04</v>
       </c>
       <c r="I57" t="n">
-        <v>1.5812</v>
+        <v>1.699</v>
       </c>
       <c r="J57" t="n">
-        <v>36.3676</v>
+        <v>39.077</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.19</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4674</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="J58" t="n">
-        <v>10.7502</v>
+        <v>11.8128</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.82</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.5953000000000001</v>
+        <v>-0.5594</v>
       </c>
       <c r="J59" t="n">
-        <v>-13.6919</v>
+        <v>-12.8662</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.76</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.75</v>
+        <v>-0.6965</v>
       </c>
       <c r="J60" t="n">
-        <v>-17.25</v>
+        <v>-16.0195</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.65</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.0198</v>
+        <v>-0.9317</v>
       </c>
       <c r="J61" t="n">
-        <v>-23.4554</v>
+        <v>-21.4291</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>2.28</v>
       </c>
       <c r="I62" t="n">
-        <v>0.9188</v>
+        <v>1.0584</v>
       </c>
       <c r="J62" t="n">
-        <v>14.7008</v>
+        <v>16.9344</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.76</v>
       </c>
       <c r="I63" t="n">
-        <v>0.6301</v>
+        <v>0.729</v>
       </c>
       <c r="J63" t="n">
-        <v>10.0816</v>
+        <v>11.664</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.37</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4005</v>
+        <v>0.4577</v>
       </c>
       <c r="J64" t="n">
-        <v>6.408</v>
+        <v>7.3232</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.16</v>
       </c>
       <c r="I65" t="n">
-        <v>0.1986</v>
+        <v>0.2247</v>
       </c>
       <c r="J65" t="n">
-        <v>3.1776</v>
+        <v>3.5952</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1.01</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.0243</v>
+        <v>-0.0097</v>
       </c>
       <c r="J66" t="n">
-        <v>-0.3888</v>
+        <v>-0.1552</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.06</v>
       </c>
       <c r="I67" t="n">
-        <v>0.243</v>
+        <v>0.2231</v>
       </c>
       <c r="J67" t="n">
-        <v>3.888</v>
+        <v>3.5696</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.76</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.2339</v>
+        <v>-0.2569</v>
       </c>
       <c r="J68" t="n">
-        <v>-3.7424</v>
+        <v>-4.1104</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.72</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.2739</v>
+        <v>-0.2957</v>
       </c>
       <c r="J69" t="n">
-        <v>-4.3824</v>
+        <v>-4.7312</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.5</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4771</v>
+        <v>-0.4896</v>
       </c>
       <c r="J70" t="n">
-        <v>-7.6336</v>
+        <v>-7.8336</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.29</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6746</v>
+        <v>-0.6724</v>
       </c>
       <c r="J71" t="n">
-        <v>-10.7936</v>
+        <v>-10.7584</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.43</v>
       </c>
       <c r="I72" t="n">
-        <v>0.6492</v>
+        <v>0.72</v>
       </c>
       <c r="J72" t="n">
-        <v>12.984</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1</v>
       </c>
       <c r="I73" t="n">
-        <v>0.0109</v>
+        <v>0.0078</v>
       </c>
       <c r="J73" t="n">
-        <v>0.218</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.89</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.1384</v>
+        <v>-0.1529</v>
       </c>
       <c r="J74" t="n">
-        <v>-2.768</v>
+        <v>-3.058</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.85</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.1807</v>
+        <v>-0.1959</v>
       </c>
       <c r="J75" t="n">
-        <v>-3.614</v>
+        <v>-3.918</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.52</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4954</v>
+        <v>-0.5012</v>
       </c>
       <c r="J76" t="n">
-        <v>-9.907999999999999</v>
+        <v>-10.024</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>2.1</v>
       </c>
       <c r="I77" t="n">
-        <v>1.556</v>
+        <v>1.6863</v>
       </c>
       <c r="J77" t="n">
-        <v>31.12</v>
+        <v>33.726</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.78</v>
       </c>
       <c r="I78" t="n">
-        <v>1.1837</v>
+        <v>1.2977</v>
       </c>
       <c r="J78" t="n">
-        <v>23.674</v>
+        <v>25.954</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.11</v>
       </c>
       <c r="I79" t="n">
-        <v>0.3047</v>
+        <v>0.3182</v>
       </c>
       <c r="J79" t="n">
-        <v>6.094</v>
+        <v>6.364</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.0751</v>
+        <v>-0.0521</v>
       </c>
       <c r="J80" t="n">
-        <v>-1.502</v>
+        <v>-1.042</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.2726</v>
+        <v>-1.1426</v>
       </c>
       <c r="J81" t="n">
-        <v>-25.452</v>
+        <v>-22.852</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.67</v>
       </c>
       <c r="I82" t="n">
-        <v>1.0596</v>
+        <v>1.1652</v>
       </c>
       <c r="J82" t="n">
-        <v>22.2516</v>
+        <v>24.4692</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.39</v>
       </c>
       <c r="I83" t="n">
-        <v>0.7106</v>
+        <v>0.7902</v>
       </c>
       <c r="J83" t="n">
-        <v>14.9226</v>
+        <v>16.5942</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.25</v>
       </c>
       <c r="I84" t="n">
-        <v>0.5286999999999999</v>
+        <v>0.5887</v>
       </c>
       <c r="J84" t="n">
-        <v>11.1027</v>
+        <v>12.3627</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.16</v>
       </c>
       <c r="I85" t="n">
-        <v>0.3997</v>
+        <v>0.4413</v>
       </c>
       <c r="J85" t="n">
-        <v>8.393700000000001</v>
+        <v>9.267300000000001</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.93</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3333</v>
+        <v>-0.3107</v>
       </c>
       <c r="J86" t="n">
-        <v>-6.9993</v>
+        <v>-6.5247</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.02</v>
       </c>
       <c r="I87" t="n">
-        <v>0.0953</v>
+        <v>0.0945</v>
       </c>
       <c r="J87" t="n">
-        <v>2.0013</v>
+        <v>1.9845</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.99</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.0072</v>
+        <v>-0.015</v>
       </c>
       <c r="J88" t="n">
-        <v>-0.1512</v>
+        <v>-0.315</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.91</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.112</v>
+        <v>-0.127</v>
       </c>
       <c r="J89" t="n">
-        <v>-2.352</v>
+        <v>-2.667</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.82</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2047</v>
+        <v>-0.2214</v>
       </c>
       <c r="J90" t="n">
-        <v>-4.2987</v>
+        <v>-4.6494</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.67</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3503</v>
+        <v>-0.3639</v>
       </c>
       <c r="J91" t="n">
-        <v>-7.3563</v>
+        <v>-7.6419</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.2</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3604</v>
+        <v>0.3721</v>
       </c>
       <c r="J92" t="n">
-        <v>7.5684</v>
+        <v>7.8141</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.89</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.1316</v>
+        <v>-0.1478</v>
       </c>
       <c r="J93" t="n">
-        <v>-2.7636</v>
+        <v>-3.1038</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.86</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1625</v>
+        <v>-0.1794</v>
       </c>
       <c r="J94" t="n">
-        <v>-3.4125</v>
+        <v>-3.7674</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3287</v>
+        <v>-0.3435</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.9027</v>
+        <v>-7.2135</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.67</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3476</v>
+        <v>-0.3618</v>
       </c>
       <c r="J96" t="n">
-        <v>-7.2996</v>
+        <v>-7.5978</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>2.18</v>
       </c>
       <c r="I97" t="n">
-        <v>0.9046</v>
+        <v>1.0361</v>
       </c>
       <c r="J97" t="n">
-        <v>18.9966</v>
+        <v>21.7581</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.24</v>
       </c>
       <c r="I98" t="n">
-        <v>0.3218</v>
+        <v>0.3413</v>
       </c>
       <c r="J98" t="n">
-        <v>6.7578</v>
+        <v>7.1673</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.04</v>
       </c>
       <c r="I99" t="n">
-        <v>0.0514</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="J99" t="n">
-        <v>1.0794</v>
+        <v>1.4511</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.95</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1029</v>
+        <v>-0.1071</v>
       </c>
       <c r="J100" t="n">
-        <v>-2.1609</v>
+        <v>-2.2491</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.1153</v>
+        <v>-0.1202</v>
       </c>
       <c r="J101" t="n">
-        <v>-2.4213</v>
+        <v>-2.5242</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.81</v>
       </c>
       <c r="I102" t="n">
-        <v>1.2067</v>
+        <v>1.324</v>
       </c>
       <c r="J102" t="n">
-        <v>22.9273</v>
+        <v>25.156</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.51</v>
       </c>
       <c r="I103" t="n">
-        <v>0.8486</v>
+        <v>0.9427</v>
       </c>
       <c r="J103" t="n">
-        <v>16.1234</v>
+        <v>17.9113</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.21</v>
       </c>
       <c r="I104" t="n">
-        <v>0.4634</v>
+        <v>0.5179</v>
       </c>
       <c r="J104" t="n">
-        <v>8.804600000000001</v>
+        <v>9.8401</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.15</v>
       </c>
       <c r="I105" t="n">
-        <v>0.3741</v>
+        <v>0.4089</v>
       </c>
       <c r="J105" t="n">
-        <v>7.1079</v>
+        <v>7.7691</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>1.11</v>
       </c>
       <c r="I106" t="n">
-        <v>0.294</v>
+        <v>0.3107</v>
       </c>
       <c r="J106" t="n">
-        <v>5.586</v>
+        <v>5.9033</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.03</v>
       </c>
       <c r="I107" t="n">
-        <v>0.1905</v>
+        <v>0.1722</v>
       </c>
       <c r="J107" t="n">
-        <v>3.6195</v>
+        <v>3.2718</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.79</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.217</v>
+        <v>-0.2376</v>
       </c>
       <c r="J108" t="n">
-        <v>-4.123</v>
+        <v>-4.5144</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.76</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2464</v>
+        <v>-0.2665</v>
       </c>
       <c r="J109" t="n">
-        <v>-4.6816</v>
+        <v>-5.0635</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.4321</v>
+        <v>-0.4455</v>
       </c>
       <c r="J110" t="n">
-        <v>-8.209899999999999</v>
+        <v>-8.464499999999999</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.53</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4601</v>
+        <v>-0.472</v>
       </c>
       <c r="J111" t="n">
-        <v>-8.741899999999999</v>
+        <v>-8.968</v>
       </c>
     </row>
     <row r="112">
@@ -6869,10 +6869,10 @@
         <v>0.58</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.3963</v>
+        <v>-0.4145</v>
       </c>
       <c r="J113" t="n">
-        <v>-6.3408</v>
+        <v>-6.632</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.57</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.4056</v>
+        <v>-0.4233</v>
       </c>
       <c r="J114" t="n">
-        <v>-6.4896</v>
+        <v>-6.7728</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.57</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.4056</v>
+        <v>-0.4233</v>
       </c>
       <c r="J115" t="n">
-        <v>-6.4896</v>
+        <v>-6.7728</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.34</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6226</v>
+        <v>-0.6253</v>
       </c>
       <c r="J116" t="n">
-        <v>-9.961600000000001</v>
+        <v>-10.0048</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.77</v>
       </c>
       <c r="I117" t="n">
-        <v>1.1354</v>
+        <v>1.253</v>
       </c>
       <c r="J117" t="n">
-        <v>18.1664</v>
+        <v>20.048</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.58</v>
       </c>
       <c r="I118" t="n">
-        <v>0.9156</v>
+        <v>1.0184</v>
       </c>
       <c r="J118" t="n">
-        <v>14.6496</v>
+        <v>16.2944</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.45</v>
       </c>
       <c r="I119" t="n">
-        <v>0.7638</v>
+        <v>0.8532999999999999</v>
       </c>
       <c r="J119" t="n">
-        <v>12.2208</v>
+        <v>13.6528</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.38</v>
       </c>
       <c r="I120" t="n">
-        <v>0.6777</v>
+        <v>0.759</v>
       </c>
       <c r="J120" t="n">
-        <v>10.8432</v>
+        <v>12.144</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1.2</v>
       </c>
       <c r="I121" t="n">
-        <v>0.4342</v>
+        <v>0.4887</v>
       </c>
       <c r="J121" t="n">
-        <v>6.9472</v>
+        <v>7.8192</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.13</v>
       </c>
       <c r="I122" t="n">
-        <v>0.339</v>
+        <v>0.338</v>
       </c>
       <c r="J122" t="n">
-        <v>6.78</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.1</v>
       </c>
       <c r="I123" t="n">
-        <v>0.2826</v>
+        <v>0.2789</v>
       </c>
       <c r="J123" t="n">
-        <v>5.652</v>
+        <v>5.578</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.86</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.1646</v>
+        <v>-0.181</v>
       </c>
       <c r="J124" t="n">
-        <v>-3.292</v>
+        <v>-3.62</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.68</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3414</v>
+        <v>-0.3552</v>
       </c>
       <c r="J125" t="n">
-        <v>-6.828</v>
+        <v>-7.104</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.66</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3602</v>
+        <v>-0.3734</v>
       </c>
       <c r="J126" t="n">
-        <v>-7.204</v>
+        <v>-7.468</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.79</v>
       </c>
       <c r="I127" t="n">
-        <v>1.2166</v>
+        <v>1.3288</v>
       </c>
       <c r="J127" t="n">
-        <v>24.332</v>
+        <v>26.576</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.43</v>
       </c>
       <c r="I128" t="n">
-        <v>0.7694</v>
+        <v>0.8526</v>
       </c>
       <c r="J128" t="n">
-        <v>15.388</v>
+        <v>17.052</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.26</v>
       </c>
       <c r="I129" t="n">
-        <v>0.5455</v>
+        <v>0.6066</v>
       </c>
       <c r="J129" t="n">
-        <v>10.91</v>
+        <v>12.132</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.04</v>
       </c>
       <c r="I130" t="n">
-        <v>0.1099</v>
+        <v>0.1313</v>
       </c>
       <c r="J130" t="n">
-        <v>2.198</v>
+        <v>2.626</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.67</v>
       </c>
       <c r="I131" t="n">
-        <v>-1.0046</v>
+        <v>-0.9133</v>
       </c>
       <c r="J131" t="n">
-        <v>-20.092</v>
+        <v>-18.266</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.58</v>
       </c>
       <c r="I132" t="n">
-        <v>1.1187</v>
+        <v>1.0758</v>
       </c>
       <c r="J132" t="n">
-        <v>21.2553</v>
+        <v>20.4402</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.79</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.2281</v>
+        <v>-0.2461</v>
       </c>
       <c r="J133" t="n">
-        <v>-4.3339</v>
+        <v>-4.6759</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.66</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.3527</v>
+        <v>-0.3674</v>
       </c>
       <c r="J134" t="n">
-        <v>-6.7013</v>
+        <v>-6.9806</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.6</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.4089</v>
+        <v>-0.4212</v>
       </c>
       <c r="J135" t="n">
-        <v>-7.7691</v>
+        <v>-8.002800000000001</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.52</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.4829</v>
+        <v>-0.4913</v>
       </c>
       <c r="J136" t="n">
-        <v>-9.1751</v>
+        <v>-9.3347</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>2.09</v>
       </c>
       <c r="I137" t="n">
-        <v>1.8009</v>
+        <v>1.8061</v>
       </c>
       <c r="J137" t="n">
-        <v>34.2171</v>
+        <v>34.3159</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.7</v>
       </c>
       <c r="I138" t="n">
-        <v>1.3502</v>
+        <v>1.3338</v>
       </c>
       <c r="J138" t="n">
-        <v>25.6538</v>
+        <v>25.3422</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.3</v>
       </c>
       <c r="I139" t="n">
-        <v>0.7632</v>
+        <v>0.7323</v>
       </c>
       <c r="J139" t="n">
-        <v>14.5008</v>
+        <v>13.9137</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.99</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1417</v>
+        <v>-0.1201</v>
       </c>
       <c r="J140" t="n">
-        <v>-2.6923</v>
+        <v>-2.2819</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.73</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.8842</v>
+        <v>-0.8042</v>
       </c>
       <c r="J141" t="n">
-        <v>-16.7998</v>
+        <v>-15.2798</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.09</v>
       </c>
       <c r="I142" t="n">
-        <v>0.3202</v>
+        <v>0.3019</v>
       </c>
       <c r="J142" t="n">
-        <v>6.0838</v>
+        <v>5.7361</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.96</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.0281</v>
+        <v>-0.0453</v>
       </c>
       <c r="J143" t="n">
-        <v>-0.5339</v>
+        <v>-0.8607</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.68</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.3242</v>
+        <v>-0.3418</v>
       </c>
       <c r="J144" t="n">
-        <v>-6.1598</v>
+        <v>-6.4942</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.6</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3994</v>
+        <v>-0.4137</v>
       </c>
       <c r="J145" t="n">
-        <v>-7.5886</v>
+        <v>-7.8603</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.49</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.5017</v>
+        <v>-0.5104</v>
       </c>
       <c r="J146" t="n">
-        <v>-9.532299999999999</v>
+        <v>-9.6976</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.96</v>
       </c>
       <c r="I147" t="n">
-        <v>1.6552</v>
+        <v>1.6542</v>
       </c>
       <c r="J147" t="n">
-        <v>31.4488</v>
+        <v>31.4298</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.57</v>
       </c>
       <c r="I148" t="n">
-        <v>1.1961</v>
+        <v>1.1691</v>
       </c>
       <c r="J148" t="n">
-        <v>22.7259</v>
+        <v>22.2129</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.21</v>
       </c>
       <c r="I149" t="n">
-        <v>0.5545</v>
+        <v>0.5465</v>
       </c>
       <c r="J149" t="n">
-        <v>10.5355</v>
+        <v>10.3835</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.15</v>
       </c>
       <c r="I150" t="n">
-        <v>0.4029</v>
+        <v>0.4099</v>
       </c>
       <c r="J150" t="n">
-        <v>7.6551</v>
+        <v>7.7881</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.88</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4955</v>
+        <v>-0.457</v>
       </c>
       <c r="J151" t="n">
-        <v>-9.4145</v>
+        <v>-8.683</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.33</v>
       </c>
       <c r="I152" t="n">
-        <v>0.4381</v>
+        <v>0.4495</v>
       </c>
       <c r="J152" t="n">
-        <v>10.5144</v>
+        <v>10.788</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.31</v>
       </c>
       <c r="I153" t="n">
-        <v>0.4149</v>
+        <v>0.4274</v>
       </c>
       <c r="J153" t="n">
-        <v>9.957599999999999</v>
+        <v>10.2576</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.18</v>
       </c>
       <c r="I154" t="n">
-        <v>0.2596</v>
+        <v>0.2767</v>
       </c>
       <c r="J154" t="n">
-        <v>6.2304</v>
+        <v>6.6408</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.07</v>
       </c>
       <c r="I155" t="n">
-        <v>0.1115</v>
+        <v>0.128</v>
       </c>
       <c r="J155" t="n">
-        <v>2.676</v>
+        <v>3.072</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.97</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.0673</v>
+        <v>-0.0716</v>
       </c>
       <c r="J156" t="n">
-        <v>-1.6152</v>
+        <v>-1.7184</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.28</v>
       </c>
       <c r="I157" t="n">
-        <v>0.4595</v>
+        <v>0.4536</v>
       </c>
       <c r="J157" t="n">
-        <v>11.028</v>
+        <v>10.8864</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.97</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.0467</v>
+        <v>-0.0557</v>
       </c>
       <c r="J158" t="n">
-        <v>-1.1208</v>
+        <v>-1.3368</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.9</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.1292</v>
+        <v>-0.1431</v>
       </c>
       <c r="J159" t="n">
-        <v>-3.1008</v>
+        <v>-3.4344</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.85</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.1826</v>
+        <v>-0.1973</v>
       </c>
       <c r="J160" t="n">
-        <v>-4.3824</v>
+        <v>-4.7352</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.77</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.2633</v>
+        <v>-0.2775</v>
       </c>
       <c r="J161" t="n">
-        <v>-6.3192</v>
+        <v>-6.66</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.32</v>
       </c>
       <c r="I162" t="n">
-        <v>0.6659</v>
+        <v>0.6392</v>
       </c>
       <c r="J162" t="n">
-        <v>13.9839</v>
+        <v>13.4232</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.14</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3359</v>
+        <v>0.3354</v>
       </c>
       <c r="J163" t="n">
-        <v>7.0539</v>
+        <v>7.0434</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.95</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.0728</v>
+        <v>-0.0837</v>
       </c>
       <c r="J164" t="n">
-        <v>-1.5288</v>
+        <v>-1.7577</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.76</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2745</v>
+        <v>-0.2883</v>
       </c>
       <c r="J165" t="n">
-        <v>-5.7645</v>
+        <v>-6.0543</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.66</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.37</v>
+        <v>-0.381</v>
       </c>
       <c r="J166" t="n">
-        <v>-7.77</v>
+        <v>-8.000999999999999</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.65</v>
       </c>
       <c r="I167" t="n">
-        <v>1.3248</v>
+        <v>1.3007</v>
       </c>
       <c r="J167" t="n">
-        <v>27.8208</v>
+        <v>27.3147</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.18</v>
       </c>
       <c r="I168" t="n">
-        <v>0.5088</v>
+        <v>0.4995</v>
       </c>
       <c r="J168" t="n">
-        <v>10.6848</v>
+        <v>10.4895</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.15</v>
       </c>
       <c r="I169" t="n">
-        <v>0.4328</v>
+        <v>0.4307</v>
       </c>
       <c r="J169" t="n">
-        <v>9.088800000000001</v>
+        <v>9.044700000000001</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.07</v>
       </c>
       <c r="I170" t="n">
-        <v>0.2101</v>
+        <v>0.2253</v>
       </c>
       <c r="J170" t="n">
-        <v>4.4121</v>
+        <v>4.7313</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1.05</v>
       </c>
       <c r="I171" t="n">
-        <v>0.1474</v>
+        <v>0.1661</v>
       </c>
       <c r="J171" t="n">
-        <v>3.0954</v>
+        <v>3.4881</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.17</v>
       </c>
       <c r="I172" t="n">
-        <v>0.4061</v>
+        <v>0.3987</v>
       </c>
       <c r="J172" t="n">
-        <v>8.5281</v>
+        <v>8.3727</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.01</v>
       </c>
       <c r="I173" t="n">
-        <v>0.0513</v>
+        <v>0.0531</v>
       </c>
       <c r="J173" t="n">
-        <v>1.0773</v>
+        <v>1.1151</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.0824</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="J174" t="n">
-        <v>-1.7304</v>
+        <v>-1.9887</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.86</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1696</v>
+        <v>-0.1848</v>
       </c>
       <c r="J175" t="n">
-        <v>-3.5616</v>
+        <v>-3.8808</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.68</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3472</v>
+        <v>-0.3597</v>
       </c>
       <c r="J176" t="n">
-        <v>-7.2912</v>
+        <v>-7.5537</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>2.02</v>
       </c>
       <c r="I177" t="n">
-        <v>1.7693</v>
+        <v>1.7663</v>
       </c>
       <c r="J177" t="n">
-        <v>37.1553</v>
+        <v>37.0923</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.52</v>
       </c>
       <c r="I178" t="n">
-        <v>1.1612</v>
+        <v>1.1265</v>
       </c>
       <c r="J178" t="n">
-        <v>24.3852</v>
+        <v>23.6565</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.93</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.3199</v>
+        <v>-0.3013</v>
       </c>
       <c r="J179" t="n">
-        <v>-6.7179</v>
+        <v>-6.3273</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.86</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.5218</v>
+        <v>-0.4868</v>
       </c>
       <c r="J180" t="n">
-        <v>-10.9578</v>
+        <v>-10.2228</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.79</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.7064</v>
+        <v>-0.6521</v>
       </c>
       <c r="J181" t="n">
-        <v>-14.8344</v>
+        <v>-13.6941</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.1</v>
       </c>
       <c r="I182" t="n">
-        <v>0.3428</v>
+        <v>0.3378</v>
       </c>
       <c r="J182" t="n">
-        <v>18.1684</v>
+        <v>17.9034</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.08</v>
       </c>
       <c r="I183" t="n">
-        <v>0.2845</v>
+        <v>0.2838</v>
       </c>
       <c r="J183" t="n">
-        <v>15.0785</v>
+        <v>15.0414</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.08</v>
       </c>
       <c r="I184" t="n">
-        <v>0.2845</v>
+        <v>0.2838</v>
       </c>
       <c r="J184" t="n">
-        <v>15.0785</v>
+        <v>15.0414</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.99</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.0571</v>
+        <v>-0.0612</v>
       </c>
       <c r="J185" t="n">
-        <v>-3.0263</v>
+        <v>-3.2436</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.84</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.5208</v>
+        <v>-0.4969</v>
       </c>
       <c r="J186" t="n">
-        <v>-27.6024</v>
+        <v>-26.3357</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.5</v>
       </c>
       <c r="I187" t="n">
-        <v>0.9121</v>
+        <v>0.8683999999999999</v>
       </c>
       <c r="J187" t="n">
-        <v>48.3413</v>
+        <v>46.0252</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.19</v>
       </c>
       <c r="I188" t="n">
-        <v>0.3958</v>
+        <v>0.3988</v>
       </c>
       <c r="J188" t="n">
-        <v>20.9774</v>
+        <v>21.1364</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.1</v>
       </c>
       <c r="I189" t="n">
-        <v>0.2289</v>
+        <v>0.2399</v>
       </c>
       <c r="J189" t="n">
-        <v>12.1317</v>
+        <v>12.7147</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.93</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1098</v>
+        <v>-0.1191</v>
       </c>
       <c r="J190" t="n">
-        <v>-5.8194</v>
+        <v>-6.3123</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.74</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3079</v>
+        <v>-0.3182</v>
       </c>
       <c r="J191" t="n">
-        <v>-16.3187</v>
+        <v>-16.8646</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>2.69</v>
       </c>
       <c r="I192" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J192" t="n">
-        <v>27.507</v>
+        <v>29.058</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.64</v>
       </c>
       <c r="I193" t="n">
-        <v>1.2484</v>
+        <v>1.2313</v>
       </c>
       <c r="J193" t="n">
-        <v>18.726</v>
+        <v>18.4695</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.26</v>
       </c>
       <c r="I194" t="n">
-        <v>0.6315</v>
+        <v>0.6233</v>
       </c>
       <c r="J194" t="n">
-        <v>9.4725</v>
+        <v>9.349500000000001</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.15</v>
       </c>
       <c r="I195" t="n">
-        <v>0.3598</v>
+        <v>0.3797</v>
       </c>
       <c r="J195" t="n">
-        <v>5.397</v>
+        <v>5.6955</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1.07</v>
       </c>
       <c r="I196" t="n">
-        <v>0.1363</v>
+        <v>0.1736</v>
       </c>
       <c r="J196" t="n">
-        <v>2.0445</v>
+        <v>2.604</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>0.89</v>
       </c>
       <c r="I197" t="n">
-        <v>-0.0683</v>
+        <v>-0.0982</v>
       </c>
       <c r="J197" t="n">
-        <v>-1.0245</v>
+        <v>-1.473</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.67</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.3111</v>
+        <v>-0.3336</v>
       </c>
       <c r="J198" t="n">
-        <v>-4.6665</v>
+        <v>-5.004</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.53</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.4387</v>
+        <v>-0.4552</v>
       </c>
       <c r="J199" t="n">
-        <v>-6.5805</v>
+        <v>-6.828</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.48</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.4857</v>
+        <v>-0.4992</v>
       </c>
       <c r="J200" t="n">
-        <v>-7.2855</v>
+        <v>-7.488</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.48</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4857</v>
+        <v>-0.4992</v>
       </c>
       <c r="J201" t="n">
-        <v>-7.2855</v>
+        <v>-7.488</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.47</v>
       </c>
       <c r="I202" t="n">
-        <v>0.6022999999999999</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="J202" t="n">
-        <v>13.8529</v>
+        <v>13.8759</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.34</v>
       </c>
       <c r="I203" t="n">
-        <v>0.4543</v>
+        <v>0.464</v>
       </c>
       <c r="J203" t="n">
-        <v>10.4489</v>
+        <v>10.672</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.09</v>
       </c>
       <c r="I204" t="n">
-        <v>0.1441</v>
+        <v>0.1605</v>
       </c>
       <c r="J204" t="n">
-        <v>3.3143</v>
+        <v>3.6915</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.92</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.1272</v>
+        <v>-0.1357</v>
       </c>
       <c r="J205" t="n">
-        <v>-2.9256</v>
+        <v>-3.1211</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.91</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.1387</v>
+        <v>-0.1476</v>
       </c>
       <c r="J206" t="n">
-        <v>-3.1901</v>
+        <v>-3.3948</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.1</v>
       </c>
       <c r="I207" t="n">
-        <v>0.2041</v>
+        <v>0.2093</v>
       </c>
       <c r="J207" t="n">
-        <v>4.6943</v>
+        <v>4.8139</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.1</v>
       </c>
       <c r="I208" t="n">
-        <v>0.2041</v>
+        <v>0.2093</v>
       </c>
       <c r="J208" t="n">
-        <v>4.6943</v>
+        <v>4.8139</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.07</v>
       </c>
       <c r="I209" t="n">
-        <v>0.1547</v>
+        <v>0.1606</v>
       </c>
       <c r="J209" t="n">
-        <v>3.5581</v>
+        <v>3.6938</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2206</v>
+        <v>-0.2359</v>
       </c>
       <c r="J210" t="n">
-        <v>-5.0738</v>
+        <v>-5.4257</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.57</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4491</v>
+        <v>-0.4574</v>
       </c>
       <c r="J211" t="n">
-        <v>-10.3293</v>
+        <v>-10.5202</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.33</v>
       </c>
       <c r="I212" t="n">
-        <v>0.6764</v>
+        <v>0.6499</v>
       </c>
       <c r="J212" t="n">
-        <v>16.2336</v>
+        <v>15.5976</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.09</v>
       </c>
       <c r="I213" t="n">
-        <v>0.2304</v>
+        <v>0.236</v>
       </c>
       <c r="J213" t="n">
-        <v>5.5296</v>
+        <v>5.664</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.03</v>
       </c>
       <c r="I214" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.1024</v>
       </c>
       <c r="J214" t="n">
-        <v>2.2848</v>
+        <v>2.4576</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.78</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.2568</v>
+        <v>-0.2704</v>
       </c>
       <c r="J215" t="n">
-        <v>-6.1632</v>
+        <v>-6.4896</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.68</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3531</v>
+        <v>-0.3644</v>
       </c>
       <c r="J216" t="n">
-        <v>-8.474399999999999</v>
+        <v>-8.7456</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.7</v>
       </c>
       <c r="I217" t="n">
-        <v>1.4218</v>
+        <v>1.3973</v>
       </c>
       <c r="J217" t="n">
-        <v>34.1232</v>
+        <v>33.5352</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.36</v>
       </c>
       <c r="I218" t="n">
-        <v>0.9575</v>
+        <v>0.8943</v>
       </c>
       <c r="J218" t="n">
-        <v>22.98</v>
+        <v>21.4632</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.89</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.4104</v>
+        <v>-0.3912</v>
       </c>
       <c r="J219" t="n">
-        <v>-9.849600000000001</v>
+        <v>-9.3888</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.87</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.4667</v>
+        <v>-0.4424</v>
       </c>
       <c r="J220" t="n">
-        <v>-11.2008</v>
+        <v>-10.6176</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.76</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.7563</v>
+        <v>-0.7009</v>
       </c>
       <c r="J221" t="n">
-        <v>-18.1512</v>
+        <v>-16.8216</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.42</v>
       </c>
       <c r="I222" t="n">
-        <v>0.8365</v>
+        <v>0.7924</v>
       </c>
       <c r="J222" t="n">
-        <v>20.076</v>
+        <v>19.0176</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.1</v>
       </c>
       <c r="I223" t="n">
-        <v>0.2549</v>
+        <v>0.2587</v>
       </c>
       <c r="J223" t="n">
-        <v>6.1176</v>
+        <v>6.2088</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.86</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.1738</v>
+        <v>-0.188</v>
       </c>
       <c r="J224" t="n">
-        <v>-4.1712</v>
+        <v>-4.512</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.8</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2352</v>
+        <v>-0.2495</v>
       </c>
       <c r="J225" t="n">
-        <v>-5.6448</v>
+        <v>-5.988</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.66</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3703</v>
+        <v>-0.3812</v>
       </c>
       <c r="J226" t="n">
-        <v>-8.8872</v>
+        <v>-9.1488</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.22</v>
       </c>
       <c r="I227" t="n">
-        <v>0.6472</v>
+        <v>0.6153</v>
       </c>
       <c r="J227" t="n">
-        <v>15.5328</v>
+        <v>14.7672</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.21</v>
       </c>
       <c r="I228" t="n">
-        <v>0.622</v>
+        <v>0.5929</v>
       </c>
       <c r="J228" t="n">
-        <v>14.928</v>
+        <v>14.2296</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.15</v>
       </c>
       <c r="I229" t="n">
-        <v>0.4668</v>
+        <v>0.4539</v>
       </c>
       <c r="J229" t="n">
-        <v>11.2032</v>
+        <v>10.8936</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.87</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.4511</v>
+        <v>-0.4315</v>
       </c>
       <c r="J230" t="n">
-        <v>-10.8264</v>
+        <v>-10.356</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.85</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.506</v>
+        <v>-0.4812</v>
       </c>
       <c r="J231" t="n">
-        <v>-12.144</v>
+        <v>-11.5488</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>0.89</v>
       </c>
       <c r="I232" t="n">
-        <v>-0.0741</v>
+        <v>-0.1028</v>
       </c>
       <c r="J232" t="n">
-        <v>-1.1115</v>
+        <v>-1.542</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>0.67</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.314</v>
+        <v>-0.3358</v>
       </c>
       <c r="J233" t="n">
-        <v>-4.71</v>
+        <v>-5.037</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.61</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.3679</v>
+        <v>-0.3877</v>
       </c>
       <c r="J234" t="n">
-        <v>-5.5185</v>
+        <v>-5.8155</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.55</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.4227</v>
+        <v>-0.4397</v>
       </c>
       <c r="J235" t="n">
-        <v>-6.3405</v>
+        <v>-6.5955</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.4</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.5642</v>
+        <v>-0.5716</v>
       </c>
       <c r="J236" t="n">
-        <v>-8.462999999999999</v>
+        <v>-8.574</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>2.31</v>
       </c>
       <c r="I237" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J237" t="n">
-        <v>27.507</v>
+        <v>29.058</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.99</v>
       </c>
       <c r="I238" t="n">
-        <v>1.6333</v>
+        <v>1.6402</v>
       </c>
       <c r="J238" t="n">
-        <v>24.4995</v>
+        <v>24.603</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.74</v>
       </c>
       <c r="I239" t="n">
-        <v>1.3574</v>
+        <v>1.3487</v>
       </c>
       <c r="J239" t="n">
-        <v>20.361</v>
+        <v>20.2305</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>1.01</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.077</v>
+        <v>-0.0323</v>
       </c>
       <c r="J240" t="n">
-        <v>-1.155</v>
+        <v>-0.4845</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.91</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.4541</v>
+        <v>-0.4095</v>
       </c>
       <c r="J241" t="n">
-        <v>-6.8115</v>
+        <v>-6.1425</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.96</v>
       </c>
       <c r="I242" t="n">
-        <v>1.0716</v>
+        <v>1.0589</v>
       </c>
       <c r="J242" t="n">
-        <v>24.6468</v>
+        <v>24.3547</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.32</v>
       </c>
       <c r="I243" t="n">
-        <v>0.4285</v>
+        <v>0.44</v>
       </c>
       <c r="J243" t="n">
-        <v>9.855499999999999</v>
+        <v>10.12</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.15</v>
       </c>
       <c r="I244" t="n">
-        <v>0.2236</v>
+        <v>0.2407</v>
       </c>
       <c r="J244" t="n">
-        <v>5.1428</v>
+        <v>5.5361</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.75</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.3049</v>
+        <v>-0.314</v>
       </c>
       <c r="J245" t="n">
-        <v>-7.0127</v>
+        <v>-7.222</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.62</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.4258</v>
+        <v>-0.4314</v>
       </c>
       <c r="J246" t="n">
-        <v>-9.7934</v>
+        <v>-9.9222</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.15</v>
       </c>
       <c r="I247" t="n">
-        <v>0.2943</v>
+        <v>0.2939</v>
       </c>
       <c r="J247" t="n">
-        <v>6.7689</v>
+        <v>6.7597</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.98</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.0243</v>
+        <v>-0.0338</v>
       </c>
       <c r="J248" t="n">
-        <v>-0.5589</v>
+        <v>-0.7774</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.97</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.0388</v>
+        <v>-0.0496</v>
       </c>
       <c r="J249" t="n">
-        <v>-0.8924</v>
+        <v>-1.1408</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2154</v>
+        <v>-0.2319</v>
       </c>
       <c r="J250" t="n">
-        <v>-4.9542</v>
+        <v>-5.3337</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.53</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.4808</v>
+        <v>-0.4883</v>
       </c>
       <c r="J251" t="n">
-        <v>-11.0584</v>
+        <v>-11.2309</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>0.93</v>
       </c>
       <c r="I252" t="n">
-        <v>0.0179</v>
+        <v>-0.0254</v>
       </c>
       <c r="J252" t="n">
-        <v>0.2685</v>
+        <v>-0.381</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>0.59</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.3766</v>
+        <v>-0.3978</v>
       </c>
       <c r="J253" t="n">
-        <v>-5.649</v>
+        <v>-5.967</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.5</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.457</v>
+        <v>-0.4739</v>
       </c>
       <c r="J254" t="n">
-        <v>-6.855</v>
+        <v>-7.1085</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.43</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.5234</v>
+        <v>-0.5356</v>
       </c>
       <c r="J255" t="n">
-        <v>-7.851</v>
+        <v>-8.034000000000001</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.35</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.6008</v>
+        <v>-0.6068</v>
       </c>
       <c r="J256" t="n">
-        <v>-9.012</v>
+        <v>-9.102</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.96</v>
       </c>
       <c r="I257" t="n">
-        <v>1.6076</v>
+        <v>1.612</v>
       </c>
       <c r="J257" t="n">
-        <v>24.114</v>
+        <v>24.18</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.65</v>
       </c>
       <c r="I258" t="n">
-        <v>1.2606</v>
+        <v>1.2443</v>
       </c>
       <c r="J258" t="n">
-        <v>18.909</v>
+        <v>18.6645</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.53</v>
       </c>
       <c r="I259" t="n">
-        <v>1.1249</v>
+        <v>1.0975</v>
       </c>
       <c r="J259" t="n">
-        <v>16.8735</v>
+        <v>16.4625</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>1.39</v>
       </c>
       <c r="I260" t="n">
-        <v>0.9235</v>
+        <v>0.8806</v>
       </c>
       <c r="J260" t="n">
-        <v>13.8525</v>
+        <v>13.209</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>1.24</v>
       </c>
       <c r="I261" t="n">
-        <v>0.5857</v>
+        <v>0.5823</v>
       </c>
       <c r="J261" t="n">
-        <v>8.785500000000001</v>
+        <v>8.734500000000001</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>2.72</v>
       </c>
       <c r="I262" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J262" t="n">
-        <v>31.1746</v>
+        <v>32.9324</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.43</v>
       </c>
       <c r="I263" t="n">
-        <v>1.0136</v>
+        <v>0.9668</v>
       </c>
       <c r="J263" t="n">
-        <v>17.2312</v>
+        <v>16.4356</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.3</v>
       </c>
       <c r="I264" t="n">
-        <v>0.7544</v>
+        <v>0.7262</v>
       </c>
       <c r="J264" t="n">
-        <v>12.8248</v>
+        <v>12.3454</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.86</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.5613</v>
+        <v>-0.5147</v>
       </c>
       <c r="J265" t="n">
-        <v>-9.5421</v>
+        <v>-8.7499</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.73</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.8923</v>
+        <v>-0.8099</v>
       </c>
       <c r="J266" t="n">
-        <v>-15.1691</v>
+        <v>-13.7683</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>0.95</v>
       </c>
       <c r="I267" t="n">
-        <v>-0.0456</v>
+        <v>-0.06270000000000001</v>
       </c>
       <c r="J267" t="n">
-        <v>-0.7752</v>
+        <v>-1.0659</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.86</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.1522</v>
+        <v>-0.1715</v>
       </c>
       <c r="J268" t="n">
-        <v>-2.5874</v>
+        <v>-2.9155</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.8</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.2137</v>
+        <v>-0.2329</v>
       </c>
       <c r="J269" t="n">
-        <v>-3.6329</v>
+        <v>-3.9593</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.7</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3077</v>
+        <v>-0.3254</v>
       </c>
       <c r="J270" t="n">
-        <v>-5.2309</v>
+        <v>-5.5318</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.59</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.4111</v>
+        <v>-0.4245</v>
       </c>
       <c r="J271" t="n">
-        <v>-6.9887</v>
+        <v>-7.2165</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>2.12</v>
       </c>
       <c r="I272" t="n">
-        <v>1.8338</v>
+        <v>1.8598</v>
       </c>
       <c r="J272" t="n">
-        <v>36.676</v>
+        <v>37.196</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.43</v>
       </c>
       <c r="I273" t="n">
-        <v>1.0295</v>
+        <v>0.981</v>
       </c>
       <c r="J273" t="n">
-        <v>20.59</v>
+        <v>19.62</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.33</v>
       </c>
       <c r="I274" t="n">
-        <v>0.8376</v>
+        <v>0.7962</v>
       </c>
       <c r="J274" t="n">
-        <v>16.752</v>
+        <v>15.924</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.92</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.3687</v>
+        <v>-0.3426</v>
       </c>
       <c r="J275" t="n">
-        <v>-7.374</v>
+        <v>-6.852</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.71</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.9214</v>
+        <v>-0.8387</v>
       </c>
       <c r="J276" t="n">
-        <v>-18.428</v>
+        <v>-16.774</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>2.12</v>
       </c>
       <c r="I277" t="n">
-        <v>1.5673</v>
+        <v>1.5693</v>
       </c>
       <c r="J277" t="n">
-        <v>31.346</v>
+        <v>31.386</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>0.78</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.2532</v>
+        <v>-0.2676</v>
       </c>
       <c r="J278" t="n">
-        <v>-5.064</v>
+        <v>-5.352</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.73</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.302</v>
+        <v>-0.3154</v>
       </c>
       <c r="J279" t="n">
-        <v>-6.04</v>
+        <v>-6.308</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.61</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.4149</v>
+        <v>-0.4243</v>
       </c>
       <c r="J280" t="n">
-        <v>-8.298</v>
+        <v>-8.486000000000001</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.52</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.4969</v>
+        <v>-0.5023</v>
       </c>
       <c r="J281" t="n">
-        <v>-9.938000000000001</v>
+        <v>-10.046</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/7365/event_7365_evp_summary.xlsx
+++ b/database/event/7365/event_7365_evp_summary.xlsx
@@ -496,16 +496,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.5962</v>
+        <v>6.8186</v>
       </c>
       <c r="C2" t="n">
-        <v>1.8933</v>
+        <v>1.9572</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3785</v>
+        <v>2.4319</v>
       </c>
       <c r="E2" t="n">
-        <v>6.5962</v>
+        <v>6.8186</v>
       </c>
       <c r="F2" t="n">
         <v>3.649</v>
@@ -542,16 +542,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.2481</v>
+        <v>6.5749</v>
       </c>
       <c r="C3" t="n">
-        <v>1.7934</v>
+        <v>1.8872</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2201</v>
+        <v>2.323</v>
       </c>
       <c r="E3" t="n">
-        <v>6.2481</v>
+        <v>6.5749</v>
       </c>
       <c r="F3" t="n">
         <v>0.0573</v>
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.0505</v>
+        <v>5.2142</v>
       </c>
       <c r="C4" t="n">
-        <v>1.4497</v>
+        <v>1.4966</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6749</v>
+        <v>1.7152</v>
       </c>
       <c r="E4" t="n">
-        <v>5.0505</v>
+        <v>5.2142</v>
       </c>
       <c r="F4" t="n">
         <v>1.315</v>
@@ -634,16 +634,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.7975</v>
+        <v>4.9363</v>
       </c>
       <c r="C5" t="n">
-        <v>1.377</v>
+        <v>1.4169</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5597</v>
+        <v>1.5911</v>
       </c>
       <c r="E5" t="n">
-        <v>4.7975</v>
+        <v>4.9363</v>
       </c>
       <c r="F5" t="n">
         <v>3.5338</v>
@@ -680,16 +680,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.1271</v>
+        <v>4.4217</v>
       </c>
       <c r="C6" t="n">
-        <v>1.1846</v>
+        <v>1.2692</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2545</v>
+        <v>1.3613</v>
       </c>
       <c r="E6" t="n">
-        <v>4.1271</v>
+        <v>4.4217</v>
       </c>
       <c r="F6" t="n">
         <v>4.1437</v>
@@ -726,16 +726,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.1116</v>
+        <v>4.1588</v>
       </c>
       <c r="C7" t="n">
-        <v>1.1802</v>
+        <v>1.1937</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2475</v>
+        <v>1.2438</v>
       </c>
       <c r="E7" t="n">
-        <v>4.1116</v>
+        <v>4.1588</v>
       </c>
       <c r="F7" t="n">
         <v>1.6743</v>
@@ -772,16 +772,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.4638</v>
+        <v>3.6016</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9942</v>
+        <v>1.0338</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9526</v>
+        <v>0.9949</v>
       </c>
       <c r="E8" t="n">
-        <v>3.4638</v>
+        <v>3.6016</v>
       </c>
       <c r="F8" t="n">
         <v>2.5708</v>
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.034</v>
+        <v>3.1475</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8709</v>
+        <v>0.9034</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7569</v>
+        <v>0.7921</v>
       </c>
       <c r="E9" t="n">
-        <v>3.034</v>
+        <v>3.1475</v>
       </c>
       <c r="F9" t="n">
         <v>2.8713</v>
@@ -864,16 +864,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.4615</v>
+        <v>2.491</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7065</v>
+        <v>0.715</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4963</v>
+        <v>0.4989</v>
       </c>
       <c r="E10" t="n">
-        <v>2.4615</v>
+        <v>2.491</v>
       </c>
       <c r="F10" t="n">
         <v>0.5719</v>
@@ -910,16 +910,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.3612</v>
+        <v>2.423</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6777</v>
+        <v>0.6955</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4507</v>
+        <v>0.4685</v>
       </c>
       <c r="E11" t="n">
-        <v>2.3612</v>
+        <v>2.423</v>
       </c>
       <c r="F11" t="n">
         <v>1.2167</v>
@@ -956,16 +956,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.3486</v>
+        <v>2.1942</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6741</v>
+        <v>0.6298</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4449</v>
+        <v>0.3663</v>
       </c>
       <c r="E12" t="n">
-        <v>2.3486</v>
+        <v>2.1942</v>
       </c>
       <c r="F12" t="n">
         <v>2.1696</v>
@@ -1002,16 +1002,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.9503</v>
+        <v>2.0482</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5598</v>
+        <v>0.5879</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2636</v>
+        <v>0.3011</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9503</v>
+        <v>2.0482</v>
       </c>
       <c r="F13" t="n">
         <v>2.0969</v>
@@ -1048,16 +1048,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.751</v>
+        <v>1.7193</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5026</v>
+        <v>0.4935</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1729</v>
+        <v>0.1542</v>
       </c>
       <c r="E14" t="n">
-        <v>1.751</v>
+        <v>1.7193</v>
       </c>
       <c r="F14" t="n">
         <v>2.1447</v>
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.6288</v>
+        <v>1.629</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4675</v>
+        <v>0.4676</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1173</v>
+        <v>0.1138</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6288</v>
+        <v>1.629</v>
       </c>
       <c r="F15" t="n">
         <v>-0.3983</v>
@@ -1136,139 +1136,139 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>Moseyuh</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.3869</v>
+        <v>1.4547</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3981</v>
+        <v>0.4175</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0071</v>
+        <v>0.036</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3869</v>
+        <v>1.4547</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1082</v>
+        <v>1.3817</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2787</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1082</v>
+        <v>1.3817</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5984</v>
+        <v>1.3817</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2787</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="L16" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8771</v>
+        <v>1.3817</v>
       </c>
       <c r="N16" t="n">
-        <v>254</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Moseyuh</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.3817</v>
+        <v>1.3234</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3966</v>
+        <v>0.3799</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0048</v>
+        <v>-0.0227</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3817</v>
+        <v>1.3234</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3817</v>
+        <v>1.1082</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.2787</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3817</v>
+        <v>1.1082</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3817</v>
+        <v>0.5984</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.2787</v>
       </c>
       <c r="K17" t="n">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="M17" t="n">
-        <v>1.3817</v>
+        <v>0.8771</v>
       </c>
       <c r="N17" t="n">
-        <v>91</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>ChildKing</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.3078</v>
+        <v>1.3202</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3754</v>
+        <v>0.3789</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0289</v>
+        <v>-0.0241</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3078</v>
+        <v>1.3202</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5074</v>
+        <v>0.8784999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8004</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5074</v>
+        <v>0.8784999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5074</v>
+        <v>0.8784999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8004</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="L18" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.3078</v>
+        <v>0.8784999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>209</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19">
@@ -1278,16 +1278,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.1933</v>
+        <v>1.3173</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3425</v>
+        <v>0.3781</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.081</v>
+        <v>-0.0254</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1933</v>
+        <v>1.3173</v>
       </c>
       <c r="F19" t="n">
         <v>1.774</v>
@@ -1320,93 +1320,93 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.0818</v>
+        <v>1.2845</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3105</v>
+        <v>0.3687</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1317</v>
+        <v>-0.0401</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0818</v>
+        <v>1.2845</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1437</v>
+        <v>0.5074</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0619</v>
+        <v>0.8004</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1437</v>
+        <v>0.5074</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1437</v>
+        <v>0.5074</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0619</v>
+        <v>0.8004</v>
       </c>
       <c r="K20" t="n">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="L20" t="n">
-        <v>61</v>
+        <v>136</v>
       </c>
       <c r="M20" t="n">
-        <v>1.0818</v>
+        <v>1.3078</v>
       </c>
       <c r="N20" t="n">
-        <v>152</v>
+        <v>209</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ChildKing</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8784999999999999</v>
+        <v>1.2217</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2522</v>
+        <v>0.3507</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2243</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8784999999999999</v>
+        <v>1.2217</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8784999999999999</v>
+        <v>1.1437</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-0.0619</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8784999999999999</v>
+        <v>1.1437</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8784999999999999</v>
+        <v>1.1437</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-0.0619</v>
       </c>
       <c r="K21" t="n">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8784999999999999</v>
+        <v>1.0818</v>
       </c>
       <c r="N21" t="n">
-        <v>53</v>
+        <v>152</v>
       </c>
     </row>
     <row r="22">
@@ -1416,16 +1416,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7537</v>
+        <v>0.9689</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2163</v>
+        <v>0.2781</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2811</v>
+        <v>-0.181</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7537</v>
+        <v>0.9689</v>
       </c>
       <c r="F22" t="n">
         <v>0.7537</v>
@@ -1458,296 +1458,296 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>Jee</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7039</v>
+        <v>0.6894</v>
       </c>
       <c r="C23" t="n">
-        <v>0.202</v>
+        <v>0.1979</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3038</v>
+        <v>-0.3059</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7039</v>
+        <v>0.6894</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3548</v>
+        <v>1.3522</v>
       </c>
       <c r="G23" t="n">
-        <v>1.0587</v>
+        <v>-0.7785</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.3548</v>
+        <v>1.3522</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1916</v>
+        <v>1.3522</v>
       </c>
       <c r="J23" t="n">
-        <v>1.0587</v>
+        <v>-0.7785</v>
       </c>
       <c r="K23" t="n">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="L23" t="n">
-        <v>135</v>
+        <v>36</v>
       </c>
       <c r="M23" t="n">
-        <v>0.8671</v>
+        <v>0.5737000000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>254</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Jee</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5737</v>
+        <v>0.6271</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1647</v>
+        <v>0.18</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.363</v>
+        <v>-0.3337</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5737</v>
+        <v>0.6271</v>
       </c>
       <c r="F24" t="n">
-        <v>1.3522</v>
+        <v>-0.3548</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.7785</v>
+        <v>1.0587</v>
       </c>
       <c r="H24" t="n">
-        <v>1.3522</v>
+        <v>-0.3548</v>
       </c>
       <c r="I24" t="n">
-        <v>1.3522</v>
+        <v>-0.1916</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.7785</v>
+        <v>1.0587</v>
       </c>
       <c r="K24" t="n">
-        <v>88</v>
+        <v>119</v>
       </c>
       <c r="L24" t="n">
-        <v>36</v>
+        <v>135</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5737000000000001</v>
+        <v>0.8671</v>
       </c>
       <c r="N24" t="n">
-        <v>124</v>
+        <v>254</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>VLDN</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.454</v>
+        <v>0.4499</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1303</v>
+        <v>0.1291</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4175</v>
+        <v>-0.4129</v>
       </c>
       <c r="E25" t="n">
-        <v>0.454</v>
+        <v>0.4499</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.5139</v>
+        <v>0.3837</v>
       </c>
       <c r="G25" t="n">
-        <v>1.9679</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.5139</v>
+        <v>0.3837</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.5139</v>
+        <v>0.3837</v>
       </c>
       <c r="J25" t="n">
-        <v>1.9679</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="L25" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.454</v>
+        <v>0.3837</v>
       </c>
       <c r="N25" t="n">
-        <v>209</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>VLDN</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.3837</v>
+        <v>0.4452</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1101</v>
+        <v>0.1278</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4495</v>
+        <v>-0.415</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3837</v>
+        <v>0.4452</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3837</v>
+        <v>-1.5139</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1.9679</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3837</v>
+        <v>-1.5139</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3837</v>
+        <v>-1.5139</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1.9679</v>
       </c>
       <c r="K26" t="n">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3837</v>
+        <v>0.454</v>
       </c>
       <c r="N26" t="n">
-        <v>91</v>
+        <v>209</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>kaze</t>
+          <t>Starry</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.3229</v>
+        <v>0.4155</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0927</v>
+        <v>0.1193</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4772</v>
+        <v>-0.4282</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3229</v>
+        <v>0.4155</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3229</v>
+        <v>0.3905</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-0.0853</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3229</v>
+        <v>0.3905</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3229</v>
+        <v>0.3905</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-0.0853</v>
       </c>
       <c r="K27" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M27" t="n">
-        <v>0.3229</v>
+        <v>0.3052</v>
       </c>
       <c r="N27" t="n">
-        <v>91</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Starry</t>
+          <t>kaze</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.3052</v>
+        <v>0.2599</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0876</v>
+        <v>0.0746</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4853</v>
+        <v>-0.4977</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3052</v>
+        <v>0.2599</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3905</v>
+        <v>0.3229</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.0853</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3905</v>
+        <v>0.3229</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3905</v>
+        <v>0.3229</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.0853</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="L28" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.3052</v>
+        <v>0.3229</v>
       </c>
       <c r="N28" t="n">
-        <v>124</v>
+        <v>91</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1493</v>
+        <v>0.1939</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0429</v>
+        <v>0.0557</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5562</v>
+        <v>-0.5272</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1493</v>
+        <v>0.1939</v>
       </c>
       <c r="F29" t="n">
         <v>-0.0702</v>
@@ -1780,231 +1780,231 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Westmelon</t>
+          <t>b0RUP</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0737</v>
+        <v>-0.1383</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0212</v>
+        <v>-0.0397</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5907</v>
+        <v>-0.6756</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0737</v>
+        <v>-0.1383</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2093</v>
+        <v>-0.725</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.1356</v>
+        <v>0.7099</v>
       </c>
       <c r="H30" t="n">
-        <v>0.2093</v>
+        <v>-0.725</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2093</v>
+        <v>-0.3915</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.1356</v>
+        <v>0.7099</v>
       </c>
       <c r="K30" t="n">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="L30" t="n">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="M30" t="n">
-        <v>0.07370000000000002</v>
+        <v>0.3184</v>
       </c>
       <c r="N30" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>b0RUP</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0151</v>
+        <v>-0.1716</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0043</v>
+        <v>-0.0493</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6311</v>
+        <v>-0.6905</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.0151</v>
+        <v>-0.1716</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.725</v>
+        <v>0.2817</v>
       </c>
       <c r="G31" t="n">
-        <v>0.7099</v>
+        <v>-0.3666</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.725</v>
+        <v>0.2817</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3915</v>
+        <v>0.1521</v>
       </c>
       <c r="J31" t="n">
-        <v>0.7099</v>
+        <v>-0.3666</v>
       </c>
       <c r="K31" t="n">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="L31" t="n">
-        <v>59</v>
+        <v>135</v>
       </c>
       <c r="M31" t="n">
-        <v>0.3184</v>
+        <v>-0.2145</v>
       </c>
       <c r="N31" t="n">
-        <v>129</v>
+        <v>254</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>Westmelon</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.0849</v>
+        <v>-0.193</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0244</v>
+        <v>-0.0554</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6629</v>
+        <v>-0.7</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.0849</v>
+        <v>-0.193</v>
       </c>
       <c r="F32" t="n">
-        <v>0.2817</v>
+        <v>0.2093</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.3666</v>
+        <v>-0.1356</v>
       </c>
       <c r="H32" t="n">
-        <v>0.2817</v>
+        <v>0.2093</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1521</v>
+        <v>0.2093</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.3666</v>
+        <v>-0.1356</v>
       </c>
       <c r="K32" t="n">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="L32" t="n">
-        <v>135</v>
+        <v>36</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.2145</v>
+        <v>0.07370000000000002</v>
       </c>
       <c r="N32" t="n">
-        <v>254</v>
+        <v>124</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.221</v>
+        <v>-0.265</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0634</v>
+        <v>-0.0761</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7248</v>
+        <v>-0.7322</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.221</v>
+        <v>-0.265</v>
       </c>
       <c r="F33" t="n">
-        <v>1.1407</v>
+        <v>-0.5647</v>
       </c>
       <c r="G33" t="n">
-        <v>-1.3617</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.1407</v>
+        <v>-0.5647</v>
       </c>
       <c r="I33" t="n">
-        <v>1.1407</v>
+        <v>-0.5647</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.3617</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="L33" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.2209999999999999</v>
+        <v>-0.5647</v>
       </c>
       <c r="N33" t="n">
-        <v>236</v>
+        <v>53</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.5647</v>
+        <v>-0.4084</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1621</v>
+        <v>-0.1172</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8813</v>
+        <v>-0.7962</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.5647</v>
+        <v>-0.4084</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.5647</v>
+        <v>1.1407</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-1.3617</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.5647</v>
+        <v>1.1407</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.5647</v>
+        <v>1.1407</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>-1.3617</v>
       </c>
       <c r="K34" t="n">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.5647</v>
+        <v>-0.2209999999999999</v>
       </c>
       <c r="N34" t="n">
-        <v>53</v>
+        <v>236</v>
       </c>
     </row>
     <row r="35">
@@ -2014,16 +2014,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.6645</v>
+        <v>-0.8359</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1907</v>
+        <v>-0.2399</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9267</v>
+        <v>-0.9872</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.6645</v>
+        <v>-0.8359</v>
       </c>
       <c r="F35" t="n">
         <v>-1.3426</v>
@@ -2060,16 +2060,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.0431</v>
+        <v>-1.3384</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2994</v>
+        <v>-0.3842</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.099</v>
+        <v>-1.2117</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.0431</v>
+        <v>-1.3384</v>
       </c>
       <c r="F36" t="n">
         <v>-1.0431</v>
@@ -2106,16 +2106,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.1147</v>
+        <v>-1.5758</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.32</v>
+        <v>-0.4523</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1316</v>
+        <v>-1.3177</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.1147</v>
+        <v>-1.5758</v>
       </c>
       <c r="F37" t="n">
         <v>-1.1147</v>
@@ -2148,93 +2148,93 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>advent</t>
+          <t>es3tag</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.2519</v>
+        <v>-1.628</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3593</v>
+        <v>-0.4673</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1941</v>
+        <v>-1.341</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.2519</v>
+        <v>-1.628</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.2519</v>
+        <v>-0.5759</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>-0.7668</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.2519</v>
+        <v>-0.5759</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.2519</v>
+        <v>-0.5759</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>-0.7668</v>
       </c>
       <c r="K38" t="n">
         <v>91</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.2519</v>
+        <v>-1.3427</v>
       </c>
       <c r="N38" t="n">
-        <v>91</v>
+        <v>152</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>es3tag</t>
+          <t>advent</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.3427</v>
+        <v>-1.6329</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3854</v>
+        <v>-0.4687</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2354</v>
+        <v>-1.3432</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.3427</v>
+        <v>-1.6329</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.5759</v>
+        <v>-1.2519</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.7668</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.5759</v>
+        <v>-1.2519</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.5759</v>
+        <v>-1.2519</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.7668</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
         <v>91</v>
       </c>
       <c r="L39" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.3427</v>
+        <v>-1.2519</v>
       </c>
       <c r="N39" t="n">
-        <v>152</v>
+        <v>91</v>
       </c>
     </row>
     <row r="40">
@@ -2244,16 +2244,16 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.4992</v>
+        <v>-1.7583</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.4303</v>
+        <v>-0.5047</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3067</v>
+        <v>-1.3992</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.4992</v>
+        <v>-1.7583</v>
       </c>
       <c r="F40" t="n">
         <v>-1.4992</v>
@@ -2290,16 +2290,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.7051</v>
+        <v>-3.0312</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.7765</v>
+        <v>-0.8701</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.8556</v>
+        <v>-1.9678</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.7051</v>
+        <v>-3.0312</v>
       </c>
       <c r="F41" t="n">
         <v>-1.7064</v>
@@ -6798,7 +6798,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7278,7 +7278,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10598,7 +10598,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -11158,7 +11158,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -11438,7 +11438,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -13038,7 +13038,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">

--- a/database/event/7365/event_7365_evp_summary.xlsx
+++ b/database/event/7365/event_7365_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.8186</v>
+        <v>6.691</v>
       </c>
       <c r="C2" t="n">
-        <v>1.9572</v>
+        <v>1.9205</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4319</v>
+        <v>2.4423</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8186</v>
+        <v>6.691</v>
       </c>
       <c r="F2" t="n">
-        <v>3.649</v>
+        <v>3.5693</v>
       </c>
       <c r="G2" t="n">
-        <v>2.9472</v>
+        <v>2.8993</v>
       </c>
       <c r="H2" t="n">
-        <v>7.1453</v>
+        <v>6.9581</v>
       </c>
       <c r="I2" t="n">
-        <v>3.8584</v>
+        <v>3.9068</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9472</v>
+        <v>2.8993</v>
       </c>
       <c r="K2" t="n">
         <v>119</v>
@@ -529,7 +529,7 @@
         <v>135</v>
       </c>
       <c r="M2" t="n">
-        <v>6.8056</v>
+        <v>6.806100000000001</v>
       </c>
       <c r="N2" t="n">
         <v>254</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.5749</v>
+        <v>6.5235</v>
       </c>
       <c r="C3" t="n">
-        <v>1.8872</v>
+        <v>1.8725</v>
       </c>
       <c r="D3" t="n">
-        <v>2.323</v>
+        <v>2.366</v>
       </c>
       <c r="E3" t="n">
-        <v>6.5749</v>
+        <v>6.5235</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0573</v>
+        <v>-0.01</v>
       </c>
       <c r="G3" t="n">
-        <v>6.1908</v>
+        <v>6.2067</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0573</v>
+        <v>-0.01</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0573</v>
+        <v>-0.01</v>
       </c>
       <c r="J3" t="n">
-        <v>6.4484</v>
+        <v>6.3957</v>
       </c>
       <c r="K3" t="n">
         <v>81</v>
@@ -575,7 +575,7 @@
         <v>155</v>
       </c>
       <c r="M3" t="n">
-        <v>6.5057</v>
+        <v>6.3857</v>
       </c>
       <c r="N3" t="n">
         <v>236</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.2142</v>
+        <v>5.1159</v>
       </c>
       <c r="C4" t="n">
-        <v>1.4966</v>
+        <v>1.4684</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7152</v>
+        <v>1.7247</v>
       </c>
       <c r="E4" t="n">
-        <v>5.2142</v>
+        <v>5.1159</v>
       </c>
       <c r="F4" t="n">
-        <v>1.315</v>
+        <v>1.3556</v>
       </c>
       <c r="G4" t="n">
-        <v>3.7355</v>
+        <v>3.5966</v>
       </c>
       <c r="H4" t="n">
-        <v>1.315</v>
+        <v>1.3556</v>
       </c>
       <c r="I4" t="n">
-        <v>1.315</v>
+        <v>1.3556</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7355</v>
+        <v>3.5966</v>
       </c>
       <c r="K4" t="n">
         <v>73</v>
@@ -621,7 +621,7 @@
         <v>136</v>
       </c>
       <c r="M4" t="n">
-        <v>5.0505</v>
+        <v>4.952199999999999</v>
       </c>
       <c r="N4" t="n">
         <v>209</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.9363</v>
+        <v>4.8001</v>
       </c>
       <c r="C5" t="n">
-        <v>1.4169</v>
+        <v>1.3778</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5911</v>
+        <v>1.5809</v>
       </c>
       <c r="E5" t="n">
-        <v>4.9363</v>
+        <v>4.8001</v>
       </c>
       <c r="F5" t="n">
-        <v>3.5338</v>
+        <v>3.4749</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2637</v>
+        <v>1.1864</v>
       </c>
       <c r="H5" t="n">
-        <v>6.7651</v>
+        <v>6.6038</v>
       </c>
       <c r="I5" t="n">
-        <v>3.6531</v>
+        <v>3.7078</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2637</v>
+        <v>1.1864</v>
       </c>
       <c r="K5" t="n">
         <v>70</v>
@@ -667,7 +667,7 @@
         <v>59</v>
       </c>
       <c r="M5" t="n">
-        <v>4.9168</v>
+        <v>4.8942</v>
       </c>
       <c r="N5" t="n">
         <v>129</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.4217</v>
+        <v>4.2871</v>
       </c>
       <c r="C6" t="n">
-        <v>1.2692</v>
+        <v>1.2305</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3613</v>
+        <v>1.3472</v>
       </c>
       <c r="E6" t="n">
-        <v>4.4217</v>
+        <v>4.2871</v>
       </c>
       <c r="F6" t="n">
-        <v>4.1437</v>
+        <v>4.0254</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0166</v>
+        <v>-0.0329</v>
       </c>
       <c r="H6" t="n">
-        <v>8.7776</v>
+        <v>8.670299999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>4.7398</v>
+        <v>4.8681</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0166</v>
+        <v>-0.0329</v>
       </c>
       <c r="K6" t="n">
         <v>70</v>
@@ -713,7 +713,7 @@
         <v>59</v>
       </c>
       <c r="M6" t="n">
-        <v>4.723199999999999</v>
+        <v>4.8352</v>
       </c>
       <c r="N6" t="n">
         <v>129</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.1588</v>
+        <v>4.1413</v>
       </c>
       <c r="C7" t="n">
-        <v>1.1937</v>
+        <v>1.1887</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2438</v>
+        <v>1.2808</v>
       </c>
       <c r="E7" t="n">
-        <v>4.1588</v>
+        <v>4.1413</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6743</v>
+        <v>1.6226</v>
       </c>
       <c r="G7" t="n">
-        <v>2.4373</v>
+        <v>2.4715</v>
       </c>
       <c r="H7" t="n">
-        <v>1.6743</v>
+        <v>1.6226</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6743</v>
+        <v>1.6226</v>
       </c>
       <c r="J7" t="n">
-        <v>2.4373</v>
+        <v>2.4715</v>
       </c>
       <c r="K7" t="n">
         <v>81</v>
@@ -759,7 +759,7 @@
         <v>155</v>
       </c>
       <c r="M7" t="n">
-        <v>4.1116</v>
+        <v>4.0941</v>
       </c>
       <c r="N7" t="n">
         <v>236</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.6016</v>
+        <v>3.5046</v>
       </c>
       <c r="C8" t="n">
-        <v>1.0338</v>
+        <v>1.0059</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9949</v>
+        <v>0.9907</v>
       </c>
       <c r="E8" t="n">
-        <v>3.6016</v>
+        <v>3.5046</v>
       </c>
       <c r="F8" t="n">
-        <v>2.5708</v>
+        <v>2.544</v>
       </c>
       <c r="G8" t="n">
-        <v>0.893</v>
+        <v>0.8228</v>
       </c>
       <c r="H8" t="n">
-        <v>2.9017</v>
+        <v>2.8799</v>
       </c>
       <c r="I8" t="n">
-        <v>2.9017</v>
+        <v>2.8799</v>
       </c>
       <c r="J8" t="n">
-        <v>0.893</v>
+        <v>0.8228</v>
       </c>
       <c r="K8" t="n">
         <v>91</v>
@@ -805,7 +805,7 @@
         <v>61</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7947</v>
+        <v>3.7027</v>
       </c>
       <c r="N8" t="n">
         <v>152</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.1475</v>
+        <v>3.1112</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9034</v>
+        <v>0.893</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7921</v>
+        <v>0.8115</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1475</v>
+        <v>3.1112</v>
       </c>
       <c r="F9" t="n">
-        <v>2.8713</v>
+        <v>2.8852</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1627</v>
+        <v>0.1125</v>
       </c>
       <c r="H9" t="n">
-        <v>4.5791</v>
+        <v>4.3897</v>
       </c>
       <c r="I9" t="n">
-        <v>2.4727</v>
+        <v>2.4647</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1627</v>
+        <v>0.1125</v>
       </c>
       <c r="K9" t="n">
         <v>70</v>
@@ -851,7 +851,7 @@
         <v>59</v>
       </c>
       <c r="M9" t="n">
-        <v>2.6354</v>
+        <v>2.5772</v>
       </c>
       <c r="N9" t="n">
         <v>129</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.491</v>
+        <v>2.4043</v>
       </c>
       <c r="C10" t="n">
-        <v>0.715</v>
+        <v>0.6901</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4989</v>
+        <v>0.4895</v>
       </c>
       <c r="E10" t="n">
-        <v>2.491</v>
+        <v>2.4043</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5719</v>
+        <v>0.4745</v>
       </c>
       <c r="G10" t="n">
-        <v>1.8896</v>
+        <v>1.9003</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5719</v>
+        <v>0.4745</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5719</v>
+        <v>0.4745</v>
       </c>
       <c r="J10" t="n">
-        <v>1.8896</v>
+        <v>1.9003</v>
       </c>
       <c r="K10" t="n">
         <v>81</v>
@@ -897,7 +897,7 @@
         <v>155</v>
       </c>
       <c r="M10" t="n">
-        <v>2.4615</v>
+        <v>2.3748</v>
       </c>
       <c r="N10" t="n">
         <v>236</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.423</v>
+        <v>2.3544</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6955</v>
+        <v>0.6758</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4685</v>
+        <v>0.4668</v>
       </c>
       <c r="E11" t="n">
-        <v>2.423</v>
+        <v>2.3544</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2167</v>
+        <v>1.175</v>
       </c>
       <c r="G11" t="n">
-        <v>1.1445</v>
+        <v>1.1176</v>
       </c>
       <c r="H11" t="n">
-        <v>1.2167</v>
+        <v>1.175</v>
       </c>
       <c r="I11" t="n">
-        <v>1.2167</v>
+        <v>1.175</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1445</v>
+        <v>1.1176</v>
       </c>
       <c r="K11" t="n">
         <v>73</v>
@@ -943,7 +943,7 @@
         <v>136</v>
       </c>
       <c r="M11" t="n">
-        <v>2.3612</v>
+        <v>2.2926</v>
       </c>
       <c r="N11" t="n">
         <v>209</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.1942</v>
+        <v>2.256</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6298</v>
+        <v>0.6475</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3663</v>
+        <v>0.4219</v>
       </c>
       <c r="E12" t="n">
-        <v>2.1942</v>
+        <v>2.256</v>
       </c>
       <c r="F12" t="n">
-        <v>2.1696</v>
+        <v>2.2723</v>
       </c>
       <c r="G12" t="n">
-        <v>0.179</v>
+        <v>0.1381</v>
       </c>
       <c r="H12" t="n">
-        <v>2.2641</v>
+        <v>2.2723</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2226</v>
+        <v>1.2758</v>
       </c>
       <c r="J12" t="n">
-        <v>0.179</v>
+        <v>0.1381</v>
       </c>
       <c r="K12" t="n">
         <v>70</v>
@@ -989,7 +989,7 @@
         <v>59</v>
       </c>
       <c r="M12" t="n">
-        <v>1.4016</v>
+        <v>1.4139</v>
       </c>
       <c r="N12" t="n">
         <v>129</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.0482</v>
+        <v>2.0774</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5879</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3011</v>
+        <v>0.3406</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0482</v>
+        <v>2.0774</v>
       </c>
       <c r="F13" t="n">
-        <v>2.0969</v>
+        <v>2.1462</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1466</v>
+        <v>-0.1667</v>
       </c>
       <c r="H13" t="n">
-        <v>2.0969</v>
+        <v>2.1462</v>
       </c>
       <c r="I13" t="n">
-        <v>2.0969</v>
+        <v>2.1462</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.1466</v>
+        <v>-0.1667</v>
       </c>
       <c r="K13" t="n">
         <v>91</v>
@@ -1035,7 +1035,7 @@
         <v>61</v>
       </c>
       <c r="M13" t="n">
-        <v>1.9503</v>
+        <v>1.9795</v>
       </c>
       <c r="N13" t="n">
         <v>152</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.7193</v>
+        <v>1.728</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4935</v>
+        <v>0.496</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1542</v>
+        <v>0.1814</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7193</v>
+        <v>1.728</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1447</v>
+        <v>2.1602</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.3937</v>
+        <v>-0.4005</v>
       </c>
       <c r="H14" t="n">
-        <v>2.1447</v>
+        <v>2.1602</v>
       </c>
       <c r="I14" t="n">
-        <v>2.1447</v>
+        <v>2.1602</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.3937</v>
+        <v>-0.4005</v>
       </c>
       <c r="K14" t="n">
         <v>81</v>
@@ -1081,7 +1081,7 @@
         <v>155</v>
       </c>
       <c r="M14" t="n">
-        <v>1.751</v>
+        <v>1.7597</v>
       </c>
       <c r="N14" t="n">
         <v>236</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.629</v>
+        <v>1.7182</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4676</v>
+        <v>0.4932</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1138</v>
+        <v>0.1769</v>
       </c>
       <c r="E15" t="n">
-        <v>1.629</v>
+        <v>1.7182</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3983</v>
+        <v>-0.4232</v>
       </c>
       <c r="G15" t="n">
-        <v>2.0271</v>
+        <v>2.1412</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.3983</v>
+        <v>-0.4232</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2151</v>
+        <v>-0.2376</v>
       </c>
       <c r="J15" t="n">
-        <v>2.0271</v>
+        <v>2.1412</v>
       </c>
       <c r="K15" t="n">
         <v>119</v>
@@ -1127,7 +1127,7 @@
         <v>135</v>
       </c>
       <c r="M15" t="n">
-        <v>1.812</v>
+        <v>1.9036</v>
       </c>
       <c r="N15" t="n">
         <v>254</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.4547</v>
+        <v>1.4453</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4175</v>
+        <v>0.4148</v>
       </c>
       <c r="D16" t="n">
-        <v>0.036</v>
+        <v>0.0526</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4547</v>
+        <v>1.4453</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3817</v>
+        <v>1.3723</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3817</v>
+        <v>1.3723</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3817</v>
+        <v>1.3723</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.3817</v>
+        <v>1.3723</v>
       </c>
       <c r="N16" t="n">
         <v>91</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.3234</v>
+        <v>1.4253</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3799</v>
+        <v>0.4091</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0227</v>
+        <v>0.0435</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3234</v>
+        <v>1.4253</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1082</v>
+        <v>1.1529</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2787</v>
+        <v>0.3359</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1082</v>
+        <v>1.1529</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5984</v>
+        <v>0.6473</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2787</v>
+        <v>0.3359</v>
       </c>
       <c r="K17" t="n">
         <v>119</v>
@@ -1219,7 +1219,7 @@
         <v>135</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8771</v>
+        <v>0.9832</v>
       </c>
       <c r="N17" t="n">
         <v>254</v>
@@ -1228,93 +1228,93 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ChildKing</t>
+          <t>headtr1ck</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.3202</v>
+        <v>1.3665</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3789</v>
+        <v>0.3922</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0241</v>
+        <v>0.0167</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3202</v>
+        <v>1.3665</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8784999999999999</v>
+        <v>1.7941</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-0.5516</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8784999999999999</v>
+        <v>1.7941</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8784999999999999</v>
+        <v>1.7941</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-0.5516</v>
       </c>
       <c r="K18" t="n">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8784999999999999</v>
+        <v>1.2425</v>
       </c>
       <c r="N18" t="n">
-        <v>53</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>headtr1ck</t>
+          <t>ChildKing</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.3173</v>
+        <v>1.2795</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3781</v>
+        <v>0.3673</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0254</v>
+        <v>-0.0229</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3173</v>
+        <v>1.2795</v>
       </c>
       <c r="F19" t="n">
-        <v>1.774</v>
+        <v>0.8378</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5807</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.774</v>
+        <v>0.8378</v>
       </c>
       <c r="I19" t="n">
-        <v>1.774</v>
+        <v>0.8378</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5807</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>91</v>
+        <v>53</v>
       </c>
       <c r="L19" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.1933</v>
+        <v>0.8378</v>
       </c>
       <c r="N19" t="n">
-        <v>152</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20">
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.2845</v>
+        <v>1.1969</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3687</v>
+        <v>0.3436</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0401</v>
+        <v>-0.0605</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2845</v>
+        <v>1.1969</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5074</v>
+        <v>0.4487</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8004</v>
+        <v>0.7715</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5074</v>
+        <v>0.4487</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5074</v>
+        <v>0.4487</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8004</v>
+        <v>0.7715</v>
       </c>
       <c r="K20" t="n">
         <v>73</v>
@@ -1357,7 +1357,7 @@
         <v>136</v>
       </c>
       <c r="M20" t="n">
-        <v>1.3078</v>
+        <v>1.2202</v>
       </c>
       <c r="N20" t="n">
         <v>209</v>
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.2217</v>
+        <v>1.1876</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3507</v>
+        <v>0.3409</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.06809999999999999</v>
+        <v>-0.0648</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2217</v>
+        <v>1.1876</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1437</v>
+        <v>1.103</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0619</v>
+        <v>-0.0553</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1437</v>
+        <v>1.103</v>
       </c>
       <c r="I21" t="n">
-        <v>1.1437</v>
+        <v>1.103</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0619</v>
+        <v>-0.0553</v>
       </c>
       <c r="K21" t="n">
         <v>91</v>
@@ -1403,7 +1403,7 @@
         <v>61</v>
       </c>
       <c r="M21" t="n">
-        <v>1.0818</v>
+        <v>1.0477</v>
       </c>
       <c r="N21" t="n">
         <v>152</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9689</v>
+        <v>0.8395</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2781</v>
+        <v>0.241</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.181</v>
+        <v>-0.2234</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9689</v>
+        <v>0.8395</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7537</v>
+        <v>0.6243</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7537</v>
+        <v>0.6243</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7537</v>
+        <v>0.6243</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7537</v>
+        <v>0.6243</v>
       </c>
       <c r="N22" t="n">
         <v>91</v>
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6894</v>
+        <v>0.735</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1979</v>
+        <v>0.211</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3059</v>
+        <v>-0.271</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6894</v>
+        <v>0.735</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3522</v>
+        <v>1.3747</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.7785</v>
+        <v>-0.7554</v>
       </c>
       <c r="H23" t="n">
-        <v>1.3522</v>
+        <v>1.3747</v>
       </c>
       <c r="I23" t="n">
-        <v>1.3522</v>
+        <v>1.3747</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.7785</v>
+        <v>-0.7554</v>
       </c>
       <c r="K23" t="n">
         <v>88</v>
@@ -1495,7 +1495,7 @@
         <v>36</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5737000000000001</v>
+        <v>0.6193000000000001</v>
       </c>
       <c r="N23" t="n">
         <v>124</v>
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6271</v>
+        <v>0.7164</v>
       </c>
       <c r="C24" t="n">
-        <v>0.18</v>
+        <v>0.2056</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3337</v>
+        <v>-0.2794</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6271</v>
+        <v>0.7164</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3548</v>
+        <v>-0.267</v>
       </c>
       <c r="G24" t="n">
-        <v>1.0587</v>
+        <v>1.0602</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.3548</v>
+        <v>-0.267</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1916</v>
+        <v>-0.1499</v>
       </c>
       <c r="J24" t="n">
-        <v>1.0587</v>
+        <v>1.0602</v>
       </c>
       <c r="K24" t="n">
         <v>119</v>
@@ -1541,7 +1541,7 @@
         <v>135</v>
       </c>
       <c r="M24" t="n">
-        <v>0.8671</v>
+        <v>0.9103</v>
       </c>
       <c r="N24" t="n">
         <v>254</v>
@@ -1550,139 +1550,139 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>VLDN</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.4499</v>
+        <v>0.4637</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1291</v>
+        <v>0.1331</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4129</v>
+        <v>-0.3946</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4499</v>
+        <v>0.4637</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3837</v>
+        <v>-1.4391</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1.9116</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3837</v>
+        <v>-1.4391</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3837</v>
+        <v>-1.4391</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1.9116</v>
       </c>
       <c r="K25" t="n">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3837</v>
+        <v>0.4724999999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>91</v>
+        <v>209</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>VLDN</t>
+          <t>Starry</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4452</v>
+        <v>0.3959</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1278</v>
+        <v>0.1136</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.415</v>
+        <v>-0.4254</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4452</v>
+        <v>0.3959</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.5139</v>
+        <v>0.4142</v>
       </c>
       <c r="G26" t="n">
-        <v>1.9679</v>
+        <v>-0.1286</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.5139</v>
+        <v>0.4142</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.5139</v>
+        <v>0.4142</v>
       </c>
       <c r="J26" t="n">
-        <v>1.9679</v>
+        <v>-0.1286</v>
       </c>
       <c r="K26" t="n">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="L26" t="n">
-        <v>136</v>
+        <v>36</v>
       </c>
       <c r="M26" t="n">
-        <v>0.454</v>
+        <v>0.2856</v>
       </c>
       <c r="N26" t="n">
-        <v>209</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Starry</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.4155</v>
+        <v>0.3696</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1193</v>
+        <v>0.1061</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4282</v>
+        <v>-0.4374</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4155</v>
+        <v>0.3696</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3905</v>
+        <v>0.3034</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.0853</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3905</v>
+        <v>0.3034</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3905</v>
+        <v>0.3034</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.0853</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="L27" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.3052</v>
+        <v>0.3034</v>
       </c>
       <c r="N27" t="n">
-        <v>124</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28">
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2599</v>
+        <v>0.2059</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0746</v>
+        <v>0.0591</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4977</v>
+        <v>-0.512</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2599</v>
+        <v>0.2059</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3229</v>
+        <v>0.2689</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3229</v>
+        <v>0.2689</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3229</v>
+        <v>0.2689</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.3229</v>
+        <v>0.2689</v>
       </c>
       <c r="N28" t="n">
         <v>91</v>
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1939</v>
+        <v>0.1857</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0557</v>
+        <v>0.0533</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5272</v>
+        <v>-0.5212</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1939</v>
+        <v>0.1857</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.0702</v>
+        <v>-0.0786</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2195</v>
+        <v>0.2197</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.0702</v>
+        <v>-0.0786</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0702</v>
+        <v>-0.0786</v>
       </c>
       <c r="J29" t="n">
-        <v>0.2195</v>
+        <v>0.2197</v>
       </c>
       <c r="K29" t="n">
         <v>88</v>
@@ -1771,7 +1771,7 @@
         <v>36</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1493</v>
+        <v>0.1411</v>
       </c>
       <c r="N29" t="n">
         <v>124</v>
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.1383</v>
+        <v>-0.081</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0397</v>
+        <v>-0.0232</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6756</v>
+        <v>-0.6427</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.1383</v>
+        <v>-0.081</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.725</v>
+        <v>-0.6152</v>
       </c>
       <c r="G30" t="n">
-        <v>0.7099</v>
+        <v>0.6574</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.725</v>
+        <v>-0.6152</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3915</v>
+        <v>-0.3454</v>
       </c>
       <c r="J30" t="n">
-        <v>0.7099</v>
+        <v>0.6574</v>
       </c>
       <c r="K30" t="n">
         <v>70</v>
@@ -1817,7 +1817,7 @@
         <v>59</v>
       </c>
       <c r="M30" t="n">
-        <v>0.3184</v>
+        <v>0.312</v>
       </c>
       <c r="N30" t="n">
         <v>129</v>
@@ -1826,47 +1826,47 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.1716</v>
+        <v>-0.2224</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0493</v>
+        <v>-0.0638</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6905</v>
+        <v>-0.7071</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.1716</v>
+        <v>-0.2224</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2817</v>
+        <v>-0.5221</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.3666</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2817</v>
+        <v>-0.5221</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1521</v>
+        <v>-0.5221</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.3666</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>119</v>
+        <v>53</v>
       </c>
       <c r="L31" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.2145</v>
+        <v>-0.5221</v>
       </c>
       <c r="N31" t="n">
-        <v>254</v>
+        <v>53</v>
       </c>
     </row>
     <row r="32">
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.193</v>
+        <v>-0.2358</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0554</v>
+        <v>-0.0677</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7</v>
+        <v>-0.7131999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.193</v>
+        <v>-0.2358</v>
       </c>
       <c r="F32" t="n">
-        <v>0.2093</v>
+        <v>0.206</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.1356</v>
+        <v>-0.1751</v>
       </c>
       <c r="H32" t="n">
-        <v>0.2093</v>
+        <v>0.206</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2093</v>
+        <v>0.206</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.1356</v>
+        <v>-0.1751</v>
       </c>
       <c r="K32" t="n">
         <v>88</v>
@@ -1909,7 +1909,7 @@
         <v>36</v>
       </c>
       <c r="M32" t="n">
-        <v>0.07370000000000002</v>
+        <v>0.03089999999999998</v>
       </c>
       <c r="N32" t="n">
         <v>124</v>
@@ -1918,47 +1918,47 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.265</v>
+        <v>-0.2851</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0761</v>
+        <v>-0.0818</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7322</v>
+        <v>-0.7357</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.265</v>
+        <v>-0.2851</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.5647</v>
+        <v>0.2383</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-0.4367</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.5647</v>
+        <v>0.2383</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.5647</v>
+        <v>0.1338</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>-0.4367</v>
       </c>
       <c r="K33" t="n">
-        <v>53</v>
+        <v>119</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5647</v>
+        <v>-0.3028999999999999</v>
       </c>
       <c r="N33" t="n">
-        <v>53</v>
+        <v>254</v>
       </c>
     </row>
     <row r="34">
@@ -1968,31 +1968,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.4084</v>
+        <v>-0.5468</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1172</v>
+        <v>-0.1569</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7962</v>
+        <v>-0.8549</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.4084</v>
+        <v>-0.5468</v>
       </c>
       <c r="F34" t="n">
-        <v>1.1407</v>
+        <v>1.0265</v>
       </c>
       <c r="G34" t="n">
-        <v>-1.3617</v>
+        <v>-1.3859</v>
       </c>
       <c r="H34" t="n">
-        <v>1.1407</v>
+        <v>1.0265</v>
       </c>
       <c r="I34" t="n">
-        <v>1.1407</v>
+        <v>1.0265</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.3617</v>
+        <v>-1.3859</v>
       </c>
       <c r="K34" t="n">
         <v>81</v>
@@ -2001,7 +2001,7 @@
         <v>155</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.2209999999999999</v>
+        <v>-0.3593999999999999</v>
       </c>
       <c r="N34" t="n">
         <v>236</v>
@@ -2014,31 +2014,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.8359</v>
+        <v>-0.9116</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2399</v>
+        <v>-0.2617</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9872</v>
+        <v>-1.0211</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.8359</v>
+        <v>-0.9116</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.3426</v>
+        <v>-1.3048</v>
       </c>
       <c r="G35" t="n">
-        <v>0.6781</v>
+        <v>0.5646</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.3426</v>
+        <v>-1.3048</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.3426</v>
+        <v>-1.3048</v>
       </c>
       <c r="J35" t="n">
-        <v>0.6781</v>
+        <v>0.5646</v>
       </c>
       <c r="K35" t="n">
         <v>73</v>
@@ -2047,7 +2047,7 @@
         <v>136</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.6645</v>
+        <v>-0.7402</v>
       </c>
       <c r="N35" t="n">
         <v>209</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.3384</v>
+        <v>-1.2993</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3842</v>
+        <v>-0.3729</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.2117</v>
+        <v>-1.1977</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.3384</v>
+        <v>-1.2993</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.0431</v>
+        <v>-1.004</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.0431</v>
+        <v>-1.004</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.0431</v>
+        <v>-1.004</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.0431</v>
+        <v>-1.004</v>
       </c>
       <c r="N36" t="n">
         <v>53</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.5758</v>
+        <v>-1.5414</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.4523</v>
+        <v>-0.4424</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.3177</v>
+        <v>-1.308</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.5758</v>
+        <v>-1.5414</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.1147</v>
+        <v>-1.0803</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.1147</v>
+        <v>-1.0803</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.1147</v>
+        <v>-1.0803</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.1147</v>
+        <v>-1.0803</v>
       </c>
       <c r="N37" t="n">
         <v>53</v>
@@ -2148,93 +2148,93 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>es3tag</t>
+          <t>advent</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.628</v>
+        <v>-1.5815</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.4673</v>
+        <v>-0.4539</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.341</v>
+        <v>-1.3262</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.628</v>
+        <v>-1.5815</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.5759</v>
+        <v>-1.2005</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.7668</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.5759</v>
+        <v>-1.2005</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.5759</v>
+        <v>-1.2005</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.7668</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>91</v>
       </c>
       <c r="L38" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.3427</v>
+        <v>-1.2005</v>
       </c>
       <c r="N38" t="n">
-        <v>152</v>
+        <v>91</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>advent</t>
+          <t>es3tag</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.6329</v>
+        <v>-1.6258</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.4687</v>
+        <v>-0.4667</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.3432</v>
+        <v>-1.3464</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.6329</v>
+        <v>-1.6258</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.2519</v>
+        <v>-0.5731000000000001</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>-0.7674</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.2519</v>
+        <v>-0.5731000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.2519</v>
+        <v>-0.5731000000000001</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>-0.7674</v>
       </c>
       <c r="K39" t="n">
         <v>91</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.2519</v>
+        <v>-1.3405</v>
       </c>
       <c r="N39" t="n">
-        <v>91</v>
+        <v>152</v>
       </c>
     </row>
     <row r="40">
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.7583</v>
+        <v>-1.7564</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5047</v>
+        <v>-0.5041</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3992</v>
+        <v>-1.4059</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.7583</v>
+        <v>-1.7564</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.4992</v>
+        <v>-1.4973</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.4992</v>
+        <v>-1.4973</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.4992</v>
+        <v>-1.4973</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.4992</v>
+        <v>-1.4973</v>
       </c>
       <c r="N40" t="n">
         <v>53</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.0312</v>
+        <v>-2.9272</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.8701</v>
+        <v>-0.8401999999999999</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.9678</v>
+        <v>-1.9393</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.0312</v>
+        <v>-2.9272</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.7064</v>
+        <v>-1.6011</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.9987</v>
+        <v>-1</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.7064</v>
+        <v>-1.6011</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.7064</v>
+        <v>-1.6011</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.9987</v>
+        <v>-1</v>
       </c>
       <c r="K41" t="n">
         <v>88</v>
@@ -2323,7 +2323,7 @@
         <v>36</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.7051</v>
+        <v>-2.6011</v>
       </c>
       <c r="N41" t="n">
         <v>124</v>
@@ -2429,10 +2429,10 @@
         <v>1.5</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9219000000000001</v>
+        <v>0.8841</v>
       </c>
       <c r="J2" t="n">
-        <v>18.438</v>
+        <v>17.682</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1579</v>
+        <v>0.1216</v>
       </c>
       <c r="J3" t="n">
-        <v>3.158</v>
+        <v>2.432</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.03</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1091</v>
+        <v>0.0804</v>
       </c>
       <c r="J4" t="n">
-        <v>2.182</v>
+        <v>1.608</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.66</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3788</v>
+        <v>-0.3661</v>
       </c>
       <c r="J5" t="n">
-        <v>-7.576</v>
+        <v>-7.322</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.47</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5439000000000001</v>
+        <v>-0.5511</v>
       </c>
       <c r="J6" t="n">
-        <v>-10.878</v>
+        <v>-11.022</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.44</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0312</v>
+        <v>1.0262</v>
       </c>
       <c r="J7" t="n">
-        <v>20.624</v>
+        <v>20.524</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.25</v>
       </c>
       <c r="I8" t="n">
-        <v>0.653</v>
+        <v>0.6206</v>
       </c>
       <c r="J8" t="n">
-        <v>13.06</v>
+        <v>12.412</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.16</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4589</v>
+        <v>0.4234</v>
       </c>
       <c r="J9" t="n">
-        <v>9.178000000000001</v>
+        <v>8.468</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.08</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2593</v>
+        <v>0.228</v>
       </c>
       <c r="J10" t="n">
-        <v>5.186</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.99</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0906</v>
+        <v>-0.0696</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.812</v>
+        <v>-1.392</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.35</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6778</v>
+        <v>0.621</v>
       </c>
       <c r="J12" t="n">
-        <v>27.112</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.06</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1714</v>
+        <v>0.1339</v>
       </c>
       <c r="J13" t="n">
-        <v>6.856</v>
+        <v>5.356</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.98</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0422</v>
+        <v>-0.0322</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.688</v>
+        <v>-1.288</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.83</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2215</v>
+        <v>-0.201</v>
       </c>
       <c r="J15" t="n">
-        <v>-8.859999999999999</v>
+        <v>-8.039999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.74</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3097</v>
+        <v>-0.2923</v>
       </c>
       <c r="J16" t="n">
-        <v>-12.388</v>
+        <v>-11.692</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.28</v>
       </c>
       <c r="I17" t="n">
-        <v>0.735</v>
+        <v>0.7039</v>
       </c>
       <c r="J17" t="n">
-        <v>29.4</v>
+        <v>28.156</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.27</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7138</v>
+        <v>0.6815</v>
       </c>
       <c r="J18" t="n">
-        <v>28.552</v>
+        <v>27.26</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.12</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3741</v>
+        <v>0.3353</v>
       </c>
       <c r="J19" t="n">
-        <v>14.964</v>
+        <v>13.412</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.97</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1529</v>
+        <v>-0.1218</v>
       </c>
       <c r="J20" t="n">
-        <v>-6.116</v>
+        <v>-4.872</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.85</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4886</v>
+        <v>-0.4468</v>
       </c>
       <c r="J21" t="n">
-        <v>-19.544</v>
+        <v>-17.872</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.66</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7748</v>
+        <v>0.8359</v>
       </c>
       <c r="J22" t="n">
-        <v>16.2708</v>
+        <v>17.5539</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.15</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2771</v>
+        <v>0.2635</v>
       </c>
       <c r="J23" t="n">
-        <v>5.8191</v>
+        <v>5.5335</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.78</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2689</v>
+        <v>-0.2495</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.6469</v>
+        <v>-5.2395</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.75</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2978</v>
+        <v>-0.2797</v>
       </c>
       <c r="J25" t="n">
-        <v>-6.2538</v>
+        <v>-5.8737</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.49</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5289</v>
+        <v>-0.5342</v>
       </c>
       <c r="J26" t="n">
-        <v>-11.1069</v>
+        <v>-11.2182</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.63</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6741</v>
+        <v>0.6311</v>
       </c>
       <c r="J27" t="n">
-        <v>14.1561</v>
+        <v>13.2531</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.29</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4028</v>
+        <v>0.3407</v>
       </c>
       <c r="J28" t="n">
-        <v>8.4588</v>
+        <v>7.1547</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.17</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2638</v>
+        <v>0.2151</v>
       </c>
       <c r="J29" t="n">
-        <v>5.5398</v>
+        <v>4.5171</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.04</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0765</v>
+        <v>0.0559</v>
       </c>
       <c r="J30" t="n">
-        <v>1.6065</v>
+        <v>1.1739</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.82</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.248</v>
+        <v>-0.2294</v>
       </c>
       <c r="J31" t="n">
-        <v>-5.208</v>
+        <v>-4.8174</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.75</v>
       </c>
       <c r="I32" t="n">
-        <v>1.3296</v>
+        <v>1.3453</v>
       </c>
       <c r="J32" t="n">
-        <v>39.888</v>
+        <v>40.359</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.02</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0886</v>
+        <v>0.0701</v>
       </c>
       <c r="J33" t="n">
-        <v>2.658</v>
+        <v>2.103</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.91</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3309</v>
+        <v>-0.2888</v>
       </c>
       <c r="J34" t="n">
-        <v>-9.927</v>
+        <v>-8.664</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.87</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4355</v>
+        <v>-0.3926</v>
       </c>
       <c r="J35" t="n">
-        <v>-13.065</v>
+        <v>-11.778</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.85</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4851</v>
+        <v>-0.443</v>
       </c>
       <c r="J36" t="n">
-        <v>-14.553</v>
+        <v>-13.29</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.44</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6913</v>
+        <v>0.6571</v>
       </c>
       <c r="J37" t="n">
-        <v>20.739</v>
+        <v>19.713</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.3</v>
       </c>
       <c r="I38" t="n">
-        <v>0.5377999999999999</v>
+        <v>0.5094</v>
       </c>
       <c r="J38" t="n">
-        <v>16.134</v>
+        <v>15.282</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.01</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0322</v>
+        <v>0.0223</v>
       </c>
       <c r="J39" t="n">
-        <v>0.966</v>
+        <v>0.669</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.99</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.0326</v>
+        <v>-0.0236</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.978</v>
+        <v>-0.708</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.77</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2905</v>
+        <v>-0.2728</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.715</v>
+        <v>-8.183999999999999</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.58</v>
       </c>
       <c r="I42" t="n">
-        <v>1.0746</v>
+        <v>1.0658</v>
       </c>
       <c r="J42" t="n">
-        <v>25.7904</v>
+        <v>25.5792</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.39</v>
       </c>
       <c r="I43" t="n">
-        <v>0.8095</v>
+        <v>0.7935</v>
       </c>
       <c r="J43" t="n">
-        <v>19.428</v>
+        <v>19.044</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.33</v>
       </c>
       <c r="I44" t="n">
-        <v>0.7215</v>
+        <v>0.7064</v>
       </c>
       <c r="J44" t="n">
-        <v>17.316</v>
+        <v>16.9536</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.93</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2907</v>
+        <v>-0.2507</v>
       </c>
       <c r="J45" t="n">
-        <v>-6.9768</v>
+        <v>-6.0168</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.59</v>
       </c>
       <c r="I46" t="n">
-        <v>-1.0649</v>
+        <v>-1.0744</v>
       </c>
       <c r="J46" t="n">
-        <v>-25.5576</v>
+        <v>-25.7856</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.49</v>
       </c>
       <c r="I47" t="n">
-        <v>0.7544</v>
+        <v>0.7189</v>
       </c>
       <c r="J47" t="n">
-        <v>18.1056</v>
+        <v>17.2536</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.35</v>
       </c>
       <c r="I48" t="n">
-        <v>0.6024</v>
+        <v>0.5737</v>
       </c>
       <c r="J48" t="n">
-        <v>14.4576</v>
+        <v>13.7688</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.1</v>
       </c>
       <c r="I49" t="n">
-        <v>0.244</v>
+        <v>0.1996</v>
       </c>
       <c r="J49" t="n">
-        <v>5.856</v>
+        <v>4.7904</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.92</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1281</v>
+        <v>-0.1091</v>
       </c>
       <c r="J50" t="n">
-        <v>-3.0744</v>
+        <v>-2.6184</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.41</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6008</v>
+        <v>-0.619</v>
       </c>
       <c r="J51" t="n">
-        <v>-14.4192</v>
+        <v>-14.856</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.26</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5269</v>
+        <v>0.4996</v>
       </c>
       <c r="J52" t="n">
-        <v>12.1187</v>
+        <v>11.4908</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.16</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3846</v>
+        <v>0.33</v>
       </c>
       <c r="J53" t="n">
-        <v>8.845800000000001</v>
+        <v>7.59</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2348</v>
+        <v>-0.2148</v>
       </c>
       <c r="J54" t="n">
-        <v>-5.4004</v>
+        <v>-4.9404</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.72</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3214</v>
+        <v>-0.3045</v>
       </c>
       <c r="J55" t="n">
-        <v>-7.3922</v>
+        <v>-7.0035</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.64</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3945</v>
+        <v>-0.383</v>
       </c>
       <c r="J56" t="n">
-        <v>-9.073499999999999</v>
+        <v>-8.808999999999999</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>2.04</v>
       </c>
       <c r="I57" t="n">
-        <v>1.699</v>
+        <v>1.7633</v>
       </c>
       <c r="J57" t="n">
-        <v>39.077</v>
+        <v>40.5559</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.19</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5135999999999999</v>
+        <v>0.4986</v>
       </c>
       <c r="J58" t="n">
-        <v>11.8128</v>
+        <v>11.4678</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.82</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.5594</v>
+        <v>-0.5198</v>
       </c>
       <c r="J59" t="n">
-        <v>-12.8662</v>
+        <v>-11.9554</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.76</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.6965</v>
+        <v>-0.6647</v>
       </c>
       <c r="J60" t="n">
-        <v>-16.0195</v>
+        <v>-15.2881</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.65</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.9317</v>
+        <v>-0.9221</v>
       </c>
       <c r="J61" t="n">
-        <v>-21.4291</v>
+        <v>-21.2083</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>2.28</v>
       </c>
       <c r="I62" t="n">
-        <v>1.0584</v>
+        <v>0.9977</v>
       </c>
       <c r="J62" t="n">
-        <v>16.9344</v>
+        <v>15.9632</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.76</v>
       </c>
       <c r="I63" t="n">
-        <v>0.729</v>
+        <v>0.6821</v>
       </c>
       <c r="J63" t="n">
-        <v>11.664</v>
+        <v>10.9136</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.37</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4577</v>
+        <v>0.4055</v>
       </c>
       <c r="J64" t="n">
-        <v>7.3232</v>
+        <v>6.488</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.16</v>
       </c>
       <c r="I65" t="n">
-        <v>0.2247</v>
+        <v>0.1821</v>
       </c>
       <c r="J65" t="n">
-        <v>3.5952</v>
+        <v>2.9136</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>1.01</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.0097</v>
+        <v>-0.0162</v>
       </c>
       <c r="J66" t="n">
-        <v>-0.1552</v>
+        <v>-0.2592</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.06</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2231</v>
+        <v>0.2296</v>
       </c>
       <c r="J67" t="n">
-        <v>3.5696</v>
+        <v>3.6736</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.76</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.2569</v>
+        <v>-0.2431</v>
       </c>
       <c r="J68" t="n">
-        <v>-4.1104</v>
+        <v>-3.8896</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.72</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.2957</v>
+        <v>-0.2829</v>
       </c>
       <c r="J69" t="n">
-        <v>-4.7312</v>
+        <v>-4.5264</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.5</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4896</v>
+        <v>-0.4865</v>
       </c>
       <c r="J70" t="n">
-        <v>-7.8336</v>
+        <v>-7.784</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.29</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6724</v>
+        <v>-0.698</v>
       </c>
       <c r="J71" t="n">
-        <v>-10.7584</v>
+        <v>-11.168</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.43</v>
       </c>
       <c r="I72" t="n">
-        <v>0.72</v>
+        <v>0.6901</v>
       </c>
       <c r="J72" t="n">
-        <v>14.4</v>
+        <v>13.802</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1</v>
       </c>
       <c r="I73" t="n">
-        <v>0.0078</v>
+        <v>0.0047</v>
       </c>
       <c r="J73" t="n">
-        <v>0.156</v>
+        <v>0.094</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.89</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.1529</v>
+        <v>-0.1339</v>
       </c>
       <c r="J74" t="n">
-        <v>-3.058</v>
+        <v>-2.678</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.85</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.1959</v>
+        <v>-0.1757</v>
       </c>
       <c r="J75" t="n">
-        <v>-3.918</v>
+        <v>-3.514</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.52</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5012</v>
+        <v>-0.5022</v>
       </c>
       <c r="J76" t="n">
-        <v>-10.024</v>
+        <v>-10.044</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>2.1</v>
       </c>
       <c r="I77" t="n">
-        <v>1.6863</v>
+        <v>1.7288</v>
       </c>
       <c r="J77" t="n">
-        <v>33.726</v>
+        <v>34.576</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.78</v>
       </c>
       <c r="I78" t="n">
-        <v>1.2977</v>
+        <v>1.3004</v>
       </c>
       <c r="J78" t="n">
-        <v>25.954</v>
+        <v>26.008</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.11</v>
       </c>
       <c r="I79" t="n">
-        <v>0.3182</v>
+        <v>0.2864</v>
       </c>
       <c r="J79" t="n">
-        <v>6.364</v>
+        <v>5.728</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.0521</v>
+        <v>-0.0477</v>
       </c>
       <c r="J80" t="n">
-        <v>-1.042</v>
+        <v>-0.954</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.1426</v>
+        <v>-1.1678</v>
       </c>
       <c r="J81" t="n">
-        <v>-22.852</v>
+        <v>-23.356</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.67</v>
       </c>
       <c r="I82" t="n">
-        <v>1.1652</v>
+        <v>1.1597</v>
       </c>
       <c r="J82" t="n">
-        <v>24.4692</v>
+        <v>24.3537</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.39</v>
       </c>
       <c r="I83" t="n">
-        <v>0.7902</v>
+        <v>0.7765</v>
       </c>
       <c r="J83" t="n">
-        <v>16.5942</v>
+        <v>16.3065</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.25</v>
       </c>
       <c r="I84" t="n">
-        <v>0.5887</v>
+        <v>0.5823</v>
       </c>
       <c r="J84" t="n">
-        <v>12.3627</v>
+        <v>12.2283</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1.16</v>
       </c>
       <c r="I85" t="n">
-        <v>0.4413</v>
+        <v>0.4129</v>
       </c>
       <c r="J85" t="n">
-        <v>9.267300000000001</v>
+        <v>8.6709</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.93</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3107</v>
+        <v>-0.273</v>
       </c>
       <c r="J86" t="n">
-        <v>-6.5247</v>
+        <v>-5.733</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.02</v>
       </c>
       <c r="I87" t="n">
-        <v>0.0945</v>
+        <v>0.0692</v>
       </c>
       <c r="J87" t="n">
-        <v>1.9845</v>
+        <v>1.4532</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.99</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.015</v>
+        <v>-0.0105</v>
       </c>
       <c r="J88" t="n">
-        <v>-0.315</v>
+        <v>-0.2205</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.91</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.127</v>
+        <v>-0.1107</v>
       </c>
       <c r="J89" t="n">
-        <v>-2.667</v>
+        <v>-2.3247</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.82</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2214</v>
+        <v>-0.2019</v>
       </c>
       <c r="J90" t="n">
-        <v>-4.6494</v>
+        <v>-4.2399</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.67</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3639</v>
+        <v>-0.3496</v>
       </c>
       <c r="J91" t="n">
-        <v>-7.6419</v>
+        <v>-7.3416</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.2</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3721</v>
+        <v>0.3706</v>
       </c>
       <c r="J92" t="n">
-        <v>7.8141</v>
+        <v>7.7826</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.89</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.1478</v>
+        <v>-0.1309</v>
       </c>
       <c r="J93" t="n">
-        <v>-3.1038</v>
+        <v>-2.7489</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.86</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1794</v>
+        <v>-0.1612</v>
       </c>
       <c r="J94" t="n">
-        <v>-3.7674</v>
+        <v>-3.3852</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3435</v>
+        <v>-0.3278</v>
       </c>
       <c r="J95" t="n">
-        <v>-7.2135</v>
+        <v>-6.8838</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.67</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3618</v>
+        <v>-0.3473</v>
       </c>
       <c r="J96" t="n">
-        <v>-7.5978</v>
+        <v>-7.2933</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>2.18</v>
       </c>
       <c r="I97" t="n">
-        <v>1.0361</v>
+        <v>0.9815</v>
       </c>
       <c r="J97" t="n">
-        <v>21.7581</v>
+        <v>20.6115</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.24</v>
       </c>
       <c r="I98" t="n">
-        <v>0.3413</v>
+        <v>0.2864</v>
       </c>
       <c r="J98" t="n">
-        <v>7.1673</v>
+        <v>6.0144</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.04</v>
       </c>
       <c r="I99" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.0494</v>
       </c>
       <c r="J99" t="n">
-        <v>1.4511</v>
+        <v>1.0374</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.95</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1071</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="J100" t="n">
-        <v>-2.2491</v>
+        <v>-1.9068</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.1202</v>
+        <v>-0.103</v>
       </c>
       <c r="J101" t="n">
-        <v>-2.5242</v>
+        <v>-2.163</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.81</v>
       </c>
       <c r="I102" t="n">
-        <v>1.324</v>
+        <v>1.3281</v>
       </c>
       <c r="J102" t="n">
-        <v>25.156</v>
+        <v>25.2339</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.51</v>
       </c>
       <c r="I103" t="n">
-        <v>0.9427</v>
+        <v>0.9306</v>
       </c>
       <c r="J103" t="n">
-        <v>17.9113</v>
+        <v>17.6814</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.21</v>
       </c>
       <c r="I104" t="n">
-        <v>0.5179</v>
+        <v>0.5132</v>
       </c>
       <c r="J104" t="n">
-        <v>9.8401</v>
+        <v>9.7508</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.15</v>
       </c>
       <c r="I105" t="n">
-        <v>0.4089</v>
+        <v>0.3778</v>
       </c>
       <c r="J105" t="n">
-        <v>7.7691</v>
+        <v>7.1782</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>1.11</v>
       </c>
       <c r="I106" t="n">
-        <v>0.3107</v>
+        <v>0.2787</v>
       </c>
       <c r="J106" t="n">
-        <v>5.9033</v>
+        <v>5.2953</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.03</v>
       </c>
       <c r="I107" t="n">
-        <v>0.1722</v>
+        <v>0.1462</v>
       </c>
       <c r="J107" t="n">
-        <v>3.2718</v>
+        <v>2.7778</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.79</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.2376</v>
+        <v>-0.2222</v>
       </c>
       <c r="J108" t="n">
-        <v>-4.5144</v>
+        <v>-4.2218</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.76</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2665</v>
+        <v>-0.2512</v>
       </c>
       <c r="J109" t="n">
-        <v>-5.0635</v>
+        <v>-4.7728</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.4455</v>
+        <v>-0.4381</v>
       </c>
       <c r="J110" t="n">
-        <v>-8.464499999999999</v>
+        <v>-8.3239</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.53</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.472</v>
+        <v>-0.4672</v>
       </c>
       <c r="J111" t="n">
-        <v>-8.968</v>
+        <v>-8.876799999999999</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.1</v>
       </c>
       <c r="I112" t="n">
-        <v>0.4005</v>
+        <v>0.3832</v>
       </c>
       <c r="J112" t="n">
-        <v>6.408</v>
+        <v>6.1312</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.58</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.4145</v>
+        <v>-0.406</v>
       </c>
       <c r="J113" t="n">
-        <v>-6.632</v>
+        <v>-6.496</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.57</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.4233</v>
+        <v>-0.4151</v>
       </c>
       <c r="J114" t="n">
-        <v>-6.7728</v>
+        <v>-6.6416</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.57</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.4233</v>
+        <v>-0.4151</v>
       </c>
       <c r="J115" t="n">
-        <v>-6.7728</v>
+        <v>-6.6416</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.34</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6253</v>
+        <v>-0.6414</v>
       </c>
       <c r="J116" t="n">
-        <v>-10.0048</v>
+        <v>-10.2624</v>
       </c>
     </row>
     <row r="117">
@@ -7069,10 +7069,10 @@
         <v>1.58</v>
       </c>
       <c r="I118" t="n">
-        <v>1.0184</v>
+        <v>1.0104</v>
       </c>
       <c r="J118" t="n">
-        <v>16.2944</v>
+        <v>16.1664</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.45</v>
       </c>
       <c r="I119" t="n">
-        <v>0.8532999999999999</v>
+        <v>0.8452</v>
       </c>
       <c r="J119" t="n">
-        <v>13.6528</v>
+        <v>13.5232</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.38</v>
       </c>
       <c r="I120" t="n">
-        <v>0.759</v>
+        <v>0.7522</v>
       </c>
       <c r="J120" t="n">
-        <v>12.144</v>
+        <v>12.0352</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1.2</v>
       </c>
       <c r="I121" t="n">
-        <v>0.4887</v>
+        <v>0.4773</v>
       </c>
       <c r="J121" t="n">
-        <v>7.8192</v>
+        <v>7.6368</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.13</v>
       </c>
       <c r="I122" t="n">
-        <v>0.338</v>
+        <v>0.2865</v>
       </c>
       <c r="J122" t="n">
-        <v>6.76</v>
+        <v>5.73</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.1</v>
       </c>
       <c r="I123" t="n">
-        <v>0.2789</v>
+        <v>0.2309</v>
       </c>
       <c r="J123" t="n">
-        <v>5.578</v>
+        <v>4.618</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.86</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.181</v>
+        <v>-0.162</v>
       </c>
       <c r="J124" t="n">
-        <v>-3.62</v>
+        <v>-3.24</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.68</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3552</v>
+        <v>-0.3403</v>
       </c>
       <c r="J125" t="n">
-        <v>-7.104</v>
+        <v>-6.806</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.66</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3734</v>
+        <v>-0.3598</v>
       </c>
       <c r="J126" t="n">
-        <v>-7.468</v>
+        <v>-7.196</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.79</v>
       </c>
       <c r="I127" t="n">
-        <v>1.3288</v>
+        <v>1.3358</v>
       </c>
       <c r="J127" t="n">
-        <v>26.576</v>
+        <v>26.716</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.43</v>
       </c>
       <c r="I128" t="n">
-        <v>0.8526</v>
+        <v>0.8376</v>
       </c>
       <c r="J128" t="n">
-        <v>17.052</v>
+        <v>16.752</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.26</v>
       </c>
       <c r="I129" t="n">
-        <v>0.6066</v>
+        <v>0.5977</v>
       </c>
       <c r="J129" t="n">
-        <v>12.132</v>
+        <v>11.954</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.04</v>
       </c>
       <c r="I130" t="n">
-        <v>0.1313</v>
+        <v>0.1078</v>
       </c>
       <c r="J130" t="n">
-        <v>2.626</v>
+        <v>2.156</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.67</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.9133</v>
+        <v>-0.9059</v>
       </c>
       <c r="J131" t="n">
-        <v>-18.266</v>
+        <v>-18.118</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.58</v>
       </c>
       <c r="I132" t="n">
-        <v>1.0758</v>
+        <v>1.0834</v>
       </c>
       <c r="J132" t="n">
-        <v>20.4402</v>
+        <v>20.5846</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.79</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.2461</v>
+        <v>-0.2276</v>
       </c>
       <c r="J133" t="n">
-        <v>-4.6759</v>
+        <v>-4.3244</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.66</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.3674</v>
+        <v>-0.3534</v>
       </c>
       <c r="J134" t="n">
-        <v>-6.9806</v>
+        <v>-6.7146</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.6</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.4212</v>
+        <v>-0.4117</v>
       </c>
       <c r="J135" t="n">
-        <v>-8.002800000000001</v>
+        <v>-7.8223</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.52</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.4913</v>
+        <v>-0.4897</v>
       </c>
       <c r="J136" t="n">
-        <v>-9.3347</v>
+        <v>-9.3043</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>2.09</v>
       </c>
       <c r="I137" t="n">
-        <v>1.8061</v>
+        <v>1.8683</v>
       </c>
       <c r="J137" t="n">
-        <v>34.3159</v>
+        <v>35.4977</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.7</v>
       </c>
       <c r="I138" t="n">
-        <v>1.3338</v>
+        <v>1.3548</v>
       </c>
       <c r="J138" t="n">
-        <v>25.3422</v>
+        <v>25.7412</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.3</v>
       </c>
       <c r="I139" t="n">
-        <v>0.7323</v>
+        <v>0.7122000000000001</v>
       </c>
       <c r="J139" t="n">
-        <v>13.9137</v>
+        <v>13.5318</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.99</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1201</v>
+        <v>-0.1017</v>
       </c>
       <c r="J140" t="n">
-        <v>-2.2819</v>
+        <v>-1.9323</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.73</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.8042</v>
+        <v>-0.7891</v>
       </c>
       <c r="J141" t="n">
-        <v>-15.2798</v>
+        <v>-14.9929</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.09</v>
       </c>
       <c r="I142" t="n">
-        <v>0.3019</v>
+        <v>0.261</v>
       </c>
       <c r="J142" t="n">
-        <v>5.7361</v>
+        <v>4.959</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.96</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.0453</v>
+        <v>-0.034</v>
       </c>
       <c r="J143" t="n">
-        <v>-0.8607</v>
+        <v>-0.646</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.68</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.3418</v>
+        <v>-0.3269</v>
       </c>
       <c r="J144" t="n">
-        <v>-6.4942</v>
+        <v>-6.2111</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.6</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.4137</v>
+        <v>-0.4034</v>
       </c>
       <c r="J145" t="n">
-        <v>-7.8603</v>
+        <v>-7.6646</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.49</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.5104</v>
+        <v>-0.5105</v>
       </c>
       <c r="J146" t="n">
-        <v>-9.6976</v>
+        <v>-9.6995</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.96</v>
       </c>
       <c r="I147" t="n">
-        <v>1.6542</v>
+        <v>1.6999</v>
       </c>
       <c r="J147" t="n">
-        <v>31.4298</v>
+        <v>32.2981</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.57</v>
       </c>
       <c r="I148" t="n">
-        <v>1.1691</v>
+        <v>1.1839</v>
       </c>
       <c r="J148" t="n">
-        <v>22.2129</v>
+        <v>22.4941</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.21</v>
       </c>
       <c r="I149" t="n">
-        <v>0.5465</v>
+        <v>0.5182</v>
       </c>
       <c r="J149" t="n">
-        <v>10.3835</v>
+        <v>9.845800000000001</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.15</v>
       </c>
       <c r="I150" t="n">
-        <v>0.4099</v>
+        <v>0.3784</v>
       </c>
       <c r="J150" t="n">
-        <v>7.7881</v>
+        <v>7.1896</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.88</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.457</v>
+        <v>-0.4209</v>
       </c>
       <c r="J151" t="n">
-        <v>-8.683</v>
+        <v>-7.9971</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.33</v>
       </c>
       <c r="I152" t="n">
-        <v>0.4495</v>
+        <v>0.3839</v>
       </c>
       <c r="J152" t="n">
-        <v>10.788</v>
+        <v>9.2136</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.31</v>
       </c>
       <c r="I153" t="n">
-        <v>0.4274</v>
+        <v>0.3631</v>
       </c>
       <c r="J153" t="n">
-        <v>10.2576</v>
+        <v>8.714399999999999</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.18</v>
       </c>
       <c r="I154" t="n">
-        <v>0.2767</v>
+        <v>0.2261</v>
       </c>
       <c r="J154" t="n">
-        <v>6.6408</v>
+        <v>5.4264</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.07</v>
       </c>
       <c r="I155" t="n">
-        <v>0.128</v>
+        <v>0.098</v>
       </c>
       <c r="J155" t="n">
-        <v>3.072</v>
+        <v>2.352</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.97</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.0716</v>
+        <v>-0.0573</v>
       </c>
       <c r="J156" t="n">
-        <v>-1.7184</v>
+        <v>-1.3752</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.28</v>
       </c>
       <c r="I157" t="n">
-        <v>0.4536</v>
+        <v>0.4584</v>
       </c>
       <c r="J157" t="n">
-        <v>10.8864</v>
+        <v>11.0016</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.97</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.0557</v>
+        <v>-0.0444</v>
       </c>
       <c r="J158" t="n">
-        <v>-1.3368</v>
+        <v>-1.0656</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.9</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.1431</v>
+        <v>-0.1242</v>
       </c>
       <c r="J159" t="n">
-        <v>-3.4344</v>
+        <v>-2.9808</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.85</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.1973</v>
+        <v>-0.1769</v>
       </c>
       <c r="J160" t="n">
-        <v>-4.7352</v>
+        <v>-4.2456</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.77</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.2775</v>
+        <v>-0.2584</v>
       </c>
       <c r="J161" t="n">
-        <v>-6.66</v>
+        <v>-6.2016</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.32</v>
       </c>
       <c r="I162" t="n">
-        <v>0.6392</v>
+        <v>0.5823</v>
       </c>
       <c r="J162" t="n">
-        <v>13.4232</v>
+        <v>12.2283</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.14</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3354</v>
+        <v>0.2824</v>
       </c>
       <c r="J163" t="n">
-        <v>7.0434</v>
+        <v>5.9304</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.95</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.0837</v>
+        <v>-0.0688</v>
       </c>
       <c r="J164" t="n">
-        <v>-1.7577</v>
+        <v>-1.4448</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.76</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2883</v>
+        <v>-0.2696</v>
       </c>
       <c r="J165" t="n">
-        <v>-6.0543</v>
+        <v>-5.6616</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.66</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.381</v>
+        <v>-0.3687</v>
       </c>
       <c r="J166" t="n">
-        <v>-8.000999999999999</v>
+        <v>-7.7427</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.65</v>
       </c>
       <c r="I167" t="n">
-        <v>1.3007</v>
+        <v>1.3208</v>
       </c>
       <c r="J167" t="n">
-        <v>27.3147</v>
+        <v>27.7368</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.18</v>
       </c>
       <c r="I168" t="n">
-        <v>0.4995</v>
+        <v>0.4659</v>
       </c>
       <c r="J168" t="n">
-        <v>10.4895</v>
+        <v>9.783899999999999</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.15</v>
       </c>
       <c r="I169" t="n">
-        <v>0.4307</v>
+        <v>0.3968</v>
       </c>
       <c r="J169" t="n">
-        <v>9.044700000000001</v>
+        <v>8.332800000000001</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.07</v>
       </c>
       <c r="I170" t="n">
-        <v>0.2253</v>
+        <v>0.1959</v>
       </c>
       <c r="J170" t="n">
-        <v>4.7313</v>
+        <v>4.1139</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1.05</v>
       </c>
       <c r="I171" t="n">
-        <v>0.1661</v>
+        <v>0.1401</v>
       </c>
       <c r="J171" t="n">
-        <v>3.4881</v>
+        <v>2.9421</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.17</v>
       </c>
       <c r="I172" t="n">
-        <v>0.3987</v>
+        <v>0.3433</v>
       </c>
       <c r="J172" t="n">
-        <v>8.3727</v>
+        <v>7.2093</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.01</v>
       </c>
       <c r="I173" t="n">
-        <v>0.0531</v>
+        <v>0.0358</v>
       </c>
       <c r="J173" t="n">
-        <v>1.1151</v>
+        <v>0.7518</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.0796</v>
       </c>
       <c r="J174" t="n">
-        <v>-1.9887</v>
+        <v>-1.6716</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.86</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1848</v>
+        <v>-0.1649</v>
       </c>
       <c r="J175" t="n">
-        <v>-3.8808</v>
+        <v>-3.4629</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.68</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3597</v>
+        <v>-0.3454</v>
       </c>
       <c r="J176" t="n">
-        <v>-7.5537</v>
+        <v>-7.2534</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>2.02</v>
       </c>
       <c r="I177" t="n">
-        <v>1.7663</v>
+        <v>1.8311</v>
       </c>
       <c r="J177" t="n">
-        <v>37.0923</v>
+        <v>38.4531</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.52</v>
       </c>
       <c r="I178" t="n">
-        <v>1.1265</v>
+        <v>1.1388</v>
       </c>
       <c r="J178" t="n">
-        <v>23.6565</v>
+        <v>23.9148</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.93</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.3013</v>
+        <v>-0.2623</v>
       </c>
       <c r="J179" t="n">
-        <v>-6.3273</v>
+        <v>-5.5083</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.86</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.4868</v>
+        <v>-0.4475</v>
       </c>
       <c r="J180" t="n">
-        <v>-10.2228</v>
+        <v>-9.397500000000001</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.79</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.6521</v>
+        <v>-0.6206</v>
       </c>
       <c r="J181" t="n">
-        <v>-13.6941</v>
+        <v>-13.0326</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.1</v>
       </c>
       <c r="I182" t="n">
-        <v>0.3378</v>
+        <v>0.2965</v>
       </c>
       <c r="J182" t="n">
-        <v>17.9034</v>
+        <v>15.7145</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.08</v>
       </c>
       <c r="I183" t="n">
-        <v>0.2838</v>
+        <v>0.2446</v>
       </c>
       <c r="J183" t="n">
-        <v>15.0414</v>
+        <v>12.9638</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.08</v>
       </c>
       <c r="I184" t="n">
-        <v>0.2838</v>
+        <v>0.2446</v>
       </c>
       <c r="J184" t="n">
-        <v>15.0414</v>
+        <v>12.9638</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.99</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.0612</v>
+        <v>-0.0441</v>
       </c>
       <c r="J185" t="n">
-        <v>-3.2436</v>
+        <v>-2.3373</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.84</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.4969</v>
+        <v>-0.4547</v>
       </c>
       <c r="J186" t="n">
-        <v>-26.3357</v>
+        <v>-24.0991</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.5</v>
       </c>
       <c r="I187" t="n">
-        <v>0.8683999999999999</v>
+        <v>0.8173</v>
       </c>
       <c r="J187" t="n">
-        <v>46.0252</v>
+        <v>43.3169</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.19</v>
       </c>
       <c r="I188" t="n">
-        <v>0.3988</v>
+        <v>0.3436</v>
       </c>
       <c r="J188" t="n">
-        <v>21.1364</v>
+        <v>18.2108</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.1</v>
       </c>
       <c r="I189" t="n">
-        <v>0.2399</v>
+        <v>0.1973</v>
       </c>
       <c r="J189" t="n">
-        <v>12.7147</v>
+        <v>10.4569</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.93</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1191</v>
+        <v>-0.1005</v>
       </c>
       <c r="J190" t="n">
-        <v>-6.3123</v>
+        <v>-5.3265</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.74</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3182</v>
+        <v>-0.3022</v>
       </c>
       <c r="J191" t="n">
-        <v>-16.8646</v>
+        <v>-16.0166</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>2.69</v>
       </c>
       <c r="I192" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J192" t="n">
-        <v>29.058</v>
+        <v>29.727</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.64</v>
       </c>
       <c r="I193" t="n">
-        <v>1.2313</v>
+        <v>1.2527</v>
       </c>
       <c r="J193" t="n">
-        <v>18.4695</v>
+        <v>18.7905</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.26</v>
       </c>
       <c r="I194" t="n">
-        <v>0.6233</v>
+        <v>0.6006</v>
       </c>
       <c r="J194" t="n">
-        <v>9.349500000000001</v>
+        <v>9.009</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.15</v>
       </c>
       <c r="I195" t="n">
-        <v>0.3797</v>
+        <v>0.3461</v>
       </c>
       <c r="J195" t="n">
-        <v>5.6955</v>
+        <v>5.1915</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1.07</v>
       </c>
       <c r="I196" t="n">
-        <v>0.1736</v>
+        <v>0.1397</v>
       </c>
       <c r="J196" t="n">
-        <v>2.604</v>
+        <v>2.0955</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>0.89</v>
       </c>
       <c r="I197" t="n">
-        <v>-0.0982</v>
+        <v>-0.0764</v>
       </c>
       <c r="J197" t="n">
-        <v>-1.473</v>
+        <v>-1.146</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.67</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.3336</v>
+        <v>-0.3235</v>
       </c>
       <c r="J198" t="n">
-        <v>-5.004</v>
+        <v>-4.8525</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.53</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.4552</v>
+        <v>-0.4495</v>
       </c>
       <c r="J199" t="n">
-        <v>-6.828</v>
+        <v>-6.7425</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.48</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.4992</v>
+        <v>-0.4973</v>
       </c>
       <c r="J200" t="n">
-        <v>-7.488</v>
+        <v>-7.4595</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.48</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4992</v>
+        <v>-0.4973</v>
       </c>
       <c r="J201" t="n">
-        <v>-7.488</v>
+        <v>-7.4595</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.47</v>
       </c>
       <c r="I202" t="n">
-        <v>0.6032999999999999</v>
+        <v>0.5322</v>
       </c>
       <c r="J202" t="n">
-        <v>13.8759</v>
+        <v>12.2406</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.34</v>
       </c>
       <c r="I203" t="n">
-        <v>0.464</v>
+        <v>0.3973</v>
       </c>
       <c r="J203" t="n">
-        <v>10.672</v>
+        <v>9.1379</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.09</v>
       </c>
       <c r="I204" t="n">
-        <v>0.1605</v>
+        <v>0.1249</v>
       </c>
       <c r="J204" t="n">
-        <v>3.6915</v>
+        <v>2.8727</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.92</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.1357</v>
+        <v>-0.1166</v>
       </c>
       <c r="J205" t="n">
-        <v>-3.1211</v>
+        <v>-2.6818</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.91</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.1476</v>
+        <v>-0.128</v>
       </c>
       <c r="J206" t="n">
-        <v>-3.3948</v>
+        <v>-2.944</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.1</v>
       </c>
       <c r="I207" t="n">
-        <v>0.2093</v>
+        <v>0.1928</v>
       </c>
       <c r="J207" t="n">
-        <v>4.8139</v>
+        <v>4.4344</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.1</v>
       </c>
       <c r="I208" t="n">
-        <v>0.2093</v>
+        <v>0.1928</v>
       </c>
       <c r="J208" t="n">
-        <v>4.8139</v>
+        <v>4.4344</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.07</v>
       </c>
       <c r="I209" t="n">
-        <v>0.1606</v>
+        <v>0.1433</v>
       </c>
       <c r="J209" t="n">
-        <v>3.6938</v>
+        <v>3.2959</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2359</v>
+        <v>-0.2158</v>
       </c>
       <c r="J210" t="n">
-        <v>-5.4257</v>
+        <v>-4.9634</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.57</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4574</v>
+        <v>-0.4527</v>
       </c>
       <c r="J211" t="n">
-        <v>-10.5202</v>
+        <v>-10.4121</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.33</v>
       </c>
       <c r="I212" t="n">
-        <v>0.6499</v>
+        <v>0.5926</v>
       </c>
       <c r="J212" t="n">
-        <v>15.5976</v>
+        <v>14.2224</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.09</v>
       </c>
       <c r="I213" t="n">
-        <v>0.236</v>
+        <v>0.1908</v>
       </c>
       <c r="J213" t="n">
-        <v>5.664</v>
+        <v>4.5792</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.03</v>
       </c>
       <c r="I214" t="n">
-        <v>0.1024</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="J214" t="n">
-        <v>2.4576</v>
+        <v>1.8096</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.78</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.2704</v>
+        <v>-0.2511</v>
       </c>
       <c r="J215" t="n">
-        <v>-6.4896</v>
+        <v>-6.0264</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.68</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3644</v>
+        <v>-0.3507</v>
       </c>
       <c r="J216" t="n">
-        <v>-8.7456</v>
+        <v>-8.4168</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.7</v>
       </c>
       <c r="I217" t="n">
-        <v>1.3973</v>
+        <v>1.4283</v>
       </c>
       <c r="J217" t="n">
-        <v>33.5352</v>
+        <v>34.2792</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.36</v>
       </c>
       <c r="I218" t="n">
-        <v>0.8943</v>
+        <v>0.8756</v>
       </c>
       <c r="J218" t="n">
-        <v>21.4632</v>
+        <v>21.0144</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.89</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.3912</v>
+        <v>-0.3486</v>
       </c>
       <c r="J219" t="n">
-        <v>-9.3888</v>
+        <v>-8.366400000000001</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.87</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.4424</v>
+        <v>-0.4001</v>
       </c>
       <c r="J220" t="n">
-        <v>-10.6176</v>
+        <v>-9.602399999999999</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.76</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.7009</v>
+        <v>-0.67</v>
       </c>
       <c r="J221" t="n">
-        <v>-16.8216</v>
+        <v>-16.08</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.42</v>
       </c>
       <c r="I222" t="n">
-        <v>0.7924</v>
+        <v>0.7423999999999999</v>
       </c>
       <c r="J222" t="n">
-        <v>19.0176</v>
+        <v>17.8176</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.1</v>
       </c>
       <c r="I223" t="n">
-        <v>0.2587</v>
+        <v>0.2113</v>
       </c>
       <c r="J223" t="n">
-        <v>6.2088</v>
+        <v>5.0712</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.86</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.188</v>
+        <v>-0.1676</v>
       </c>
       <c r="J224" t="n">
-        <v>-4.512</v>
+        <v>-4.0224</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.8</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2495</v>
+        <v>-0.2295</v>
       </c>
       <c r="J225" t="n">
-        <v>-5.988</v>
+        <v>-5.508</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.66</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3812</v>
+        <v>-0.3689</v>
       </c>
       <c r="J226" t="n">
-        <v>-9.1488</v>
+        <v>-8.8536</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.22</v>
       </c>
       <c r="I227" t="n">
-        <v>0.6153</v>
+        <v>0.5773</v>
       </c>
       <c r="J227" t="n">
-        <v>14.7672</v>
+        <v>13.8552</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.21</v>
       </c>
       <c r="I228" t="n">
-        <v>0.5929</v>
+        <v>0.5541</v>
       </c>
       <c r="J228" t="n">
-        <v>14.2296</v>
+        <v>13.2984</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.15</v>
       </c>
       <c r="I229" t="n">
-        <v>0.4539</v>
+        <v>0.4124</v>
       </c>
       <c r="J229" t="n">
-        <v>10.8936</v>
+        <v>9.897600000000001</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.87</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.4315</v>
+        <v>-0.3885</v>
       </c>
       <c r="J230" t="n">
-        <v>-10.356</v>
+        <v>-9.324</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.85</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4812</v>
+        <v>-0.4388</v>
       </c>
       <c r="J231" t="n">
-        <v>-11.5488</v>
+        <v>-10.5312</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>0.89</v>
       </c>
       <c r="I232" t="n">
-        <v>-0.1028</v>
+        <v>-0.0823</v>
       </c>
       <c r="J232" t="n">
-        <v>-1.542</v>
+        <v>-1.2345</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>0.67</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.3358</v>
+        <v>-0.3254</v>
       </c>
       <c r="J233" t="n">
-        <v>-5.037</v>
+        <v>-4.881</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.61</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.3877</v>
+        <v>-0.3784</v>
       </c>
       <c r="J234" t="n">
-        <v>-5.8155</v>
+        <v>-5.676</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.55</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.4397</v>
+        <v>-0.4327</v>
       </c>
       <c r="J235" t="n">
-        <v>-6.5955</v>
+        <v>-6.4905</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.4</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.5716</v>
+        <v>-0.5789</v>
       </c>
       <c r="J236" t="n">
-        <v>-8.574</v>
+        <v>-8.6835</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>2.31</v>
       </c>
       <c r="I237" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J237" t="n">
-        <v>29.058</v>
+        <v>29.727</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.99</v>
       </c>
       <c r="I238" t="n">
-        <v>1.6402</v>
+        <v>1.6828</v>
       </c>
       <c r="J238" t="n">
-        <v>24.603</v>
+        <v>25.242</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.74</v>
       </c>
       <c r="I239" t="n">
-        <v>1.3487</v>
+        <v>1.3743</v>
       </c>
       <c r="J239" t="n">
-        <v>20.2305</v>
+        <v>20.6145</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>1.01</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.0323</v>
+        <v>-0.0502</v>
       </c>
       <c r="J240" t="n">
-        <v>-0.4845</v>
+        <v>-0.753</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.91</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.4095</v>
+        <v>-0.381</v>
       </c>
       <c r="J241" t="n">
-        <v>-6.1425</v>
+        <v>-5.715</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.96</v>
       </c>
       <c r="I242" t="n">
-        <v>1.0589</v>
+        <v>1.0215</v>
       </c>
       <c r="J242" t="n">
-        <v>24.3547</v>
+        <v>23.4945</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.32</v>
       </c>
       <c r="I243" t="n">
-        <v>0.44</v>
+        <v>0.3747</v>
       </c>
       <c r="J243" t="n">
-        <v>10.12</v>
+        <v>8.6181</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.15</v>
       </c>
       <c r="I244" t="n">
-        <v>0.2407</v>
+        <v>0.194</v>
       </c>
       <c r="J244" t="n">
-        <v>5.5361</v>
+        <v>4.462</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.75</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.314</v>
+        <v>-0.2984</v>
       </c>
       <c r="J245" t="n">
-        <v>-7.222</v>
+        <v>-6.8632</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.62</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.4314</v>
+        <v>-0.4265</v>
       </c>
       <c r="J246" t="n">
-        <v>-9.9222</v>
+        <v>-9.8095</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.15</v>
       </c>
       <c r="I247" t="n">
-        <v>0.2939</v>
+        <v>0.2831</v>
       </c>
       <c r="J247" t="n">
-        <v>6.7597</v>
+        <v>6.5113</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.98</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.0338</v>
+        <v>-0.0262</v>
       </c>
       <c r="J248" t="n">
-        <v>-0.7774</v>
+        <v>-0.6026</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.97</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.0496</v>
+        <v>-0.0399</v>
       </c>
       <c r="J249" t="n">
-        <v>-1.1408</v>
+        <v>-0.9177</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2319</v>
+        <v>-0.2123</v>
       </c>
       <c r="J250" t="n">
-        <v>-5.3337</v>
+        <v>-4.8829</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.53</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.4883</v>
+        <v>-0.4869</v>
       </c>
       <c r="J251" t="n">
-        <v>-11.2309</v>
+        <v>-11.1987</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>0.93</v>
       </c>
       <c r="I252" t="n">
-        <v>-0.0254</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="J252" t="n">
-        <v>-0.381</v>
+        <v>0.1485</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>0.59</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.3978</v>
+        <v>-0.3918</v>
       </c>
       <c r="J253" t="n">
-        <v>-5.967</v>
+        <v>-5.877</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.5</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.4739</v>
+        <v>-0.4707</v>
       </c>
       <c r="J254" t="n">
-        <v>-7.1085</v>
+        <v>-7.0605</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.43</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.5356</v>
+        <v>-0.5377999999999999</v>
       </c>
       <c r="J255" t="n">
-        <v>-8.034000000000001</v>
+        <v>-8.067</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.35</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.6068</v>
+        <v>-0.6187</v>
       </c>
       <c r="J256" t="n">
-        <v>-9.102</v>
+        <v>-9.2805</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.96</v>
       </c>
       <c r="I257" t="n">
-        <v>1.612</v>
+        <v>1.6522</v>
       </c>
       <c r="J257" t="n">
-        <v>24.18</v>
+        <v>24.783</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.65</v>
       </c>
       <c r="I258" t="n">
-        <v>1.2443</v>
+        <v>1.2657</v>
       </c>
       <c r="J258" t="n">
-        <v>18.6645</v>
+        <v>18.9855</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.53</v>
       </c>
       <c r="I259" t="n">
-        <v>1.0975</v>
+        <v>1.1168</v>
       </c>
       <c r="J259" t="n">
-        <v>16.4625</v>
+        <v>16.752</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>1.39</v>
       </c>
       <c r="I260" t="n">
-        <v>0.8806</v>
+        <v>0.8767</v>
       </c>
       <c r="J260" t="n">
-        <v>13.209</v>
+        <v>13.1505</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>1.24</v>
       </c>
       <c r="I261" t="n">
-        <v>0.5823</v>
+        <v>0.5573</v>
       </c>
       <c r="J261" t="n">
-        <v>8.734500000000001</v>
+        <v>8.359500000000001</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>2.72</v>
       </c>
       <c r="I262" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J262" t="n">
-        <v>32.9324</v>
+        <v>33.6906</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.43</v>
       </c>
       <c r="I263" t="n">
-        <v>0.9668</v>
+        <v>0.9661</v>
       </c>
       <c r="J263" t="n">
-        <v>16.4356</v>
+        <v>16.4237</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.3</v>
       </c>
       <c r="I264" t="n">
-        <v>0.7262</v>
+        <v>0.7075</v>
       </c>
       <c r="J264" t="n">
-        <v>12.3454</v>
+        <v>12.0275</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.86</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.5147</v>
+        <v>-0.4818</v>
       </c>
       <c r="J265" t="n">
-        <v>-8.7499</v>
+        <v>-8.1906</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.73</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.8099</v>
+        <v>-0.7968</v>
       </c>
       <c r="J266" t="n">
-        <v>-13.7683</v>
+        <v>-13.5456</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>0.95</v>
       </c>
       <c r="I267" t="n">
-        <v>-0.06270000000000001</v>
+        <v>-0.0506</v>
       </c>
       <c r="J267" t="n">
-        <v>-1.0659</v>
+        <v>-0.8602</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.86</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.1715</v>
+        <v>-0.1555</v>
       </c>
       <c r="J268" t="n">
-        <v>-2.9155</v>
+        <v>-2.6435</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.8</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.2329</v>
+        <v>-0.2162</v>
       </c>
       <c r="J269" t="n">
-        <v>-3.9593</v>
+        <v>-3.6754</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.7</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3254</v>
+        <v>-0.3095</v>
       </c>
       <c r="J270" t="n">
-        <v>-5.5318</v>
+        <v>-5.2615</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.59</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.4245</v>
+        <v>-0.4151</v>
       </c>
       <c r="J271" t="n">
-        <v>-7.2165</v>
+        <v>-7.0567</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>2.12</v>
       </c>
       <c r="I272" t="n">
-        <v>1.8598</v>
+        <v>1.9318</v>
       </c>
       <c r="J272" t="n">
-        <v>37.196</v>
+        <v>38.636</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.43</v>
       </c>
       <c r="I273" t="n">
-        <v>0.981</v>
+        <v>0.9774</v>
       </c>
       <c r="J273" t="n">
-        <v>19.62</v>
+        <v>19.548</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.33</v>
       </c>
       <c r="I274" t="n">
-        <v>0.7962</v>
+        <v>0.7764</v>
       </c>
       <c r="J274" t="n">
-        <v>15.924</v>
+        <v>15.528</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.92</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.3426</v>
+        <v>-0.3048</v>
       </c>
       <c r="J275" t="n">
-        <v>-6.852</v>
+        <v>-6.096</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.71</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.8387</v>
+        <v>-0.8252</v>
       </c>
       <c r="J276" t="n">
-        <v>-16.774</v>
+        <v>-16.504</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>2.12</v>
       </c>
       <c r="I277" t="n">
-        <v>1.5693</v>
+        <v>1.6061</v>
       </c>
       <c r="J277" t="n">
-        <v>31.386</v>
+        <v>32.122</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>0.78</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.2676</v>
+        <v>-0.2482</v>
       </c>
       <c r="J278" t="n">
-        <v>-5.352</v>
+        <v>-4.964</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.73</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.3154</v>
+        <v>-0.2981</v>
       </c>
       <c r="J279" t="n">
-        <v>-6.308</v>
+        <v>-5.962</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.61</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.4243</v>
+        <v>-0.4161</v>
       </c>
       <c r="J280" t="n">
-        <v>-8.486000000000001</v>
+        <v>-8.321999999999999</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.52</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.5023</v>
+        <v>-0.5037</v>
       </c>
       <c r="J281" t="n">
-        <v>-10.046</v>
+        <v>-10.074</v>
       </c>
     </row>
   </sheetData>
